--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岗位明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="概览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="岗位明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -198,13 +198,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -228,7 +228,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -277,7 +277,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -292,9 +292,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-05 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-06 04:48 UTC</t>
+          <t>数据日期 2026-07-06 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-06 05:07 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4013157894736842</v>
+        <v>0.3698630136986301</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3092105263157895</v>
+        <v>0.3150684931506849</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3223684210526316</v>
+        <v>0.3082191780821918</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1907894736842105</v>
+        <v>0.2191780821917808</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09868421052631579</v>
+        <v>0.0958904109589041</v>
       </c>
     </row>
     <row r="15">
@@ -806,36 +806,36 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1644736842105263</v>
+        <v>0.1643835616438356</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1381578947368421</v>
+        <v>0.1438356164383562</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1301369863013699</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1118421052631579</v>
+        <v>0.0958904109589041</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09868421052631579</v>
+        <v>0.0958904109589041</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.0958904109589041</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7651,8 +7651,648 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Website Analyst – E-Commerce Management (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、A/B测试</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ionos-se/senior-website-analyst-e-commerce-management-karlsruhe-53256</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce Data Architect</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>NeuraFlash</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/neuraflash/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>Salesforce Senior Solution Consultant: Business Analyst</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Guidehouse</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr"/>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/guidehouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer II, Navigation</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Diligent Robotics</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/diligent-robotics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>Zuora Revenue- Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Sophos</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sophos/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>Supply Chain Analyst</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>DIVA</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-supply-chain-analyst-diva-1134516</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>Service Desk Analyst I - 3rd Shift</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr"/>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/core-bts/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>Data Enrichment Specialist (Part-time)</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr"/>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hireframe/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>Experienced Data Scientist</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>Mindera</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Snowflake、AWS、Azure、GCP、统计学</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H173" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mindera/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>Cyber Security Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>glueckkanja AG</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/glueckkanja-ag/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>CapsLock</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/capslock/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Stress Analyst</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>Superior Skilled Trades</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr"/>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/superior-skilled-trades/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>Information Security Specialist/Analyst III - Information Solutions</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>Medical University of South Carolina</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr"/>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H177" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/musc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>NeuraFlash</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr"/>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/neuraflash/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>Teya</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/teya/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>量化交易系统——数据管道模块外包</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr"/>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr"/>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/dDfX4Q</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H164"/>
+  <autoFilter ref="A1:H180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7663,7 +8303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7713,7 +8353,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>2</v>
@@ -7725,7 +8365,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -7757,19 +8397,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -7804,16 +8444,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -7823,7 +8463,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -7835,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -7863,44 +8503,66 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>拉美</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>欧洲</t>
+          <t>拉美</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>15</v>
       </c>
     </row>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-06 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-06 05:07 UTC</t>
+          <t>数据日期 2026-07-06 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-06 23:35 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.410958904109589</v>
+        <v>0.3856209150326798</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3660130718954248</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.3856209150326798</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3150684931506849</v>
+        <v>0.326797385620915</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3082191780821918</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.1830065359477124</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1917808219178082</v>
+        <v>0.1699346405228758</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,49 +793,49 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.1241830065359477</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1643835616438356</v>
+        <v>0.1568627450980392</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1438356164383562</v>
+        <v>0.1372549019607843</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1301369863013699</v>
+        <v>0.1241830065359477</v>
       </c>
     </row>
     <row r="18">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.1045751633986928</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.0915032679738562</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8291,8 +8291,938 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>Rotaract Club of NIBM Kandy</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-analyst-rotaract-club-of-nibm-kandy-1134504</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>Senior CRM Manager Data &amp; Automation (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Lyto Brands Group</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/lyto-brands-group/senior-crm-manager-data-automation-dusseldorf-205885</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer I</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-machine-learning-engineer-i-berlin-493840</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>VOIDS Technology GmbH</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/voids-technology-gmbh/senior-data-engineer-hamburg-116855</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent:in (m/w/d) - Quality Control Analyst (Wärmepumpe)</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>1KOMMA5˚</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E185" s="8" t="inlineStr"/>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G185" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H185" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/1komma50/werkstudentin-quality-control-analyst-warmepumpe-berlin-496419</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent:in (m/w/d) - Quality Control Analyst (Photovoltaik)</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>1KOMMA5˚</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr"/>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/1komma50/werkstudentin-quality-control-analyst-photovoltaik-berlin-463916</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>IT Consultant &amp; Business Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="inlineStr"/>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H187" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/it-consultant-business-analyst-munster-476880</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst - Banking Regulation &amp; Reporting (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr"/>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/business-analyst-banking-regulation-reporting-munster-483111</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H189" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-367017</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Frankfurt, Germany</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-frankfurt-germany-60496</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H191" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-berlin-germany-312490</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (Azure) - Remote, Latin America</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bluelight-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>JLL</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、GCP、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/jll/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>[Job-30277] Senior Data Steward ( Data Governance), Brazil</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>CI&amp;T</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Python、ETL</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ci-t/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>Antifraud Analyst</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>Novacard</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H195" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/novacard/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Technical Support Analyst</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>Remote Recruitment</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr"/>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/remote-recruitment/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>Data Manager for Clinical Trials</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>PSI CRO</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E197" s="8" t="inlineStr"/>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H197" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/psi-cro/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Business Operations Analyst I</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>BigCommerce, Inc.</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr"/>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bigcommerce-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - India</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>Dutch Speaking Digital Trust and Safety Analyst</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Mercier Consultancy BG</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr"/>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercier-consultancy-bg/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>Senior Procurement Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>Assembly Industries</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H201" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/assembly-industries/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>Freelance Investment Research Analyst - China</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Gain.pro</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr"/>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gain-pro/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>Research Analyst</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>H1 Insights</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/h1-insights/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H180"/>
+  <autoFilter ref="A1:H203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8353,19 +9283,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -8397,7 +9327,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>20</v>
@@ -8409,7 +9339,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -8441,19 +9371,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -8507,7 +9437,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -8516,10 +9446,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-06 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-06 23:35 UTC</t>
+          <t>数据日期 2026-07-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-07 23:28 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
         <v>59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3856209150326798</v>
+        <v>0.3881578947368421</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3660130718954248</v>
+        <v>0.3618421052631579</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3856209150326798</v>
+        <v>0.3815789473684211</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.326797385620915</v>
+        <v>0.3552631578947368</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3092105263157895</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1830065359477124</v>
+        <v>0.1776315789473684</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1699346405228758</v>
+        <v>0.1907894736842105</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1241830065359477</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1644736842105263</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1372549019607843</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1241830065359477</v>
+        <v>0.1118421052631579</v>
       </c>
     </row>
     <row r="18">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1045751633986928</v>
+        <v>0.09210526315789473</v>
       </c>
     </row>
     <row r="19">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.08552631578947369</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0915032679738562</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9221,8 +9221,698 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>Associate Analyst</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Trinity Life Sciences</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>Excel、统计学</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-associate-analyst-trinity-life-sciences-1134551</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst - Bankbilanzierung &amp; Jahresabschluss (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>CPU Consulting &amp; Software GmbH</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cpu-consulting-software-gmbh/business-analyst-bankbilanzierung-jahresabschluss-munster-442346</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>AI Full Stack Software Engineer im E-Commerce Startup (E-Commerce &amp; Data)</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Sayano Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sayano-deutschland-gmbh/ai-full-stack-software-engineer-im-e-commerce-startup-e-commerce-data-stuttgart-111639</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>Data Management Coordinator (M/W/D)</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>sera Gruppe</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E207" s="8" t="inlineStr"/>
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G207" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sera-gruppe/data-management-coordinator-immenhausen-283212</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Business Analyst – KI/AI Champion (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Prokuras Beteiligungs GmbH</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/prokuras-beteiligungs-gmbh/junior-business-analyst-ki-ai-champion-hamburg-411937</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>Working Student: AI Product Engineering - Data (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Retorio GmbH</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F209" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G209" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/retorio-gmbh/working-student-ai-product-engineering-data-munich-252542</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>Financial Analyst Corporate Finance (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>MY Humancapital GmbH</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/my-humancapital-gmbh/financial-analyst-corporate-finance-munich-183005</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer - Run &amp; Grow</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F211" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G211" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-analytics-engineer-run-grow-berlin-330888</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Principal AI Data Analyst</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/148891-principal-ai-data-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="inlineStr"/>
+      <c r="F213" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G213" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H213" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1712616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Corporate Credit Analyst II (US)</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>Seagate Technology, LLC</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>Excel、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/seagate-technology-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Aker Systems</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G215" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H215" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/aker-systems/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Epic PB Claims Analyst</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>Prominence Advisors</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr"/>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/prominence-advisors/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>Dispute Resolution Analyst I</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>J29, Inc</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="inlineStr"/>
+      <c r="F217" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G217" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H217" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/j29-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst III</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>Astreya</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Looker、统计学</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/astreya/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>Analyst, Business &amp; Competitive Intelligence</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>Precision for Medicine</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E219" s="8" t="inlineStr"/>
+      <c r="F219" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G219" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H219" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/precision-for-medicine/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>数据分析师 报道！！15k~20k</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr"/>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/x0f1Qz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H203"/>
+  <autoFilter ref="A1:H220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9283,19 +9973,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -9305,7 +9995,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -9317,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -9327,7 +10017,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>20</v>
@@ -9339,7 +10029,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -9349,7 +10039,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -9361,7 +10051,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -9371,7 +10061,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>6</v>
@@ -9383,7 +10073,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -9437,7 +10127,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -9449,7 +10139,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$244</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-07 23:28 UTC</t>
+          <t>数据日期 2026-07-08 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-08 23:34 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,38 +706,38 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>0.3881578947368421</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>其他数据岗</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>55</v>
-      </c>
       <c r="H11" s="7" t="n">
-        <v>0.3618421052631579</v>
+        <v>0.3734177215189873</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.379746835443038</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>54</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3552631578947368</v>
+        <v>0.3417721518987342</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3092105263157895</v>
+        <v>0.310126582278481</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1776315789473684</v>
+        <v>0.189873417721519</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1907894736842105</v>
+        <v>0.1772151898734177</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.0949367088607595</v>
       </c>
     </row>
     <row r="15">
@@ -806,36 +806,36 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1644736842105263</v>
+        <v>0.1518987341772152</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1265822784810127</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1118421052631579</v>
+        <v>0.1265822784810127</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.0949367088607595</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08552631578947369</v>
+        <v>0.08227848101265822</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.08227848101265822</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9911,8 +9911,964 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>Compliance Market Surveillance Analyst</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E221" s="8" t="inlineStr"/>
+      <c r="F221" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G221" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H221" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-compliance-market-surveillance-analyst-crypto-com-1134599</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>Associate Data Analyst</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>Arabian Private Holdings</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr"/>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-associate-data-analyst-arabian-private-holdings-1134566</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>Junior Business Analyst</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Arabian Private Holdings</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E223" s="8" t="inlineStr"/>
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G223" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H223" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-junior-business-analyst-arabian-private-holdings-1134577</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>AWS Cloud Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>Unigy GmbH</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/unigy-gmbh/aws-cloud-data-engineer-essen-139122</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G225" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-461128</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Machine Learning / Neuronale Netze / Automatisierungstechnik</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>INP Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/inp-deutschland-gmbh/werkstudent-machine-learning-neuronale-netze-automatisierungstechnik-romerberg-90107</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>Costpoint Cognos Report Writer and General Ledger Business Analyst</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>ManTech</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G227" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149012-costpoint-cognos-report-writer-and-general-ledger-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>Strategic Account Manager - Data Center Cooling (HDLC)</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>nVent</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr"/>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nvent/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>Clinical Genomic Scientist II (genome analyst): REMOTE, USA</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>Ambry Genetics</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr"/>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G229" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ambry-genetics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>Claims Analyst III</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Trend Health Partners</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G230" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H230" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/trend-health-partners/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>Network Project Manager (Data Center Builds)</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Telnyx</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr"/>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G231" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H231" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/telnyx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>Engineering Manager (Data Direction)</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>JustMarkets</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr"/>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/justmarkets/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>Sr Analyst Non-Product, Procurement</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr"/>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H233" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rtx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (System Integration)</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr"/>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/n-ix/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>Business Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>WWT</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr"/>
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G235" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H235" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wwt/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>Customer Success Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Sphera</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sphera/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist - Medical Records</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>Sharecare</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr"/>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sharecare/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analyst, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Tabby</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、A/B测试、pandas</t>
+        </is>
+      </c>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/tabby/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer, Engineering Foundation</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>CookUnity</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、A/B测试</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G239" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cookunity/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Pricing)</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>Emerging Travel Group</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/emerging-travel-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Junior (Remote or Onsite)</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>Free2move</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Spark、ETL</t>
+        </is>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G241" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/free2move/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>Cambium Learning Group</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cambium-learning-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Research Scientist</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、Airflow、AWS、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G243" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/smarterdx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>免费推荐/神仙外企/WLB/HR直招/全程远程or坐标杭州-- 数据 Team Lead or 高级数据工程师(英语好)</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr"/>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr"/>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/njf9dr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H220"/>
+  <autoFilter ref="A1:H244"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9973,19 +10929,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -9995,7 +10951,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -10007,7 +10963,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -10017,19 +10973,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -10039,7 +10995,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -10048,10 +11004,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -10061,19 +11017,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-08 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-08 23:34 UTC</t>
+          <t>数据日期 2026-07-09 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-09 23:44 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.379746835443038</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3734177215189873</v>
+        <v>0.363013698630137</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.379746835443038</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3417721518987342</v>
+        <v>0.3356164383561644</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.310126582278481</v>
+        <v>0.3150684931506849</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.189873417721519</v>
+        <v>0.1986301369863014</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1772151898734177</v>
+        <v>0.1643835616438356</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -796,85 +796,85 @@
         <v>15</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0949367088607595</v>
+        <v>0.1027397260273973</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1518987341772152</v>
+        <v>0.1438356164383562</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1265822784810127</v>
+        <v>0.1301369863013699</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1265822784810127</v>
+        <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0949367088607595</v>
+        <v>0.08904109589041095</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08227848101265822</v>
+        <v>0.0821917808219178</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08227848101265822</v>
+        <v>0.0821917808219178</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10867,8 +10867,954 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>Data center technician Dispatch</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Sharp Brains</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr"/>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G245" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-center-technician-dispatch-sharp-brains-1134595</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist Assistant Administrator</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>ReLytics Hire</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H246" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-assistant-administrator-relytics-hire-1134602</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Typist</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>Argus Medical Management, LLC</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="inlineStr"/>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G247" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-typist-argus-medical-management-llc-1134579</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>Tier III Service Desk Engineer</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>Unio Digital</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/information-technology/tier-iii-service-desk-engineer-2091045</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>NFON</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G249" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nfon/machine-learning-engineer-all-genders-bremen-414400</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>NFON</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G250" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nfon/machine-learning-engineer-all-genders-bremen-387333</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>Working Student Finance Data &amp; Analytics (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>Recare Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Looker、Snowflake</t>
+        </is>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G251" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H251" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/recare-deutschland-gmbh/working-student-finance-data-analytics-berlin-165739</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (w/m/d) | SSIS &amp; SQL DWH</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>FlexIT Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G252" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flexit-consulting-gmbh/senior-data-engineer-ssis-sql-dwh-dusseldorf-20377</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Düsseldorf, Germany</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E253" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G253" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H253" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-dusseldorf-germany-dusseldorf-337212</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>Skylum</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149063-machine-learning-engineer-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>Data Manager</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F255" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G255" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H255" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sts-systems-support-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analyst, FP&amp;A</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>Skyward Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G256" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/skyward-specialty-insurance/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>Data Manager</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>Bristol Bay Shared Services, LLC</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F257" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G257" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H257" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bristol-bay-shared-services-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>Consulting Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>FiscalNote</t>
+        </is>
+      </c>
+      <c r="C258" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D258" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E258" s="6" t="inlineStr"/>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G258" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fiscalnote/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>Client Service Analyst - Livechat (Burmese)</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E259" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F259" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G259" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H259" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bybit/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>Technical Audit Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Wiz</t>
+        </is>
+      </c>
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D260" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E260" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G260" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wiz/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>Revecore</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G261" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H261" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/revecore/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>Financial Crimes Compliance Modeling &amp; Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D262" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G262" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercury/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>Account Manager - Tactical Data Link Solutions</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>Curtiss-Wright Corporation</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E263" s="8" t="inlineStr"/>
+      <c r="F263" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G263" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/curtiss-wright-corporation/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Value Creation &amp; AI Transformation</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>QAD, Inc.</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D264" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/qad-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>Client Service Analyst - Livechat (Cambodian)</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F265" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G265" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bybit/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Product Analyst II, State Management - General Motors Insurance</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E266" s="6" t="inlineStr"/>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H266" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gm-financial/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>[Job - 30340] Senior Data Developer (Analytics Engineer), Colombia</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>CI&amp;T</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E267" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F267" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G267" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ci-t/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H244"/>
+  <autoFilter ref="A1:H267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10929,19 +11875,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -10951,7 +11897,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -10963,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -10973,19 +11919,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -11004,10 +11950,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -11017,19 +11963,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -11039,7 +11985,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -11051,7 +11997,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -11083,7 +12029,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -11095,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -11130,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
@@ -11139,7 +12085,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$292</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-09 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-09 23:44 UTC</t>
+          <t>数据日期 2026-07-10 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-10 23:26 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>60</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.363013698630137</v>
+        <v>0.3648648648648649</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.3445945945945946</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.3561643835616438</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>数据分析/BI</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>49</v>
-      </c>
       <c r="H12" s="7" t="n">
-        <v>0.3356164383561644</v>
+        <v>0.3513513513513514</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3150684931506849</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1986301369863014</v>
+        <v>0.2094594594594595</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1643835616438356</v>
+        <v>0.1621621621621622</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1027397260273973</v>
+        <v>0.07432432432432433</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1438356164383562</v>
+        <v>0.1148648648648649</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1301369863013699</v>
+        <v>0.1148648648648649</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1095890410958904</v>
+        <v>0.1013513513513514</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08904109589041095</v>
+        <v>0.08783783783783784</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0821917808219178</v>
+        <v>0.08108108108108109</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0821917808219178</v>
+        <v>0.08108108108108109</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11813,8 +11813,1030 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Product Sales Specialist - Pet Health</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>Tribe Wellness</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E268" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Spark</t>
+        </is>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H268" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/sales/product-sales-specialist-pet-health-2091048</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>Online Data Analyst Canada</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E269" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F269" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G269" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/all-others/online-data-analyst-canada-2091047</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Financial Analyst Corporate Finance (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>MY Humancapital GmbH</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E270" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H270" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/my-humancapital-gmbh/financial-analyst-corporate-finance-munich-47214</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>IT Business Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>MY Humancapital GmbH</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F271" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G271" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/my-humancapital-gmbh/it-business-analyst-munich-168601</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>Investment Analyst mit Marketingerfahrung (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t>FinMent GmbH</t>
+        </is>
+      </c>
+      <c r="C272" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D272" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E272" s="6" t="inlineStr"/>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G272" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H272" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/finment-gmbh/investment-analyst-mit-marketingerfahrung-berlin-68378</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>Robot Perception/ML Engineer (f/m/d) Autonomous Mobile Robots</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>Magazino GmbH</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F273" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G273" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/magazino-gmbh/robot-perception-ml-engineer-autonomous-mobile-robots-munich-327983</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>Robot Perception/ML Engineer (w/m/d) Autonomous Mobile Robots</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>Magazino GmbH</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D274" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E274" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G274" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/magazino-gmbh/robot-perception-ml-engineer-autonomous-mobile-robots-munich-423510</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>SAP Data &amp; Analytics Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>Pertemps ERP</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E275" s="8" t="inlineStr"/>
+      <c r="F275" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G275" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pertemps-erp/sap-data-analytics-consultant-frankfurt-am-main-345581</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C276" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D276" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E276" s="6" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G276" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-262806</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>Applied Scientist / Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E277" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F277" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G277" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/applied-scientist-machine-learning-engineer-berlin-389240</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D278" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-483212</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>IT-Forensiker / Analysten (mIwId)</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>LeySelect GmbH</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D279" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="inlineStr"/>
+      <c r="F279" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G279" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H279" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/leyselect-gmbh/it-forensiker-analysten-miwid-frankfurt-am-main-295341</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager / Business Analyst (m/w/d) - Enterprise Banking</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t>XALT Business Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C280" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D280" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E280" s="6" t="inlineStr"/>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G280" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H280" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/xalt-business-consulting-gmbh/product-manager-business-analyst-enterprise-banking-munich-233538</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer - CAD, 3D Geometry &amp; Machine Learning (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
+        <is>
+          <t>TOOLPLACE GmbH</t>
+        </is>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D281" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E281" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F281" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G281" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H281" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/toolplace-gmbh/senior-python-engineer-cad-3d-geometry-machine-learning-leipzig-314152</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Consumer Core</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C282" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D282" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E282" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Looker、A/B测试</t>
+        </is>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G282" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/senior-data-scientist-consumer-core-berlin-331913</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>Data Analytics Senior Consultant I</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D283" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E283" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F283" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G283" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H283" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/147343-data-analytics-senior-consultant-i</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="inlineStr">
+        <is>
+          <t>AI Content Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C284" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D284" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E284" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G284" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1719512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E285" s="8" t="inlineStr"/>
+      <c r="F285" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G285" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H285" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1719508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="6" t="inlineStr">
+        <is>
+          <t>Legal Analyst</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>Zippi</t>
+        </is>
+      </c>
+      <c r="C286" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D286" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E286" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G286" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H286" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zippi/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>Data Editor (TV &amp; Streaming) - German&amp;English (RO/MD)</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>Simply TV</t>
+        </is>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr"/>
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G287" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/simply-tv/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>Data Intelligence Analyst (DoD Secret | Remote)</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>Rackner</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E288" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、pandas</t>
+        </is>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G288" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rackner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>Research &amp; Advisory Analyst</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>RGH-Global Limited</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D289" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E289" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F289" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G289" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rgh-global-limited/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>Security Analyst 2nd Lvl (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>water IT Security GmbH</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E290" s="6" t="inlineStr"/>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G290" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/water-security/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>FBS - Vendor Experience and Support Analyst</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>Capgemini Technology Services</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E291" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F291" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G291" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/capgemini-technology-services/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>Credit Business Analyst</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>Zippi</t>
+        </is>
+      </c>
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D292" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E292" s="6" t="inlineStr">
+        <is>
+          <t>SQL、R</t>
+        </is>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G292" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zippi/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H267"/>
+  <autoFilter ref="A1:H292"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11875,10 +12897,10 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>7</v>
@@ -11887,7 +12909,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -11897,7 +12919,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -11909,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -11919,7 +12941,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>23</v>
@@ -11928,10 +12950,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
@@ -11963,7 +12985,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>7</v>
@@ -11972,10 +12994,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -11985,7 +13007,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -11997,7 +13019,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-10 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-10 23:26 UTC</t>
+          <t>数据日期 2026-07-11 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-11 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.43125</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3648648648648649</v>
+        <v>0.4125</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3445945945945946</v>
+        <v>0.3125</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.275</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2094594594594595</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.18125</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07432432432432433</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1013513513513514</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08783783783783784</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -861,20 +861,20 @@
         <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.06875000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -12835,8 +12835,1004 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>Administrative Data Entry File Clerk</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
+          <t>Recruitlytixs Hirings</t>
+        </is>
+      </c>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D293" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F293" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G293" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-administrative-data-entry-file-clerk-recruitlytixs-hirings-1134665</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist Assistant Administrator</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>Recruitlytixs Hirings</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-assistant-administrator-recruitlytixs-hirings-1134677</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist Assistant Admin</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t>Recruitlytixs Hirings</t>
+        </is>
+      </c>
+      <c r="C295" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D295" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E295" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F295" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G295" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-assistant-admin-recruitlytixs-hirings-1134681</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (Belo Horizonte)</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-belo-horizonte-2091056</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (Montevideo)</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D297" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E297" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F297" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G297" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H297" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-montevideo-2091058</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (São Paulo)</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-sao-paulo-2091055</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (Mexico City)</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D299" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E299" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F299" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G299" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H299" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-mexico-city-2091050</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (Campinas)</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C300" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D300" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-campinas-2091049</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Product (Florianópolis)</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F301" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G301" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/staff-software-engineer-product-florianopolis-2091059</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>Staff Product Engineer (Mexico City)</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C302" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D302" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E302" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G302" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/product/staff-product-engineer-mexico-city-2091057</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>Staff Product Engineer (Montevideo)</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D303" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E303" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F303" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G303" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H303" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/product/staff-product-engineer-montevideo-2091054</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>Staff Product Engineer (Campinas)</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D304" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E304" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F304" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G304" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H304" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/product/staff-product-engineer-campinas-2091053</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="8" t="inlineStr">
+        <is>
+          <t>Staff Product Engineer (Belo Horizonte)</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G305" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H305" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/product/staff-product-engineer-belo-horizonte-2091052</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>Staff Product Engineer (Florianópolis)</t>
+        </is>
+      </c>
+      <c r="B306" s="6" t="inlineStr">
+        <is>
+          <t>LawnStarter</t>
+        </is>
+      </c>
+      <c r="C306" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D306" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E306" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F306" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G306" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/product/staff-product-engineer-florianopolis-2091051</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="8" t="inlineStr">
+        <is>
+          <t>ERP Support &amp; Optimization Business Analysts || Work from Home ||</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>Outforce</t>
+        </is>
+      </c>
+      <c r="C307" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D307" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E307" s="8" t="inlineStr"/>
+      <c r="F307" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G307" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H307" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/outforce-com/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (Bureau &amp; Regulatory)</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t>Mission Underwriting Managers</t>
+        </is>
+      </c>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D308" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E308" s="6" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F308" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G308" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H308" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mission-underwriting-managers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="8" t="inlineStr">
+        <is>
+          <t>Sr. Director, Analyst -  Physical AI and Autonomous Technologies (Remote Europe)</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G309" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H309" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="6" t="inlineStr">
+        <is>
+          <t>Senior Program Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>CACI International Inc</t>
+        </is>
+      </c>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D310" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E310" s="6" t="inlineStr"/>
+      <c r="F310" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G310" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H310" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/caci-international-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="8" t="inlineStr">
+        <is>
+          <t>Benefits Analyst</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>Rocket Software</t>
+        </is>
+      </c>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G311" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rocket-software/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
+        <is>
+          <t>IT Data Analyst</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>Resource Staff</t>
+        </is>
+      </c>
+      <c r="C312" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D312" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E312" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F312" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G312" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/resource-staff/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="8" t="inlineStr">
+        <is>
+          <t>XTN-B2E3410 |  AUTOMATION TEST ANALYST (ROBOT FRAMEWORK)</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>KMC Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F313" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G313" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kmc-solutions-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>Senior Strategy &amp; Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>Akamai Technologies</t>
+        </is>
+      </c>
+      <c r="C314" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D314" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E314" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau</t>
+        </is>
+      </c>
+      <c r="F314" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G314" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/akamai-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>TheHiveCareers</t>
+        </is>
+      </c>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/thehivecareers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="6" t="inlineStr">
+        <is>
+          <t>Senior Director, Analyst – Threat and Exposure Management</t>
+        </is>
+      </c>
+      <c r="B316" s="6" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D316" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E316" s="6" t="inlineStr"/>
+      <c r="F316" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G316" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="H316" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H292"/>
+  <autoFilter ref="A1:H316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12919,7 +13915,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -12931,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -12941,7 +13937,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>23</v>
@@ -12953,7 +13949,7 @@
         <v>25</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
@@ -12985,19 +13981,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -13016,10 +14012,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$325</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-11 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-11 23:23 UTC</t>
+          <t>数据日期 2026-07-12 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-12 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.43125</v>
+        <v>0.4563758389261745</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4125</v>
+        <v>0.4093959731543624</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.3221476510067114</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>数据分析/BI</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>54</v>
-      </c>
       <c r="H12" s="7" t="n">
-        <v>0.3375</v>
+        <v>0.3355704697986577</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.275</v>
+        <v>0.261744966442953</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.175</v>
+        <v>0.1812080536912752</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.18125</v>
+        <v>0.1879194630872483</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.075</v>
+        <v>0.0738255033557047</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.15625</v>
+        <v>0.1476510067114094</v>
       </c>
     </row>
     <row r="16">
@@ -819,36 +819,36 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1125</v>
+        <v>0.1140939597315436</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08724832214765101</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08053691275167785</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.075</v>
+        <v>0.0738255033557047</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.06875000000000001</v>
+        <v>0.0738255033557047</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -13831,8 +13831,362 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>Graduate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>Work Force Nexus</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr"/>
+      <c r="F317" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G317" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-graduate-data-scientist-work-force-nexus-1134707</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="6" t="inlineStr">
+        <is>
+          <t>KYC Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>KAST</t>
+        </is>
+      </c>
+      <c r="C318" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E318" s="6" t="inlineStr"/>
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G318" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-kyc-compliance-analyst-kast-1134740</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst, Revenue Analytics</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G319" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H319" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/147605-senior-business-analyst-revenue-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Video Collection (LATAM) - Freelance AI Trainer Project</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
+        <is>
+          <t>Invisible Technologies</t>
+        </is>
+      </c>
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="E320" s="6" t="inlineStr"/>
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149160-video-collection-latam-freelance-ai-trainer-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="8" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer, Advanced Analytics Platform</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>Spark、AWS、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F321" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G321" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H321" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/toasttab/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Assistant</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>Talent Sam</t>
+        </is>
+      </c>
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E322" s="6" t="inlineStr"/>
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/talent-sam/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="8" t="inlineStr">
+        <is>
+          <t>Financial Auditor / Analyst</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr">
+        <is>
+          <t>Remote VA</t>
+        </is>
+      </c>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G323" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H323" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/remote-va/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Operations &amp; Data Analyst</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
+        <is>
+          <t>Pavago</t>
+        </is>
+      </c>
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E324" s="6" t="inlineStr"/>
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pavago/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="8" t="inlineStr">
+        <is>
+          <t>Director, B2B Data Strategy &amp; Revenue Analytics</t>
+        </is>
+      </c>
+      <c r="B325" s="8" t="inlineStr">
+        <is>
+          <t>Wpromote</t>
+        </is>
+      </c>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D325" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E325" s="8" t="inlineStr"/>
+      <c r="F325" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G325" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H325" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wpromote/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H316"/>
+  <autoFilter ref="A1:H325"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13937,7 +14291,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>23</v>
@@ -13949,7 +14303,7 @@
         <v>25</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -13968,10 +14322,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -13981,10 +14335,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>11</v>
@@ -13993,7 +14347,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -14078,10 +14432,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$339</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-12 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-12 23:23 UTC</t>
+          <t>数据日期 2026-07-13 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-13 23:24 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4563758389261745</v>
+        <v>0.4375</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4093959731543624</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3221476510067114</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3355704697986577</v>
+        <v>0.3402777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.261744966442953</v>
+        <v>0.2569444444444444</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1812080536912752</v>
+        <v>0.1597222222222222</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1879194630872483</v>
+        <v>0.1875</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0738255033557047</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1476510067114094</v>
+        <v>0.1597222222222222</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1140939597315436</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.08724832214765101</v>
+        <v>0.09027777777777778</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08053691275167785</v>
+        <v>0.0763888888888889</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0738255033557047</v>
+        <v>0.0763888888888889</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0738255033557047</v>
+        <v>0.06944444444444445</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H325"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -14185,8 +14185,584 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Typist</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>DevHub</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E326" s="6" t="inlineStr"/>
+      <c r="F326" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G326" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H326" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-typist-devhub-1134736</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Grow the Roses</t>
+        </is>
+      </c>
+      <c r="C327" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D327" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E327" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F327" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G327" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H327" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-grow-the-roses-1134778</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (m/f/*)</t>
+        </is>
+      </c>
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t>Peregrine Technologies GmbH</t>
+        </is>
+      </c>
+      <c r="C328" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F328" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G328" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/peregrine-technologies-gmbh/senior-machine-learning-engineer-m-f-berlin-422797</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="8" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C329" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D329" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E329" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F329" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G329" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H329" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-342273</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E330" s="6" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F330" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G330" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-401452</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="8" t="inlineStr">
+        <is>
+          <t>Praktikum im Bereich Prototyping &amp; Data für Automotive Computer Vision</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr">
+        <is>
+          <t>Simi Reality Motion Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C331" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D331" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E331" s="8" t="inlineStr">
+        <is>
+          <t>Python、R、机器学习</t>
+        </is>
+      </c>
+      <c r="F331" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G331" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H331" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/simi-reality-motion-systems-gmbh/praktikum-im-bereich-prototyping-data-fur-automotive-computer-vision-unterschleissheim-199311</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr">
+        <is>
+          <t>Market &amp; Regulation Analyst Intern/Werkstudent @Atmen</t>
+        </is>
+      </c>
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t>Atmen Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C332" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D332" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E332" s="6" t="inlineStr"/>
+      <c r="F332" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G332" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/atmen-solutions-gmbh/market-regulation-analyst-intern-werkstudent-at-atmen-munich-90756</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="8" t="inlineStr">
+        <is>
+          <t>Quantitative Analyst &amp; Financial Modeller (x/w/m)</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr">
+        <is>
+          <t>Hypofriend GmbH</t>
+        </is>
+      </c>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、R</t>
+        </is>
+      </c>
+      <c r="F333" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G333" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H333" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hypofriend-gmbh/quantitative-analyst-financial-modeller-berlin-46771</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Stuttgart, Germany</t>
+        </is>
+      </c>
+      <c r="B334" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C334" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D334" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E334" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F334" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G334" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H334" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-stuttgart-germany-275854</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="8" t="inlineStr">
+        <is>
+          <t>Senior Statistician</t>
+        </is>
+      </c>
+      <c r="B335" s="8" t="inlineStr">
+        <is>
+          <t>Worldwide Clinical Trials</t>
+        </is>
+      </c>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D335" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E335" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F335" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G335" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H335" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149258-senior-statistician</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t>Content Performance Analyst</t>
+        </is>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t>RELX</t>
+        </is>
+      </c>
+      <c r="C336" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E336" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G336" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/relx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, DGXC Data Services</t>
+        </is>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D337" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E337" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F337" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G337" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H337" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nvidia/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>Quality Assurance (QA) Analyst</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>Kreato Global</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E338" s="6" t="inlineStr"/>
+      <c r="F338" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G338" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H338" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kreato-global/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst I</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="C339" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D339" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E339" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Snowflake</t>
+        </is>
+      </c>
+      <c r="F339" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G339" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H339" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/clevelandcliniclondon/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H325"/>
+  <autoFilter ref="A1:H339"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14247,19 +14823,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -14291,7 +14867,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>23</v>
@@ -14300,10 +14876,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -14335,7 +14911,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>8</v>
@@ -14344,10 +14920,10 @@
         <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-13 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-13 23:24 UTC</t>
+          <t>数据日期 2026-07-14 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-14 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4375</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4375</v>
+        <v>0.4210526315789473</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3194444444444444</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3092105263157895</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.2828947368421053</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1597222222222222</v>
+        <v>0.1776315789473684</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1875</v>
+        <v>0.1776315789473684</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0625</v>
+        <v>0.09210526315789473</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1597222222222222</v>
+        <v>0.1644736842105263</v>
       </c>
     </row>
     <row r="16">
@@ -819,62 +819,62 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09027777777777778</v>
+        <v>0.09210526315789473</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0763888888888889</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0763888888888889</v>
+        <v>0.07236842105263158</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.06578947368421052</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -14761,8 +14761,988 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="6" t="inlineStr">
+        <is>
+          <t>Supply Chain Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="C340" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D340" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E340" s="6" t="inlineStr"/>
+      <c r="F340" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G340" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-supply-chain-systems-analyst-wing-1134803</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Excel</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C341" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D341" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E341" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F341" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G341" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H341" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-excel-jobsinmass-com-1134777</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst Healthcare</t>
+        </is>
+      </c>
+      <c r="B342" s="6" t="inlineStr">
+        <is>
+          <t>City of Hope</t>
+        </is>
+      </c>
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="inlineStr"/>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G342" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-healthcare-city-of-hope-1134759</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="8" t="inlineStr">
+        <is>
+          <t>Administrative Data Entry File Clerk</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>ReLytics Hires</t>
+        </is>
+      </c>
+      <c r="C343" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F343" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G343" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H343" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-administrative-data-entry-file-clerk-relytics-hires-1134761</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist Assistant Administrator</t>
+        </is>
+      </c>
+      <c r="B344" s="6" t="inlineStr">
+        <is>
+          <t>ReLytics Hires</t>
+        </is>
+      </c>
+      <c r="C344" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E344" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G344" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-assistant-administrator-relytics-hires-1134772</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Clerk</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t>RemoteHunter</t>
+        </is>
+      </c>
+      <c r="C345" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="inlineStr"/>
+      <c r="F345" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G345" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H345" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-clerk-remotehunter-1134755</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t>InterEx Group</t>
+        </is>
+      </c>
+      <c r="C346" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="inlineStr"/>
+      <c r="F346" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G346" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-analyst-interex-group-1134750</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="8" t="inlineStr">
+        <is>
+          <t>Senior Product Engineer (Fullstack)</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr">
+        <is>
+          <t>Clipster</t>
+        </is>
+      </c>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G347" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H347" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-product-engineer-fullstack-2091062</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer / ML Engineer (m/w/x) im Bildungsumfeld / Remote</t>
+        </is>
+      </c>
+      <c r="B348" s="6" t="inlineStr">
+        <is>
+          <t>GFN GmbH</t>
+        </is>
+      </c>
+      <c r="C348" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E348" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G348" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gfn-gmbh/senior-software-engineer-ml-engineer-im-bildungsumfeld-remote-heidelberg-356036</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="8" t="inlineStr">
+        <is>
+          <t>Manager Financial Planning &amp; Analysis (FP&amp;A), BI &amp; Reporting (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr">
+        <is>
+          <t>DIHAG Holding GmbH</t>
+        </is>
+      </c>
+      <c r="C349" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D349" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E349" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F349" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G349" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H349" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dihag-holding-gmbh/manager-financial-planning-analysis-fpa-bi-reporting-dusseldorf-490595</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="6" t="inlineStr">
+        <is>
+          <t>BI Consultant / Power BI &amp; Microsoft Fabric Spezialist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B350" s="6" t="inlineStr">
+        <is>
+          <t>innomotion media GmbH</t>
+        </is>
+      </c>
+      <c r="C350" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D350" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E350" s="6" t="inlineStr">
+        <is>
+          <t>Power BI、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F350" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G350" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H350" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/innomotion-media-gmbh/bi-consultant-power-bi-microsoft-fabric-spezialist-hamburg-377849</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - AI Data Platform &amp; Snowflake (d/f/m, Berlin)</t>
+        </is>
+      </c>
+      <c r="B351" s="8" t="inlineStr">
+        <is>
+          <t>Monda Labs</t>
+        </is>
+      </c>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D351" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E351" s="8" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、Airflow、Azure、BigQuery</t>
+        </is>
+      </c>
+      <c r="F351" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G351" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H351" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/monda-labs/staff-software-engineer-ai-data-platform-snowflake-berlin-75874</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Munich, Germany</t>
+        </is>
+      </c>
+      <c r="B352" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C352" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D352" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E352" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G352" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H352" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-munich-germany-382903</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Ads Content Understanding</t>
+        </is>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C353" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D353" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E353" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F353" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G353" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H353" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149299-senior-machine-learning-engineer-ads-content-understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>Call Center Quality Analyst- Remote</t>
+        </is>
+      </c>
+      <c r="B354" s="6" t="inlineStr">
+        <is>
+          <t>Colibri Group</t>
+        </is>
+      </c>
+      <c r="C354" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E354" s="6" t="inlineStr"/>
+      <c r="F354" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G354" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H354" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/colibri-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="8" t="inlineStr">
+        <is>
+          <t>DBA &amp; Bulk Data Management Engineer</t>
+        </is>
+      </c>
+      <c r="B355" s="8" t="inlineStr">
+        <is>
+          <t>Webbing</t>
+        </is>
+      </c>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D355" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E355" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F355" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G355" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H355" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/webbing/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="6" t="inlineStr">
+        <is>
+          <t>Senior Marketing Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B356" s="6" t="inlineStr">
+        <is>
+          <t>Wellhub</t>
+        </is>
+      </c>
+      <c r="C356" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E356" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F356" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G356" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H356" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wellhub/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="8" t="inlineStr">
+        <is>
+          <t>eCommerce Business Analyst &amp; Project Coordinator</t>
+        </is>
+      </c>
+      <c r="B357" s="8" t="inlineStr">
+        <is>
+          <t>Mirantis</t>
+        </is>
+      </c>
+      <c r="C357" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D357" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E357" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Looker、Snowflake、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F357" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G357" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H357" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mirantis/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;D Technology Services Analyst</t>
+        </is>
+      </c>
+      <c r="B358" s="6" t="inlineStr">
+        <is>
+          <t>Greystar</t>
+        </is>
+      </c>
+      <c r="C358" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D358" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E358" s="6" t="inlineStr"/>
+      <c r="F358" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G358" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H358" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/greystar/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B359" s="8" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="C359" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D359" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E359" s="8" t="inlineStr">
+        <is>
+          <t>SQL、A/B测试</t>
+        </is>
+      </c>
+      <c r="F359" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G359" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H359" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/autodesk/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist, Marketing</t>
+        </is>
+      </c>
+      <c r="B360" s="6" t="inlineStr">
+        <is>
+          <t>Launch Potato</t>
+        </is>
+      </c>
+      <c r="C360" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E360" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G360" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H360" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/launch-potato/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer - AI Coding Expert</t>
+        </is>
+      </c>
+      <c r="B361" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C361" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D361" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E361" s="8" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="F361" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G361" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H361" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Learned Planning/Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="B362" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C362" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E362" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G362" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H362" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/torc-robotics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="8" t="inlineStr">
+        <is>
+          <t>Analyst, Revenue Integrity</t>
+        </is>
+      </c>
+      <c r="B363" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D363" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E363" s="8" t="inlineStr"/>
+      <c r="F363" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G363" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H363" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/northwestern-memorial-healthcare/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H339"/>
+  <autoFilter ref="A1:H363"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14823,19 +15803,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -14867,19 +15847,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -14889,7 +15869,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -14901,7 +15881,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -14911,19 +15891,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -14942,10 +15922,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -15030,10 +16010,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$374</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-14 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-14 23:23 UTC</t>
+          <t>数据日期 2026-07-15 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-15 23:26 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4344827586206896</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.296551724137931</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>数据分析/BI</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>47</v>
-      </c>
       <c r="H12" s="7" t="n">
-        <v>0.3092105263157895</v>
+        <v>0.303448275862069</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2828947368421053</v>
+        <v>0.2620689655172414</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1776315789473684</v>
+        <v>0.1724137931034483</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1776315789473684</v>
+        <v>0.1862068965517241</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.0896551724137931</v>
       </c>
     </row>
     <row r="15">
@@ -809,7 +809,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1644736842105263</v>
+        <v>0.1724137931034483</v>
       </c>
     </row>
     <row r="16">
@@ -819,62 +819,62 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.131578947368421</v>
+        <v>0.1517241379310345</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.08275862068965517</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.08275862068965517</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07236842105263158</v>
+        <v>0.07586206896551724</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.06578947368421052</v>
+        <v>0.06896551724137931</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H363"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -15741,8 +15741,458 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="6" t="inlineStr">
+        <is>
+          <t>Entry Level Data Entry Clerk Fully</t>
+        </is>
+      </c>
+      <c r="B364" s="6" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C364" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D364" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E364" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F364" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G364" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H364" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-entry-level-data-entry-clerk-fully-jobsinmass-com-1134807</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst Project Support</t>
+        </is>
+      </c>
+      <c r="B365" s="8" t="inlineStr">
+        <is>
+          <t>Cint</t>
+        </is>
+      </c>
+      <c r="C365" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D365" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E365" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F365" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G365" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H365" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-analyst-project-support-cint-1134818</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Clerk Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="B366" s="6" t="inlineStr">
+        <is>
+          <t>Burjline Builders</t>
+        </is>
+      </c>
+      <c r="C366" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E366" s="6" t="inlineStr"/>
+      <c r="F366" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G366" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H366" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-clerk-data-entry-specialist-burjline-builders-1134805</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="8" t="inlineStr">
+        <is>
+          <t>Revenue Operations Analyst - (all genders)</t>
+        </is>
+      </c>
+      <c r="B367" s="8" t="inlineStr">
+        <is>
+          <t>fino data services GmbH</t>
+        </is>
+      </c>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D367" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E367" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、统计学</t>
+        </is>
+      </c>
+      <c r="F367" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G367" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H367" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/fino-data-services-gmbh/revenue-operations-analyst-all-genders-100-homeoffice-kassel-439988</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="6" t="inlineStr">
+        <is>
+          <t>Insights Analyst</t>
+        </is>
+      </c>
+      <c r="B368" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C368" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E368" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G368" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H368" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/oddup/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist Senior</t>
+        </is>
+      </c>
+      <c r="B369" s="8" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D369" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E369" s="8" t="inlineStr">
+        <is>
+          <t>AWS、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F369" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G369" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H369" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/general-dynamics-information-technology/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="6" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer Associate</t>
+        </is>
+      </c>
+      <c r="B370" s="6" t="inlineStr">
+        <is>
+          <t>Geisinger</t>
+        </is>
+      </c>
+      <c r="C370" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E370" s="6" t="inlineStr"/>
+      <c r="F370" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G370" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H370" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/geisinger/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="8" t="inlineStr">
+        <is>
+          <t>Senior People Technology Analyst - Workday</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C371" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D371" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E371" s="8" t="inlineStr"/>
+      <c r="F371" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G371" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H371" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/samsara/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="6" t="inlineStr">
+        <is>
+          <t>Analyst I, Full Stack</t>
+        </is>
+      </c>
+      <c r="B372" s="6" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="C372" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E372" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F372" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G372" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H372" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/affirm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="8" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B373" s="8" t="inlineStr">
+        <is>
+          <t>Huzzle</t>
+        </is>
+      </c>
+      <c r="C373" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E373" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F373" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G373" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H373" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/huzzle/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="inlineStr">
+        <is>
+          <t>Senior AI / ML / Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B374" s="6" t="inlineStr">
+        <is>
+          <t>QAVION GROUP GmbH</t>
+        </is>
+      </c>
+      <c r="C374" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E374" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G374" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="H374" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/qavion-group-gmbh/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H363"/>
+  <autoFilter ref="A1:H374"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15803,19 +16253,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -15847,19 +16297,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -15891,7 +16341,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>9</v>
@@ -15900,10 +16350,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
@@ -15957,7 +16407,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -15969,7 +16419,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-15 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-15 23:26 UTC</t>
+          <t>数据日期 2026-07-16 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-16 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4632352941176471</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4344827586206896</v>
+        <v>0.4632352941176471</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.296551724137931</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.303448275862069</v>
+        <v>0.3014705882352941</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2620689655172414</v>
+        <v>0.2794117647058824</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1617647058823529</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1862068965517241</v>
+        <v>0.1985294117647059</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0896551724137931</v>
+        <v>0.07352941176470588</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1617647058823529</v>
       </c>
     </row>
     <row r="16">
@@ -819,36 +819,36 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1517241379310345</v>
+        <v>0.1470588235294118</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.08275862068965517</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08275862068965517</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07586206896551724</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.07352941176470588</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -16191,8 +16191,774 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B375" s="8" t="inlineStr">
+        <is>
+          <t>EasyPark</t>
+        </is>
+      </c>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D375" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E375" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F375" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G375" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H375" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-analyst-easypark-1134922</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="6" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B376" s="6" t="inlineStr">
+        <is>
+          <t>Base.com</t>
+        </is>
+      </c>
+      <c r="C376" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E376" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Power BI、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G376" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H376" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-intelligence-developer-base-com-1134926</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="8" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B377" s="8" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D377" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E377" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F377" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G377" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H377" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/devops/senior-devops-engineer-2091067</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="inlineStr">
+        <is>
+          <t>Data Labeling Specialists</t>
+        </is>
+      </c>
+      <c r="B378" s="6" t="inlineStr">
+        <is>
+          <t>Workada</t>
+        </is>
+      </c>
+      <c r="C378" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E378" s="6" t="inlineStr"/>
+      <c r="F378" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G378" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H378" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/data/data-labeling-specialists-2090903</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer / ML Engineer (m/w/x) im Bildungsumfeld / Remote</t>
+        </is>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>GFN GmbH</t>
+        </is>
+      </c>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D379" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E379" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F379" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G379" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H379" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gfn-gmbh/senior-software-engineer-ml-engineer-im-bildungsumfeld-remote-heidelberg-276710</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="6" t="inlineStr">
+        <is>
+          <t>KYC Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B380" s="6" t="inlineStr">
+        <is>
+          <t>Tangany GmbH</t>
+        </is>
+      </c>
+      <c r="C380" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D380" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E380" s="6" t="inlineStr"/>
+      <c r="F380" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G380" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H380" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tangany-gmbh/kyc-analyst-munich-193689</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D381" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E381" s="8" t="inlineStr"/>
+      <c r="F381" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G381" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H381" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1732355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="6" t="inlineStr">
+        <is>
+          <t>Senior Staff Software Engineer, Backend (Data and Storage Services)</t>
+        </is>
+      </c>
+      <c r="B382" s="6" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="C382" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E382" s="6" t="inlineStr">
+        <is>
+          <t>Spark、Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G382" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H382" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/affirm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="8" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer- Lead Consultant</t>
+        </is>
+      </c>
+      <c r="B383" s="8" t="inlineStr">
+        <is>
+          <t>Lingaro</t>
+        </is>
+      </c>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D383" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E383" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Spark、dbt、Airflow、Azure、GCP、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F383" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G383" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H383" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lingaro/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager / QA Analyst (Full-Time Remote Contractor)</t>
+        </is>
+      </c>
+      <c r="B384" s="6" t="inlineStr">
+        <is>
+          <t>Khibraty</t>
+        </is>
+      </c>
+      <c r="C384" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E384" s="6" t="inlineStr"/>
+      <c r="F384" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G384" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H384" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/khibraty/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Healthcare</t>
+        </is>
+      </c>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>Mariner</t>
+        </is>
+      </c>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D385" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="inlineStr">
+        <is>
+          <t>Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F385" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G385" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H385" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/marinerpartners/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B386" s="6" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="C386" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D386" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E386" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F386" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G386" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H386" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/dayforce/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="8" t="inlineStr">
+        <is>
+          <t>SEO Analyst (India Remote)</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>Snapscale</t>
+        </is>
+      </c>
+      <c r="C387" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E387" s="8" t="inlineStr"/>
+      <c r="F387" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G387" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H387" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/snapscale/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="6" t="inlineStr">
+        <is>
+          <t>Cerner Data Integration Consultant</t>
+        </is>
+      </c>
+      <c r="B388" s="6" t="inlineStr">
+        <is>
+          <t>Atria Group LLC</t>
+        </is>
+      </c>
+      <c r="C388" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E388" s="6" t="inlineStr"/>
+      <c r="F388" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G388" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H388" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/atria-group-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Data Scientist</t>
+        </is>
+      </c>
+      <c r="B389" s="8" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="C389" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D389" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E389" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F389" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G389" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H389" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/extend-app/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="6" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst (FP&amp;A) | Egypt</t>
+        </is>
+      </c>
+      <c r="B390" s="6" t="inlineStr">
+        <is>
+          <t>HireHawk</t>
+        </is>
+      </c>
+      <c r="C390" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D390" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E390" s="6" t="inlineStr"/>
+      <c r="F390" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G390" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H390" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hirehawk/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst (FP&amp;A) | Colombia</t>
+        </is>
+      </c>
+      <c r="B391" s="8" t="inlineStr">
+        <is>
+          <t>HireHawk</t>
+        </is>
+      </c>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D391" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E391" s="8" t="inlineStr"/>
+      <c r="F391" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G391" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H391" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hirehawk/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist, Consumer</t>
+        </is>
+      </c>
+      <c r="B392" s="6" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C392" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E392" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F392" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G392" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H392" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/reddit/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer, Data Centers - Remote (U.S.)</t>
+        </is>
+      </c>
+      <c r="B393" s="8" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C393" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D393" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E393" s="8" t="inlineStr">
+        <is>
+          <t>Airflow</t>
+        </is>
+      </c>
+      <c r="F393" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G393" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H393" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/aecom/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H374"/>
+  <autoFilter ref="A1:H393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16253,10 +17019,10 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>11</v>
@@ -16265,7 +17031,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -16300,16 +17066,16 @@
         <v>62</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -16319,7 +17085,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -16331,7 +17097,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -16341,7 +17107,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>9</v>
@@ -16353,7 +17119,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -16366,16 +17132,16 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -16407,19 +17173,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -16460,10 +17226,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$412</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-16 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-16 23:23 UTC</t>
+          <t>数据日期 2026-07-17 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-17 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4632352941176471</v>
+        <v>0.481203007518797</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4632352941176471</v>
+        <v>0.4360902255639098</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3458646616541353</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3014705882352941</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2794117647058824</v>
+        <v>0.3082706766917293</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1617647058823529</v>
+        <v>0.1879699248120301</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1985294117647059</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.09022556390977443</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1617647058823529</v>
+        <v>0.1503759398496241</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1353383458646616</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.112781954887218</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.09774436090225563</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.09022556390977443</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H393"/>
+  <dimension ref="A1:H412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -16957,8 +16957,798 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="6" t="inlineStr">
+        <is>
+          <t>Junior Power BI Analyst</t>
+        </is>
+      </c>
+      <c r="B394" s="6" t="inlineStr">
+        <is>
+          <t>StatusNeo</t>
+        </is>
+      </c>
+      <c r="C394" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D394" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E394" s="6" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F394" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G394" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H394" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-junior-power-bi-analyst-statusneo-1134912</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="8" t="inlineStr">
+        <is>
+          <t>Head of Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="B395" s="8" t="inlineStr">
+        <is>
+          <t>garden3d</t>
+        </is>
+      </c>
+      <c r="C395" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D395" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E395" s="8" t="inlineStr"/>
+      <c r="F395" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G395" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H395" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/marketing/head-of-marketing-communications-2091068</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B396" s="6" t="inlineStr">
+        <is>
+          <t>Atolls</t>
+        </is>
+      </c>
+      <c r="C396" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D396" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E396" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F396" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G396" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H396" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/atolls/data-engineer-berlin-466297</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B397" s="8" t="inlineStr">
+        <is>
+          <t>Atolls</t>
+        </is>
+      </c>
+      <c r="C397" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D397" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E397" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F397" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G397" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H397" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/atolls/data-engineer-munich-309780</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B398" s="6" t="inlineStr">
+        <is>
+          <t>Atolls</t>
+        </is>
+      </c>
+      <c r="C398" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D398" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E398" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F398" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G398" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H398" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/atolls/data-engineer-berlin-363381</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="8" t="inlineStr">
+        <is>
+          <t>Bachelorarbeit (m/w/d) – KI-gestützte Automatisierung des Datenimports im Data Warehouse</t>
+        </is>
+      </c>
+      <c r="B399" s="8" t="inlineStr">
+        <is>
+          <t>accantec group</t>
+        </is>
+      </c>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D399" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E399" s="8" t="inlineStr">
+        <is>
+          <t>SQL、ETL</t>
+        </is>
+      </c>
+      <c r="F399" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G399" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H399" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/accantec-group/bachelorarbeit-ki-gestutzte-automatisierung-des-datenimports-im-data-warehouse-heidelberg-199638</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Business Intelligence Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B400" s="6" t="inlineStr">
+        <is>
+          <t>Homaris Service GmbH</t>
+        </is>
+      </c>
+      <c r="C400" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D400" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E400" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G400" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H400" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/homaris-service-gmbh/junior-business-intelligence-analyst-all-genders-berlin-62137</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B401" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C401" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D401" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E401" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F401" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G401" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H401" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-92499</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B402" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C402" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E402" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G402" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H402" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-125959</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="8" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B403" s="8" t="inlineStr">
+        <is>
+          <t>exmox GmbH</t>
+        </is>
+      </c>
+      <c r="C403" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D403" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E403" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F403" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G403" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H403" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/exmox-gmbh/principal-machine-learning-engineer-hamburg-429549</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B404" s="6" t="inlineStr">
+        <is>
+          <t>Rockstardevelopers GmbH</t>
+        </is>
+      </c>
+      <c r="C404" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D404" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E404" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G404" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H404" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/machine-learning-engineer-stuttgart-412768</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Scientist</t>
+        </is>
+      </c>
+      <c r="B405" s="8" t="inlineStr">
+        <is>
+          <t>Fieldguide</t>
+        </is>
+      </c>
+      <c r="C405" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D405" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E405" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、dbt、Airflow、机器学习、统计学、ETL、pandas</t>
+        </is>
+      </c>
+      <c r="F405" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G405" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H405" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149403-lead-data-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Innovation Lab</t>
+        </is>
+      </c>
+      <c r="B406" s="6" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C406" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D406" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E406" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G406" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H406" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149399-senior-data-scientist-innovation-lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B407" s="8" t="inlineStr">
+        <is>
+          <t>SmartLight Analytics</t>
+        </is>
+      </c>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D407" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E407" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Snowflake、dbt、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F407" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G407" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H407" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/smartlight-analytics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist</t>
+        </is>
+      </c>
+      <c r="B408" s="6" t="inlineStr">
+        <is>
+          <t>AF Group</t>
+        </is>
+      </c>
+      <c r="C408" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D408" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E408" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、A/B测试、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F408" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G408" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H408" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/af-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="8" t="inlineStr">
+        <is>
+          <t>REMOTE Data Analyst - POWER BI+MONGO+ DAX EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="B409" s="8" t="inlineStr">
+        <is>
+          <t>Catasys Health</t>
+        </is>
+      </c>
+      <c r="C409" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D409" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E409" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F409" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G409" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H409" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/catasys-health/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B410" s="6" t="inlineStr">
+        <is>
+          <t>Cybermedia Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C410" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D410" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E410" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G410" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H410" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cybermedia-technologies-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B411" s="8" t="inlineStr">
+        <is>
+          <t>Striveworks</t>
+        </is>
+      </c>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D411" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E411" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F411" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G411" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H411" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/striveworks/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr">
+        <is>
+          <t>Senior Project Manager/Business Analyst, Life Sciences</t>
+        </is>
+      </c>
+      <c r="B412" s="6" t="inlineStr">
+        <is>
+          <t>fme US, LLC</t>
+        </is>
+      </c>
+      <c r="C412" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D412" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E412" s="6" t="inlineStr"/>
+      <c r="F412" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G412" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H412" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fme-us-llc/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H393"/>
+  <autoFilter ref="A1:H412"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17019,19 +17809,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>11</v>
-      </c>
       <c r="E2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -17063,19 +17853,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>33</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -17094,10 +17884,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -17173,7 +17963,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -17185,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$416</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-17 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-17 23:14 UTC</t>
+          <t>数据日期 2026-07-18 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-18 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.481203007518797</v>
+        <v>0.4732824427480916</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4360902255639098</v>
+        <v>0.4580152671755725</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3458646616541353</v>
+        <v>0.3358778625954199</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2824427480916031</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3082706766917293</v>
+        <v>0.2900763358778626</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1879699248120301</v>
+        <v>0.183206106870229</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2061068702290076</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09022556390977443</v>
+        <v>0.07633587786259542</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1503759398496241</v>
+        <v>0.1450381679389313</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1353383458646616</v>
+        <v>0.1297709923664122</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.112781954887218</v>
+        <v>0.09923664122137404</v>
       </c>
     </row>
     <row r="18">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.09923664122137404</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09774436090225563</v>
+        <v>0.07633587786259542</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09022556390977443</v>
+        <v>0.07633587786259542</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H412"/>
+  <dimension ref="A1:H416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -17747,8 +17747,168 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="8" t="inlineStr">
+        <is>
+          <t>Patient Care Specialist</t>
+        </is>
+      </c>
+      <c r="B413" s="8" t="inlineStr">
+        <is>
+          <t>STATLINX</t>
+        </is>
+      </c>
+      <c r="C413" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D413" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E413" s="8" t="inlineStr"/>
+      <c r="F413" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G413" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H413" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/medical/patient-care-specialist-2091069</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="6" t="inlineStr">
+        <is>
+          <t>IME Quality Analyst - Auto &amp; Liability</t>
+        </is>
+      </c>
+      <c r="B414" s="6" t="inlineStr">
+        <is>
+          <t>Dane Street</t>
+        </is>
+      </c>
+      <c r="C414" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D414" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E414" s="6" t="inlineStr"/>
+      <c r="F414" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G414" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H414" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/danestreet/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="8" t="inlineStr">
+        <is>
+          <t>Analytics and Insights Lead (CX)</t>
+        </is>
+      </c>
+      <c r="B415" s="8" t="inlineStr">
+        <is>
+          <t>Who Gives A Crap</t>
+        </is>
+      </c>
+      <c r="C415" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D415" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E415" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F415" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G415" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H415" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/whogivesacrap/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="6" t="inlineStr">
+        <is>
+          <t>Senior Financial Data Analyst / FP&amp;A Business Partner</t>
+        </is>
+      </c>
+      <c r="B416" s="6" t="inlineStr">
+        <is>
+          <t>iSpeedtoLead</t>
+        </is>
+      </c>
+      <c r="C416" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D416" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E416" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F416" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G416" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H416" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ispeedtolead/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H412"/>
+  <autoFilter ref="A1:H416"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17831,7 +17991,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>1</v>
@@ -17843,7 +18003,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -17853,7 +18013,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>32</v>
@@ -17862,10 +18022,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
@@ -17897,7 +18057,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>9</v>
@@ -17909,7 +18069,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$430</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-18 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-18 23:23 UTC</t>
+          <t>数据日期 2026-07-19 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-19 23:26 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,21 +710,21 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.4744525547445255</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>0.4732824427480916</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>其他数据岗</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>60</v>
-      </c>
       <c r="H11" s="7" t="n">
-        <v>0.4580152671755725</v>
+        <v>0.4525547445255474</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3358778625954199</v>
+        <v>0.3576642335766423</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2824427480916031</v>
+        <v>0.2554744525547445</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2900763358778626</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.183206106870229</v>
+        <v>0.1751824817518248</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.2061068702290076</v>
+        <v>0.218978102189781</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,49 +793,49 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.1167883211678832</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1450381679389313</v>
+        <v>0.1313868613138686</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1297709923664122</v>
+        <v>0.1167883211678832</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09923664122137404</v>
+        <v>0.1021897810218978</v>
       </c>
     </row>
     <row r="18">
@@ -845,23 +845,23 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09923664122137404</v>
+        <v>0.1021897810218978</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.0948905109489051</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.0948905109489051</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H416"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -17907,8 +17907,580 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B417" s="8" t="inlineStr">
+        <is>
+          <t>GLS/NXT</t>
+        </is>
+      </c>
+      <c r="C417" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D417" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E417" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、Snowflake、dbt、Airflow、AWS、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F417" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G417" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H417" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/glsnxt/senior-data-engineer-berlin-391080</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="6" t="inlineStr">
+        <is>
+          <t>VP, Data</t>
+        </is>
+      </c>
+      <c r="B418" s="6" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C418" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D418" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E418" s="6" t="inlineStr">
+        <is>
+          <t>Excel、机器学习</t>
+        </is>
+      </c>
+      <c r="F418" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G418" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H418" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/img-academy/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (PowerBI and Fabric) - Fully Remote Opportunity</t>
+        </is>
+      </c>
+      <c r="B419" s="8" t="inlineStr">
+        <is>
+          <t>Zealogics</t>
+        </is>
+      </c>
+      <c r="C419" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D419" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E419" s="8" t="inlineStr">
+        <is>
+          <t>Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F419" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G419" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H419" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zealogics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Complaint Analyst - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B420" s="6" t="inlineStr">
+        <is>
+          <t>Calyxo</t>
+        </is>
+      </c>
+      <c r="C420" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D420" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E420" s="6" t="inlineStr"/>
+      <c r="F420" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G420" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H420" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/calyxo/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="8" t="inlineStr">
+        <is>
+          <t>Director Analyst - Sourcing, Contracts and Negotiations – Digital Experience Pla</t>
+        </is>
+      </c>
+      <c r="B421" s="8" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C421" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D421" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E421" s="8" t="inlineStr"/>
+      <c r="F421" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G421" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H421" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="6" t="inlineStr">
+        <is>
+          <t>Technical Product Manager - Client Intelligence &amp; Data</t>
+        </is>
+      </c>
+      <c r="B422" s="6" t="inlineStr">
+        <is>
+          <t>Yuno</t>
+        </is>
+      </c>
+      <c r="C422" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D422" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E422" s="6" t="inlineStr"/>
+      <c r="F422" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G422" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H422" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/yuno/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B423" s="8" t="inlineStr">
+        <is>
+          <t>Fusemachines</t>
+        </is>
+      </c>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D423" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E423" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F423" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G423" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H423" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fusemachines/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B424" s="6" t="inlineStr">
+        <is>
+          <t>Particle41</t>
+        </is>
+      </c>
+      <c r="C424" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D424" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E424" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G424" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H424" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/particle41/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="8" t="inlineStr">
+        <is>
+          <t>SAP Application Security Analyst II (HUIXQUILUCAN, Estado de México, MX, 52779)</t>
+        </is>
+      </c>
+      <c r="B425" s="8" t="inlineStr">
+        <is>
+          <t>McCormick &amp; Company</t>
+        </is>
+      </c>
+      <c r="C425" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D425" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E425" s="8" t="inlineStr"/>
+      <c r="F425" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G425" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H425" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mccormick-company/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst - Water Infrastructure</t>
+        </is>
+      </c>
+      <c r="B426" s="6" t="inlineStr">
+        <is>
+          <t>Pavago</t>
+        </is>
+      </c>
+      <c r="C426" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D426" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E426" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F426" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G426" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H426" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pavago/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="8" t="inlineStr">
+        <is>
+          <t>Bigdata Engineer -Spark</t>
+        </is>
+      </c>
+      <c r="B427" s="8" t="inlineStr">
+        <is>
+          <t>Marktine Technology Solutions Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C427" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D427" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E427" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Spark、ETL</t>
+        </is>
+      </c>
+      <c r="F427" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G427" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H427" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/marktine-technology-solutions-pvt-ltd/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineering Manager</t>
+        </is>
+      </c>
+      <c r="B428" s="6" t="inlineStr">
+        <is>
+          <t>YipitData</t>
+        </is>
+      </c>
+      <c r="C428" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D428" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E428" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Airflow、ETL</t>
+        </is>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G428" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H428" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/yipitdata/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="8" t="inlineStr">
+        <is>
+          <t>UX Researcher, Data Analyst &amp; Optimization Specialist</t>
+        </is>
+      </c>
+      <c r="B429" s="8" t="inlineStr">
+        <is>
+          <t>Anatta Design</t>
+        </is>
+      </c>
+      <c r="C429" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D429" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E429" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F429" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G429" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H429" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/anatta-design/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="6" t="inlineStr">
+        <is>
+          <t>Data and Analytics Practice Coordinator - Senior</t>
+        </is>
+      </c>
+      <c r="B430" s="6" t="inlineStr">
+        <is>
+          <t>Dijital Team Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C430" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D430" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E430" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F430" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G430" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H430" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/dijital-team-pty-ltd/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H416"/>
+  <autoFilter ref="A1:H430"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17975,13 +18547,13 @@
         <v>16</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -18000,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -18013,19 +18585,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
@@ -18057,7 +18629,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>9</v>
@@ -18069,7 +18641,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
@@ -18129,13 +18701,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$455</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-19 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-19 23:26 UTC</t>
+          <t>数据日期 2026-07-20 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-20 23:29 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4744525547445255</v>
+        <v>0.4097222222222222</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4525547445255474</v>
+        <v>0.4722222222222222</v>
       </c>
     </row>
     <row r="12">
@@ -737,7 +737,7 @@
         <v>49</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3576642335766423</v>
+        <v>0.3402777777777778</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2554744525547445</v>
+        <v>0.2916666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2992700729927008</v>
+        <v>0.2847222222222222</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1751824817518248</v>
+        <v>0.1458333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.218978102189781</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1167883211678832</v>
+        <v>0.09027777777777778</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1313868613138686</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1167883211678832</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.1041666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.09027777777777778</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0948905109489051</v>
+        <v>0.09027777777777778</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0948905109489051</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -18479,8 +18479,1034 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="8" t="inlineStr">
+        <is>
+          <t>Data Mapping Analyst</t>
+        </is>
+      </c>
+      <c r="B431" s="8" t="inlineStr">
+        <is>
+          <t>Buyers Edge Platform, LLC</t>
+        </is>
+      </c>
+      <c r="C431" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D431" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E431" s="8" t="inlineStr"/>
+      <c r="F431" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G431" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H431" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-mapping-analyst-buyers-edge-platform-llc-1135069</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Assistant</t>
+        </is>
+      </c>
+      <c r="B432" s="6" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C432" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D432" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E432" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G432" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H432" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-assistant-jobsinmass-com-1135073</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="8" t="inlineStr">
+        <is>
+          <t>Entry Level Data Entry Clerk Admin</t>
+        </is>
+      </c>
+      <c r="B433" s="8" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C433" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D433" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E433" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F433" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G433" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H433" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-entry-level-data-entry-clerk-admin-jobsinmass-com-1135071</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="6" t="inlineStr">
+        <is>
+          <t>Virtual Data Entry Clerk</t>
+        </is>
+      </c>
+      <c r="B434" s="6" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C434" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E434" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F434" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G434" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H434" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-virtual-data-entry-clerk-jobsinmass-com-1135074</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="8" t="inlineStr">
+        <is>
+          <t>Entry Level Data Entry Clerk</t>
+        </is>
+      </c>
+      <c r="B435" s="8" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D435" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E435" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F435" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G435" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H435" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-entry-level-data-entry-clerk-jobsinmass-com-1135072</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Typist</t>
+        </is>
+      </c>
+      <c r="B436" s="6" t="inlineStr">
+        <is>
+          <t>JobsInMass.com</t>
+        </is>
+      </c>
+      <c r="C436" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D436" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E436" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F436" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G436" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H436" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-typist-jobsinmass-com-1135070</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="B437" s="8" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C437" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D437" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E437" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F437" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G437" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H437" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-berlin-germany-255908</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="B438" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C438" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E438" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F438" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G438" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H438" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-hamburg-germany-95082</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B439" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C439" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D439" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E439" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Power BI、Spark、Snowflake</t>
+        </is>
+      </c>
+      <c r="F439" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G439" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H439" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-analyst-berlin-22732</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B440" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C440" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D440" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E440" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Power BI、Spark、Snowflake</t>
+        </is>
+      </c>
+      <c r="F440" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G440" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H440" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-analyst-munich-205657</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="8" t="inlineStr">
+        <is>
+          <t>Senior Product Analyst</t>
+        </is>
+      </c>
+      <c r="B441" s="8" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C441" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D441" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E441" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Snowflake、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F441" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G441" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H441" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-product-analyst-berlin-418374</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Courier and Logistics Analytics</t>
+        </is>
+      </c>
+      <c r="B442" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C442" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D442" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E442" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F442" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G442" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H442" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/analytics-manager-courier-and-logistics-analytics-munich-218608</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Courier and Logistics Analytics</t>
+        </is>
+      </c>
+      <c r="B443" s="8" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C443" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D443" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E443" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F443" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G443" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H443" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/analytics-manager-courier-and-logistics-analytics-berlin-240088</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B444" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C444" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E444" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F444" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G444" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H444" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-40999</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B445" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C445" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D445" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E445" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F445" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G445" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H445" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-459633</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="inlineStr">
+        <is>
+          <t>Investment Analyst (m/w/d) im Bereich Kapitalmärkte</t>
+        </is>
+      </c>
+      <c r="B446" s="6" t="inlineStr">
+        <is>
+          <t>DeltaValue GmbH</t>
+        </is>
+      </c>
+      <c r="C446" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E446" s="6" t="inlineStr"/>
+      <c r="F446" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G446" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H446" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/deltavalue-gmbh/investment-analyst-im-bereich-kapitalmarkte-essen-354245</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="8" t="inlineStr">
+        <is>
+          <t>Sr Data Reviewer - Small Molecule</t>
+        </is>
+      </c>
+      <c r="B447" s="8" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C447" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D447" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E447" s="8" t="inlineStr"/>
+      <c r="F447" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G447" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H447" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149474-sr-data-reviewer-small-molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="inlineStr">
+        <is>
+          <t>Clinical Data Team Lead</t>
+        </is>
+      </c>
+      <c r="B448" s="6" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C448" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D448" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E448" s="6" t="inlineStr"/>
+      <c r="F448" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G448" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H448" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149471-clinical-data-team-lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="8" t="inlineStr">
+        <is>
+          <t>Director, AI Commerce Analytics (USA Based Remote)</t>
+        </is>
+      </c>
+      <c r="B449" s="8" t="inlineStr">
+        <is>
+          <t>NielsenIQ</t>
+        </is>
+      </c>
+      <c r="C449" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D449" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E449" s="8" t="inlineStr"/>
+      <c r="F449" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G449" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H449" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149463-director-ai-commerce-analytics-usa-based-remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="6" t="inlineStr">
+        <is>
+          <t>Director, Data Analytics (Customer Experience / Member Growth &amp; Retention)</t>
+        </is>
+      </c>
+      <c r="B450" s="6" t="inlineStr">
+        <is>
+          <t>Molina Healthcare</t>
+        </is>
+      </c>
+      <c r="C450" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D450" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E450" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G450" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H450" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149452-director-data-analytics-customer-experience-member-growth-retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (Product &amp; Customer Analytics)</t>
+        </is>
+      </c>
+      <c r="B451" s="8" t="inlineStr">
+        <is>
+          <t>Oowlish Technology</t>
+        </is>
+      </c>
+      <c r="C451" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D451" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E451" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、R、BigQuery、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F451" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G451" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H451" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149448-data-analyst-product-customer-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B452" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C452" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E452" s="6" t="inlineStr">
+        <is>
+          <t>SQL、ETL</t>
+        </is>
+      </c>
+      <c r="F452" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G452" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H452" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/press-ganey/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="8" t="inlineStr">
+        <is>
+          <t>Senior FP&amp;A Analyst</t>
+        </is>
+      </c>
+      <c r="B453" s="8" t="inlineStr">
+        <is>
+          <t>Ledgebrook</t>
+        </is>
+      </c>
+      <c r="C453" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D453" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E453" s="8" t="inlineStr"/>
+      <c r="F453" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G453" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H453" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ledgebrook/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="6" t="inlineStr">
+        <is>
+          <t>Pricing Analyst</t>
+        </is>
+      </c>
+      <c r="B454" s="6" t="inlineStr">
+        <is>
+          <t>SupplyHouse.com</t>
+        </is>
+      </c>
+      <c r="C454" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D454" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E454" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Power BI、R</t>
+        </is>
+      </c>
+      <c r="F454" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G454" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H454" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/supplyhouse-com/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="8" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer (Mission Critical/Data Center) - Remote</t>
+        </is>
+      </c>
+      <c r="B455" s="8" t="inlineStr">
+        <is>
+          <t>WSP Africa</t>
+        </is>
+      </c>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D455" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E455" s="8" t="inlineStr">
+        <is>
+          <t>Airflow</t>
+        </is>
+      </c>
+      <c r="F455" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G455" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H455" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wsp-africa/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H430"/>
+  <autoFilter ref="A1:H455"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18541,19 +19567,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -18585,19 +19611,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -18607,7 +19633,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -18619,7 +19645,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -18629,7 +19655,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>9</v>
@@ -18638,10 +19664,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$455</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$475</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-20 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-20 23:29 UTC</t>
+          <t>数据日期 2026-07-21 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-21 23:27 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4097222222222222</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.4313725490196079</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3464052287581699</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3137254901960784</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2847222222222222</v>
+        <v>0.3006535947712418</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1568627450980392</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1805555555555556</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09027777777777778</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="15">
@@ -809,7 +809,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1568627450980392</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1241830065359477</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.1045751633986928</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09027777777777778</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09027777777777778</v>
+        <v>0.0915032679738562</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.08496732026143791</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H455"/>
+  <dimension ref="A1:H475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -19505,8 +19505,816 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst FlixTrain Operations (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B456" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E456" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Snowflake</t>
+        </is>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G456" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H456" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/data-analyst-flixtrain-operations-berlin-393690</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer - Run &amp; Grow</t>
+        </is>
+      </c>
+      <c r="B457" s="8" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C457" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F457" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G457" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H457" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-analytics-engineer-run-grow-berlin-92066</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent:in YouTube Growth &amp; Analytics (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B458" s="6" t="inlineStr">
+        <is>
+          <t>HitchOn</t>
+        </is>
+      </c>
+      <c r="C458" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D458" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E458" s="6" t="inlineStr"/>
+      <c r="F458" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G458" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H458" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hitchon/werkstudentin-youtube-growth-analytics-mainz-282681</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B459" s="8" t="inlineStr">
+        <is>
+          <t>Stahlwerk Annahütte  Max Aicher GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C459" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D459" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E459" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F459" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G459" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H459" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stahlwerk-annahutte-max-aicher-gmbh-co-kg/data-engineer-ainring-326977</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B460" s="6" t="inlineStr">
+        <is>
+          <t>Stahlwerk Annahütte  Max Aicher GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C460" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E460" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G460" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H460" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stahlwerk-annahutte-max-aicher-gmbh-co-kg/junior-data-engineer-ainring-376653</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Financial Analyst, FP&amp;A and Operations Finance (m/f/d), Xylem Analytics</t>
+        </is>
+      </c>
+      <c r="B461" s="8" t="inlineStr">
+        <is>
+          <t>Xylem</t>
+        </is>
+      </c>
+      <c r="C461" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D461" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E461" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F461" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G461" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H461" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/xylem/senior-financial-analyst-fpa-and-operations-finance-xylem-analytics-weilheim-in-oberbayern-418180</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr">
+        <is>
+          <t>Data Strategy Analyst | NDA</t>
+        </is>
+      </c>
+      <c r="B462" s="6" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="C462" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D462" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E462" s="6" t="inlineStr"/>
+      <c r="F462" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G462" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H462" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149500-data-strategy-analyst-nda</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="8" t="inlineStr">
+        <is>
+          <t>Senior Kohl's Media Network Analytics Analyst</t>
+        </is>
+      </c>
+      <c r="B463" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C463" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D463" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E463" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Power BI、Looker</t>
+        </is>
+      </c>
+      <c r="F463" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G463" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H463" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kohl-s/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="6" t="inlineStr">
+        <is>
+          <t>Senior Quality Systems Application Analyst</t>
+        </is>
+      </c>
+      <c r="B464" s="6" t="inlineStr">
+        <is>
+          <t>Simtra BioPharma Solutions</t>
+        </is>
+      </c>
+      <c r="C464" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E464" s="6" t="inlineStr"/>
+      <c r="F464" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G464" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H464" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/simtra-biopharma-solutions/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="8" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B465" s="8" t="inlineStr">
+        <is>
+          <t>IDT Corporation</t>
+        </is>
+      </c>
+      <c r="C465" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D465" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E465" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F465" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G465" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H465" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/idt-corporation/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist / Data Analyst</t>
+        </is>
+      </c>
+      <c r="B466" s="6" t="inlineStr">
+        <is>
+          <t>B3 Consulting Poland</t>
+        </is>
+      </c>
+      <c r="C466" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E466" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F466" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G466" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H466" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/b3-consulting-poland/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B467" s="8" t="inlineStr">
+        <is>
+          <t>B3 Consulting Poland</t>
+        </is>
+      </c>
+      <c r="C467" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D467" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E467" s="8" t="inlineStr">
+        <is>
+          <t>Python、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F467" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G467" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H467" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/b3-consulting-poland/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="6" t="inlineStr">
+        <is>
+          <t>Binance Accelerator Program - LLM Data Scientist</t>
+        </is>
+      </c>
+      <c r="B468" s="6" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="C468" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D468" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E468" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F468" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G468" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H468" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/binance/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="8" t="inlineStr">
+        <is>
+          <t>Director, Product Analytics</t>
+        </is>
+      </c>
+      <c r="B469" s="8" t="inlineStr">
+        <is>
+          <t>Ethos</t>
+        </is>
+      </c>
+      <c r="C469" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D469" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E469" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F469" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G469" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H469" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ethos/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist - Agriculture</t>
+        </is>
+      </c>
+      <c r="B470" s="6" t="inlineStr">
+        <is>
+          <t>Syngenta Group</t>
+        </is>
+      </c>
+      <c r="C470" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E470" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F470" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G470" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H470" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/syngentagroup/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer Senior – ETL &amp; Python 2976</t>
+        </is>
+      </c>
+      <c r="B471" s="8" t="inlineStr">
+        <is>
+          <t>Xideral</t>
+        </is>
+      </c>
+      <c r="C471" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D471" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E471" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、BigQuery、ETL、pandas</t>
+        </is>
+      </c>
+      <c r="F471" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G471" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H471" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/xideral/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="6" t="inlineStr">
+        <is>
+          <t>Frontier Investment Analyst for a Crypto &amp; AI Focused Venture Capital Firm</t>
+        </is>
+      </c>
+      <c r="B472" s="6" t="inlineStr">
+        <is>
+          <t>Palermo Advisors</t>
+        </is>
+      </c>
+      <c r="C472" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E472" s="6" t="inlineStr"/>
+      <c r="F472" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G472" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H472" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/palermo-advisors/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor Design Manager, Data Center</t>
+        </is>
+      </c>
+      <c r="B473" s="8" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C473" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D473" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E473" s="8" t="inlineStr"/>
+      <c r="F473" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G473" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H473" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/aecom/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="6" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="B474" s="6" t="inlineStr">
+        <is>
+          <t>NECSWS</t>
+        </is>
+      </c>
+      <c r="C474" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D474" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E474" s="6" t="inlineStr"/>
+      <c r="F474" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G474" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H474" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/necsws/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="8" t="inlineStr">
+        <is>
+          <t>【招聘】运营主管（视频数据采集项目）｜月薪 27.2K｜接受出差｜急招</t>
+        </is>
+      </c>
+      <c r="B475" s="8" t="inlineStr"/>
+      <c r="C475" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D475" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E475" s="8" t="inlineStr"/>
+      <c r="F475" s="8" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G475" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H475" s="8" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/yGfKva</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H455"/>
+  <autoFilter ref="A1:H475"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19567,19 +20375,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -19592,7 +20400,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -19601,7 +20409,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -19611,19 +20419,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
@@ -19658,16 +20466,16 @@
         <v>49</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -19721,10 +20529,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>4</v>
@@ -19733,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -19765,7 +20573,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4</v>
@@ -19777,7 +20585,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$493</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-21 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-21 23:27 UTC</t>
+          <t>数据日期 2026-07-22 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-22 23:28 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3986486486486486</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>66</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.4459459459459459</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3464052287581699</v>
+        <v>0.3040540540540541</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3040540540540541</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3006535947712418</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1621621621621622</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1621621621621622</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.08783783783783784</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1554054054054054</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1241830065359477</v>
+        <v>0.1554054054054054</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1045751633986928</v>
+        <v>0.1148648648648649</v>
       </c>
     </row>
     <row r="18">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.0945945945945946</v>
       </c>
     </row>
     <row r="19">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0915032679738562</v>
+        <v>0.08783783783783784</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08496732026143791</v>
+        <v>0.07432432432432433</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H475"/>
+  <dimension ref="A1:H493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -20313,8 +20313,752 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B476" s="6" t="inlineStr">
+        <is>
+          <t>AB InBev</t>
+        </is>
+      </c>
+      <c r="C476" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D476" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E476" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F476" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G476" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H476" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-analyst-ab-inbev-1135150</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B477" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C477" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D477" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E477" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F477" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G477" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H477" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-scientist-munchen-69004</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B478" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C478" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D478" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E478" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F478" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G478" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H478" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-scientist-berlin-246511</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B479" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C479" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D479" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E479" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、AWS、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F479" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G479" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H479" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-platform-engineer-berlin-142531</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="6" t="inlineStr">
+        <is>
+          <t>Online Data Analyst - United States Spanish speakers</t>
+        </is>
+      </c>
+      <c r="B480" s="6" t="inlineStr">
+        <is>
+          <t>TELUS International</t>
+        </is>
+      </c>
+      <c r="C480" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D480" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E480" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F480" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G480" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H480" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149630-telus-digital-online-data-analyst-united-states-spanish-speakers</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="8" t="inlineStr">
+        <is>
+          <t>Senior Product Scientist, Agentic Growth &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="B481" s="8" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C481" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D481" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E481" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试</t>
+        </is>
+      </c>
+      <c r="F481" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G481" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H481" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149604-senior-product-scientist-agentic-growth-marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="6" t="inlineStr">
+        <is>
+          <t>Bioinformatics Manager (Oncology Product Development)</t>
+        </is>
+      </c>
+      <c r="B482" s="6" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C482" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D482" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E482" s="6" t="inlineStr">
+        <is>
+          <t>Python、R、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G482" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H482" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149598-bioinformatics-manager-oncology-product-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="8" t="inlineStr">
+        <is>
+          <t>Senior Applied Scientist</t>
+        </is>
+      </c>
+      <c r="B483" s="8" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D483" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E483" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F483" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G483" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H483" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149596-senior-applied-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="6" t="inlineStr">
+        <is>
+          <t>Lead/Staff Biostatistician (Analytical Validation)</t>
+        </is>
+      </c>
+      <c r="B484" s="6" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C484" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D484" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E484" s="6" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F484" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G484" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H484" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149594-lead-staff-biostatistician-analytical-validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="8" t="inlineStr">
+        <is>
+          <t>Online Data Analyst United States Spanish Speaker</t>
+        </is>
+      </c>
+      <c r="B485" s="8" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C485" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D485" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E485" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F485" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G485" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H485" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1743873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="6" t="inlineStr">
+        <is>
+          <t>PMO Support Analyst  |  Management Consultant III (MC-III)</t>
+        </is>
+      </c>
+      <c r="B486" s="6" t="inlineStr">
+        <is>
+          <t>BizFirst</t>
+        </is>
+      </c>
+      <c r="C486" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D486" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E486" s="6" t="inlineStr"/>
+      <c r="F486" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G486" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H486" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bizfirst/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="8" t="inlineStr">
+        <is>
+          <t>Solution Sales Specialist, MedTech De-Identified Health Data</t>
+        </is>
+      </c>
+      <c r="B487" s="8" t="inlineStr">
+        <is>
+          <t>Lifelancer</t>
+        </is>
+      </c>
+      <c r="C487" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D487" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E487" s="8" t="inlineStr"/>
+      <c r="F487" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G487" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H487" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lifelancer/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Computer Vision</t>
+        </is>
+      </c>
+      <c r="B488" s="6" t="inlineStr">
+        <is>
+          <t>CompanyCam</t>
+        </is>
+      </c>
+      <c r="C488" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G488" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H488" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/companycam/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="8" t="inlineStr">
+        <is>
+          <t>Sr Data Team Lead</t>
+        </is>
+      </c>
+      <c r="B489" s="8" t="inlineStr">
+        <is>
+          <t>Lifelancer</t>
+        </is>
+      </c>
+      <c r="C489" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D489" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E489" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F489" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G489" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H489" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lifelancer/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="6" t="inlineStr">
+        <is>
+          <t>Senior Deal Desk Analyst - EMEA</t>
+        </is>
+      </c>
+      <c r="B490" s="6" t="inlineStr">
+        <is>
+          <t>DoiT International</t>
+        </is>
+      </c>
+      <c r="C490" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D490" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E490" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G490" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H490" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/doit-international/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="8" t="inlineStr">
+        <is>
+          <t>Lead Director, Healthcare Medicaid Risk Adjustment Analytics</t>
+        </is>
+      </c>
+      <c r="B491" s="8" t="inlineStr">
+        <is>
+          <t>Lifelancer</t>
+        </is>
+      </c>
+      <c r="C491" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D491" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E491" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F491" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G491" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H491" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lifelancer/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="6" t="inlineStr">
+        <is>
+          <t>Bi-Lingual Collections Agent (Greenville, SC, US, 29601)</t>
+        </is>
+      </c>
+      <c r="B492" s="6" t="inlineStr">
+        <is>
+          <t>Purpose Financial</t>
+        </is>
+      </c>
+      <c r="C492" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E492" s="6" t="inlineStr"/>
+      <c r="F492" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G492" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H492" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/purpose-financial/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="8" t="inlineStr">
+        <is>
+          <t>Project Chiron - German Data Trainer</t>
+        </is>
+      </c>
+      <c r="B493" s="8" t="inlineStr">
+        <is>
+          <t>Welo Global</t>
+        </is>
+      </c>
+      <c r="C493" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D493" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E493" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F493" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G493" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H493" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/welo-global/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H475"/>
+  <autoFilter ref="A1:H493"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20378,16 +21122,16 @@
         <v>47</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -20419,19 +21163,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
@@ -20463,7 +21207,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
@@ -20475,7 +21219,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$523</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-22 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-22 23:28 UTC</t>
+          <t>数据日期 2026-07-23 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-23 23:26 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3986486486486486</v>
+        <v>0.4144736842105263</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.4407894736842105</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3040540540540541</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3040540540540541</v>
+        <v>0.2894736842105263</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.2960526315789473</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1710526315789474</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1907894736842105</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.08783783783783784</v>
+        <v>0.09868421052631579</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1554054054054054</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="16">
@@ -822,7 +822,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1554054054054054</v>
+        <v>0.1513157894736842</v>
       </c>
     </row>
     <row r="17">
@@ -835,46 +835,46 @@
         <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.1118421052631579</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0945945945945946</v>
+        <v>0.09210526315789473</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08783783783783784</v>
+        <v>0.08552631578947369</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07432432432432433</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H493"/>
+  <dimension ref="A1:H523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -21057,8 +21057,1248 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="6" t="inlineStr">
+        <is>
+          <t>Asistente de Marketing</t>
+        </is>
+      </c>
+      <c r="B494" s="6" t="inlineStr">
+        <is>
+          <t>Universia PerÃº</t>
+        </is>
+      </c>
+      <c r="C494" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E494" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F494" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G494" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H494" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-asistente-de-marketing-universia-peru-1135259</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="8" t="inlineStr">
+        <is>
+          <t>Administrative Data Entry File Clerk</t>
+        </is>
+      </c>
+      <c r="B495" s="8" t="inlineStr">
+        <is>
+          <t>Re Lytics Hire</t>
+        </is>
+      </c>
+      <c r="C495" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D495" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E495" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F495" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G495" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H495" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-administrative-data-entry-file-clerk-re-lytics-hire-1135220</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist Assistant Administrator</t>
+        </is>
+      </c>
+      <c r="B496" s="6" t="inlineStr">
+        <is>
+          <t>Re Lytics Hire</t>
+        </is>
+      </c>
+      <c r="C496" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D496" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E496" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F496" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G496" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H496" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-assistant-administrator-re-lytics-hire-1135226</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="8" t="inlineStr">
+        <is>
+          <t>Monitor PedagÃ³gico OAB</t>
+        </is>
+      </c>
+      <c r="B497" s="8" t="inlineStr">
+        <is>
+          <t>VÃ­cio</t>
+        </is>
+      </c>
+      <c r="C497" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D497" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E497" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F497" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G497" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H497" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-monitor-pedagogico-oab-vicio-1135254</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="6" t="inlineStr">
+        <is>
+          <t>Junior Help Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B498" s="6" t="inlineStr">
+        <is>
+          <t>Work Force Nexus</t>
+        </is>
+      </c>
+      <c r="C498" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D498" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E498" s="6" t="inlineStr"/>
+      <c r="F498" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G498" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H498" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-junior-help-desk-analyst-work-force-nexus-1135168</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Assistant</t>
+        </is>
+      </c>
+      <c r="B499" s="8" t="inlineStr">
+        <is>
+          <t>Blue Oak Consulting</t>
+        </is>
+      </c>
+      <c r="C499" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D499" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E499" s="8" t="inlineStr">
+        <is>
+          <t>Python、Excel</t>
+        </is>
+      </c>
+      <c r="F499" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G499" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H499" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-assistant-blue-oak-consulting-1135326</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="6" t="inlineStr">
+        <is>
+          <t>Freelance grabaciÃ³n de tareas cotidianas para proyecto de IA</t>
+        </is>
+      </c>
+      <c r="B500" s="6" t="inlineStr">
+        <is>
+          <t>Mindrift Data Annotation Projects</t>
+        </is>
+      </c>
+      <c r="C500" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D500" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E500" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F500" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G500" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H500" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-freelance-grabacion-de-tareas-cotidianas-para-proyecto-de-ia-mindrift-data-annotation-projects-1135257</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="8" t="inlineStr">
+        <is>
+          <t>Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B501" s="8" t="inlineStr">
+        <is>
+          <t>Owl.co</t>
+        </is>
+      </c>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D501" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E501" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F501" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G501" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H501" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-quality-analyst-owl-co-1135274</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="6" t="inlineStr">
+        <is>
+          <t>Product Sales Specialist - Pet Health (CST timezone)</t>
+        </is>
+      </c>
+      <c r="B502" s="6" t="inlineStr">
+        <is>
+          <t>Tribe Wellness</t>
+        </is>
+      </c>
+      <c r="C502" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E502" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Spark</t>
+        </is>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G502" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H502" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/sales/product-sales-specialist-pet-health-cst-timezone-2091072</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="8" t="inlineStr">
+        <is>
+          <t>Investment Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B503" s="8" t="inlineStr">
+        <is>
+          <t>P3A</t>
+        </is>
+      </c>
+      <c r="C503" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D503" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E503" s="8" t="inlineStr"/>
+      <c r="F503" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G503" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H503" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/p3a/investment-analyst-berlin-228437</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B504" s="6" t="inlineStr">
+        <is>
+          <t>Rockstardevelopers GmbH</t>
+        </is>
+      </c>
+      <c r="C504" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D504" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E504" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G504" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H504" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rockstardevelopers-gmbh/machine-learning-engineer-stuttgart-382224</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B505" s="8" t="inlineStr">
+        <is>
+          <t>PeakSoft GmbH</t>
+        </is>
+      </c>
+      <c r="C505" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D505" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E505" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F505" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G505" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H505" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/peaksoft-gmbh/ai-data-engineer-wuppertal-419595</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B506" s="6" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C506" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D506" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E506" s="6" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、dbt、Airflow、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F506" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G506" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H506" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/data-engineer-berlin-193215</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="8" t="inlineStr">
+        <is>
+          <t>Working Student SEO Data Analyst​ (m|w|d)</t>
+        </is>
+      </c>
+      <c r="B507" s="8" t="inlineStr">
+        <is>
+          <t>idealo internet GmbH</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D507" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E507" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F507" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G507" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H507" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/idealo-internet-gmbh/working-student-seo-data-analyst-mwd-berlin-39329</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Ops Engineer - Personalization (m|w|d)</t>
+        </is>
+      </c>
+      <c r="B508" s="6" t="inlineStr">
+        <is>
+          <t>idealo internet GmbH</t>
+        </is>
+      </c>
+      <c r="C508" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E508" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F508" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G508" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H508" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/idealo-internet-gmbh/machine-learning-ops-engineer-personalization-mwd-berlin-492895</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst / Analytics Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B509" s="8" t="inlineStr">
+        <is>
+          <t>AccountOne GmbH</t>
+        </is>
+      </c>
+      <c r="C509" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D509" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E509" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Looker、Snowflake、dbt、BigQuery</t>
+        </is>
+      </c>
+      <c r="F509" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G509" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H509" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/accountone-gmbh/data-analyst-analytics-engineer-flensburg-194471</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer - Automotive (M/W/D) - VISPIRON SYSTEMS</t>
+        </is>
+      </c>
+      <c r="B510" s="6" t="inlineStr">
+        <is>
+          <t>VISPIRON GmbH</t>
+        </is>
+      </c>
+      <c r="C510" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D510" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E510" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F510" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G510" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H510" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vispiron-gmbh/data-engineer-automotive-systems-munich-220852</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="8" t="inlineStr">
+        <is>
+          <t>DevOps Engineer / System Engineer Linux &amp; Data (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B511" s="8" t="inlineStr">
+        <is>
+          <t>FlexIT Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D511" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E511" s="8" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="F511" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G511" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H511" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flexit-consulting-gmbh/devops-engineer-system-engineer-linux-data-duisburg-114188</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="6" t="inlineStr">
+        <is>
+          <t>Customer Master Data Specialist</t>
+        </is>
+      </c>
+      <c r="B512" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C512" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D512" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E512" s="6" t="inlineStr"/>
+      <c r="F512" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G512" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H512" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/state-systems/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (AI Data Platform)</t>
+        </is>
+      </c>
+      <c r="B513" s="8" t="inlineStr">
+        <is>
+          <t>Applaudo Studios</t>
+        </is>
+      </c>
+      <c r="C513" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D513" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E513" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、AWS、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F513" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G513" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H513" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/applaudo-studios/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr">
+        <is>
+          <t>Manual QA Analyst</t>
+        </is>
+      </c>
+      <c r="B514" s="6" t="inlineStr">
+        <is>
+          <t>Swyfft</t>
+        </is>
+      </c>
+      <c r="C514" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D514" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E514" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F514" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G514" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H514" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/swyfft/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="8" t="inlineStr">
+        <is>
+          <t>Specialist, Circular Economy Data Management</t>
+        </is>
+      </c>
+      <c r="B515" s="8" t="inlineStr">
+        <is>
+          <t>Circular Materials</t>
+        </is>
+      </c>
+      <c r="C515" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D515" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E515" s="8" t="inlineStr">
+        <is>
+          <t>Power BI、统计学</t>
+        </is>
+      </c>
+      <c r="F515" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G515" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H515" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/circular-materials/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="6" t="inlineStr">
+        <is>
+          <t>Data Center Migration Project Manager (Contractor)</t>
+        </is>
+      </c>
+      <c r="B516" s="6" t="inlineStr">
+        <is>
+          <t>RESPEC</t>
+        </is>
+      </c>
+      <c r="C516" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D516" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E516" s="6" t="inlineStr"/>
+      <c r="F516" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G516" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H516" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/respec/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B517" s="8" t="inlineStr">
+        <is>
+          <t>Omnidian</t>
+        </is>
+      </c>
+      <c r="C517" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D517" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E517" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F517" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G517" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H517" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/omnidian/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B518" s="6" t="inlineStr">
+        <is>
+          <t>Codest Ltd. Company No. 12590542, VAT number: GB363431020</t>
+        </is>
+      </c>
+      <c r="C518" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D518" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E518" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、Airflow、GCP、BigQuery、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G518" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H518" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/codest-ltd-company-no-12590542-vat-number-gb363431020/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="8" t="inlineStr">
+        <is>
+          <t>Program Analyst/Business Analyst</t>
+        </is>
+      </c>
+      <c r="B519" s="8" t="inlineStr">
+        <is>
+          <t>Artemis ARC</t>
+        </is>
+      </c>
+      <c r="C519" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D519" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E519" s="8" t="inlineStr"/>
+      <c r="F519" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G519" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H519" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/artemis-arc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="6" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Strategic Contract Data Governance - Canada</t>
+        </is>
+      </c>
+      <c r="B520" s="6" t="inlineStr">
+        <is>
+          <t>Circular Materials</t>
+        </is>
+      </c>
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D520" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E520" s="6" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G520" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H520" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/circular-materials/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="8" t="inlineStr">
+        <is>
+          <t>Power BI 24x7 Modeling Admin</t>
+        </is>
+      </c>
+      <c r="B521" s="8" t="inlineStr">
+        <is>
+          <t>Unisys</t>
+        </is>
+      </c>
+      <c r="C521" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D521" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E521" s="8" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F521" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G521" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H521" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/unisys/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="6" t="inlineStr">
+        <is>
+          <t>Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="B522" s="6" t="inlineStr">
+        <is>
+          <t>Kinetic by Windstream</t>
+        </is>
+      </c>
+      <c r="C522" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D522" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E522" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F522" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G522" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H522" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kinetic-by-windstream/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="8" t="inlineStr">
+        <is>
+          <t>Cyber Security Analyst</t>
+        </is>
+      </c>
+      <c r="B523" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C523" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D523" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E523" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F523" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G523" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H523" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nvidia/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H493"/>
+  <autoFilter ref="A1:H523"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21119,19 +22359,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -21163,19 +22403,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -21194,10 +22434,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -21207,19 +22447,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -21229,7 +22469,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3</v>
@@ -21238,10 +22478,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$546</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-23 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-23 23:26 UTC</t>
+          <t>数据日期 2026-07-24 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-24 23:30 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4144736842105263</v>
+        <v>0.4093959731543624</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4407894736842105</v>
+        <v>0.4832214765100671</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.302013422818792</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.2550335570469799</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2960526315789473</v>
+        <v>0.2885906040268457</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1710526315789474</v>
+        <v>0.1677852348993289</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1907894736842105</v>
+        <v>0.1677852348993289</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09868421052631579</v>
+        <v>0.09395973154362416</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1610738255033557</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1513157894736842</v>
+        <v>0.1208053691275168</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1118421052631579</v>
+        <v>0.08724832214765101</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09210526315789473</v>
+        <v>0.08724832214765101</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08552631578947369</v>
+        <v>0.08053691275167785</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.08053691275167785</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H523"/>
+  <dimension ref="A1:H546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -22297,8 +22297,962 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="6" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="B524" s="6" t="inlineStr">
+        <is>
+          <t>Temu</t>
+        </is>
+      </c>
+      <c r="C524" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D524" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E524" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F524" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G524" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H524" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-development-manager-temu-1135291</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="B525" s="8" t="inlineStr">
+        <is>
+          <t>Morgan McKinley</t>
+        </is>
+      </c>
+      <c r="C525" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D525" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E525" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F525" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G525" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H525" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-specialist-morgan-mckinley-1135273</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="6" t="inlineStr">
+        <is>
+          <t>Consultor para estrategia de SBC de Primera Infancia Programme Effectiveness Quito Ecuador Remoto 7 meses Nacional</t>
+        </is>
+      </c>
+      <c r="B526" s="6" t="inlineStr">
+        <is>
+          <t>UNICEF Bangladesh</t>
+        </is>
+      </c>
+      <c r="C526" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D526" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E526" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F526" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G526" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H526" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-consultor-para-estrategia-de-sbc-de-primera-infancia-programme-effectiveness-quito-ecuador-remoto-7-meses-nacional-unicef-bangladesh-1135260</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="8" t="inlineStr">
+        <is>
+          <t>CoordenaÃ§Ã£o de Tecnologia I CloudOps</t>
+        </is>
+      </c>
+      <c r="B527" s="8" t="inlineStr">
+        <is>
+          <t>Aurum</t>
+        </is>
+      </c>
+      <c r="C527" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D527" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E527" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F527" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G527" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H527" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-coordenacao-de-tecnologia-i-cloudops-aurum-1135258</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="6" t="inlineStr">
+        <is>
+          <t>Appointment Setter</t>
+        </is>
+      </c>
+      <c r="B528" s="6" t="inlineStr">
+        <is>
+          <t>Everlast Bathrooms</t>
+        </is>
+      </c>
+      <c r="C528" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D528" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E528" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F528" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G528" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H528" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-appointment-setter-everlast-bathrooms-1135256</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="8" t="inlineStr">
+        <is>
+          <t>Analista de Atendimento TEMPORÃRIO Remoto</t>
+        </is>
+      </c>
+      <c r="B529" s="8" t="inlineStr">
+        <is>
+          <t>Melhor Envio</t>
+        </is>
+      </c>
+      <c r="C529" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D529" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E529" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F529" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G529" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H529" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-analista-de-atendimento-temporario-remoto-melhor-envio-1135251</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="6" t="inlineStr">
+        <is>
+          <t>Programa de EstÃ¡gio Atendimento Remoto</t>
+        </is>
+      </c>
+      <c r="B530" s="6" t="inlineStr">
+        <is>
+          <t>Nibo</t>
+        </is>
+      </c>
+      <c r="C530" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D530" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E530" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F530" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G530" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H530" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-programa-de-estagio-atendimento-remoto-nibo-1135250</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="8" t="inlineStr">
+        <is>
+          <t>Performance Analyst</t>
+        </is>
+      </c>
+      <c r="B531" s="8" t="inlineStr">
+        <is>
+          <t>Ministry of Housing, Communities and Local Government</t>
+        </is>
+      </c>
+      <c r="C531" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D531" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E531" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F531" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G531" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H531" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-performance-analyst-ministry-of-housing-communities-and-local-government-1135348</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Science/ML Engineer - Financial Crime</t>
+        </is>
+      </c>
+      <c r="B532" s="6" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C532" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D532" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E532" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F532" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G532" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H532" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-data-science-ml-engineer-financial-crime-berlin-119994</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant Azure Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B533" s="8" t="inlineStr">
+        <is>
+          <t>Kubidat GmbH</t>
+        </is>
+      </c>
+      <c r="C533" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D533" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E533" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Spark、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F533" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G533" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H533" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kubidat-gmbh/senior-consultant-azure-data-engineer-mannheim-157148</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Machine Learning Engineer, Robot Learning (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B534" s="6" t="inlineStr">
+        <is>
+          <t>Batch Robotics GmbH</t>
+        </is>
+      </c>
+      <c r="C534" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D534" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E534" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F534" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G534" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H534" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/batch-robotics-gmbh/senior-machine-learning-engineer-robot-learning-munich-424832</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="8" t="inlineStr">
+        <is>
+          <t>Junior Manager Data &amp; Operations (m/w/d) (60-80%)</t>
+        </is>
+      </c>
+      <c r="B535" s="8" t="inlineStr">
+        <is>
+          <t>FASE</t>
+        </is>
+      </c>
+      <c r="C535" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D535" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E535" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F535" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G535" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H535" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/fase/junior-manager-data-operations-60-80-munich-329814</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="6" t="inlineStr">
+        <is>
+          <t>Investment Analyst (m/w/d) im Bereich Kapitalmärkte</t>
+        </is>
+      </c>
+      <c r="B536" s="6" t="inlineStr">
+        <is>
+          <t>DeltaValue GmbH</t>
+        </is>
+      </c>
+      <c r="C536" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D536" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E536" s="6" t="inlineStr"/>
+      <c r="F536" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G536" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H536" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/deltavalue-gmbh/investment-analyst-im-bereich-kapitalmarkte-essen-51186</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B537" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C537" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D537" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E537" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F537" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G537" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H537" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-345727</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B538" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C538" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D538" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E538" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F538" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G538" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H538" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-333557</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B539" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C539" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D539" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E539" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、pandas</t>
+        </is>
+      </c>
+      <c r="F539" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G539" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H539" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/option/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="6" t="inlineStr">
+        <is>
+          <t>Chief Data Officer (CDO)</t>
+        </is>
+      </c>
+      <c r="B540" s="6" t="inlineStr">
+        <is>
+          <t>TheHiveCareers</t>
+        </is>
+      </c>
+      <c r="C540" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D540" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E540" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F540" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G540" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H540" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/thehivecareers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="8" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer - Remote, Latin America</t>
+        </is>
+      </c>
+      <c r="B541" s="8" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C541" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D541" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E541" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F541" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G541" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H541" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bluelight-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B542" s="6" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C542" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D542" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E542" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F542" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G542" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H542" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/motional/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="8" t="inlineStr">
+        <is>
+          <t>Lead Clinical Data Manager</t>
+        </is>
+      </c>
+      <c r="B543" s="8" t="inlineStr">
+        <is>
+          <t>Orca Bio</t>
+        </is>
+      </c>
+      <c r="C543" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D543" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E543" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F543" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G543" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H543" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/orca-bio/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="6" t="inlineStr">
+        <is>
+          <t>Administrative &amp; Data Entry Clerk Position</t>
+        </is>
+      </c>
+      <c r="B544" s="6" t="inlineStr">
+        <is>
+          <t>Jobs for Humanity</t>
+        </is>
+      </c>
+      <c r="C544" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D544" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E544" s="6" t="inlineStr"/>
+      <c r="F544" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G544" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H544" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/jobs-for-humanity/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="8" t="inlineStr">
+        <is>
+          <t>Senior ServiceNow Business Analyst- Netherlands</t>
+        </is>
+      </c>
+      <c r="B545" s="8" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C545" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D545" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E545" s="8" t="inlineStr"/>
+      <c r="F545" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G545" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H545" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/newrocket/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="6" t="inlineStr">
+        <is>
+          <t>AI Data Intelligence Lead</t>
+        </is>
+      </c>
+      <c r="B546" s="6" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C546" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D546" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E546" s="6" t="inlineStr">
+        <is>
+          <t>Python、R、Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F546" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G546" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H546" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/newrocket/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H523"/>
+  <autoFilter ref="A1:H546"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22359,19 +23313,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -22406,16 +23360,16 @@
         <v>86</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -22434,10 +23388,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -22447,19 +23401,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$546</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$560</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-24 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-24 23:30 UTC</t>
+          <t>数据日期 2026-07-25 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-25 23:28 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4093959731543624</v>
+        <v>0.4144736842105263</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4832214765100671</v>
+        <v>0.4671052631578947</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.302013422818792</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>数据分析/BI</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>38</v>
-      </c>
       <c r="H12" s="7" t="n">
-        <v>0.2550335570469799</v>
+        <v>0.2960526315789473</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2885906040268457</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1677852348993289</v>
+        <v>0.1644736842105263</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1677852348993289</v>
+        <v>0.1776315789473684</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.09395973154362416</v>
+        <v>0.07236842105263158</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1610738255033557</v>
+        <v>0.1513157894736842</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1208053691275168</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
@@ -835,33 +835,33 @@
         <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.08724832214765101</v>
+        <v>0.08552631578947369</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08724832214765101</v>
+        <v>0.08552631578947369</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08053691275167785</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08053691275167785</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H546"/>
+  <dimension ref="A1:H560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -23251,8 +23251,576 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" s="8" t="inlineStr">
+        <is>
+          <t>Business Development Representative</t>
+        </is>
+      </c>
+      <c r="B547" s="8" t="inlineStr">
+        <is>
+          <t>Outsite</t>
+        </is>
+      </c>
+      <c r="C547" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D547" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E547" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F547" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G547" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H547" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/sales/business-development-representative-2091075</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="6" t="inlineStr">
+        <is>
+          <t>Content Reviewer - United States</t>
+        </is>
+      </c>
+      <c r="B548" s="6" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C548" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D548" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E548" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F548" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G548" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H548" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/all-others/content-reviewer-united-states-2091074</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="8" t="inlineStr">
+        <is>
+          <t>Performance Manager IT &amp; Controlling &amp; Data analytics (all gender)</t>
+        </is>
+      </c>
+      <c r="B549" s="8" t="inlineStr">
+        <is>
+          <t>Actana Consulting Services GmbH</t>
+        </is>
+      </c>
+      <c r="C549" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D549" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E549" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F549" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G549" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H549" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/actana-consulting-services-gmbh/performance-manager-it-controlling-data-analytics-all-gender-ulm-375375</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager, Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B550" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C550" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D550" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E550" s="6" t="inlineStr"/>
+      <c r="F550" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G550" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H550" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/academic-partnerships/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="8" t="inlineStr">
+        <is>
+          <t>Advertising Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="B551" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C551" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D551" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E551" s="8" t="inlineStr"/>
+      <c r="F551" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G551" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H551" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kestra-financial/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="6" t="inlineStr">
+        <is>
+          <t>Statistical &amp; Claim Data Analyst</t>
+        </is>
+      </c>
+      <c r="B552" s="6" t="inlineStr">
+        <is>
+          <t>Crawford &amp; Company</t>
+        </is>
+      </c>
+      <c r="C552" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D552" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E552" s="6" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F552" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G552" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H552" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/crawford-company/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="8" t="inlineStr">
+        <is>
+          <t>Security Architect - Data, Fabric &amp; AI Security</t>
+        </is>
+      </c>
+      <c r="B553" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C553" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D553" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E553" s="8" t="inlineStr">
+        <is>
+          <t>Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F553" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G553" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H553" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/proarch/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="6" t="inlineStr">
+        <is>
+          <t>Workday Integration Analyst – Full remote Spain or Portugal</t>
+        </is>
+      </c>
+      <c r="B554" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C554" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D554" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E554" s="6" t="inlineStr"/>
+      <c r="F554" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G554" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H554" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sedgwick/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Direct Mail Acquisition</t>
+        </is>
+      </c>
+      <c r="B555" s="8" t="inlineStr">
+        <is>
+          <t>Road Scholar</t>
+        </is>
+      </c>
+      <c r="C555" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D555" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E555" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F555" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G555" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H555" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/road-scholar/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Trading &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B556" s="6" t="inlineStr">
+        <is>
+          <t>FreedX</t>
+        </is>
+      </c>
+      <c r="C556" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D556" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E556" s="6" t="inlineStr"/>
+      <c r="F556" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G556" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H556" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/freedx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="8" t="inlineStr">
+        <is>
+          <t>Health IT Business Analyst II - Program Advisory</t>
+        </is>
+      </c>
+      <c r="B557" s="8" t="inlineStr">
+        <is>
+          <t>Aptive</t>
+        </is>
+      </c>
+      <c r="C557" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D557" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E557" s="8" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F557" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G557" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H557" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/aptive/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Lead</t>
+        </is>
+      </c>
+      <c r="B558" s="6" t="inlineStr">
+        <is>
+          <t>Guidehouse</t>
+        </is>
+      </c>
+      <c r="C558" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D558" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E558" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F558" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G558" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H558" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/guidehouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="8" t="inlineStr">
+        <is>
+          <t>Temporary - Data Entry Clerk</t>
+        </is>
+      </c>
+      <c r="B559" s="8" t="inlineStr">
+        <is>
+          <t>Crawford &amp; Company</t>
+        </is>
+      </c>
+      <c r="C559" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D559" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E559" s="8" t="inlineStr"/>
+      <c r="F559" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G559" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H559" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/crawford-company/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Sales Operations</t>
+        </is>
+      </c>
+      <c r="B560" s="6" t="inlineStr">
+        <is>
+          <t>VB Spine, LLC</t>
+        </is>
+      </c>
+      <c r="C560" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D560" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E560" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F560" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G560" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H560" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/vb-spine-llc/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H546"/>
+  <autoFilter ref="A1:H560"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23313,7 +23881,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>22</v>
@@ -23325,7 +23893,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -23335,7 +23903,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>2</v>
@@ -23347,7 +23915,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -23357,19 +23925,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>36</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -23401,7 +23969,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
@@ -23413,7 +23981,7 @@
         <v>63</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -23476,10 +24044,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -23520,10 +24088,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$560</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$606</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-25 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-25 23:28 UTC</t>
+          <t>数据日期 2026-07-26 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-26 23:27 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>559</v>
+        <v>605</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4144736842105263</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4671052631578947</v>
+        <v>0.4573170731707317</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2960526315789473</v>
+        <v>0.298780487804878</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1644736842105263</v>
+        <v>0.1707317073170732</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1776315789473684</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07236842105263158</v>
+        <v>0.07317073170731707</v>
       </c>
     </row>
     <row r="15">
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1513157894736842</v>
+        <v>0.1402439024390244</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1280487804878049</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.08552631578947369</v>
+        <v>0.0975609756097561</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08552631578947369</v>
+        <v>0.08536585365853659</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.07317073170731707</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.06707317073170732</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H560"/>
+  <dimension ref="A1:H606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -23819,8 +23819,1888 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" s="8" t="inlineStr">
+        <is>
+          <t>IT Support Analyst</t>
+        </is>
+      </c>
+      <c r="B561" s="8" t="inlineStr">
+        <is>
+          <t>Work Force Nexus</t>
+        </is>
+      </c>
+      <c r="C561" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D561" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E561" s="8" t="inlineStr"/>
+      <c r="F561" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G561" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H561" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-it-support-analyst-work-force-nexus-1135393</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="6" t="inlineStr">
+        <is>
+          <t>Safety Data Analyst</t>
+        </is>
+      </c>
+      <c r="B562" s="6" t="inlineStr">
+        <is>
+          <t>SkyWest Airlines</t>
+        </is>
+      </c>
+      <c r="C562" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D562" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E562" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Tableau、统计学</t>
+        </is>
+      </c>
+      <c r="F562" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G562" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H562" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant Data Management (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B563" s="8" t="inlineStr">
+        <is>
+          <t>Natuvion GmbH</t>
+        </is>
+      </c>
+      <c r="C563" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D563" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E563" s="8" t="inlineStr"/>
+      <c r="F563" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G563" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H563" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/natuvion-gmbh/remote-senior-consultant-data-management-berlin-484200</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="6" t="inlineStr">
+        <is>
+          <t>Data &amp; Platform Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B564" s="6" t="inlineStr">
+        <is>
+          <t>Nextwind</t>
+        </is>
+      </c>
+      <c r="C564" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D564" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E564" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F564" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G564" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H564" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nextwind/data-platform-analyst-berlin-10021</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent*in Machine Learning - Fokus Sustainability</t>
+        </is>
+      </c>
+      <c r="B565" s="8" t="inlineStr">
+        <is>
+          <t>Pacemaker</t>
+        </is>
+      </c>
+      <c r="C565" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D565" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E565" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F565" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G565" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H565" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pacemaker/remote-werkstudentin-machine-learning-fokus-sustainability-185590</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="6" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer II - Agentic AI Platform</t>
+        </is>
+      </c>
+      <c r="B566" s="6" t="inlineStr">
+        <is>
+          <t>paiqo GmbH</t>
+        </is>
+      </c>
+      <c r="C566" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D566" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E566" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F566" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G566" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H566" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/paiqo-gmbh/remote-azure-data-engineer-ii-agentic-ai-platform-paderborn-270575</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="8" t="inlineStr">
+        <is>
+          <t>Senior Azure Data Engineer - Agentic AI Platform</t>
+        </is>
+      </c>
+      <c r="B567" s="8" t="inlineStr">
+        <is>
+          <t>paiqo GmbH</t>
+        </is>
+      </c>
+      <c r="C567" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D567" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E567" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F567" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G567" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H567" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/paiqo-gmbh/remote-senior-azure-data-engineer-agentic-ai-platform-paderborn-486076</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="6" t="inlineStr">
+        <is>
+          <t>Lead Azure Data Engineer - Agentic AI Platform</t>
+        </is>
+      </c>
+      <c r="B568" s="6" t="inlineStr">
+        <is>
+          <t>paiqo GmbH</t>
+        </is>
+      </c>
+      <c r="C568" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D568" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E568" s="6" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="F568" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G568" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H568" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/paiqo-gmbh/remote-lead-azure-data-engineer-agentic-ai-platform-paderborn-239773</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager Data Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B569" s="8" t="inlineStr">
+        <is>
+          <t>Eraneos</t>
+        </is>
+      </c>
+      <c r="C569" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D569" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E569" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、AWS、Azure、GCP、BigQuery、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F569" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G569" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H569" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eraneos/remote-senior-manager-data-analytics-466945</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="6" t="inlineStr">
+        <is>
+          <t>Senior Berater SAP Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B570" s="6" t="inlineStr">
+        <is>
+          <t>Westernacher Consulting</t>
+        </is>
+      </c>
+      <c r="C570" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D570" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E570" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F570" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G570" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H570" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/westernacher-consulting/senior-berater-sap-analytics-heidelberg-germany-184708</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="8" t="inlineStr">
+        <is>
+          <t>Principal Data Strategist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B571" s="8" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C571" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D571" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E571" s="8" t="inlineStr"/>
+      <c r="F571" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G571" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H571" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/thoughtworks/principal-data-strategist-hamburg-15817</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="6" t="inlineStr">
+        <is>
+          <t>Praktikant im Bereich Data Science R&amp;D (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B572" s="6" t="inlineStr">
+        <is>
+          <t>Vulcan Energie Ressourcen GmbH</t>
+        </is>
+      </c>
+      <c r="C572" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D572" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E572" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F572" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G572" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H572" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vulcan-energie-ressourcen-gmbh/praktikant-im-bereich-data-science-rd-karlsruhe-111716</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Analyst Investment Finance (m/w/d) | Python</t>
+        </is>
+      </c>
+      <c r="B573" s="8" t="inlineStr">
+        <is>
+          <t>Qplix</t>
+        </is>
+      </c>
+      <c r="C573" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D573" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E573" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F573" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G573" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H573" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/qplix/senior-analyst-investment-finance-python-munchen-60754</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="6" t="inlineStr">
+        <is>
+          <t>People Analytics Specialist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B574" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C574" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D574" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E574" s="6" t="inlineStr"/>
+      <c r="F574" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G574" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H574" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/people-analytics-specialist-germany-munich-hq-125992</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="8" t="inlineStr">
+        <is>
+          <t>Intern (m/f/d) Robot Teaching &amp; VLA Data Engineering</t>
+        </is>
+      </c>
+      <c r="B575" s="8" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C575" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D575" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E575" s="8" t="inlineStr"/>
+      <c r="F575" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G575" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H575" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/intern-robot-teaching-vla-data-engineering-germany-munich-hq-479137</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="6" t="inlineStr">
+        <is>
+          <t>Head of Talent Growth &amp; Analytics (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B576" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C576" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D576" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E576" s="6" t="inlineStr"/>
+      <c r="F576" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G576" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H576" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/head-of-talent-growth-analytics-germany-munich-hq-180204</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="8" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B577" s="8" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C577" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D577" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E577" s="8" t="inlineStr"/>
+      <c r="F577" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G577" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H577" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/data-quality-engineer-germany-munich-hq-48714</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="6" t="inlineStr">
+        <is>
+          <t>Data Quality Coordinator (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B578" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C578" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D578" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E578" s="6" t="inlineStr"/>
+      <c r="F578" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G578" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H578" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/data-quality-coordinator-germany-munich-hq-432323</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Robotic Software Engineer (m/f/d) Teleoperation &amp; Robotic Data Collection</t>
+        </is>
+      </c>
+      <c r="B579" s="8" t="inlineStr">
+        <is>
+          <t>Agile Robots SE</t>
+        </is>
+      </c>
+      <c r="C579" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D579" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E579" s="8" t="inlineStr"/>
+      <c r="F579" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G579" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H579" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se/senior-robotic-software-engineer-teleoperation-robotic-data-collection-germany-munich-hq-35059</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager of Data - Finance</t>
+        </is>
+      </c>
+      <c r="B580" s="6" t="inlineStr">
+        <is>
+          <t>mewssystems</t>
+        </is>
+      </c>
+      <c r="C580" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D580" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E580" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F580" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G580" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H580" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mewssystems/senior-manager-of-data-finance-372219</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Transaction Monitoring &amp; Fraud</t>
+        </is>
+      </c>
+      <c r="B581" s="8" t="inlineStr">
+        <is>
+          <t>mewssystems</t>
+        </is>
+      </c>
+      <c r="C581" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D581" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E581" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F581" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G581" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H581" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mewssystems/senior-data-analyst-transaction-monitoring-fraud-155139</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Data Analyst - Finance</t>
+        </is>
+      </c>
+      <c r="B582" s="6" t="inlineStr">
+        <is>
+          <t>Emma – The Sleep Company</t>
+        </is>
+      </c>
+      <c r="C582" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D582" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E582" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F582" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G582" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H582" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/emma-the-sleep-company/senior-data-analyst-finance-frankfurt-60978</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="8" t="inlineStr">
+        <is>
+          <t>Working Student-Real Estate Software &amp; Data Integration</t>
+        </is>
+      </c>
+      <c r="B583" s="8" t="inlineStr">
+        <is>
+          <t>Gus Germany</t>
+        </is>
+      </c>
+      <c r="C583" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D583" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E583" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F583" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G583" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H583" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gus-germany/working-student-real-estate-software-data-integration-berlin-408345</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B584" s="6" t="inlineStr">
+        <is>
+          <t>Nfon</t>
+        </is>
+      </c>
+      <c r="C584" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D584" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E584" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F584" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G584" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H584" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nfon/machine-learning-engineer-all-genders-bremen-132236</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="8" t="inlineStr">
+        <is>
+          <t>Praktikant (all genders) Social Selling, Data &amp; CRM – Gestalte die Digitalisierung unseres Vertriebsmarketings mit</t>
+        </is>
+      </c>
+      <c r="B585" s="8" t="inlineStr">
+        <is>
+          <t>Valuenet Group</t>
+        </is>
+      </c>
+      <c r="C585" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D585" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E585" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F585" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G585" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H585" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/valuenet-group/praktikant-all-genders-social-selling-data-crm-gestalte-die-digitalisierung-unseres-vertriebsmarketings-mit-munchen-59532</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="6" t="inlineStr">
+        <is>
+          <t>Product Owner (all genders) – Big Data &amp; Security</t>
+        </is>
+      </c>
+      <c r="B586" s="6" t="inlineStr">
+        <is>
+          <t>Baramundi Software Ag</t>
+        </is>
+      </c>
+      <c r="C586" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D586" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E586" s="6" t="inlineStr">
+        <is>
+          <t>Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F586" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G586" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H586" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/baramundi-software-ag/product-owner-all-genders-big-data-security-augsburg-335640</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="8" t="inlineStr">
+        <is>
+          <t>Principal Analytics Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B587" s="8" t="inlineStr">
+        <is>
+          <t>Trusted Shops SE (DE)</t>
+        </is>
+      </c>
+      <c r="C587" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D587" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E587" s="8" t="inlineStr">
+        <is>
+          <t>dbt、A/B测试</t>
+        </is>
+      </c>
+      <c r="F587" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G587" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H587" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusted-shops-se-de/principal-analytics-engineer-berlin-195954</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B588" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C588" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D588" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E588" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、BigQuery、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F588" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G588" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H588" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/data-platform-engineer-data-operations-all-genders-munich-92748</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="8" t="inlineStr">
+        <is>
+          <t>PIM Data Cleansing Administrator (1 year fixed-term)</t>
+        </is>
+      </c>
+      <c r="B589" s="8" t="inlineStr">
+        <is>
+          <t>Lovehoney Group</t>
+        </is>
+      </c>
+      <c r="C589" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D589" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E589" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F589" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G589" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H589" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/lovehoney-group/pim-data-cleansing-administrator-1-year-fixed-term-berlin-187463</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Website Analyst – E-Commerce Management (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B590" s="6" t="inlineStr">
+        <is>
+          <t>Ionos2</t>
+        </is>
+      </c>
+      <c r="C590" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D590" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E590" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F590" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G590" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H590" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ionos2/senior-website-analyst-e-commerce-management-hinterm-hauptbahnhof-3-5-76137-karlsruhe-490042</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B591" s="8" t="inlineStr">
+        <is>
+          <t>Blend360</t>
+        </is>
+      </c>
+      <c r="C591" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D591" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E591" s="8" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、AWS</t>
+        </is>
+      </c>
+      <c r="F591" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G591" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H591" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/blend360/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="6" t="inlineStr">
+        <is>
+          <t>Financial Analyst (with knowledge of the Czech language)</t>
+        </is>
+      </c>
+      <c r="B592" s="6" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C592" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D592" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E592" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F592" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G592" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H592" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pwc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="8" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning Engineer- LLM Fine-tuning and Optimization</t>
+        </is>
+      </c>
+      <c r="B593" s="8" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C593" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D593" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E593" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F593" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G593" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H593" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/airbnb/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist - Healthcare</t>
+        </is>
+      </c>
+      <c r="B594" s="6" t="inlineStr">
+        <is>
+          <t>Kainos</t>
+        </is>
+      </c>
+      <c r="C594" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D594" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E594" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F594" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G594" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H594" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kainos/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="8" t="inlineStr">
+        <is>
+          <t>Product Manager II Analytics/Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B595" s="8" t="inlineStr">
+        <is>
+          <t>Kohl's</t>
+        </is>
+      </c>
+      <c r="C595" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D595" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E595" s="8" t="inlineStr">
+        <is>
+          <t>Looker、Airflow、GCP</t>
+        </is>
+      </c>
+      <c r="F595" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G595" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H595" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kohl-s/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="6" t="inlineStr">
+        <is>
+          <t>Business Support Analyst</t>
+        </is>
+      </c>
+      <c r="B596" s="6" t="inlineStr">
+        <is>
+          <t>Focus Finance International</t>
+        </is>
+      </c>
+      <c r="C596" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D596" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E596" s="6" t="inlineStr"/>
+      <c r="F596" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G596" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H596" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/focus-finance-international/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="8" t="inlineStr">
+        <is>
+          <t>News Analyst</t>
+        </is>
+      </c>
+      <c r="B597" s="8" t="inlineStr">
+        <is>
+          <t>Focus Finance International</t>
+        </is>
+      </c>
+      <c r="C597" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D597" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E597" s="8" t="inlineStr"/>
+      <c r="F597" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G597" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H597" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/focus-finance-international/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="6" t="inlineStr">
+        <is>
+          <t>Human Resources Analyst</t>
+        </is>
+      </c>
+      <c r="B598" s="6" t="inlineStr">
+        <is>
+          <t>Focus Finance International</t>
+        </is>
+      </c>
+      <c r="C598" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D598" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E598" s="6" t="inlineStr"/>
+      <c r="F598" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G598" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H598" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/focus-finance-international/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="8" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - Spanish (MX)</t>
+        </is>
+      </c>
+      <c r="B599" s="8" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C599" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D599" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E599" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F599" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G599" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H599" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="6" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - Thai</t>
+        </is>
+      </c>
+      <c r="B600" s="6" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C600" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D600" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E600" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F600" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G600" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H600" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="8" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - Swedish</t>
+        </is>
+      </c>
+      <c r="B601" s="8" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C601" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D601" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E601" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F601" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G601" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H601" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="6" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - Telugu</t>
+        </is>
+      </c>
+      <c r="B602" s="6" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C602" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D602" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E602" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F602" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G602" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H602" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B603" s="8" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="C603" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D603" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E603" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F603" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G603" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H603" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/affirm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="6" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - Bengali</t>
+        </is>
+      </c>
+      <c r="B604" s="6" t="inlineStr">
+        <is>
+          <t>RWS Group</t>
+        </is>
+      </c>
+      <c r="C604" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D604" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E604" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F604" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G604" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H604" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/rws-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst - Health Insurance (Fully Remote)</t>
+        </is>
+      </c>
+      <c r="B605" s="8" t="inlineStr">
+        <is>
+          <t>CoverGo</t>
+        </is>
+      </c>
+      <c r="C605" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D605" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E605" s="8" t="inlineStr"/>
+      <c r="F605" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G605" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H605" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/covergo/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Analytics Lead</t>
+        </is>
+      </c>
+      <c r="B606" s="6" t="inlineStr">
+        <is>
+          <t>UpGuard</t>
+        </is>
+      </c>
+      <c r="C606" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D606" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E606" s="6" t="inlineStr">
+        <is>
+          <t>dbt</t>
+        </is>
+      </c>
+      <c r="F606" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G606" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H606" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/upguard/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H560"/>
+  <autoFilter ref="A1:H606"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23881,19 +25761,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -23903,10 +25783,10 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -23915,7 +25795,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -23925,10 +25805,10 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>12</v>
@@ -23937,7 +25817,7 @@
         <v>52</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
@@ -23969,19 +25849,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
@@ -23994,7 +25874,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -24003,7 +25883,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -24044,10 +25924,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$606</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$640</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-26 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-26 23:27 UTC</t>
+          <t>数据日期 2026-07-27 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-27 23:32 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>605</v>
+        <v>639</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4573170731707317</v>
+        <v>0.3856209150326798</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.298780487804878</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2875816993464052</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1699346405228758</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1402439024390244</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1280487804878049</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08536585365853659</v>
+        <v>0.09803921568627451</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.0915032679738562</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.06707317073170732</v>
+        <v>0.08496732026143791</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H606"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -25699,8 +25699,1376 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="8" t="inlineStr">
+        <is>
+          <t>Graduate Analyst</t>
+        </is>
+      </c>
+      <c r="B607" s="8" t="inlineStr">
+        <is>
+          <t>Renewable Careers</t>
+        </is>
+      </c>
+      <c r="C607" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D607" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E607" s="8" t="inlineStr"/>
+      <c r="F607" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G607" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H607" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-graduate-analyst-renewable-careers-1135440</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="6" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B608" s="6" t="inlineStr">
+        <is>
+          <t>MediPulse</t>
+        </is>
+      </c>
+      <c r="C608" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D608" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E608" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F608" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G608" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H608" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/medipulse/data-ai-engineer-munich-125354</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="8" t="inlineStr">
+        <is>
+          <t>1157 Senior Business Analyst - ServiceNow SecOps</t>
+        </is>
+      </c>
+      <c r="B609" s="8" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C609" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D609" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E609" s="8" t="inlineStr"/>
+      <c r="F609" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G609" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H609" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1157-senior-business-analyst-servicenow-secops-germany-395135</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="6" t="inlineStr">
+        <is>
+          <t>1156 Senior Business Analyst - ServiceNow GRC / IRM</t>
+        </is>
+      </c>
+      <c r="B610" s="6" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C610" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D610" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E610" s="6" t="inlineStr"/>
+      <c r="F610" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G610" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H610" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1156-senior-business-analyst-servicenow-grc-irm-germany-458341</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="8" t="inlineStr">
+        <is>
+          <t>1155 Senior Business Analyst - ServiceNow Interface Analysis</t>
+        </is>
+      </c>
+      <c r="B611" s="8" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C611" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D611" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E611" s="8" t="inlineStr"/>
+      <c r="F611" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G611" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H611" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1155-senior-business-analyst-servicenow-interface-analysis-germany-72074</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="6" t="inlineStr">
+        <is>
+          <t>1154 Senior Business Analyst - ServiceNow Solution / Platform Architecture</t>
+        </is>
+      </c>
+      <c r="B612" s="6" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C612" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D612" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E612" s="6" t="inlineStr"/>
+      <c r="F612" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G612" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H612" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1154-senior-business-analyst-servicenow-solution-platform-architecture-germany-433789</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="8" t="inlineStr">
+        <is>
+          <t>1153 Senior Business Analyst - ServiceNow SAM (Software Asset Management)</t>
+        </is>
+      </c>
+      <c r="B613" s="8" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C613" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D613" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E613" s="8" t="inlineStr"/>
+      <c r="F613" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G613" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H613" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1153-senior-business-analyst-servicenow-sam-software-asset-management-germany-393842</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="6" t="inlineStr">
+        <is>
+          <t>1152 Senior Business Analyst - ServiceNow ITOM / ITAM</t>
+        </is>
+      </c>
+      <c r="B614" s="6" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C614" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D614" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E614" s="6" t="inlineStr"/>
+      <c r="F614" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G614" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H614" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1152-senior-business-analyst-servicenow-itom-itam-germany-322837</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="8" t="inlineStr">
+        <is>
+          <t>1151 Senior Business Analyst - ServiceNow SPM (Strategic Portfolio Management)</t>
+        </is>
+      </c>
+      <c r="B615" s="8" t="inlineStr">
+        <is>
+          <t>Intetics 2</t>
+        </is>
+      </c>
+      <c r="C615" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D615" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E615" s="8" t="inlineStr"/>
+      <c r="F615" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G615" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H615" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intetics-2/remote-1151-senior-business-analyst-servicenow-spm-strategic-portfolio-management-germany-436018</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="6" t="inlineStr">
+        <is>
+          <t>AI Researcher – Multilingual Data</t>
+        </is>
+      </c>
+      <c r="B616" s="6" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C616" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D616" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E616" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F616" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G616" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H616" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobgether/ai-researcher-multilingual-data-germany-13863</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="8" t="inlineStr">
+        <is>
+          <t>AI Director - Machine Learning</t>
+        </is>
+      </c>
+      <c r="B617" s="8" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C617" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D617" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E617" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F617" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G617" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H617" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobgether/ai-director-machine-learning-germany-42237</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Analyst Grid Connection &amp; Market Intelligence</t>
+        </is>
+      </c>
+      <c r="B618" s="6" t="inlineStr">
+        <is>
+          <t>Q Energy</t>
+        </is>
+      </c>
+      <c r="C618" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D618" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E618" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F618" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G618" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H618" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/q-energy/senior-analyst-grid-connection-market-intelligence-berlin-hamburg-wiesbaden-stuttgart-449183</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B619" s="8" t="inlineStr">
+        <is>
+          <t>Makersite GmbH</t>
+        </is>
+      </c>
+      <c r="C619" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D619" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E619" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F619" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G619" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H619" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/makersite-gmbh/remote-senior-data-scientist-berlin-366454</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst und ETRM-Admin (m/w/d) - Hybrid Remote (Ruhrgebiet)</t>
+        </is>
+      </c>
+      <c r="B620" s="6" t="inlineStr">
+        <is>
+          <t>DWWA Personalberatung GmbH</t>
+        </is>
+      </c>
+      <c r="C620" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D620" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E620" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F620" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G620" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H620" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dwwa-personalberatung-gmbh/business-analyst-und-etrm-admin-hybrid-remote-ruhrgebiet-essen-215945</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="8" t="inlineStr">
+        <is>
+          <t>Insights Analyst – Compliance &amp; Operational Risk Analytics</t>
+        </is>
+      </c>
+      <c r="B621" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiveScore Group </t>
+        </is>
+      </c>
+      <c r="C621" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D621" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E621" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F621" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G621" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H621" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/livescore-group/insights-analyst-compliance-operational-risk-analytics-london-309082</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="6" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B622" s="6" t="inlineStr">
+        <is>
+          <t>intercom</t>
+        </is>
+      </c>
+      <c r="C622" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D622" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E622" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F622" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G622" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H622" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/intercom/staff-machine-learning-scientist-london-290457</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="8" t="inlineStr">
+        <is>
+          <t>Product Quality Analyst M/W/D</t>
+        </is>
+      </c>
+      <c r="B623" s="8" t="inlineStr">
+        <is>
+          <t>Contservice GmbH</t>
+        </is>
+      </c>
+      <c r="C623" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D623" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E623" s="8" t="inlineStr"/>
+      <c r="F623" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G623" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H623" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/contservice-gmbh/product-quality-analyst-frankfurt-am-main-53764</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B624" s="6" t="inlineStr">
+        <is>
+          <t>Vrame Consult Gmbh</t>
+        </is>
+      </c>
+      <c r="C624" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D624" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E624" s="6" t="inlineStr"/>
+      <c r="F624" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G624" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H624" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vrame-consult-gmbh/data-engineer-all-genders-hamburg-214194</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B625" s="8" t="inlineStr">
+        <is>
+          <t>Jedox GmbH</t>
+        </is>
+      </c>
+      <c r="C625" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D625" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E625" s="8" t="inlineStr"/>
+      <c r="F625" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G625" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H625" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jedox-gmbh/remote-data-engineer-409534</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="6" t="inlineStr">
+        <is>
+          <t>Transformation Agent Data Infrastructure (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B626" s="6" t="inlineStr">
+        <is>
+          <t>cigus GmbH</t>
+        </is>
+      </c>
+      <c r="C626" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D626" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E626" s="6" t="inlineStr"/>
+      <c r="F626" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G626" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H626" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cigus-gmbh/transformation-agent-data-infrastructure-oberkochen-251335</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="8" t="inlineStr">
+        <is>
+          <t>Kreditanalyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B627" s="8" t="inlineStr">
+        <is>
+          <t>marschner consulting GbR</t>
+        </is>
+      </c>
+      <c r="C627" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D627" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E627" s="8" t="inlineStr"/>
+      <c r="F627" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G627" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H627" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/marschner-consulting-gbr/kreditanalyst-wurzburg-124778</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Data Platform, C++)</t>
+        </is>
+      </c>
+      <c r="B628" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C628" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D628" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E628" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Spark、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F628" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G628" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H628" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nebius/senior-software-engineer-data-platform-c-czech-republic-united-kingdom-57791</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="8" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (Token Factory)</t>
+        </is>
+      </c>
+      <c r="B629" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C629" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D629" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E629" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F629" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G629" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H629" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nebius/remote-senior-ml-engineer-token-factory-30647</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="6" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (Token Factory)</t>
+        </is>
+      </c>
+      <c r="B630" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C630" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D630" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E630" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F630" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G630" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H630" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nebius/remote-senior-ml-engineer-token-factory-223220</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="8" t="inlineStr">
+        <is>
+          <t>Working Student - Data Pipeline Development</t>
+        </is>
+      </c>
+      <c r="B631" s="8" t="inlineStr">
+        <is>
+          <t>Snke</t>
+        </is>
+      </c>
+      <c r="C631" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D631" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E631" s="8" t="inlineStr"/>
+      <c r="F631" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G631" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H631" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/snke/working-student-data-pipeline-development-munchen-492971</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="6" t="inlineStr">
+        <is>
+          <t>(Canada) Sr. Data Governance Analyst, 6 month contract</t>
+        </is>
+      </c>
+      <c r="B632" s="6" t="inlineStr">
+        <is>
+          <t>PointClickCare</t>
+        </is>
+      </c>
+      <c r="C632" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D632" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E632" s="6" t="inlineStr"/>
+      <c r="F632" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G632" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H632" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pointclickcare/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="B633" s="8" t="inlineStr">
+        <is>
+          <t>Blend360</t>
+        </is>
+      </c>
+      <c r="C633" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D633" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E633" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F633" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G633" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H633" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/blend360/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (Senior) - ETL (Python+Snowflake) - Remote, Latin América</t>
+        </is>
+      </c>
+      <c r="B634" s="6" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C634" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D634" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E634" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Snowflake、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F634" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G634" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H634" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bluelight-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="8" t="inlineStr">
+        <is>
+          <t>Senior Compensation Analyst</t>
+        </is>
+      </c>
+      <c r="B635" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C635" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D635" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E635" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F635" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G635" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H635" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nebius/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="6" t="inlineStr">
+        <is>
+          <t>Solution Data Engineer Sr.</t>
+        </is>
+      </c>
+      <c r="B636" s="6" t="inlineStr">
+        <is>
+          <t>Sequoia Connect</t>
+        </is>
+      </c>
+      <c r="C636" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D636" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E636" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、Airflow、AWS、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F636" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G636" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H636" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sequoia-connect/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer (Microsoft Fabric)</t>
+        </is>
+      </c>
+      <c r="B637" s="8" t="inlineStr">
+        <is>
+          <t>Blend360</t>
+        </is>
+      </c>
+      <c r="C637" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D637" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E637" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F637" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G637" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H637" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/blend360/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager II - eCommerce Analytics &amp; Business Intelligence (Adobe CJA)</t>
+        </is>
+      </c>
+      <c r="B638" s="6" t="inlineStr">
+        <is>
+          <t>DICK'S Sporting Goods</t>
+        </is>
+      </c>
+      <c r="C638" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D638" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E638" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F638" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G638" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H638" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/dick-s-sporting-goods/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="8" t="inlineStr">
+        <is>
+          <t>Support Business Analyst | Remote LATAM Only</t>
+        </is>
+      </c>
+      <c r="B639" s="8" t="inlineStr">
+        <is>
+          <t>Agentic Dream</t>
+        </is>
+      </c>
+      <c r="C639" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D639" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E639" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F639" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G639" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H639" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/agentic-dream/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B640" s="6" t="inlineStr">
+        <is>
+          <t>Bridge33 Capital</t>
+        </is>
+      </c>
+      <c r="C640" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D640" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E640" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Snowflake、dbt、Airflow</t>
+        </is>
+      </c>
+      <c r="F640" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G640" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H640" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bridge33-capital/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H606"/>
+  <autoFilter ref="A1:H640"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25761,19 +27129,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -25783,7 +27151,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>3</v>
@@ -25795,7 +27163,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -25805,7 +27173,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>37</v>
@@ -25817,7 +27185,7 @@
         <v>52</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
@@ -25849,19 +27217,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>67</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -25871,7 +27239,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>4</v>
@@ -25883,7 +27251,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$640</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$680</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-27 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-27 23:32 UTC</t>
+          <t>数据日期 2026-07-28 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-28 23:28 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>639</v>
+        <v>679</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4451219512195122</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3856209150326798</v>
+        <v>0.3780487804878049</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3109756097560976</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3475609756097561</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2875816993464052</v>
+        <v>0.298780487804878</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1699346405228758</v>
+        <v>0.1890243902439024</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1585365853658537</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.08536585365853659</v>
       </c>
     </row>
     <row r="15">
@@ -806,75 +806,75 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1341463414634146</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.1280487804878049</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.1036585365853658</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.0975609756097561</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0915032679738562</v>
+        <v>0.09146341463414634</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08496732026143791</v>
+        <v>0.07317073170731707</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -27067,8 +27067,1652 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="8" t="inlineStr">
+        <is>
+          <t>Transportation Analyst</t>
+        </is>
+      </c>
+      <c r="B641" s="8" t="inlineStr">
+        <is>
+          <t>RemoteFront</t>
+        </is>
+      </c>
+      <c r="C641" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D641" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E641" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F641" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G641" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H641" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-transportation-analyst-remotefront-1135538</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="6" t="inlineStr">
+        <is>
+          <t>Market Research Analyst</t>
+        </is>
+      </c>
+      <c r="B642" s="6" t="inlineStr">
+        <is>
+          <t>Blend</t>
+        </is>
+      </c>
+      <c r="C642" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D642" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E642" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F642" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G642" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H642" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-market-research-analyst-blend-1135535</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="8" t="inlineStr">
+        <is>
+          <t>Entry Level Analyst</t>
+        </is>
+      </c>
+      <c r="B643" s="8" t="inlineStr">
+        <is>
+          <t>Renewable Careers</t>
+        </is>
+      </c>
+      <c r="C643" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D643" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E643" s="8" t="inlineStr"/>
+      <c r="F643" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G643" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H643" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-entry-level-analyst-renewable-careers-1135534</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B644" s="6" t="inlineStr">
+        <is>
+          <t>sparetech</t>
+        </is>
+      </c>
+      <c r="C644" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D644" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E644" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、R</t>
+        </is>
+      </c>
+      <c r="F644" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G644" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H644" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sparetech/senior-data-analyst-45138</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="8" t="inlineStr">
+        <is>
+          <t>Payments Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B645" s="8" t="inlineStr">
+        <is>
+          <t>Congrify Payments Intelligence (an Ixopay Company)</t>
+        </is>
+      </c>
+      <c r="C645" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D645" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E645" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F645" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G645" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H645" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/congrify-payments-intelligence-an-ixopay-company/payments-operations-analyst-munich-367198</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B646" s="6" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C646" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D646" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E646" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F646" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G646" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H646" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/senior-data-engineer-berlin-296119</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B647" s="8" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C647" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D647" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E647" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F647" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G647" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H647" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/data-platform-engineer-berlin-273541</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B648" s="6" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH Personalberatung</t>
+        </is>
+      </c>
+      <c r="C648" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D648" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E648" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Airflow、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F648" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G648" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H648" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh-personalberatung/data-engineer-berlin-32772</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/w/d) BI &amp; Konsolidierung</t>
+        </is>
+      </c>
+      <c r="B649" s="8" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C649" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D649" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E649" s="8" t="inlineStr"/>
+      <c r="F649" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G649" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H649" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/senior-consultant-bi-konsolidierung-stuttgart-15860</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B650" s="6" t="inlineStr">
+        <is>
+          <t>Peter Park</t>
+        </is>
+      </c>
+      <c r="C650" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D650" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E650" s="6" t="inlineStr"/>
+      <c r="F650" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G650" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H650" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/peter-park/senior-data-scientist-munchen-40585</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="8" t="inlineStr">
+        <is>
+          <t>Senior Director of Machine Learning (Experiences)</t>
+        </is>
+      </c>
+      <c r="B651" s="8" t="inlineStr">
+        <is>
+          <t>tripadvisor</t>
+        </is>
+      </c>
+      <c r="C651" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D651" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E651" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F651" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G651" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H651" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tripadvisor/senior-director-of-machine-learning-experiences-london-oxford-poland-krakow-481393</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="6" t="inlineStr">
+        <is>
+          <t>Director of Data</t>
+        </is>
+      </c>
+      <c r="B652" s="6" t="inlineStr">
+        <is>
+          <t>alpaca</t>
+        </is>
+      </c>
+      <c r="C652" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D652" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E652" s="6" t="inlineStr">
+        <is>
+          <t>Spark、dbt、Airflow、ETL</t>
+        </is>
+      </c>
+      <c r="F652" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G652" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H652" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/alpaca/director-of-data-370921</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B653" s="8" t="inlineStr">
+        <is>
+          <t>oliver</t>
+        </is>
+      </c>
+      <c r="C653" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D653" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E653" s="8" t="inlineStr">
+        <is>
+          <t>Looker、Spark、BigQuery</t>
+        </is>
+      </c>
+      <c r="F653" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G653" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H653" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/oliver/senior-data-analyst-london-197206</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="6" t="inlineStr">
+        <is>
+          <t>Senior/Staff Data Scientist - Measurement, Experimentation &amp; Causal Inference</t>
+        </is>
+      </c>
+      <c r="B654" s="6" t="inlineStr">
+        <is>
+          <t>sonyinteractiveentertainmentglobal</t>
+        </is>
+      </c>
+      <c r="C654" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D654" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E654" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F654" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G654" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H654" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sonyinteractiveentertainmentglobal/senior-staff-data-scientist-measurement-experimentation-causal-inference-london-451865</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist - Measurement, Experimentation &amp; Causal Inference</t>
+        </is>
+      </c>
+      <c r="B655" s="8" t="inlineStr">
+        <is>
+          <t>sonyinteractiveentertainmentglobal</t>
+        </is>
+      </c>
+      <c r="C655" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D655" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E655" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F655" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G655" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H655" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sonyinteractiveentertainmentglobal/data-scientist-measurement-experimentation-causal-inference-london-320720</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="6" t="inlineStr">
+        <is>
+          <t>Senior Trust Security Analyst</t>
+        </is>
+      </c>
+      <c r="B656" s="6" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="C656" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D656" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E656" s="6" t="inlineStr"/>
+      <c r="F656" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G656" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H656" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/nice/senior-trust-security-analyst-137278</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI-Native Fullstack Engineer (m/f/d) - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B657" s="8" t="inlineStr">
+        <is>
+          <t>Zvoove</t>
+        </is>
+      </c>
+      <c r="C657" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D657" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E657" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS</t>
+        </is>
+      </c>
+      <c r="F657" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G657" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H657" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/zvoove/remote-senior-ai-native-fullstack-engineer-data-analytics-195686</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B658" s="6" t="inlineStr">
+        <is>
+          <t>PHMG Careers</t>
+        </is>
+      </c>
+      <c r="C658" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D658" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E658" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F658" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G658" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H658" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/phmg-careers/data-scientist-manchester-489762</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B659" s="8" t="inlineStr">
+        <is>
+          <t>OLIVER Agency</t>
+        </is>
+      </c>
+      <c r="C659" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D659" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E659" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker、Spark、BigQuery</t>
+        </is>
+      </c>
+      <c r="F659" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G659" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H659" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/oliver-agency/senior-data-analyst-weybridge-377054</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B660" s="6" t="inlineStr">
+        <is>
+          <t>OLIVER Agency</t>
+        </is>
+      </c>
+      <c r="C660" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D660" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E660" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Looker、Spark、BigQuery</t>
+        </is>
+      </c>
+      <c r="F660" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G660" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H660" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/oliver-agency/data-analyst-surrey-heath-98862</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (Mid-Level) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B661" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C661" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D661" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E661" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F661" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G661" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H661" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/data-platform-engineer-mid-level-berlin-231606</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer Data &amp; ML (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B662" s="6" t="inlineStr">
+        <is>
+          <t>amentis solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C662" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D662" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E662" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F662" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G662" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H662" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/amentis-solutions-gmbh/software-engineer-data-ml-tholey-369299</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer - Data Platform (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B663" s="8" t="inlineStr">
+        <is>
+          <t>1KOMMA5˚</t>
+        </is>
+      </c>
+      <c r="C663" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D663" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E663" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F663" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G663" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H663" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/1komma50/junior-data-engineer-data-platform-berlin-266979</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B664" s="6" t="inlineStr">
+        <is>
+          <t>Lever Implementation Training Environment</t>
+        </is>
+      </c>
+      <c r="C664" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D664" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E664" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F664" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G664" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H664" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/lever-implementation-training-environment/data-scientist-berlin-germany-98700</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant Analytics &amp; Consulting (Mensch)</t>
+        </is>
+      </c>
+      <c r="B665" s="8" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C665" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D665" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E665" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F665" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G665" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H665" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wppmedia/senior-consultant-analytics-consulting-mensch-dusseldorf-469418</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer - AFRICOM</t>
+        </is>
+      </c>
+      <c r="B666" s="6" t="inlineStr">
+        <is>
+          <t>Agile Defense</t>
+        </is>
+      </c>
+      <c r="C666" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D666" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E666" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Spark、AWS、Azure、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F666" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G666" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H666" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-defense/data-engineer-africom-stuttgart-germany-50591</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B667" s="8" t="inlineStr">
+        <is>
+          <t>Unifonic</t>
+        </is>
+      </c>
+      <c r="C667" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D667" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E667" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F667" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G667" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H667" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/unifonic/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="6" t="inlineStr">
+        <is>
+          <t>Principal Engineer - Data Center Modelling</t>
+        </is>
+      </c>
+      <c r="B668" s="6" t="inlineStr">
+        <is>
+          <t>Electric Power Engineers</t>
+        </is>
+      </c>
+      <c r="C668" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D668" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E668" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F668" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G668" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H668" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/electric-power-engineers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B669" s="8" t="inlineStr">
+        <is>
+          <t>Óscala</t>
+        </is>
+      </c>
+      <c r="C669" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D669" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E669" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Snowflake、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F669" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G669" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H669" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/oscala/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="6" t="inlineStr">
+        <is>
+          <t>Vice President, Data Architecture, Engineering &amp; AI</t>
+        </is>
+      </c>
+      <c r="B670" s="6" t="inlineStr">
+        <is>
+          <t>Kohl's</t>
+        </is>
+      </c>
+      <c r="C670" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D670" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E670" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F670" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G670" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H670" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kohl-s/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Operation Research</t>
+        </is>
+      </c>
+      <c r="B671" s="8" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C671" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D671" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E671" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F671" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G671" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H671" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/tiger-analytics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (with Vertex AI Experience)</t>
+        </is>
+      </c>
+      <c r="B672" s="6" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C672" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D672" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E672" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP、BigQuery、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F672" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G672" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H672" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/tiger-analytics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Director - Business Data</t>
+        </is>
+      </c>
+      <c r="B673" s="8" t="inlineStr">
+        <is>
+          <t>Canonical</t>
+        </is>
+      </c>
+      <c r="C673" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D673" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E673" s="8" t="inlineStr">
+        <is>
+          <t>Python、ETL</t>
+        </is>
+      </c>
+      <c r="F673" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G673" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H673" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/canonical/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="6" t="inlineStr">
+        <is>
+          <t>Underwriting Support Analyst</t>
+        </is>
+      </c>
+      <c r="B674" s="6" t="inlineStr">
+        <is>
+          <t>Ledgebrook</t>
+        </is>
+      </c>
+      <c r="C674" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D674" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E674" s="6" t="inlineStr"/>
+      <c r="F674" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G674" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H674" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ledgebrook/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="8" t="inlineStr">
+        <is>
+          <t>Ecommerce Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B675" s="8" t="inlineStr">
+        <is>
+          <t>etaily</t>
+        </is>
+      </c>
+      <c r="C675" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D675" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E675" s="8" t="inlineStr"/>
+      <c r="F675" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G675" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H675" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/etaily/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="6" t="inlineStr">
+        <is>
+          <t>Project Manager (AI &amp; Big Data)</t>
+        </is>
+      </c>
+      <c r="B676" s="6" t="inlineStr">
+        <is>
+          <t>Addepto</t>
+        </is>
+      </c>
+      <c r="C676" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D676" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E676" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F676" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G676" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H676" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/addepto/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (Azure Data Factory)</t>
+        </is>
+      </c>
+      <c r="B677" s="8" t="inlineStr">
+        <is>
+          <t>Addepto</t>
+        </is>
+      </c>
+      <c r="C677" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D677" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E677" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Azure、A/B测试、ETL</t>
+        </is>
+      </c>
+      <c r="F677" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G677" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H677" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/addepto/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="6" t="inlineStr">
+        <is>
+          <t>Sr Director Analyst - AI Strategy, Leadership and Operating Models (Remote - U.S</t>
+        </is>
+      </c>
+      <c r="B678" s="6" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C678" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D678" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E678" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F678" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G678" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H678" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="8" t="inlineStr">
+        <is>
+          <t>Audit Planning &amp; Risk Coverage Expert (Director/Analyst, Remote United States)</t>
+        </is>
+      </c>
+      <c r="B679" s="8" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C679" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D679" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E679" s="8" t="inlineStr"/>
+      <c r="F679" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G679" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H679" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="6" t="inlineStr">
+        <is>
+          <t>数据标注员招募</t>
+        </is>
+      </c>
+      <c r="B680" s="6" t="inlineStr"/>
+      <c r="C680" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D680" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E680" s="6" t="inlineStr"/>
+      <c r="F680" s="6" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G680" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H680" s="6" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/wwfZ1r</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H640"/>
+  <autoFilter ref="A1:H680"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27129,19 +28773,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
@@ -27160,10 +28804,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -27173,19 +28817,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -27204,10 +28848,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -27217,7 +28861,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
@@ -27226,10 +28870,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
@@ -27242,7 +28886,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -27251,7 +28895,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$704</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-28 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-28 23:28 UTC</t>
+          <t>数据日期 2026-07-29 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-29 23:29 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>679</v>
+        <v>703</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4451219512195122</v>
+        <v>0.4295774647887324</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3780487804878049</v>
+        <v>0.4084507042253521</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3109756097560976</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3475609756097561</v>
+        <v>0.323943661971831</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.298780487804878</v>
+        <v>0.2535211267605634</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1890243902439024</v>
+        <v>0.1619718309859155</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1585365853658537</v>
+        <v>0.147887323943662</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.08536585365853659</v>
+        <v>0.1056338028169014</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1341463414634146</v>
+        <v>0.1338028169014084</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1280487804878049</v>
+        <v>0.1267605633802817</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1036585365853658</v>
+        <v>0.09859154929577464</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.09154929577464789</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09146341463414634</v>
+        <v>0.09154929577464789</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.08450704225352113</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H680"/>
+  <dimension ref="A1:H704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -28711,8 +28711,988 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" s="8" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B681" s="8" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C681" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D681" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E681" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F681" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G681" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H681" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-devops-engineer-lemon-io-1135562</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B682" s="6" t="inlineStr">
+        <is>
+          <t>YO AI Labs</t>
+        </is>
+      </c>
+      <c r="C682" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D682" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E682" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F682" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G682" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H682" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-yo-ai-labs-1135558</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="8" t="inlineStr">
+        <is>
+          <t>Contract Business Analyst</t>
+        </is>
+      </c>
+      <c r="B683" s="8" t="inlineStr">
+        <is>
+          <t>YLD.com</t>
+        </is>
+      </c>
+      <c r="C683" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D683" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E683" s="8" t="inlineStr"/>
+      <c r="F683" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G683" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H683" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yldcom/contract-business-analyst-trochtelborn-42088</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Engineer - Finance</t>
+        </is>
+      </c>
+      <c r="B684" s="6" t="inlineStr">
+        <is>
+          <t>mewssystems</t>
+        </is>
+      </c>
+      <c r="C684" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D684" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E684" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F684" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G684" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H684" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mewssystems/analytics-engineer-finance-460067</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Product Manager</t>
+        </is>
+      </c>
+      <c r="B685" s="8" t="inlineStr">
+        <is>
+          <t>liberis</t>
+        </is>
+      </c>
+      <c r="C685" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D685" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E685" s="8" t="inlineStr"/>
+      <c r="F685" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G685" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H685" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/liberis/senior-data-product-manager-london-467030</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="B686" s="6" t="inlineStr">
+        <is>
+          <t>liberis</t>
+        </is>
+      </c>
+      <c r="C686" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D686" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E686" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F686" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G686" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H686" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/liberis/lead-data-engineer-mumbai-242719</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="B687" s="8" t="inlineStr">
+        <is>
+          <t>liberis</t>
+        </is>
+      </c>
+      <c r="C687" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D687" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E687" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F687" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G687" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H687" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/liberis/lead-data-engineer-london-485443</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="6" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning Scientist (Experiences)</t>
+        </is>
+      </c>
+      <c r="B688" s="6" t="inlineStr">
+        <is>
+          <t>tripadvisor</t>
+        </is>
+      </c>
+      <c r="C688" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D688" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E688" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F688" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G688" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H688" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tripadvisor/principal-machine-learning-scientist-experiences-london-48596</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="8" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist</t>
+        </is>
+      </c>
+      <c r="B689" s="8" t="inlineStr">
+        <is>
+          <t>onrunning</t>
+        </is>
+      </c>
+      <c r="C689" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D689" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E689" s="8" t="inlineStr"/>
+      <c r="F689" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G689" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H689" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/onrunning/principal-data-scientist-london-zurich-302530</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="6" t="inlineStr">
+        <is>
+          <t>Product Growth Analytics Lead</t>
+        </is>
+      </c>
+      <c r="B690" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C690" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D690" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E690" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F690" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G690" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H690" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/nebius/product-growth-analytics-lead-amsterdam-netherlands-london-252385</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist - Cybersecurity Analyst (Position located in Cheltenham, United Kingdom)</t>
+        </is>
+      </c>
+      <c r="B691" s="8" t="inlineStr">
+        <is>
+          <t>knowbe4</t>
+        </is>
+      </c>
+      <c r="C691" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D691" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E691" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F691" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G691" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H691" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/knowbe4/data-scientist-cybersecurity-analyst-position-located-in-cheltenham-united-kingdom-228967</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Newcastle, United Kingdom</t>
+        </is>
+      </c>
+      <c r="B692" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C692" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D692" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E692" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F692" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G692" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H692" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-newcastle-united-kingdom-newcastle-upon-tyne-137659</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Manchester, United Kingdom</t>
+        </is>
+      </c>
+      <c r="B693" s="8" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C693" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D693" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E693" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F693" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G693" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H693" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-manchester-united-kingdom-20234</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Newcastle, United Kingdom</t>
+        </is>
+      </c>
+      <c r="B694" s="6" t="inlineStr">
+        <is>
+          <t>speechify</t>
+        </is>
+      </c>
+      <c r="C694" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D694" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E694" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F694" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G694" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H694" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-newcastle-united-kingdom-307481</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Manchester, United Kingdom</t>
+        </is>
+      </c>
+      <c r="B695" s="8" t="inlineStr">
+        <is>
+          <t>speechify</t>
+        </is>
+      </c>
+      <c r="C695" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D695" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E695" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F695" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G695" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H695" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-manchester-united-kingdom-176602</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="6" t="inlineStr">
+        <is>
+          <t>Junior Data Governance Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B696" s="6" t="inlineStr">
+        <is>
+          <t>EWERK GROUP</t>
+        </is>
+      </c>
+      <c r="C696" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D696" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E696" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F696" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G696" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H696" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ewerk-group/junior-data-governance-manager-stuttgart-172819</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B697" s="8" t="inlineStr">
+        <is>
+          <t>OXG Glasfaser GmbH</t>
+        </is>
+      </c>
+      <c r="C697" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D697" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E697" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F697" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G697" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H697" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/oxg-glasfaser-gmbh/remote-data-analyst-213636</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="6" t="inlineStr">
+        <is>
+          <t>Director, Clinical Data Management</t>
+        </is>
+      </c>
+      <c r="B698" s="6" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C698" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D698" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E698" s="6" t="inlineStr">
+        <is>
+          <t>Excel、GCP、统计学</t>
+        </is>
+      </c>
+      <c r="F698" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G698" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H698" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/alnylam-pharmaceuticals/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Web Analytics</t>
+        </is>
+      </c>
+      <c r="B699" s="8" t="inlineStr">
+        <is>
+          <t>LeadVenture</t>
+        </is>
+      </c>
+      <c r="C699" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D699" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E699" s="8" t="inlineStr"/>
+      <c r="F699" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G699" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H699" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/leadventure/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="6" t="inlineStr">
+        <is>
+          <t>Application Analyst II, Business Applications/Information Solutions</t>
+        </is>
+      </c>
+      <c r="B700" s="6" t="inlineStr">
+        <is>
+          <t>Medical University of South Carolina</t>
+        </is>
+      </c>
+      <c r="C700" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D700" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E700" s="6" t="inlineStr"/>
+      <c r="F700" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G700" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H700" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/musc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="8" t="inlineStr">
+        <is>
+          <t>EverHealth - Sales Insights Analyst (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B701" s="8" t="inlineStr">
+        <is>
+          <t>EverCommerce</t>
+        </is>
+      </c>
+      <c r="C701" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D701" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E701" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F701" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G701" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H701" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/evercommerce/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="6" t="inlineStr">
+        <is>
+          <t>Recurring - Analyst</t>
+        </is>
+      </c>
+      <c r="B702" s="6" t="inlineStr">
+        <is>
+          <t>Walt Disney Parks and Resorts U.S., Inc.</t>
+        </is>
+      </c>
+      <c r="C702" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D702" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E702" s="6" t="inlineStr"/>
+      <c r="F702" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G702" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H702" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/walt-disney-parks-and-resorts-u-s-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="8" t="inlineStr">
+        <is>
+          <t>Cash Reconciliation Analyst</t>
+        </is>
+      </c>
+      <c r="B703" s="8" t="inlineStr">
+        <is>
+          <t>WellNow Urgent Care</t>
+        </is>
+      </c>
+      <c r="C703" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D703" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E703" s="8" t="inlineStr"/>
+      <c r="F703" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G703" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H703" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/wellnow-urgent-care/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="6" t="inlineStr">
+        <is>
+          <t>Data Strategy &amp; AI Advisory.</t>
+        </is>
+      </c>
+      <c r="B704" s="6" t="inlineStr">
+        <is>
+          <t>Intetics</t>
+        </is>
+      </c>
+      <c r="C704" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D704" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E704" s="6" t="inlineStr">
+        <is>
+          <t>Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F704" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G704" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H704" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/intetics/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H680"/>
+  <autoFilter ref="A1:H704"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28773,19 +29753,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
@@ -28804,10 +29784,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -28817,7 +29797,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>38</v>
@@ -28826,10 +29806,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
@@ -28848,10 +29828,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -28861,7 +29841,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>10</v>
@@ -28873,7 +29853,7 @@
         <v>68</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$704</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$756</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-29 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-29 23:29 UTC</t>
+          <t>数据日期 2026-07-30 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-30 23:30 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>703</v>
+        <v>755</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4295774647887324</v>
+        <v>0.440251572327044</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4084507042253521</v>
+        <v>0.4276729559748428</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2816901408450704</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.323943661971831</v>
+        <v>0.2893081761006289</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2535211267605634</v>
+        <v>0.2767295597484277</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1619718309859155</v>
+        <v>0.1761006289308176</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.147887323943662</v>
+        <v>0.2075471698113208</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1056338028169014</v>
+        <v>0.1069182389937107</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.1446540880503145</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1267605633802817</v>
+        <v>0.1320754716981132</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09859154929577464</v>
+        <v>0.1069182389937107</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09154929577464789</v>
+        <v>0.09433962264150944</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09154929577464789</v>
+        <v>0.0880503144654088</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.08176100628930817</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H704"/>
+  <dimension ref="A1:H756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -29691,8 +29691,2116 @@
         </is>
       </c>
     </row>
+    <row r="705">
+      <c r="A705" s="8" t="inlineStr">
+        <is>
+          <t>Junior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B705" s="8" t="inlineStr">
+        <is>
+          <t>HiredBuddy</t>
+        </is>
+      </c>
+      <c r="C705" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D705" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E705" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI、Looker、R、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F705" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G705" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H705" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-junior-data-analyst-hiredbuddy-1135673</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="6" t="inlineStr">
+        <is>
+          <t>Senior Graphic Designer</t>
+        </is>
+      </c>
+      <c r="B706" s="6" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C706" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D706" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E706" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F706" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G706" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H706" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/design/senior-graphic-designer-2091081</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/w/d) BI &amp; Konsolidierung</t>
+        </is>
+      </c>
+      <c r="B707" s="8" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C707" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D707" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E707" s="8" t="inlineStr"/>
+      <c r="F707" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G707" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H707" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/remote-senior-consultant-bi-konsolidierung-stuttgart-127601</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B708" s="6" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C708" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D708" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E708" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F708" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G708" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H708" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/data-platform-engineer-berlin-338774</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B709" s="8" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C709" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D709" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E709" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、dbt、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F709" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G709" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H709" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/senior-data-engineer-berlin-129969</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant SAP Data Transformation &amp; Migration (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B710" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C710" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D710" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E710" s="6" t="inlineStr"/>
+      <c r="F710" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G710" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H710" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-consultant-sap-data-transformation-migration-heidelberg-355830</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant SAP Analytics Cloud/ SAP Business Data Cloud (m/w/d) SAP BDC</t>
+        </is>
+      </c>
+      <c r="B711" s="8" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C711" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D711" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E711" s="8" t="inlineStr"/>
+      <c r="F711" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G711" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H711" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-consultant-sap-analytics-cloud-sap-business-data-cloud-sap-bdc-heidelberg-227591</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant SAP MDG (m/w/d) Master Data Governance</t>
+        </is>
+      </c>
+      <c r="B712" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C712" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D712" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E712" s="6" t="inlineStr"/>
+      <c r="F712" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G712" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H712" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-consultant-sap-mdg-master-data-governance-heidelberg-238350</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="8" t="inlineStr">
+        <is>
+          <t>Manager (m/w/d) Data &amp; Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="B713" s="8" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C713" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D713" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E713" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Power BI、Snowflake、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F713" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G713" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H713" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/manager-data-analytics-consulting-heidelberg-250184</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Solution Architect (m/w/d) SAP Datasphere/ SAP Business Data Cloud</t>
+        </is>
+      </c>
+      <c r="B714" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C714" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D714" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E714" s="6" t="inlineStr"/>
+      <c r="F714" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G714" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H714" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-solution-architect-sap-datasphere-sap-business-data-cloud-heidelberg-7426</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant SAP BI (m/w/d) im Application Management Support</t>
+        </is>
+      </c>
+      <c r="B715" s="8" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C715" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D715" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E715" s="8" t="inlineStr"/>
+      <c r="F715" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G715" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H715" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-consultant-sap-bi-im-application-management-support-heidelberg-5595</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="6" t="inlineStr">
+        <is>
+          <t>Trainee SAP Master Data Management (MDM) Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B716" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C716" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D716" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E716" s="6" t="inlineStr"/>
+      <c r="F716" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G716" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H716" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/trainee-sap-master-data-management-mdm-consultant-heidelberg-21285</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent - Master Data Management (MDM) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B717" s="8" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C717" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D717" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E717" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F717" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G717" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H717" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/werkstudent-master-data-management-mdm-heidelberg-53965</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Expert Material Master Data  &amp; End-to-End Product Data (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B718" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C718" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D718" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E718" s="6" t="inlineStr"/>
+      <c r="F718" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G718" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H718" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-expert-material-master-data-end-to-end-product-data-heidelberg-100982</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B719" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiveScore Group </t>
+        </is>
+      </c>
+      <c r="C719" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D719" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E719" s="8" t="inlineStr">
+        <is>
+          <t>GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F719" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G719" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H719" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/livescore-group/senior-data-engineer-london-121041</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B720" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiveScore Group </t>
+        </is>
+      </c>
+      <c r="C720" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D720" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E720" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F720" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G720" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H720" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/livescore-group/data-engineer-london-313309</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B721" s="8" t="inlineStr">
+        <is>
+          <t>Atolls</t>
+        </is>
+      </c>
+      <c r="C721" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D721" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E721" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、AWS、GCP</t>
+        </is>
+      </c>
+      <c r="F721" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G721" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H721" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/atolls/data-engineer-london-350221</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B722" s="6" t="inlineStr">
+        <is>
+          <t>Atolls</t>
+        </is>
+      </c>
+      <c r="C722" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D722" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E722" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、AWS、GCP</t>
+        </is>
+      </c>
+      <c r="F722" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G722" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H722" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/atolls/data-engineer-london-346649</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering Manager (UK Remote)</t>
+        </is>
+      </c>
+      <c r="B723" s="8" t="inlineStr">
+        <is>
+          <t>Ivcevidensia</t>
+        </is>
+      </c>
+      <c r="C723" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D723" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E723" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Azure</t>
+        </is>
+      </c>
+      <c r="F723" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G723" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H723" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ivcevidensia/data-engineering-manager-uk-remote-36619</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B724" s="6" t="inlineStr">
+        <is>
+          <t>tripledotstudios</t>
+        </is>
+      </c>
+      <c r="C724" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D724" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E724" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F724" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G724" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H724" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tripledotstudios/senior-machine-learning-engineer-serbia-25174</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B725" s="8" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C725" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D725" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E725" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt、BigQuery</t>
+        </is>
+      </c>
+      <c r="F725" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G725" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H725" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/numan/senior-analytics-engineer-london-364300</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="6" t="inlineStr">
+        <is>
+          <t>Software/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B726" s="6" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C726" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D726" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E726" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、A/B测试、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F726" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G726" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H726" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/software-data-engineer-london-333304</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="8" t="inlineStr">
+        <is>
+          <t>Software / Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B727" s="8" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C727" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D727" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E727" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、A/B测试、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F727" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G727" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H727" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/software-machine-learning-engineer-london-493945</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B728" s="6" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C728" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D728" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E728" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F728" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G728" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H728" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/senior-machine-learning-engineer-london-65419</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B729" s="8" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C729" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D729" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E729" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F729" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G729" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H729" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/machine-learning-engineer-london-260196</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="6" t="inlineStr">
+        <is>
+          <t>Data Software Engineer</t>
+        </is>
+      </c>
+      <c r="B730" s="6" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C730" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D730" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E730" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F730" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G730" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H730" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/data-software-engineer-london-369758</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B731" s="8" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C731" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D731" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E731" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F731" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G731" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H731" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/data-scientist-london-404024</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B732" s="6" t="inlineStr">
+        <is>
+          <t>Prima</t>
+        </is>
+      </c>
+      <c r="C732" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D732" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E732" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、A/B测试、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F732" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G732" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H732" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prima/data-engineer-london-134322</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="8" t="inlineStr">
+        <is>
+          <t>Marketing Analytics &amp; Attribution Manager – FX &amp; CFDs</t>
+        </is>
+      </c>
+      <c r="B733" s="8" t="inlineStr">
+        <is>
+          <t>ThinkMarkets</t>
+        </is>
+      </c>
+      <c r="C733" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D733" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E733" s="8" t="inlineStr"/>
+      <c r="F733" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G733" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H733" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/thinkmarkets/marketing-analytics-attribution-manager-fx-cfds-london-198182</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="6" t="inlineStr">
+        <is>
+          <t>SVP, Data &amp; Tech Lead</t>
+        </is>
+      </c>
+      <c r="B734" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C734" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D734" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E734" s="6" t="inlineStr"/>
+      <c r="F734" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G734" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H734" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/svp-data-tech-lead-london-6720</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B735" s="8" t="inlineStr">
+        <is>
+          <t>Octopus Energy Group jobs</t>
+        </is>
+      </c>
+      <c r="C735" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D735" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E735" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F735" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G735" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H735" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/octopus-energy-group-jobs/data-scientist-london-gb-317468</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="6" t="inlineStr">
+        <is>
+          <t>Trainee Process Mining Consultant (Signavio / Celonis) – Fokus Data &amp; Process Analytics (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B736" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C736" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D736" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E736" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F736" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G736" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H736" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/trainee-process-mining-consultant-signavio-celonis-fokus-data-process-analytics-heidelberg-220662</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="8" t="inlineStr">
+        <is>
+          <t>Trainee (SAP) Process Management Consultant – Fokus Data-driven Performance Improvement / Process Mining (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B737" s="8" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C737" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D737" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E737" s="8" t="inlineStr"/>
+      <c r="F737" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G737" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H737" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/trainee-sap-process-management-consultant-fokus-data-driven-performance-improvement-process-mining-heidelberg-261270</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) AI Analyst m/w/d</t>
+        </is>
+      </c>
+      <c r="B738" s="6" t="inlineStr">
+        <is>
+          <t>cbs Corporate Business Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C738" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D738" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E738" s="6" t="inlineStr">
+        <is>
+          <t>Python、pandas</t>
+        </is>
+      </c>
+      <c r="F738" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G738" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H738" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-ai-analyst-heidelberg-421557</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst &amp; Finance Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B739" s="8" t="inlineStr">
+        <is>
+          <t>Start To Finish Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C739" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D739" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E739" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Power BI、Looker</t>
+        </is>
+      </c>
+      <c r="F739" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G739" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H739" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/start-to-finish-consulting-gmbh/senior-business-analyst-finance-manager-hamburg-259919</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B740" s="6" t="inlineStr">
+        <is>
+          <t>Quantum-Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C740" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D740" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E740" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F740" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G740" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H740" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/quantum-systems-gmbh/senior-machine-learning-engineer-gilching-417351</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="8" t="inlineStr">
+        <is>
+          <t>Contract Business Analyst</t>
+        </is>
+      </c>
+      <c r="B741" s="8" t="inlineStr">
+        <is>
+          <t>YLD.com</t>
+        </is>
+      </c>
+      <c r="C741" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D741" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E741" s="8" t="inlineStr"/>
+      <c r="F741" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G741" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H741" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yldcom/contract-business-analyst-trochtelborn-54657</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B742" s="6" t="inlineStr">
+        <is>
+          <t>Quantum-Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C742" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D742" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E742" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F742" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G742" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H742" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/quantum-systems-gmbh/senior-machine-learning-engineer-gilching-11379</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="8" t="inlineStr">
+        <is>
+          <t>Project Leader Data &amp; AI Solutions (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B743" s="8" t="inlineStr">
+        <is>
+          <t>Rewire</t>
+        </is>
+      </c>
+      <c r="C743" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D743" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E743" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F743" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G743" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H743" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rewire/remote-project-leader-data-ai-solutions-heidelberg-35123</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="6" t="inlineStr">
+        <is>
+          <t>Engagement Manager Data &amp; AI Solutions (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B744" s="6" t="inlineStr">
+        <is>
+          <t>Rewire</t>
+        </is>
+      </c>
+      <c r="C744" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D744" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E744" s="6" t="inlineStr"/>
+      <c r="F744" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G744" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H744" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rewire/remote-engagement-manager-data-ai-solutions-heidelberg-376974</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B745" s="8" t="inlineStr">
+        <is>
+          <t>Rewire</t>
+        </is>
+      </c>
+      <c r="C745" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D745" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E745" s="8" t="inlineStr">
+        <is>
+          <t>Excel、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F745" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G745" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H745" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rewire/data-scientist-heidelberg-132489</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data &amp; AI Solutions (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B746" s="6" t="inlineStr">
+        <is>
+          <t>Rewire</t>
+        </is>
+      </c>
+      <c r="C746" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D746" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E746" s="6" t="inlineStr"/>
+      <c r="F746" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G746" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H746" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rewire/remote-principal-data-ai-solutions-heidelberg-326332</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Data Platform Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B747" s="8" t="inlineStr">
+        <is>
+          <t>wetter.com GmbH</t>
+        </is>
+      </c>
+      <c r="C747" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D747" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E747" s="8" t="inlineStr">
+        <is>
+          <t>Python、Spark、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F747" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G747" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H747" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wettercom-gmbh/senior-data-platform-engineer-konstanz-65621</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="6" t="inlineStr">
+        <is>
+          <t>Senior/Principal Biostatistician Consultant remote (Infectious Disease)</t>
+        </is>
+      </c>
+      <c r="B748" s="6" t="inlineStr">
+        <is>
+          <t>ClinChoice</t>
+        </is>
+      </c>
+      <c r="C748" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D748" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E748" s="6" t="inlineStr">
+        <is>
+          <t>R、统计学</t>
+        </is>
+      </c>
+      <c r="F748" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G748" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H748" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149864-senior-principal-biostatistician-consultant-remote-infectious-disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI Research Scientist (Model-based RL)</t>
+        </is>
+      </c>
+      <c r="B749" s="8" t="inlineStr">
+        <is>
+          <t>Phaidra</t>
+        </is>
+      </c>
+      <c r="C749" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D749" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E749" s="8" t="inlineStr"/>
+      <c r="F749" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G749" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H749" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149862-senior-ai-research-scientist-model-based-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="6" t="inlineStr">
+        <is>
+          <t>Product Growth Analytics Lead - Token Factory</t>
+        </is>
+      </c>
+      <c r="B750" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C750" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D750" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E750" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F750" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G750" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H750" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/149856-product-growth-analytics-lead-token-factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="8" t="inlineStr">
+        <is>
+          <t>Admin and data analyst Assistant (ZM0625)</t>
+        </is>
+      </c>
+      <c r="B751" s="8" t="inlineStr">
+        <is>
+          <t>Virtual Talent Latam</t>
+        </is>
+      </c>
+      <c r="C751" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D751" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E751" s="8" t="inlineStr">
+        <is>
+          <t>Excel、统计学</t>
+        </is>
+      </c>
+      <c r="F751" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G751" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H751" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/virtual-talent-latam/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager L6, Data Platform - Analytics Experience</t>
+        </is>
+      </c>
+      <c r="B752" s="6" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="C752" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D752" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E752" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F752" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G752" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H752" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/netflix/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="8" t="inlineStr">
+        <is>
+          <t>Senior Programming Analyst</t>
+        </is>
+      </c>
+      <c r="B753" s="8" t="inlineStr">
+        <is>
+          <t>Lifelancer</t>
+        </is>
+      </c>
+      <c r="C753" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D753" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E753" s="8" t="inlineStr"/>
+      <c r="F753" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G753" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H753" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lifelancer/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="6" t="inlineStr">
+        <is>
+          <t>Systems Analyst Lead</t>
+        </is>
+      </c>
+      <c r="B754" s="6" t="inlineStr">
+        <is>
+          <t>Cribl</t>
+        </is>
+      </c>
+      <c r="C754" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D754" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E754" s="6" t="inlineStr"/>
+      <c r="F754" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G754" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H754" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cribl/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="8" t="inlineStr">
+        <is>
+          <t>Senior Epic Lab Analyst</t>
+        </is>
+      </c>
+      <c r="B755" s="8" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C755" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D755" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E755" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F755" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G755" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H755" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/appex-innovation/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="6" t="inlineStr">
+        <is>
+          <t>考种软件长粒种子识别算法</t>
+        </is>
+      </c>
+      <c r="B756" s="6" t="inlineStr"/>
+      <c r="C756" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D756" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E756" s="6" t="inlineStr"/>
+      <c r="F756" s="6" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G756" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H756" s="6" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/W9fmD1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H704"/>
+  <autoFilter ref="A1:H756"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29753,19 +31861,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>204</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -29797,19 +31905,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>55</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
@@ -29844,7 +31952,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>22</v>
@@ -29853,7 +31961,7 @@
         <v>68</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -29951,7 +32059,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>4</v>
@@ -29960,10 +32068,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$784</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-30 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-30 23:30 UTC</t>
+          <t>数据日期 2026-07-31 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-31 23:28 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>755</v>
+        <v>783</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.440251572327044</v>
+        <v>0.4685314685314685</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4276729559748428</v>
+        <v>0.4405594405594406</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3018867924528302</v>
+        <v>0.3286713286713286</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2893081761006289</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2767295597484277</v>
+        <v>0.3286713286713286</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1761006289308176</v>
+        <v>0.2027972027972028</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.2075471698113208</v>
+        <v>0.1888111888111888</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1069182389937107</v>
+        <v>0.08391608391608392</v>
       </c>
     </row>
     <row r="15">
@@ -809,20 +809,20 @@
         <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1446540880503145</v>
+        <v>0.1608391608391608</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.1258741258741259</v>
       </c>
     </row>
     <row r="17">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1069182389937107</v>
+        <v>0.1118881118881119</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1118881118881119</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0880503144654088</v>
+        <v>0.1118881118881119</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08176100628930817</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H756"/>
+  <dimension ref="A1:H784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -31799,8 +31799,1164 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B757" s="8" t="inlineStr">
+        <is>
+          <t>Sparksoft Corporation</t>
+        </is>
+      </c>
+      <c r="C757" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D757" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E757" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI、R、机器学习</t>
+        </is>
+      </c>
+      <c r="F757" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G757" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H757" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-analyst-sparksoft-corporation-1135698</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="6" t="inlineStr">
+        <is>
+          <t>AI Trainer Freelance Data Annotator</t>
+        </is>
+      </c>
+      <c r="B758" s="6" t="inlineStr">
+        <is>
+          <t>Mindrift - Data annotation</t>
+        </is>
+      </c>
+      <c r="C758" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D758" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E758" s="6" t="inlineStr"/>
+      <c r="F758" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G758" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H758" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-trainer-freelance-data-annotator-mindrift-data-annotation-1135680</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, AI Platform</t>
+        </is>
+      </c>
+      <c r="B759" s="8" t="inlineStr">
+        <is>
+          <t>smartlyio</t>
+        </is>
+      </c>
+      <c r="C759" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D759" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E759" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、GCP、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F759" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G759" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H759" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/smartlyio/senior-machine-learning-engineer-ai-platform-berlin-319677</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="6" t="inlineStr">
+        <is>
+          <t>Managing Director, Data &amp; AI - Pharma</t>
+        </is>
+      </c>
+      <c r="B760" s="6" t="inlineStr">
+        <is>
+          <t>Unit8</t>
+        </is>
+      </c>
+      <c r="C760" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D760" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E760" s="6" t="inlineStr"/>
+      <c r="F760" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G760" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H760" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/unit8/managing-director-data-ai-pharma-munich-193076</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="8" t="inlineStr">
+        <is>
+          <t>Managing Director, Data &amp; AI - Pharma</t>
+        </is>
+      </c>
+      <c r="B761" s="8" t="inlineStr">
+        <is>
+          <t>Unit8</t>
+        </is>
+      </c>
+      <c r="C761" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D761" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E761" s="8" t="inlineStr"/>
+      <c r="F761" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G761" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H761" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/unit8/managing-director-data-ai-pharma-frankfurt-am-main-44883</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B762" s="6" t="inlineStr">
+        <is>
+          <t>Remotewoman</t>
+        </is>
+      </c>
+      <c r="C762" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D762" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E762" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、GCP</t>
+        </is>
+      </c>
+      <c r="F762" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G762" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H762" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/remotewoman/remote-senior-analytics-engineer-88923</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B763" s="8" t="inlineStr">
+        <is>
+          <t>Agentur Philipp GmbH</t>
+        </is>
+      </c>
+      <c r="C763" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D763" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E763" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F763" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G763" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H763" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agentur-philipp-gmbh/machine-learning-engineer-dingolfing-478273</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B764" s="6" t="inlineStr">
+        <is>
+          <t>Agentur Philipp GmbH</t>
+        </is>
+      </c>
+      <c r="C764" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D764" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E764" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、ETL、pandas</t>
+        </is>
+      </c>
+      <c r="F764" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G764" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H764" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agentur-philipp-gmbh/data-scientist-dingolfing-413488</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst - Supply</t>
+        </is>
+      </c>
+      <c r="B765" s="8" t="inlineStr">
+        <is>
+          <t>prolific</t>
+        </is>
+      </c>
+      <c r="C765" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D765" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E765" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Looker、A/B测试、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F765" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G765" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H765" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/prolific/data-analyst-supply-139841</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B766" s="6" t="inlineStr">
+        <is>
+          <t>Remotewoman</t>
+        </is>
+      </c>
+      <c r="C766" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D766" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E766" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、GCP</t>
+        </is>
+      </c>
+      <c r="F766" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G766" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H766" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/remotewoman/remote-senior-analytics-engineer-193086</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="8" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor in Data Science Computer - Science (Immediate Appointment)</t>
+        </is>
+      </c>
+      <c r="B767" s="8" t="inlineStr">
+        <is>
+          <t>Schiller International University</t>
+        </is>
+      </c>
+      <c r="C767" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D767" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E767" s="8" t="inlineStr">
+        <is>
+          <t>Python、Excel、R、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F767" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G767" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H767" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/schiller-international-university/adjunct-instructor-in-data-science-computer-science-immediate-appointment-heidelberg-416576</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="6" t="inlineStr">
+        <is>
+          <t>Senior/Staff Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B768" s="6" t="inlineStr">
+        <is>
+          <t>Vestiairecollective</t>
+        </is>
+      </c>
+      <c r="C768" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D768" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E768" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F768" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G768" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H768" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vestiairecollective/senior-staff-machine-learning-engineer-berlin-459797</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B769" s="8" t="inlineStr">
+        <is>
+          <t>1KOMMA5˚</t>
+        </is>
+      </c>
+      <c r="C769" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D769" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E769" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F769" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G769" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H769" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/1komma50/senior-analytics-engineer-berlin-255697</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B770" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C770" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D770" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E770" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F770" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G770" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H770" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-scientist-munchen-342406</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B771" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C771" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D771" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E771" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F771" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G771" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H771" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/senior-data-scientist-berlin-442899</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Modeler (Data Vault)</t>
+        </is>
+      </c>
+      <c r="B772" s="6" t="inlineStr">
+        <is>
+          <t>Visium</t>
+        </is>
+      </c>
+      <c r="C772" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D772" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E772" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F772" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G772" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H772" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/visium/senior-data-modeler-data-vault-berlin-131375</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Modeler (Data Vault)</t>
+        </is>
+      </c>
+      <c r="B773" s="8" t="inlineStr">
+        <is>
+          <t>Visium</t>
+        </is>
+      </c>
+      <c r="C773" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D773" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E773" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F773" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G773" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H773" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/visium/senior-data-modeler-data-vault-munich-187539</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="6" t="inlineStr">
+        <is>
+          <t>Senior Sales Engineer - Data &amp; AI Security</t>
+        </is>
+      </c>
+      <c r="B774" s="6" t="inlineStr">
+        <is>
+          <t>Veeamsoftware</t>
+        </is>
+      </c>
+      <c r="C774" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D774" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E774" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F774" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G774" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H774" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/veeamsoftware/remote-senior-sales-engineer-data-ai-security-201142</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="8" t="inlineStr">
+        <is>
+          <t>Director, Sales - Data &amp; AI Security</t>
+        </is>
+      </c>
+      <c r="B775" s="8" t="inlineStr">
+        <is>
+          <t>Veeamsoftware</t>
+        </is>
+      </c>
+      <c r="C775" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D775" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E775" s="8" t="inlineStr"/>
+      <c r="F775" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G775" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H775" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/veeamsoftware/director-sales-data-ai-security-munich-469367</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B776" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C776" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D776" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E776" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F776" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G776" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H776" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-185968</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B777" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C777" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D777" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E777" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F777" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G777" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H777" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-121841</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B778" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C778" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D778" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E778" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、机器学习</t>
+        </is>
+      </c>
+      <c r="F778" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G778" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H778" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/machine-learning-consultant-munich-285689</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="8" t="inlineStr">
+        <is>
+          <t>SAP Data Integration Consultant</t>
+        </is>
+      </c>
+      <c r="B779" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C779" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D779" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E779" s="8" t="inlineStr">
+        <is>
+          <t>SQL、ETL</t>
+        </is>
+      </c>
+      <c r="F779" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G779" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H779" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bright-vision-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="6" t="inlineStr">
+        <is>
+          <t>AI Automation &amp; Workflow Analyst</t>
+        </is>
+      </c>
+      <c r="B780" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C780" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D780" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E780" s="6" t="inlineStr"/>
+      <c r="F780" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G780" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H780" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/worldvia/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="8" t="inlineStr">
+        <is>
+          <t>Open-Source Machine Learning Engineer - US Remote</t>
+        </is>
+      </c>
+      <c r="B781" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C781" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D781" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E781" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F781" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G781" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H781" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hugging-face/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="6" t="inlineStr">
+        <is>
+          <t>Open-Source Machine Learning Engineer - EMEA Remote</t>
+        </is>
+      </c>
+      <c r="B782" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C782" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D782" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E782" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F782" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G782" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H782" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hugging-face/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="8" t="inlineStr">
+        <is>
+          <t>Salesforce Consultant CPQ Business analyst Role( work from home)</t>
+        </is>
+      </c>
+      <c r="B783" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C783" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D783" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E783" s="8" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="F783" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G783" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H783" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bayapps-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B784" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C784" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D784" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E784" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F784" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G784" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H784" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bayapps-inc/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H756"/>
+  <autoFilter ref="A1:H784"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31861,19 +33017,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>42</v>
-      </c>
       <c r="F2" s="6" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3">
@@ -31905,19 +33061,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
@@ -31936,10 +33092,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -31952,7 +33108,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>22</v>
@@ -31961,7 +33117,7 @@
         <v>68</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -32015,7 +33171,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -32027,7 +33183,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$784</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$797</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-07-31 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-07-31 23:28 UTC</t>
+          <t>数据日期 2026-08-01 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-01 23:27 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4685314685314685</v>
+        <v>0.4577464788732394</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4405594405594406</v>
+        <v>0.4507042253521127</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3286713286713286</v>
+        <v>0.3169014084507042</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2676056338028169</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3286713286713286</v>
+        <v>0.3028169014084507</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2027972027972028</v>
+        <v>0.2112676056338028</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1888111888111888</v>
+        <v>0.1830985915492958</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.08391608391608392</v>
+        <v>0.07042253521126761</v>
       </c>
     </row>
     <row r="15">
@@ -806,23 +806,23 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1608391608391608</v>
+        <v>0.1549295774647887</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1258741258741259</v>
+        <v>0.1267605633802817</v>
       </c>
     </row>
     <row r="17">
@@ -832,36 +832,36 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1118881118881119</v>
+        <v>0.1056338028169014</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1118881118881119</v>
+        <v>0.09859154929577464</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1118881118881119</v>
+        <v>0.09154929577464789</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08450704225352113</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H784"/>
+  <dimension ref="A1:H797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -32955,8 +32955,542 @@
         </is>
       </c>
     </row>
+    <row r="785">
+      <c r="A785" s="8" t="inlineStr">
+        <is>
+          <t>Accounts Assistant</t>
+        </is>
+      </c>
+      <c r="B785" s="8" t="inlineStr">
+        <is>
+          <t>CUBE Construction Group Ltd.</t>
+        </is>
+      </c>
+      <c r="C785" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D785" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E785" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F785" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G785" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H785" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-accounts-assistant-cube-construction-group-ltd-1135829</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="6" t="inlineStr">
+        <is>
+          <t>Teacher Assistant - Introduction to Algorithms and Data Structures (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B786" s="6" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C786" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D786" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E786" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F786" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G786" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H786" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/code/teacher-assistant-introduction-to-algorithms-and-data-structures-berlin-295716</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B787" s="8" t="inlineStr">
+        <is>
+          <t>Makersite GmbH</t>
+        </is>
+      </c>
+      <c r="C787" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D787" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E787" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F787" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G787" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H787" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/makersite-gmbh/remote-senior-data-scientist-berlin-113549</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B788" s="6" t="inlineStr">
+        <is>
+          <t>workato</t>
+        </is>
+      </c>
+      <c r="C788" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D788" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E788" s="6" t="inlineStr"/>
+      <c r="F788" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G788" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H788" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/workato/senior-data-scientist-berlin-425579</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist (Experiences)</t>
+        </is>
+      </c>
+      <c r="B789" s="8" t="inlineStr">
+        <is>
+          <t>tripadvisor</t>
+        </is>
+      </c>
+      <c r="C789" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D789" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E789" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F789" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G789" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H789" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tripadvisor/senior-machine-learning-scientist-experiences-london-61648</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B790" s="6" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C790" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D790" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E790" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F790" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G790" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H790" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-senior-analytics-engineer-393648</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer - Data Platform (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B791" s="8" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C791" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D791" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E791" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F791" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G791" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H791" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-junior-data-engineer-data-platform-127223</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Real time analytics</t>
+        </is>
+      </c>
+      <c r="B792" s="6" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C792" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D792" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E792" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F792" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G792" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H792" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/aircall/senior-data-engineer-real-time-analytics-london-office-303664</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="8" t="inlineStr">
+        <is>
+          <t>Security Analyst - Governance, Risk, and Compliance</t>
+        </is>
+      </c>
+      <c r="B793" s="8" t="inlineStr">
+        <is>
+          <t>LaunchDarkly</t>
+        </is>
+      </c>
+      <c r="C793" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D793" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E793" s="8" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F793" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G793" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H793" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/launchdarkly/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B794" s="6" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C794" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D794" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E794" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F794" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G794" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H794" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/motional/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="8" t="inlineStr">
+        <is>
+          <t>Epic Radiant/Cupid Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B795" s="8" t="inlineStr">
+        <is>
+          <t>Nordic Global</t>
+        </is>
+      </c>
+      <c r="C795" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D795" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E795" s="8" t="inlineStr"/>
+      <c r="F795" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G795" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H795" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nordic-global/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="6" t="inlineStr">
+        <is>
+          <t>BI &amp; Data Analytics Consultant (Tableau)</t>
+        </is>
+      </c>
+      <c r="B796" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C796" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D796" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E796" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Snowflake、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F796" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G796" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H796" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/keyrus/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Manager for Clinical Trials</t>
+        </is>
+      </c>
+      <c r="B797" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C797" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D797" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E797" s="8" t="inlineStr"/>
+      <c r="F797" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G797" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H797" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/psi-cro/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H784"/>
+  <autoFilter ref="A1:H797"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33020,16 +33554,16 @@
         <v>98</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -33061,10 +33595,10 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>15</v>
@@ -33073,7 +33607,7 @@
         <v>56</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -33114,10 +33648,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$797</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$835</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-01 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-01 23:27 UTC</t>
+          <t>数据日期 2026-08-02 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-02 23:27 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>796</v>
+        <v>834</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4577464788732394</v>
+        <v>0.4451612903225807</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4507042253521127</v>
+        <v>0.3225806451612903</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3169014084507042</v>
+        <v>0.3612903225806451</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.2838709677419355</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3028169014084507</v>
+        <v>0.2774193548387097</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,112 +769,112 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2112676056338028</v>
+        <v>0.2258064516129032</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.2645161290322581</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>0.1830985915492958</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>数据开发/工程</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" s="7" t="n">
-        <v>0.07042253521126761</v>
+        <v>0.167741935483871</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1549295774647887</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1267605633802817</v>
+        <v>0.1870967741935484</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1056338028169014</v>
+        <v>0.167741935483871</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09859154929577464</v>
+        <v>0.1225806451612903</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09154929577464789</v>
+        <v>0.09677419354838709</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.09032258064516129</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H797"/>
+  <dimension ref="A1:H835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -33489,8 +33489,1584 @@
         </is>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B798" s="6" t="inlineStr">
+        <is>
+          <t>GALVANY</t>
+        </is>
+      </c>
+      <c r="C798" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D798" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E798" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F798" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G798" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H798" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/galvany/senior-data-engineer-berlin-262882</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="8" t="inlineStr">
+        <is>
+          <t>Visiting Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B799" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C799" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D799" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E799" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F799" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G799" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H799" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/visiting-finance-analyst-berlin-81095</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="6" t="inlineStr">
+        <is>
+          <t>Founding ML Engineer – Demand Generation</t>
+        </is>
+      </c>
+      <c r="B800" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C800" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D800" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E800" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F800" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G800" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H800" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-ml-engineer-demand-generation-364258</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="8" t="inlineStr">
+        <is>
+          <t>Founding Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B801" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C801" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D801" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E801" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F801" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G801" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H801" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-machine-learning-engineer-282981</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="6" t="inlineStr">
+        <is>
+          <t>Staff Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B802" s="6" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C802" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D802" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E802" s="6" t="inlineStr"/>
+      <c r="F802" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G802" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H802" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/staff-analytics-engineer-cardiff-156117</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist, Borrowing</t>
+        </is>
+      </c>
+      <c r="B803" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C803" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D803" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E803" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F803" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G803" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H803" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/senior-machine-learning-scientist-borrowing-cardiff-481672</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="6" t="inlineStr">
+        <is>
+          <t>Performance Analytics and Insight Analyst</t>
+        </is>
+      </c>
+      <c r="B804" s="6" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C804" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D804" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E804" s="6" t="inlineStr">
+        <is>
+          <t>Looker、统计学</t>
+        </is>
+      </c>
+      <c r="F804" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G804" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H804" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/performance-analytics-and-insight-analyst-cardiff-201880</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Manager, Fincrime</t>
+        </is>
+      </c>
+      <c r="B805" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C805" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D805" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E805" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F805" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G805" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H805" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/machine-learning-manager-fincrime-cardiff-337105</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="6" t="inlineStr">
+        <is>
+          <t>Lead Machine Learning Scientist, Search</t>
+        </is>
+      </c>
+      <c r="B806" s="6" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C806" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D806" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E806" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F806" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G806" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H806" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/lead-machine-learning-scientist-search-cardiff-387080</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="8" t="inlineStr">
+        <is>
+          <t>Lead Machine Learning Scientist, FinCrime</t>
+        </is>
+      </c>
+      <c r="B807" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C807" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D807" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E807" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F807" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G807" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H807" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/lead-machine-learning-scientist-fincrime-cardiff-116493</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="6" t="inlineStr">
+        <is>
+          <t>Credit Model Validation Manager (Machine Learning &amp; NPV Models)</t>
+        </is>
+      </c>
+      <c r="B808" s="6" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C808" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D808" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E808" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F808" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G808" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H808" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/credit-model-validation-manager-machine-learning-npv-models-cardiff-482295</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="8" t="inlineStr">
+        <is>
+          <t>Data Accountant (12month FTC)</t>
+        </is>
+      </c>
+      <c r="B809" s="8" t="inlineStr">
+        <is>
+          <t>Inizio</t>
+        </is>
+      </c>
+      <c r="C809" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D809" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E809" s="8" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F809" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G809" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H809" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/inizio/data-accountant-12month-ftc-manchester-142425</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B810" s="6" t="inlineStr">
+        <is>
+          <t>Almedia</t>
+        </is>
+      </c>
+      <c r="C810" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D810" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E810" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F810" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G810" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H810" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/almedia/machine-learning-engineer-london-84747</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B811" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C811" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D811" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E811" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、统计学</t>
+        </is>
+      </c>
+      <c r="F811" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G811" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H811" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/business-analyst-hamburg-30820</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="6" t="inlineStr">
+        <is>
+          <t>Data Analytics Lead (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B812" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C812" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D812" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E812" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Looker、dbt、Airflow、机器学习</t>
+        </is>
+      </c>
+      <c r="F812" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G812" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H812" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/data-analytics-lead-hamburg-77208</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="8" t="inlineStr">
+        <is>
+          <t>Business Solutions Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B813" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C813" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D813" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E813" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、dbt、Airflow</t>
+        </is>
+      </c>
+      <c r="F813" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G813" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H813" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/business-solutions-analyst-hamburg-74125</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="6" t="inlineStr">
+        <is>
+          <t>Intern - Business Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B814" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C814" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D814" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E814" s="6" t="inlineStr"/>
+      <c r="F814" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G814" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H814" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/intern-business-analyst-hamburg-284640</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B815" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C815" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D815" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E815" s="8" t="inlineStr">
+        <is>
+          <t>Spark、Airflow、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F815" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G815" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H815" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-machine-learning-engineer-hamburg-350096</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="6" t="inlineStr">
+        <is>
+          <t>Data Science Director (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B816" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C816" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D816" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E816" s="6" t="inlineStr">
+        <is>
+          <t>Python、Spark、Airflow、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F816" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G816" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H816" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/data-science-director-hamburg-394915</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B817" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C817" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D817" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E817" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、A/B测试、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F817" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G817" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H817" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-data-scientist-hamburg-95795</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B818" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C818" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D818" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E818" s="6" t="inlineStr">
+        <is>
+          <t>Python、dbt、Airflow、AWS、A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F818" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G818" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H818" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-data-engineer-hamburg-78506</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Business Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B819" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C819" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D819" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E819" s="8" t="inlineStr">
+        <is>
+          <t>SQL、统计学</t>
+        </is>
+      </c>
+      <c r="F819" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G819" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H819" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-business-analyst-hamburg-8909</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B820" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C820" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D820" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E820" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F820" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G820" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H820" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-data-analyst-hamburg-13022</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="8" t="inlineStr">
+        <is>
+          <t>QA Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B821" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C821" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D821" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E821" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F821" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G821" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H821" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/qa-analyst-hamburg-267931</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="6" t="inlineStr">
+        <is>
+          <t>Junior Kreditanalyst*in (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B822" s="6" t="inlineStr">
+        <is>
+          <t>iwoca</t>
+        </is>
+      </c>
+      <c r="C822" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D822" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E822" s="6" t="inlineStr"/>
+      <c r="F822" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G822" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H822" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/iwoca/junior-kreditanalystin-frankfurt-259227</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="8" t="inlineStr">
+        <is>
+          <t>Credit Analyst</t>
+        </is>
+      </c>
+      <c r="B823" s="8" t="inlineStr">
+        <is>
+          <t>iwoca</t>
+        </is>
+      </c>
+      <c r="C823" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D823" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E823" s="8" t="inlineStr"/>
+      <c r="F823" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G823" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H823" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/iwoca/credit-analyst-frankfurt-210976</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer - 3D Geometry for CAD (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B824" s="6" t="inlineStr">
+        <is>
+          <t>Kyrall</t>
+        </is>
+      </c>
+      <c r="C824" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D824" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E824" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F824" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G824" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H824" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kyrall/ml-engineer-3d-geometry-for-cad-munich-344289</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B825" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C825" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D825" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E825" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F825" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G825" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H825" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/senior-data-scientist-munich-173808</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B826" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C826" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D826" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E826" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F826" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G826" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H826" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/data-scientist-munich-35805</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="8" t="inlineStr">
+        <is>
+          <t>DevOps/ML Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B827" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C827" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D827" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E827" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、GCP、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F827" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G827" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H827" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/devops-ml-engineer-munich-133885</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Machine Learning (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B828" s="6" t="inlineStr">
+        <is>
+          <t>Voize</t>
+        </is>
+      </c>
+      <c r="C828" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D828" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E828" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F828" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G828" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H828" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/voize/senior-product-manager-machine-learning-berlin-338603</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="8" t="inlineStr">
+        <is>
+          <t>Senior Staff Data Scientist - Consumer Relevance</t>
+        </is>
+      </c>
+      <c r="B829" s="8" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C829" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D829" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E829" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F829" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G829" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H829" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/reddit/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="6" t="inlineStr">
+        <is>
+          <t>Technical Sales Specialist (BioAnalytics)</t>
+        </is>
+      </c>
+      <c r="B830" s="6" t="inlineStr">
+        <is>
+          <t>Sartorius</t>
+        </is>
+      </c>
+      <c r="C830" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D830" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E830" s="6" t="inlineStr"/>
+      <c r="F830" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G830" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H830" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sartorius/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B831" s="8" t="inlineStr">
+        <is>
+          <t>Highmark Health</t>
+        </is>
+      </c>
+      <c r="C831" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D831" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E831" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F831" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G831" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H831" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/highmark-health/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="6" t="inlineStr">
+        <is>
+          <t>Senior Staff Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B832" s="6" t="inlineStr">
+        <is>
+          <t>Zocdoc</t>
+        </is>
+      </c>
+      <c r="C832" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D832" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E832" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F832" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G832" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H832" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zocdoc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, Latin America</t>
+        </is>
+      </c>
+      <c r="B833" s="8" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C833" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D833" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E833" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、AWS</t>
+        </is>
+      </c>
+      <c r="F833" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G833" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H833" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bluelight-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer - Latin America, Remote</t>
+        </is>
+      </c>
+      <c r="B834" s="6" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C834" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D834" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E834" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、AWS</t>
+        </is>
+      </c>
+      <c r="F834" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G834" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H834" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bluelight-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="8" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Revenue Operations (ROPS)</t>
+        </is>
+      </c>
+      <c r="B835" s="8" t="inlineStr">
+        <is>
+          <t>DaVita Kidney Care</t>
+        </is>
+      </c>
+      <c r="C835" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D835" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E835" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau</t>
+        </is>
+      </c>
+      <c r="F835" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G835" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="H835" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/davita-kidney-care/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H797"/>
+  <autoFilter ref="A1:H835"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33551,19 +35127,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -33595,19 +35171,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>56</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
@@ -33645,13 +35221,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>70</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$835</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$889</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-02 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-02 23:27 UTC</t>
+          <t>数据日期 2026-08-03 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-03 23:33 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>834</v>
+        <v>888</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4451612903225807</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3933333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3612903225806451</v>
+        <v>0.2933333333333333</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2838709677419355</v>
+        <v>0.3066666666666666</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2774193548387097</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1933333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.2645161290322581</v>
+        <v>0.1866666666666667</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.167741935483871</v>
+        <v>0.1066666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1870967741935484</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.167741935483871</v>
+        <v>0.1266666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1225806451612903</v>
+        <v>0.1133333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09032258064516129</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H835"/>
+  <dimension ref="A1:H889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -35065,8 +35065,2252 @@
         </is>
       </c>
     </row>
+    <row r="836">
+      <c r="A836" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Administrator</t>
+        </is>
+      </c>
+      <c r="B836" s="6" t="inlineStr">
+        <is>
+          <t>PulseMediaNL</t>
+        </is>
+      </c>
+      <c r="C836" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D836" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E836" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F836" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G836" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H836" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-administrator-pulsemedianl-1135903</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="8" t="inlineStr">
+        <is>
+          <t>Director of Data (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B837" s="8" t="inlineStr">
+        <is>
+          <t>Moonfare</t>
+        </is>
+      </c>
+      <c r="C837" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D837" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E837" s="8" t="inlineStr"/>
+      <c r="F837" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G837" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H837" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/moonfare/director-of-data-berlin-456700</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B838" s="6" t="inlineStr">
+        <is>
+          <t>Moonfare</t>
+        </is>
+      </c>
+      <c r="C838" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D838" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E838" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F838" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G838" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H838" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/moonfare/data-engineer-berlin-38343</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="8" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer - Data Lakes</t>
+        </is>
+      </c>
+      <c r="B839" s="8" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C839" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D839" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E839" s="8" t="inlineStr">
+        <is>
+          <t>dbt、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F839" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G839" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H839" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/fivetran/remote-principal-software-engineer-data-lakes-398416</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer (all genders) - Data Lake Platform</t>
+        </is>
+      </c>
+      <c r="B840" s="6" t="inlineStr">
+        <is>
+          <t>moia</t>
+        </is>
+      </c>
+      <c r="C840" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D840" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E840" s="6" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F840" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G840" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H840" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/moia/senior-data-platform-engineer-all-genders-data-lake-platform-berlin-hamburg-58977</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Commercial &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B841" s="8" t="inlineStr">
+        <is>
+          <t>Angi</t>
+        </is>
+      </c>
+      <c r="C841" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D841" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E841" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F841" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G841" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H841" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angi/senior-analyst-commercial-analytics-berlin-297623</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="6" t="inlineStr">
+        <is>
+          <t>Lead Analyst, Customer Service Analytics</t>
+        </is>
+      </c>
+      <c r="B842" s="6" t="inlineStr">
+        <is>
+          <t>Angi</t>
+        </is>
+      </c>
+      <c r="C842" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D842" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E842" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F842" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G842" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H842" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angi/lead-analyst-customer-service-analytics-berlin-30011</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/f/d) Data &amp; AI Strategy</t>
+        </is>
+      </c>
+      <c r="B843" s="8" t="inlineStr">
+        <is>
+          <t>Artefact</t>
+        </is>
+      </c>
+      <c r="C843" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D843" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E843" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F843" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G843" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H843" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/artefact/senior-consultant-data-ai-strategy-berlin-berlin-munchen-bavaria-204514</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="6" t="inlineStr">
+        <is>
+          <t>Consulting Manager (m/f/d) Data &amp; AI Strategy</t>
+        </is>
+      </c>
+      <c r="B844" s="6" t="inlineStr">
+        <is>
+          <t>Artefact</t>
+        </is>
+      </c>
+      <c r="C844" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D844" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E844" s="6" t="inlineStr"/>
+      <c r="F844" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G844" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H844" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/artefact/consulting-manager-data-ai-strategy-berlin-berlin-munchen-bavaria-26684</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="8" t="inlineStr">
+        <is>
+          <t>Working Student – Italian-speaking Data Researcher</t>
+        </is>
+      </c>
+      <c r="B845" s="8" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C845" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D845" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E845" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F845" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G845" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H845" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/working-student-italian-speaking-data-researcher-hamburg-12833</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="6" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B846" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C846" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D846" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E846" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F846" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G846" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H846" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/data-analytics-engineer-hamburg-or-berlin-317017</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B847" s="8" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C847" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D847" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E847" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、BigQuery</t>
+        </is>
+      </c>
+      <c r="F847" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G847" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H847" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/analytics-engineer-hamburg-or-berlin-1744</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="6" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Data &amp; Content Delivery (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B848" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C848" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D848" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E848" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F848" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G848" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H848" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/engineering-manager-data-content-delivery-hamburg-or-berlin-31477</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="8" t="inlineStr">
+        <is>
+          <t>Consultant - Healthcare Data (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B849" s="8" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C849" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D849" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E849" s="8" t="inlineStr"/>
+      <c r="F849" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G849" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H849" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/consultant-healthcare-data-hamburg-or-berlin-114529</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="6" t="inlineStr">
+        <is>
+          <t>Team Lead Data &amp; AI Engineering (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B850" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C850" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D850" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E850" s="6" t="inlineStr">
+        <is>
+          <t>Python、Airflow、AWS、A/B测试</t>
+        </is>
+      </c>
+      <c r="F850" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G850" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H850" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/team-lead-data-ai-engineering-hamburg-or-berlin-351332</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering Lead - Data &amp; AI Tools (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B851" s="8" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C851" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D851" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E851" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F851" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G851" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H851" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/data-engineering-lead-data-ai-tools-hamburg-or-berlin-302188</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B852" s="6" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C852" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D852" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E852" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F852" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G852" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H852" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/constructor/senior-data-scientist-munich-140193</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="8" t="inlineStr">
+        <is>
+          <t>Customer Marketing &amp; Analyst Relations</t>
+        </is>
+      </c>
+      <c r="B853" s="8" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C853" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D853" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E853" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F853" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G853" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H853" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/constructor/customer-marketing-analyst-relations-munich-259907</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Merchant Intelligence and Analytics</t>
+        </is>
+      </c>
+      <c r="B854" s="6" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C854" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D854" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E854" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F854" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G854" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H854" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/constructor/senior-product-manager-merchant-intelligence-and-analytics-munich-46067</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B855" s="8" t="inlineStr">
+        <is>
+          <t>Lupa Pets</t>
+        </is>
+      </c>
+      <c r="C855" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D855" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E855" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker、dbt</t>
+        </is>
+      </c>
+      <c r="F855" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G855" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H855" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lupa-pets/analytics-engineer-london-368474</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B856" s="6" t="inlineStr">
+        <is>
+          <t>Lupa Pets</t>
+        </is>
+      </c>
+      <c r="C856" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D856" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E856" s="6" t="inlineStr">
+        <is>
+          <t>Python、Spark、dbt、Airflow、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F856" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G856" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H856" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lupa-pets/data-engineer-london-46651</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="8" t="inlineStr">
+        <is>
+          <t>Scientist II / Senior ML Scientist, Data-Efficient Learning for Drug Discovery</t>
+        </is>
+      </c>
+      <c r="B857" s="8" t="inlineStr">
+        <is>
+          <t>Lilasciences</t>
+        </is>
+      </c>
+      <c r="C857" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D857" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E857" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F857" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G857" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H857" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lilasciences/scientist-ii-senior-ml-scientist-data-efficient-learning-for-drug-discovery-cambridge-ma-usa-london-san-francisco-ca-usa-266070</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="6" t="inlineStr">
+        <is>
+          <t>Scientist II / Senior ML Scientist, Cofolding and Structure-Aware ML</t>
+        </is>
+      </c>
+      <c r="B858" s="6" t="inlineStr">
+        <is>
+          <t>Lilasciences</t>
+        </is>
+      </c>
+      <c r="C858" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D858" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E858" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F858" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G858" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H858" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lilasciences/scientist-ii-senior-ml-scientist-cofolding-and-structure-aware-ml-cambridge-ma-usa-london-san-francisco-ca-usa-242394</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="8" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B859" s="8" t="inlineStr">
+        <is>
+          <t>sonyinteractiveentertainmentglobal</t>
+        </is>
+      </c>
+      <c r="C859" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D859" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E859" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F859" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G859" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H859" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sonyinteractiveentertainmentglobal/staff-machine-learning-engineer-london-365835</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer, Agents &amp; Reasoning</t>
+        </is>
+      </c>
+      <c r="B860" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C860" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D860" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E860" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F860" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G860" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H860" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/ml-engineer-agents-reasoning-berlin-153674</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data &amp; AI (all genders)</t>
+        </is>
+      </c>
+      <c r="B861" s="8" t="inlineStr">
+        <is>
+          <t>Cmbluenergyag</t>
+        </is>
+      </c>
+      <c r="C861" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D861" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E861" s="8" t="inlineStr"/>
+      <c r="F861" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G861" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H861" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cmbluenergyag/senior-software-engineer-data-ai-all-genders-alzenau-bavaria-3311</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, ADAS</t>
+        </is>
+      </c>
+      <c r="B862" s="6" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C862" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D862" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E862" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F862" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G862" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H862" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wayve/machine-learning-engineer-adas-125792</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B863" s="8" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C863" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D863" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E863" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F863" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G863" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H863" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wayve/machine-learning-engineer-82085</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B864" s="6" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C864" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D864" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E864" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F864" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G864" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H864" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wayve/data-engineer-352712</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="8" t="inlineStr">
+        <is>
+          <t>Technical Lead Software &amp; Data Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B865" s="8" t="inlineStr">
+        <is>
+          <t>hubside - Die Recruitingwerkstatt</t>
+        </is>
+      </c>
+      <c r="C865" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D865" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E865" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F865" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G865" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H865" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hubside-die-recruitingwerkstatt/technical-lead-software-data-solutions-munich-269636</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B866" s="6" t="inlineStr">
+        <is>
+          <t>hubside - Die Recruitingwerkstatt</t>
+        </is>
+      </c>
+      <c r="C866" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D866" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E866" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F866" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G866" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H866" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hubside-die-recruitingwerkstatt/data-platform-engineer-landsberg-am-lech-125930</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Buyer</t>
+        </is>
+      </c>
+      <c r="B867" s="8" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C867" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D867" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E867" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F867" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G867" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H867" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/senior-data-scientist-buyer-berlin-421572</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Marketing DSA</t>
+        </is>
+      </c>
+      <c r="B868" s="6" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C868" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D868" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E868" s="6" t="inlineStr">
+        <is>
+          <t>Python、dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F868" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G868" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H868" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/senior-analytics-engineer-marketing-dsa-berlin-325386</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="8" t="inlineStr">
+        <is>
+          <t>Manager of Data Science &amp; Analytics, Marketing</t>
+        </is>
+      </c>
+      <c r="B869" s="8" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C869" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D869" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E869" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F869" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G869" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H869" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/manager-of-data-science-analytics-marketing-berlin-91144</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Scientist, Revenue - Ads, Revenue</t>
+        </is>
+      </c>
+      <c r="B870" s="6" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C870" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D870" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E870" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F870" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G870" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H870" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/lead-data-scientist-revenue-ads-revenue-berlin-285714</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Marketing Modelling Intelligence</t>
+        </is>
+      </c>
+      <c r="B871" s="8" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C871" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D871" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E871" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F871" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G871" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H871" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/data-scientist-marketing-modelling-intelligence-berlin-68226</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, Marketing DSA</t>
+        </is>
+      </c>
+      <c r="B872" s="6" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C872" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D872" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E872" s="6" t="inlineStr">
+        <is>
+          <t>Python、dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F872" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G872" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H872" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/analytics-engineer-marketing-dsa-berlin-216916</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Python Software Engineer</t>
+        </is>
+      </c>
+      <c r="B873" s="8" t="inlineStr">
+        <is>
+          <t>Ceartas</t>
+        </is>
+      </c>
+      <c r="C873" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D873" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E873" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F873" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G873" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H873" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ceartas/senior-data-python-software-engineer-berlin-87350</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="6" t="inlineStr">
+        <is>
+          <t>Workforce Scheduling Analyst II</t>
+        </is>
+      </c>
+      <c r="B874" s="6" t="inlineStr">
+        <is>
+          <t>Centene Corporation</t>
+        </is>
+      </c>
+      <c r="C874" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D874" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E874" s="6" t="inlineStr"/>
+      <c r="F874" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G874" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H874" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150167-workforce-scheduling-analyst-ii</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="8" t="inlineStr">
+        <is>
+          <t>Director, Business Analytics, Customer Insights &amp; Performance (Remote, United St</t>
+        </is>
+      </c>
+      <c r="B875" s="8" t="inlineStr">
+        <is>
+          <t>Sonova Group</t>
+        </is>
+      </c>
+      <c r="C875" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D875" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E875" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Power BI、统计学</t>
+        </is>
+      </c>
+      <c r="F875" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G875" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H875" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sonova-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="6" t="inlineStr">
+        <is>
+          <t>Capital Markets Research Analyst</t>
+        </is>
+      </c>
+      <c r="B876" s="6" t="inlineStr">
+        <is>
+          <t>Financial Technology Partners</t>
+        </is>
+      </c>
+      <c r="C876" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D876" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E876" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F876" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G876" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H876" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/financial-technology-partners/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="8" t="inlineStr">
+        <is>
+          <t>Accounts Receivable Process Analyst</t>
+        </is>
+      </c>
+      <c r="B877" s="8" t="inlineStr">
+        <is>
+          <t>BrightSpring Health Services</t>
+        </is>
+      </c>
+      <c r="C877" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D877" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E877" s="8" t="inlineStr">
+        <is>
+          <t>Excel、R</t>
+        </is>
+      </c>
+      <c r="F877" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G877" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H877" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/brightspring-health-services/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="6" t="inlineStr">
+        <is>
+          <t>Business Process Analyst</t>
+        </is>
+      </c>
+      <c r="B878" s="6" t="inlineStr">
+        <is>
+          <t>YoungWilliams</t>
+        </is>
+      </c>
+      <c r="C878" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D878" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E878" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F878" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G878" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H878" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/youngwilliams/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer II, AI Native</t>
+        </is>
+      </c>
+      <c r="B879" s="8" t="inlineStr">
+        <is>
+          <t>Life360</t>
+        </is>
+      </c>
+      <c r="C879" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D879" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E879" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F879" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G879" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H879" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/life360/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="6" t="inlineStr">
+        <is>
+          <t>Manager, eCommerce Analytics</t>
+        </is>
+      </c>
+      <c r="B880" s="6" t="inlineStr">
+        <is>
+          <t>Otter Products</t>
+        </is>
+      </c>
+      <c r="C880" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D880" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E880" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F880" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G880" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H880" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/otter-products/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="8" t="inlineStr">
+        <is>
+          <t>Data Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B881" s="8" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C881" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D881" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E881" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI、统计学</t>
+        </is>
+      </c>
+      <c r="F881" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G881" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H881" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/leidos/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="6" t="inlineStr">
+        <is>
+          <t>Senior Sales Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B882" s="6" t="inlineStr">
+        <is>
+          <t>SPS Commerce</t>
+        </is>
+      </c>
+      <c r="C882" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D882" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E882" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Power BI、R</t>
+        </is>
+      </c>
+      <c r="F882" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G882" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H882" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sps-commerce/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="8" t="inlineStr">
+        <is>
+          <t>GROUP PRODUCT MANAGER, DATA PRODUCTS &amp; ANALYTICS - REMOTE (#Wayne, PA, US, 19087</t>
+        </is>
+      </c>
+      <c r="B883" s="8" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="C883" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D883" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E883" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F883" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G883" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H883" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/te-connectivity/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="6" t="inlineStr">
+        <is>
+          <t>Fraud Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="B884" s="6" t="inlineStr">
+        <is>
+          <t>Realpage</t>
+        </is>
+      </c>
+      <c r="C884" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D884" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E884" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F884" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G884" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H884" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/realpage/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="8" t="inlineStr">
+        <is>
+          <t>Senior Snowflake Data Engineer - Talent Pipeline</t>
+        </is>
+      </c>
+      <c r="B885" s="8" t="inlineStr">
+        <is>
+          <t>blueworks AG</t>
+        </is>
+      </c>
+      <c r="C885" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D885" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E885" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F885" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G885" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H885" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/blueworks-ag/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="6" t="inlineStr">
+        <is>
+          <t>Associate Director, Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="B886" s="6" t="inlineStr">
+        <is>
+          <t>ConnectiveRx</t>
+        </is>
+      </c>
+      <c r="C886" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D886" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E886" s="6" t="inlineStr">
+        <is>
+          <t>SQL、统计学</t>
+        </is>
+      </c>
+      <c r="F886" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G886" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H886" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/connectiverx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer - Clearance Required</t>
+        </is>
+      </c>
+      <c r="B887" s="8" t="inlineStr">
+        <is>
+          <t>Logistics Management Institute</t>
+        </is>
+      </c>
+      <c r="C887" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D887" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E887" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F887" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G887" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H887" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/logistics-management-institute/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="6" t="inlineStr">
+        <is>
+          <t>Sr Product Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="B888" s="6" t="inlineStr">
+        <is>
+          <t>HealthEquity</t>
+        </is>
+      </c>
+      <c r="C888" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D888" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E888" s="6" t="inlineStr"/>
+      <c r="F888" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G888" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H888" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/healthequity/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="8" t="inlineStr">
+        <is>
+          <t>Underwriting Analyst II</t>
+        </is>
+      </c>
+      <c r="B889" s="8" t="inlineStr">
+        <is>
+          <t>Maverick Payments</t>
+        </is>
+      </c>
+      <c r="C889" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D889" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E889" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F889" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G889" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H889" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/maverick-payments/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H835"/>
+  <autoFilter ref="A1:H889"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35127,19 +37371,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>303</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
@@ -35171,19 +37415,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>56</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5">
@@ -35224,10 +37468,10 @@
         <v>24</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -35281,7 +37525,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -35293,7 +37537,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$889</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$933</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-03 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-03 23:33 UTC</t>
+          <t>数据日期 2026-08-04 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-04 23:31 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>888</v>
+        <v>932</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4066666666666667</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>59</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3933333333333333</v>
+        <v>0.4214285714285714</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.3214285714285715</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1933333333333333</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.1642857142857143</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.04285714285714286</v>
       </c>
     </row>
     <row r="15">
@@ -806,23 +806,23 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1642857142857143</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.14</v>
+        <v>0.1571428571428571</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1266666666666667</v>
+        <v>0.1285714285714286</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1133333333333333</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09285714285714286</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08</v>
+        <v>0.09285714285714286</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H889"/>
+  <dimension ref="A1:H933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -37309,8 +37309,1828 @@
         </is>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry &amp;amp; Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="B890" s="6" t="inlineStr">
+        <is>
+          <t>Re Lytics Hires</t>
+        </is>
+      </c>
+      <c r="C890" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D890" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E890" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F890" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G890" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H890" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-amp-administrative-assistant-re-lytics-hires-1136107</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="8" t="inlineStr">
+        <is>
+          <t>Staff Engineer - Data Platform (m|w|d)</t>
+        </is>
+      </c>
+      <c r="B891" s="8" t="inlineStr">
+        <is>
+          <t>idealo internet GmbH</t>
+        </is>
+      </c>
+      <c r="C891" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D891" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E891" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、AWS、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F891" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G891" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H891" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/idealo-internet-gmbh/staff-engineer-data-platform-mwd-berlin-425986</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst FlixTrain Operations (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B892" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C892" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D892" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E892" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Snowflake</t>
+        </is>
+      </c>
+      <c r="F892" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G892" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H892" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/data-analyst-flixtrain-operations-berlin-338466</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Data &amp; Automation Manager - Energy Operations (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B893" s="8" t="inlineStr">
+        <is>
+          <t>Vrey</t>
+        </is>
+      </c>
+      <c r="C893" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D893" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E893" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F893" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G893" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H893" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vrey/junior-data-automation-manager-energy-operations-berlin-307216</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="6" t="inlineStr">
+        <is>
+          <t>Senior CRM Automation &amp; Data Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="B894" s="6" t="inlineStr">
+        <is>
+          <t>Sunday Natural</t>
+        </is>
+      </c>
+      <c r="C894" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D894" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E894" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Looker、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F894" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G894" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H894" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sunday-natural/senior-crm-automation-data-manager-all-genders-berlin-346665</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="8" t="inlineStr">
+        <is>
+          <t>Marketing Data Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B895" s="8" t="inlineStr">
+        <is>
+          <t>Sunday Natural</t>
+        </is>
+      </c>
+      <c r="C895" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D895" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E895" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、dbt、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F895" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G895" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H895" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sunday-natural/marketing-data-analyst-all-genders-berlin-66503</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="6" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B896" s="6" t="inlineStr">
+        <is>
+          <t>Sunday Natural</t>
+        </is>
+      </c>
+      <c r="C896" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D896" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E896" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、AWS、GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F896" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G896" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H896" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sunday-natural/ai-ml-engineer-all-genders-berlin-23246</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="8" t="inlineStr">
+        <is>
+          <t>ML Engineer, Agents &amp; Reasoning</t>
+        </is>
+      </c>
+      <c r="B897" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C897" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D897" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E897" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F897" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G897" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H897" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/ml-engineer-agents-reasoning-berlin-12089</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="6" t="inlineStr">
+        <is>
+          <t>Visiting Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B898" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C898" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D898" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E898" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F898" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G898" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H898" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/visiting-finance-analyst-berlin-228908</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B899" s="8" t="inlineStr">
+        <is>
+          <t>Primer.io</t>
+        </is>
+      </c>
+      <c r="C899" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D899" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E899" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F899" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G899" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H899" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/primerio/data-engineer-iii-united-kingdom-67090</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="6" t="inlineStr">
+        <is>
+          <t>Senior Digital Insight Analyst</t>
+        </is>
+      </c>
+      <c r="B900" s="6" t="inlineStr">
+        <is>
+          <t>Vmlenterprisesolutions</t>
+        </is>
+      </c>
+      <c r="C900" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D900" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E900" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、AWS、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F900" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G900" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H900" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/vmlenterprisesolutions/senior-digital-insight-analyst-london-manchester-433221</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="8" t="inlineStr">
+        <is>
+          <t>Python Developer - Data &amp; Analytics Team - Options Market Making</t>
+        </is>
+      </c>
+      <c r="B901" s="8" t="inlineStr">
+        <is>
+          <t>Mavensecuritiesholdingltd</t>
+        </is>
+      </c>
+      <c r="C901" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D901" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E901" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F901" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G901" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H901" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mavensecuritiesholdingltd/python-developer-data-analytics-team-options-market-making-london-360202</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="6" t="inlineStr">
+        <is>
+          <t>Market Data Manager</t>
+        </is>
+      </c>
+      <c r="B902" s="6" t="inlineStr">
+        <is>
+          <t>Mavensecuritiesholdingltd</t>
+        </is>
+      </c>
+      <c r="C902" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D902" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E902" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F902" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G902" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H902" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mavensecuritiesholdingltd/market-data-manager-london-484385</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="8" t="inlineStr">
+        <is>
+          <t>Head of Market Data</t>
+        </is>
+      </c>
+      <c r="B903" s="8" t="inlineStr">
+        <is>
+          <t>Mavensecuritiesholdingltd</t>
+        </is>
+      </c>
+      <c r="C903" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D903" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E903" s="8" t="inlineStr"/>
+      <c r="F903" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G903" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H903" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mavensecuritiesholdingltd/head-of-market-data-london-193201</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="6" t="inlineStr">
+        <is>
+          <t>Founding ML Engineer – Demand Generation</t>
+        </is>
+      </c>
+      <c r="B904" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C904" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D904" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E904" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F904" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G904" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H904" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-ml-engineer-demand-generation-38627</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="8" t="inlineStr">
+        <is>
+          <t>Founding Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B905" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C905" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D905" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E905" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F905" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G905" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H905" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-machine-learning-engineer-364585</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="6" t="inlineStr">
+        <is>
+          <t>Studentische Hilfskraft, Team Transparent Social Analytics (SHK-CSS-38)</t>
+        </is>
+      </c>
+      <c r="B906" s="6" t="inlineStr">
+        <is>
+          <t>GESIS – Leibniz-Institut für Sozialwissenschaften</t>
+        </is>
+      </c>
+      <c r="C906" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D906" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E906" s="6" t="inlineStr">
+        <is>
+          <t>Python、R</t>
+        </is>
+      </c>
+      <c r="F906" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G906" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H906" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gesis-leibniz-institut-fur-sozialwissenschaften/studentische-hilfskraft-team-transparent-social-analytics-shk-css-38-koln-251305</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="8" t="inlineStr">
+        <is>
+          <t>Erfahrene*r Business Analyst / Consultant bei Softwarefirma (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B907" s="8" t="inlineStr">
+        <is>
+          <t>Coduct Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C907" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D907" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E907" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F907" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G907" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H907" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/coduct-solutions-gmbh/erfahrener-business-analyst-consultant-bei-softwarefirma-cologne-284581</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="6" t="inlineStr">
+        <is>
+          <t>Erfahrene*r Business Analyst / Consultant bei Softwarefirma (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B908" s="6" t="inlineStr">
+        <is>
+          <t>Coduct Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C908" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D908" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E908" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F908" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G908" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H908" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/coduct-solutions-gmbh/erfahrener-business-analyst-consultant-bei-softwarefirma-berlin-328728</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="8" t="inlineStr">
+        <is>
+          <t>Principal Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B909" s="8" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C909" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D909" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E909" s="8" t="inlineStr"/>
+      <c r="F909" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G909" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H909" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/thoughtworks/principal-data-engineer-cologne-440133</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Architect / Strategist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B910" s="6" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C910" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D910" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E910" s="6" t="inlineStr"/>
+      <c r="F910" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G910" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H910" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/thoughtworks/principal-data-architect-strategist-cologne-205290</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="8" t="inlineStr">
+        <is>
+          <t>Head of Analytics and Data Science (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B911" s="8" t="inlineStr">
+        <is>
+          <t>Zenjob</t>
+        </is>
+      </c>
+      <c r="C911" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D911" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E911" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F911" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G911" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H911" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/zenjob/head-of-analytics-and-data-science-berlin-453449</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Forecasting &amp; Elasticity (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B912" s="6" t="inlineStr">
+        <is>
+          <t>rebuy</t>
+        </is>
+      </c>
+      <c r="C912" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D912" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E912" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F912" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G912" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H912" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rebuy/senior-data-scientist-forecasting-elasticity-berlin-80406</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Forecasting &amp; Elasticity (m/f/x) Freelance</t>
+        </is>
+      </c>
+      <c r="B913" s="8" t="inlineStr">
+        <is>
+          <t>rebuy</t>
+        </is>
+      </c>
+      <c r="C913" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D913" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E913" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F913" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G913" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H913" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rebuy/senior-data-scientist-forecasting-elasticity-freelance-berlin-186763</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="6" t="inlineStr">
+        <is>
+          <t>DATA ENGINEER (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B914" s="6" t="inlineStr">
+        <is>
+          <t>Omnisent</t>
+        </is>
+      </c>
+      <c r="C914" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D914" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E914" s="6" t="inlineStr">
+        <is>
+          <t>SQL、机器学习</t>
+        </is>
+      </c>
+      <c r="F914" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G914" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H914" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/omnisent/data-engineer-munich-208534</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="8" t="inlineStr">
+        <is>
+          <t>ML ENGINEER (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B915" s="8" t="inlineStr">
+        <is>
+          <t>Omnisent</t>
+        </is>
+      </c>
+      <c r="C915" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D915" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E915" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F915" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G915" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H915" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/omnisent/ml-engineer-munich-243364</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="6" t="inlineStr">
+        <is>
+          <t>Platform Hardware Engineer – Data Center Accelerator Platforms</t>
+        </is>
+      </c>
+      <c r="B916" s="6" t="inlineStr">
+        <is>
+          <t>Openchip And Software Technologies SL</t>
+        </is>
+      </c>
+      <c r="C916" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D916" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E916" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F916" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G916" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H916" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/openchip-and-software-technologies-sl/platform-hardware-engineer-data-center-accelerator-platforms-karlsruhe-267152</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data Collection (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B917" s="8" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C917" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D917" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E917" s="8" t="inlineStr"/>
+      <c r="F917" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G917" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H917" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/head-of-data-collection-hamburg-or-berlin-258408</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="6" t="inlineStr">
+        <is>
+          <t>Vice President Data Strategy Consulting (Mensch)</t>
+        </is>
+      </c>
+      <c r="B918" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C918" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D918" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E918" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F918" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G918" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H918" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wppmedia/vice-president-data-strategy-consulting-mensch-dusseldorf-frankfurt-hamburg-munich-169886</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="8" t="inlineStr">
+        <is>
+          <t>Social Data Strategist (gn)</t>
+        </is>
+      </c>
+      <c r="B919" s="8" t="inlineStr">
+        <is>
+          <t>Intermate Media GmbH</t>
+        </is>
+      </c>
+      <c r="C919" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D919" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E919" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F919" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G919" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H919" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intermate-media-gmbh/social-data-strategist-gn-berlin-157586</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist, Customer Operations</t>
+        </is>
+      </c>
+      <c r="B920" s="6" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C920" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D920" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E920" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F920" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G920" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H920" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150220-senior-machine-learning-scientist-customer-operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst, AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B921" s="8" t="inlineStr">
+        <is>
+          <t>phData</t>
+        </is>
+      </c>
+      <c r="C921" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D921" s="8" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="E921" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt、AWS、Azure、GCP、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F921" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G921" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H921" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150207-senior-business-analyst-ai-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+        </is>
+      </c>
+      <c r="B922" s="6" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C922" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D922" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E922" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F922" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G922" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H922" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150206-staff-data-scientist-ads-measurement-signals-privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="8" t="inlineStr">
+        <is>
+          <t>Sr. Staff Data Scientist - Ads Measurement, Signals, Privacy</t>
+        </is>
+      </c>
+      <c r="B923" s="8" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C923" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D923" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E923" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F923" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G923" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H923" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150205-sr-staff-data-scientist-ads-measurement-signals-privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="B924" s="6" t="inlineStr">
+        <is>
+          <t>NielsenIQ</t>
+        </is>
+      </c>
+      <c r="C924" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D924" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E924" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F924" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G924" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H924" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150190-senior-analytics-consultant</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="8" t="inlineStr">
+        <is>
+          <t>Workflow Annotator — Finance &amp; Data Analysis</t>
+        </is>
+      </c>
+      <c r="B925" s="8" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C925" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D925" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E925" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Power BI、Looker、Snowflake</t>
+        </is>
+      </c>
+      <c r="F925" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G925" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H925" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="6" t="inlineStr">
+        <is>
+          <t>Gameplay Data Capture Specialist</t>
+        </is>
+      </c>
+      <c r="B926" s="6" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C926" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D926" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E926" s="6" t="inlineStr"/>
+      <c r="F926" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G926" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H926" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="8" t="inlineStr">
+        <is>
+          <t>Business Intelligence Consultant (Excel)</t>
+        </is>
+      </c>
+      <c r="B927" s="8" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C927" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D927" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E927" s="8" t="inlineStr">
+        <is>
+          <t>Excel、机器学习</t>
+        </is>
+      </c>
+      <c r="F927" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G927" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H927" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="6" t="inlineStr">
+        <is>
+          <t>Investment Banking Associate – Remote Analyst</t>
+        </is>
+      </c>
+      <c r="B928" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C928" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D928" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E928" s="6" t="inlineStr"/>
+      <c r="F928" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G928" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H928" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="8" t="inlineStr">
+        <is>
+          <t>Data Science Specialist - Fully Remote</t>
+        </is>
+      </c>
+      <c r="B929" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C929" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D929" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E929" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F929" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G929" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H929" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="6" t="inlineStr">
+        <is>
+          <t>Bilingual Content Analyst - Fully Remote | Upto $20/hr Part-time</t>
+        </is>
+      </c>
+      <c r="B930" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C930" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D930" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E930" s="6" t="inlineStr"/>
+      <c r="F930" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G930" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H930" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="8" t="inlineStr">
+        <is>
+          <t>Senior Power BI Developer (5 Years Minimum Experience) - Pakistan TECH Recruiter</t>
+        </is>
+      </c>
+      <c r="B931" s="8" t="inlineStr">
+        <is>
+          <t>Taraki</t>
+        </is>
+      </c>
+      <c r="C931" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D931" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E931" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI</t>
+        </is>
+      </c>
+      <c r="F931" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G931" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H931" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/taraki/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="6" t="inlineStr">
+        <is>
+          <t>Principal /Senior Data scientist</t>
+        </is>
+      </c>
+      <c r="B932" s="6" t="inlineStr">
+        <is>
+          <t>Newbridge</t>
+        </is>
+      </c>
+      <c r="C932" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D932" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E932" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F932" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G932" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H932" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/newbridge/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="8" t="inlineStr">
+        <is>
+          <t>JR-179501 Data Consultant Senior</t>
+        </is>
+      </c>
+      <c r="B933" s="8" t="inlineStr">
+        <is>
+          <t>Customertimes</t>
+        </is>
+      </c>
+      <c r="C933" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D933" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E933" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F933" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G933" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H933" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/customertimes/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H889"/>
+  <autoFilter ref="A1:H933"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37371,19 +39191,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>340</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3">
@@ -37393,10 +39213,10 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -37405,7 +39225,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -37415,19 +39235,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -37437,7 +39257,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -37446,10 +39266,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -37459,19 +39279,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -37481,10 +39301,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -37493,7 +39313,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -37547,7 +39367,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
@@ -37559,7 +39379,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$933</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$981</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-04 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-04 23:31 UTC</t>
+          <t>数据日期 2026-08-05 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-05 23:27 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4428571428571428</v>
+        <v>0.46</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4214285714285714</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3266666666666667</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3133333333333334</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2866666666666667</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1642857142857143</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1642857142857143</v>
+        <v>0.1533333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1571428571428571</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1285714285714286</v>
+        <v>0.1133333333333333</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1133333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09285714285714286</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09285714285714286</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H933"/>
+  <dimension ref="A1:H981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -39129,8 +39129,1988 @@
         </is>
       </c>
     </row>
+    <row r="934">
+      <c r="A934" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Assistant</t>
+        </is>
+      </c>
+      <c r="B934" s="6" t="inlineStr">
+        <is>
+          <t>PT. Mastersystem Infotama</t>
+        </is>
+      </c>
+      <c r="C934" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D934" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E934" s="6" t="inlineStr"/>
+      <c r="F934" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G934" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H934" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-entry-assistant-pt-mastersystem-infotama-1136103</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="8" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) - Data Compliance Team</t>
+        </is>
+      </c>
+      <c r="B935" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C935" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D935" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E935" s="8" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F935" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G935" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H935" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/working-student-data-compliance-team-berlin-43589</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="6" t="inlineStr">
+        <is>
+          <t>Senior InfoSec GRC Analyst</t>
+        </is>
+      </c>
+      <c r="B936" s="6" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="C936" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D936" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E936" s="6" t="inlineStr"/>
+      <c r="F936" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G936" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H936" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/camunda/remote-senior-infosec-grc-analyst-338793</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst (middle/senior)</t>
+        </is>
+      </c>
+      <c r="B937" s="8" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C937" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D937" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E937" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F937" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G937" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H937" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobgether/business-analyst-middle-senior-germany-425632</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="6" t="inlineStr">
+        <is>
+          <t>Fincrime Analyst (Relocation to Luxembourg)</t>
+        </is>
+      </c>
+      <c r="B938" s="6" t="inlineStr">
+        <is>
+          <t>Satispay</t>
+        </is>
+      </c>
+      <c r="C938" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D938" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E938" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Looker</t>
+        </is>
+      </c>
+      <c r="F938" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G938" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H938" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/satispay/fincrime-analyst-relocation-to-luxembourg-berlin-364471</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="8" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Oversight Analyst (Relocation to Luxembourg)</t>
+        </is>
+      </c>
+      <c r="B939" s="8" t="inlineStr">
+        <is>
+          <t>Satispay</t>
+        </is>
+      </c>
+      <c r="C939" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D939" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E939" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker</t>
+        </is>
+      </c>
+      <c r="F939" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G939" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H939" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/satispay/monitoring-oversight-analyst-relocation-to-luxembourg-berlin-413677</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="6" t="inlineStr">
+        <is>
+          <t>Legal Data Strategy Director</t>
+        </is>
+      </c>
+      <c r="B940" s="6" t="inlineStr">
+        <is>
+          <t>Legora</t>
+        </is>
+      </c>
+      <c r="C940" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D940" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E940" s="6" t="inlineStr"/>
+      <c r="F940" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G940" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H940" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/legora/legal-data-strategy-director-munich-467450</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B941" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C941" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D941" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E941" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F941" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G941" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H941" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/junior-data-engineer-berlin-476263</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Engineer (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B942" s="6" t="inlineStr">
+        <is>
+          <t>Stackfuel</t>
+        </is>
+      </c>
+      <c r="C942" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D942" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E942" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Snowflake、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F942" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G942" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H942" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stackfuel/analytics-engineer-berlin-382440</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="8" t="inlineStr">
+        <is>
+          <t>Data Portfolio Lead - Learning Content (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B943" s="8" t="inlineStr">
+        <is>
+          <t>Stackfuel</t>
+        </is>
+      </c>
+      <c r="C943" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D943" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E943" s="8" t="inlineStr"/>
+      <c r="F943" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G943" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H943" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stackfuel/data-portfolio-lead-learning-content-berlin-480694</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="6" t="inlineStr">
+        <is>
+          <t>Tutor/Lehrkraft Business Intelligence (all genders)</t>
+        </is>
+      </c>
+      <c r="B944" s="6" t="inlineStr">
+        <is>
+          <t>Stackfuel</t>
+        </is>
+      </c>
+      <c r="C944" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D944" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E944" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI</t>
+        </is>
+      </c>
+      <c r="F944" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G944" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H944" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stackfuel/tutor-lehrkraft-business-intelligence-all-genders-berlin-59394</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="8" t="inlineStr">
+        <is>
+          <t>Manager, Data Platform</t>
+        </is>
+      </c>
+      <c r="B945" s="8" t="inlineStr">
+        <is>
+          <t>KAYAK</t>
+        </is>
+      </c>
+      <c r="C945" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D945" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E945" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F945" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G945" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H945" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kayak/manager-data-platform-berlin-360355</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, AI Performance</t>
+        </is>
+      </c>
+      <c r="B946" s="6" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C946" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D946" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E946" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F946" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G946" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H946" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wayve/senior-machine-learning-engineer-ai-performance-london-243118</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="8" t="inlineStr">
+        <is>
+          <t>Business Development Director - (Data &amp; Measurement)</t>
+        </is>
+      </c>
+      <c r="B947" s="8" t="inlineStr">
+        <is>
+          <t>Verve</t>
+        </is>
+      </c>
+      <c r="C947" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D947" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E947" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F947" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G947" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H947" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/verve/business-development-director-data-measurement-london-433820</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="B948" s="6" t="inlineStr">
+        <is>
+          <t>Beamery</t>
+        </is>
+      </c>
+      <c r="C948" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D948" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E948" s="6" t="inlineStr"/>
+      <c r="F948" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G948" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H948" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/beamery/staff-data-engineer-london-123884</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B949" s="8" t="inlineStr">
+        <is>
+          <t>Beamery</t>
+        </is>
+      </c>
+      <c r="C949" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D949" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E949" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F949" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G949" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H949" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/beamery/senior-data-engineer-london-378223</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst (middle/senior)</t>
+        </is>
+      </c>
+      <c r="B950" s="6" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C950" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D950" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E950" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F950" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G950" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H950" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobgether/business-analyst-middle-senior-uk-331817</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B951" s="8" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C951" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D951" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E951" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F951" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G951" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H951" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-senior-analytics-engineer-443926</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer - Data Platform (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B952" s="6" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C952" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D952" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E952" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F952" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G952" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H952" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-junior-data-engineer-data-platform-355717</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="8" t="inlineStr">
+        <is>
+          <t>Growth Analyst</t>
+        </is>
+      </c>
+      <c r="B953" s="8" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C953" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D953" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E953" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、dbt、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F953" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G953" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H953" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/growth-analyst-london-472399</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="6" t="inlineStr">
+        <is>
+          <t>Strategy Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B954" s="6" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C954" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D954" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E954" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F954" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G954" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H954" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/strategy-analytics-manager-london-209085</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (6 month FTC)</t>
+        </is>
+      </c>
+      <c r="B955" s="8" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C955" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D955" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E955" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F955" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G955" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H955" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/senior-analytics-engineer-6-month-ftc-london-7138</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="6" t="inlineStr">
+        <is>
+          <t>Security GRC Analyst</t>
+        </is>
+      </c>
+      <c r="B956" s="6" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C956" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D956" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E956" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F956" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G956" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H956" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/security-grc-analyst-london-408279</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="8" t="inlineStr">
+        <is>
+          <t>Financial Crime QA Analyst</t>
+        </is>
+      </c>
+      <c r="B957" s="8" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C957" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D957" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E957" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F957" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G957" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H957" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/financial-crime-qa-analyst-london-280805</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B958" s="6" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C958" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D958" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E958" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F958" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G958" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H958" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/analytics-engineer-london-411423</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B959" s="8" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C959" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D959" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E959" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F959" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G959" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H959" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/data-scientist-london-31396</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B960" s="6" t="inlineStr">
+        <is>
+          <t>Jedox</t>
+        </is>
+      </c>
+      <c r="C960" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D960" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E960" s="6" t="inlineStr"/>
+      <c r="F960" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G960" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H960" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jedox/remote-data-engineer-266403</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="8" t="inlineStr">
+        <is>
+          <t>Application Manager (m/w/d) Data Integration</t>
+        </is>
+      </c>
+      <c r="B961" s="8" t="inlineStr">
+        <is>
+          <t>Janitza electronics GmbH</t>
+        </is>
+      </c>
+      <c r="C961" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D961" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E961" s="8" t="inlineStr"/>
+      <c r="F961" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G961" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H961" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/janitza-electronics-gmbh/application-manager-data-integration-wetzlar-411882</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B962" s="6" t="inlineStr">
+        <is>
+          <t>bunch</t>
+        </is>
+      </c>
+      <c r="C962" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D962" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E962" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F962" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G962" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H962" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bunch/senior-analytics-engineer-berlin-317004</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) im Bereich Datenmanagement</t>
+        </is>
+      </c>
+      <c r="B963" s="8" t="inlineStr">
+        <is>
+          <t>Wirtschaftsrat Der Cdu E V</t>
+        </is>
+      </c>
+      <c r="C963" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D963" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E963" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F963" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G963" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H963" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wirtschaftsrat-der-cdu-e-v/werkstudent-im-bereich-datenmanagement-bundesgeschaftsstelle-berlin-7370</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="6" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer (Python)</t>
+        </is>
+      </c>
+      <c r="B964" s="6" t="inlineStr">
+        <is>
+          <t>Proxify</t>
+        </is>
+      </c>
+      <c r="C964" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D964" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E964" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、GCP</t>
+        </is>
+      </c>
+      <c r="F964" s="6" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G964" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H964" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1773165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Python)</t>
+        </is>
+      </c>
+      <c r="B965" s="8" t="inlineStr">
+        <is>
+          <t>Proxify</t>
+        </is>
+      </c>
+      <c r="C965" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D965" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E965" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Airflow、AWS、Azure、GCP、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F965" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G965" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H965" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1773159/</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B966" s="6" t="inlineStr">
+        <is>
+          <t>Proxify</t>
+        </is>
+      </c>
+      <c r="C966" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D966" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E966" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、BigQuery、ETL、pandas</t>
+        </is>
+      </c>
+      <c r="F966" s="6" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G966" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H966" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1773153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="8" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Developer (React.js / Node.js)</t>
+        </is>
+      </c>
+      <c r="B967" s="8" t="inlineStr">
+        <is>
+          <t>Proxify</t>
+        </is>
+      </c>
+      <c r="C967" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D967" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E967" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F967" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G967" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H967" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1773149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="6" t="inlineStr">
+        <is>
+          <t>Senior Ruby on Rails Developer</t>
+        </is>
+      </c>
+      <c r="B968" s="6" t="inlineStr">
+        <is>
+          <t>Proxify</t>
+        </is>
+      </c>
+      <c r="C968" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D968" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E968" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F968" s="6" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G968" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H968" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1773141/</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="8" t="inlineStr">
+        <is>
+          <t>Settlement Analyst (AP/AR)</t>
+        </is>
+      </c>
+      <c r="B969" s="8" t="inlineStr">
+        <is>
+          <t>eClerx</t>
+        </is>
+      </c>
+      <c r="C969" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D969" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E969" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F969" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G969" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H969" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/eclerx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="6" t="inlineStr">
+        <is>
+          <t>Program Analyst - Senior</t>
+        </is>
+      </c>
+      <c r="B970" s="6" t="inlineStr">
+        <is>
+          <t>Artemis ARC</t>
+        </is>
+      </c>
+      <c r="C970" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D970" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E970" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F970" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G970" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H970" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/artemis-arc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B971" s="8" t="inlineStr">
+        <is>
+          <t>KKCompany Technologies</t>
+        </is>
+      </c>
+      <c r="C971" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D971" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E971" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、AWS、GCP、A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F971" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G971" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H971" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kkcompany-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B972" s="6" t="inlineStr">
+        <is>
+          <t>Deploy</t>
+        </is>
+      </c>
+      <c r="C972" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D972" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E972" s="6" t="inlineStr">
+        <is>
+          <t>Power BI、Spark、机器学习</t>
+        </is>
+      </c>
+      <c r="F972" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G972" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H972" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/deploy/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (AI/BI) | Databricks-Centric - RibbitZ</t>
+        </is>
+      </c>
+      <c r="B973" s="8" t="inlineStr">
+        <is>
+          <t>Taraki</t>
+        </is>
+      </c>
+      <c r="C973" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D973" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E973" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F973" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G973" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H973" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/taraki/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="6" t="inlineStr">
+        <is>
+          <t>BMC Helix Process &amp; ITSM Analyst / Workflow Engineer</t>
+        </is>
+      </c>
+      <c r="B974" s="6" t="inlineStr">
+        <is>
+          <t>Müller`s Solutions</t>
+        </is>
+      </c>
+      <c r="C974" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D974" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E974" s="6" t="inlineStr"/>
+      <c r="F974" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G974" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H974" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/muller-s-solutions/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B975" s="8" t="inlineStr">
+        <is>
+          <t>Remerge</t>
+        </is>
+      </c>
+      <c r="C975" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D975" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E975" s="8" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F975" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G975" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H975" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/remerge/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B976" s="6" t="inlineStr">
+        <is>
+          <t>Suzega</t>
+        </is>
+      </c>
+      <c r="C976" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D976" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E976" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS、Azure、GCP、BigQuery、机器学习、ETL、pandas</t>
+        </is>
+      </c>
+      <c r="F976" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G976" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H976" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/suzega/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer - Databricks</t>
+        </is>
+      </c>
+      <c r="B977" s="8" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="C977" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D977" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E977" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F977" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G977" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H977" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/oz/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Analyst</t>
+        </is>
+      </c>
+      <c r="B978" s="6" t="inlineStr">
+        <is>
+          <t>Nuvei</t>
+        </is>
+      </c>
+      <c r="C978" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D978" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E978" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F978" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G978" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H978" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nuvei/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Process Automation Executive / Analyst</t>
+        </is>
+      </c>
+      <c r="B979" s="8" t="inlineStr">
+        <is>
+          <t>MindPlus (Pvt) Ltd</t>
+        </is>
+      </c>
+      <c r="C979" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D979" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E979" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F979" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G979" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H979" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mindplus-pvt-ltd/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="6" t="inlineStr">
+        <is>
+          <t>Billing Analyst</t>
+        </is>
+      </c>
+      <c r="B980" s="6" t="inlineStr">
+        <is>
+          <t>PM Consulting</t>
+        </is>
+      </c>
+      <c r="C980" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D980" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E980" s="6" t="inlineStr"/>
+      <c r="F980" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G980" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H980" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pm-consulting/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform Leaders &amp; Engineers -  Programmatic Advertising &amp; Ecommerce Data</t>
+        </is>
+      </c>
+      <c r="B981" s="8" t="inlineStr">
+        <is>
+          <t>Newbridge</t>
+        </is>
+      </c>
+      <c r="C981" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D981" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E981" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、dbt、Airflow、AWS、Azure、GCP、BigQuery、A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F981" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G981" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H981" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/newbridge/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H933"/>
+  <autoFilter ref="A1:H981"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39191,19 +41171,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>369</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
@@ -39235,7 +41215,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>43</v>
@@ -39244,10 +41224,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -39279,19 +41259,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -39351,13 +41331,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$981</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1038</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-05 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-05 23:27 UTC</t>
+          <t>数据日期 2026-08-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-07 01:36 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>980</v>
+        <v>1037</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3266666666666667</v>
+        <v>0.275</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3133333333333334</v>
+        <v>0.36875</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2866666666666667</v>
+        <v>0.26875</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.16875</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.14</v>
+        <v>0.05625</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1533333333333333</v>
+        <v>0.14375</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1375</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1133333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1133333333333333</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.08749999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H981"/>
+  <dimension ref="A1:H1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -41109,8 +41109,2322 @@
         </is>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" s="6" t="inlineStr">
+        <is>
+          <t>Sales Jedi</t>
+        </is>
+      </c>
+      <c r="B982" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Creative Force </t>
+        </is>
+      </c>
+      <c r="C982" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D982" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E982" s="6" t="inlineStr"/>
+      <c r="F982" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G982" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H982" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/sales/sales-jedi-2091088</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="8" t="inlineStr">
+        <is>
+          <t>SaaS Product Support Jedi</t>
+        </is>
+      </c>
+      <c r="B983" s="8" t="inlineStr">
+        <is>
+          <t>Creative Force</t>
+        </is>
+      </c>
+      <c r="C983" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D983" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E983" s="8" t="inlineStr"/>
+      <c r="F983" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G983" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H983" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/customer-service/saas-product-support-jedi-2091087</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B984" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C984" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D984" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E984" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F984" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G984" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H984" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/analytics-manager-marketing-analytics-berlin-280796</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="8" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Data and API</t>
+        </is>
+      </c>
+      <c r="B985" s="8" t="inlineStr">
+        <is>
+          <t>Climatiq</t>
+        </is>
+      </c>
+      <c r="C985" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D985" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E985" s="8" t="inlineStr"/>
+      <c r="F985" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G985" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H985" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/climatiq/senior-product-manager-data-and-api-berlin-221982</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Earth Observation Data Supplier Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B986" s="6" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C986" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D986" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E986" s="6" t="inlineStr"/>
+      <c r="F986" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G986" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H986" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/senior-earth-observation-data-supplier-manager-liveeo-gmbh-berlin-office-hybrid-461664</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B987" s="8" t="inlineStr">
+        <is>
+          <t>Engelhart</t>
+        </is>
+      </c>
+      <c r="C987" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D987" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E987" s="8" t="inlineStr"/>
+      <c r="F987" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G987" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H987" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/engelhart/software-engineer-data-berlin-291596</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="6" t="inlineStr">
+        <is>
+          <t>Market Analyst - AI Trainer - Freelance - 8-20 hrs/week - Remote</t>
+        </is>
+      </c>
+      <c r="B988" s="6" t="inlineStr">
+        <is>
+          <t>10Xteam</t>
+        </is>
+      </c>
+      <c r="C988" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D988" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E988" s="6" t="inlineStr"/>
+      <c r="F988" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G988" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H988" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/10xteam/market-analyst-ai-trainer-freelance-8-20-hrs-week-remote-berlin-409556</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="8" t="inlineStr">
+        <is>
+          <t>Intellectual Property Analyst - AI Trainer - Freelance - 8-20 hrs/week - Remote</t>
+        </is>
+      </c>
+      <c r="B989" s="8" t="inlineStr">
+        <is>
+          <t>10Xteam</t>
+        </is>
+      </c>
+      <c r="C989" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D989" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E989" s="8" t="inlineStr"/>
+      <c r="F989" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G989" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H989" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/10xteam/intellectual-property-analyst-ai-trainer-freelance-8-20-hrs-week-remote-berlin-370048</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="6" t="inlineStr">
+        <is>
+          <t>Investment Banking Analyst - AI Trainer - Freelance - 8-20hrs/week - Remote</t>
+        </is>
+      </c>
+      <c r="B990" s="6" t="inlineStr">
+        <is>
+          <t>10Xteam</t>
+        </is>
+      </c>
+      <c r="C990" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D990" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E990" s="6" t="inlineStr"/>
+      <c r="F990" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G990" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H990" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/10xteam/investment-banking-analyst-ai-trainer-freelance-8-20hrs-week-remote-berlin-201853</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="8" t="inlineStr">
+        <is>
+          <t>Data Architect - AI Trainer - Freelance - 8-20hrs/week - Remote</t>
+        </is>
+      </c>
+      <c r="B991" s="8" t="inlineStr">
+        <is>
+          <t>10Xteam</t>
+        </is>
+      </c>
+      <c r="C991" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D991" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E991" s="8" t="inlineStr"/>
+      <c r="F991" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G991" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H991" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/10xteam/data-architect-ai-trainer-freelance-8-20hrs-week-remote-berlin-354910</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - AI Trainer - Freelance - 8-20 hrs/week - Remote</t>
+        </is>
+      </c>
+      <c r="B992" s="6" t="inlineStr">
+        <is>
+          <t>10Xteam</t>
+        </is>
+      </c>
+      <c r="C992" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D992" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E992" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F992" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G992" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H992" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/10xteam/machine-learning-engineer-ai-trainer-freelance-8-20-hrs-week-remote-berlin-376362</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Web Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B993" s="8" t="inlineStr">
+        <is>
+          <t>Spread Group</t>
+        </is>
+      </c>
+      <c r="C993" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D993" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E993" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Snowflake、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F993" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G993" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H993" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/spread-group/remote-senior-web-analyst-leipzig-207214</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B994" s="6" t="inlineStr">
+        <is>
+          <t>All Your BI</t>
+        </is>
+      </c>
+      <c r="C994" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D994" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E994" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F994" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G994" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H994" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/all-your-bi/data-engineer-berlin-468631</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B995" s="8" t="inlineStr">
+        <is>
+          <t>All Your BI</t>
+        </is>
+      </c>
+      <c r="C995" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D995" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E995" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Azure</t>
+        </is>
+      </c>
+      <c r="F995" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G995" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H995" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/all-your-bi/senior-data-engineer-berlin-362738</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="6" t="inlineStr">
+        <is>
+          <t>Data and Analytics Intern</t>
+        </is>
+      </c>
+      <c r="B996" s="6" t="inlineStr">
+        <is>
+          <t>Inizio</t>
+        </is>
+      </c>
+      <c r="C996" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D996" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E996" s="6" t="inlineStr"/>
+      <c r="F996" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G996" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H996" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/inizio/data-and-analytics-intern-manchester-414063</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="8" t="inlineStr">
+        <is>
+          <t>Senior Deal Desk Analyst, Central Europe</t>
+        </is>
+      </c>
+      <c r="B997" s="8" t="inlineStr">
+        <is>
+          <t>Wizinc</t>
+        </is>
+      </c>
+      <c r="C997" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D997" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E997" s="8" t="inlineStr"/>
+      <c r="F997" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G997" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H997" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wizinc/senior-deal-desk-analyst-central-europe-274100</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B998" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C998" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D998" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E998" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F998" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G998" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H998" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wolt-english/analytics-manager-marketing-analytics-london-2254</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="8" t="inlineStr">
+        <is>
+          <t>Founding Forward-Deployed ML Engineer</t>
+        </is>
+      </c>
+      <c r="B999" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C999" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D999" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E999" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F999" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G999" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H999" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-founding-forward-deployed-ml-engineer-105660</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="6" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1000" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1000" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1000" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1000" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F1000" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1000" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1000" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-senior-geospatial-machine-learning-engineer-113270</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="8" t="inlineStr">
+        <is>
+          <t>Junior  Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1001" s="8" t="inlineStr">
+        <is>
+          <t>Recraft</t>
+        </is>
+      </c>
+      <c r="C1001" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1001" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1001" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1001" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1001" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1001" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/recraft/junior-machine-learning-engineer-london-253739</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="6" t="inlineStr">
+        <is>
+          <t>Senior/Staff Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1002" s="6" t="inlineStr">
+        <is>
+          <t>MoonPay</t>
+        </is>
+      </c>
+      <c r="C1002" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1002" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1002" s="6" t="inlineStr">
+        <is>
+          <t>dbt、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1002" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1002" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1002" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/moonpay/senior-staff-data-analyst-london-hybrid-302149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer - Crypto and Payments</t>
+        </is>
+      </c>
+      <c r="B1003" s="8" t="inlineStr">
+        <is>
+          <t>MoonPay</t>
+        </is>
+      </c>
+      <c r="C1003" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1003" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1003" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1003" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1003" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1003" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/moonpay/analytics-engineer-crypto-and-payments-london-187907</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="6" t="inlineStr">
+        <is>
+          <t>Customer Analytics Lead</t>
+        </is>
+      </c>
+      <c r="B1004" s="6" t="inlineStr">
+        <is>
+          <t>heliosx</t>
+        </is>
+      </c>
+      <c r="C1004" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1004" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1004" s="6" t="inlineStr"/>
+      <c r="F1004" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1004" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1004" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/heliosx/customer-analytics-lead-london-150028</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist — Agent Evaluations &amp; Quality</t>
+        </is>
+      </c>
+      <c r="B1005" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1005" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1005" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1005" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1005" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1005" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1005" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-data-scientist-agent-evaluations-quality-298047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="6" t="inlineStr">
+        <is>
+          <t>Founding Forward-Deployed ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1006" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1006" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1006" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1006" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1006" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1006" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1006" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-founding-forward-deployed-ml-engineer-437983</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="8" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1007" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1007" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1007" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1007" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F1007" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1007" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1007" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-senior-geospatial-machine-learning-engineer-364737</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer - Robotics</t>
+        </is>
+      </c>
+      <c r="B1008" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1008" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1008" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1008" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1008" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1008" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1008" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-ml-engineer-robotics-351960</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="8" t="inlineStr">
+        <is>
+          <t>Founding Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1009" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1009" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1009" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1009" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1009" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1009" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1009" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clera/remote-founding-machine-learning-engineer-270447</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="6" t="inlineStr">
+        <is>
+          <t>Finance Data Manager</t>
+        </is>
+      </c>
+      <c r="B1010" s="6" t="inlineStr">
+        <is>
+          <t>Octopus Energy Group jobs</t>
+        </is>
+      </c>
+      <c r="C1010" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1010" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1010" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow</t>
+        </is>
+      </c>
+      <c r="F1010" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1010" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1010" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/octopus-energy-group-jobs/finance-data-manager-london-gb-441130</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst mit Schwerpunkt Power BI &amp; Databricks (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1011" s="8" t="inlineStr">
+        <is>
+          <t>pmX Group</t>
+        </is>
+      </c>
+      <c r="C1011" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1011" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1011" s="8" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F1011" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1011" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1011" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmx-group/data-analyst-mit-schwerpunkt-power-bi-databricks-stuttgart-286658</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="6" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer - Data Intelligence Applications (several headcounts)</t>
+        </is>
+      </c>
+      <c r="B1012" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C1012" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1012" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1012" s="6" t="inlineStr">
+        <is>
+          <t>SQL、AWS</t>
+        </is>
+      </c>
+      <c r="F1012" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1012" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1012" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/senior-full-stack-engineer-data-intelligence-applications-several-headcounts-hamburg-or-berlin-21449</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="8" t="inlineStr">
+        <is>
+          <t>Team Lead SAP ABAP Development – Data Migration (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1013" s="8" t="inlineStr">
+        <is>
+          <t>Natuvion GmbH</t>
+        </is>
+      </c>
+      <c r="C1013" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1013" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1013" s="8" t="inlineStr"/>
+      <c r="F1013" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1013" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1013" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/natuvion-gmbh/remote-team-lead-sap-abap-development-data-migration-berlin-106136</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer &amp; Consultant (all genders) – Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B1014" s="6" t="inlineStr">
+        <is>
+          <t>teccle group GmbH</t>
+        </is>
+      </c>
+      <c r="C1014" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1014" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1014" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Spark、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1014" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1014" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1014" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/teccle-group-gmbh/remote-senior-data-engineer-consultant-all-genders-microsoft-fabric-berlin-342860</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="8" t="inlineStr">
+        <is>
+          <t>IT Business Analyst - Banking Regulation &amp; Reporting (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1015" s="8" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1015" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1015" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1015" s="8" t="inlineStr"/>
+      <c r="F1015" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1015" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1015" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/it-business-analyst-banking-regulation-reporting-munster-475019</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="6" t="inlineStr">
+        <is>
+          <t>IT Consultant &amp; Business Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1016" s="6" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1016" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1016" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1016" s="6" t="inlineStr"/>
+      <c r="F1016" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1016" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1016" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/it-consultant-business-analyst-munster-131618</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Web Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1017" s="8" t="inlineStr">
+        <is>
+          <t>Spread Group</t>
+        </is>
+      </c>
+      <c r="C1017" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1017" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1017" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Snowflake、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1017" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1017" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1017" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/spread-group/senior-web-analyst-leipzig-82946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer - Robotics</t>
+        </is>
+      </c>
+      <c r="B1018" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1018" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1018" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1018" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1018" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1018" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1018" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-ml-engineer-robotics-303416</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="8" t="inlineStr">
+        <is>
+          <t>Founding Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1019" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1019" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1019" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1019" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1019" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1019" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1019" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-machine-learning-engineer-413326</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="6" t="inlineStr">
+        <is>
+          <t>FBS Product Analyst Customer Retention</t>
+        </is>
+      </c>
+      <c r="B1020" s="6" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C1020" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1020" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1020" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1020" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1020" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1020" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150290-fbs-product-analyst-customer-retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="8" t="inlineStr">
+        <is>
+          <t>AI Content Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B1021" s="8" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C1021" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1021" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1021" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1021" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G1021" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1021" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1775657/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B1022" s="6" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C1022" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1022" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1022" s="6" t="inlineStr"/>
+      <c r="F1022" s="6" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G1022" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1022" s="6" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1775628/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (No Experience Required)</t>
+        </is>
+      </c>
+      <c r="B1023" s="8" t="inlineStr">
+        <is>
+          <t>Peroptyx</t>
+        </is>
+      </c>
+      <c r="C1023" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1023" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1023" s="8" t="inlineStr"/>
+      <c r="F1023" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G1023" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1023" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1775548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1024" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1024" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1024" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1024" s="6" t="inlineStr">
+        <is>
+          <t>Tableau、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1024" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1024" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1024" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/magnetics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst – CRM, BI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B1025" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1025" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1025" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1025" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1025" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1025" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1025" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sqdm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="6" t="inlineStr">
+        <is>
+          <t>Senior Clinical Trials Budget Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="B1026" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1026" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1026" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1026" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1026" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1026" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1026" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/vitalief/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="8" t="inlineStr">
+        <is>
+          <t>Senior Presales Solutions Architect – Salesforce Practice – Data Cloud (Future O</t>
+        </is>
+      </c>
+      <c r="B1027" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1027" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1027" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1027" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1027" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1027" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1027" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/argano/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1028" s="6" t="inlineStr">
+        <is>
+          <t>Technatomy</t>
+        </is>
+      </c>
+      <c r="C1028" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1028" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1028" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1028" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1028" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1028" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/technatomy/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="8" t="inlineStr">
+        <is>
+          <t>Power BI Analyst &amp; Dashboard Developer</t>
+        </is>
+      </c>
+      <c r="B1029" s="8" t="inlineStr">
+        <is>
+          <t>Remote Raven</t>
+        </is>
+      </c>
+      <c r="C1029" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1029" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1029" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、统计学</t>
+        </is>
+      </c>
+      <c r="F1029" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1029" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1029" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/remote-raven/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="6" t="inlineStr">
+        <is>
+          <t>Principal Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B1030" s="6" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C1030" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1030" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1030" s="6" t="inlineStr">
+        <is>
+          <t>Azure、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1030" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1030" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1030" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ensemble-health-partners/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="8" t="inlineStr">
+        <is>
+          <t>Business Analytics Senior Analyst - EviCore - Remote</t>
+        </is>
+      </c>
+      <c r="B1031" s="8" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C1031" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1031" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1031" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F1031" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1031" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1031" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/the-cigna-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="6" t="inlineStr">
+        <is>
+          <t>Clinical Analyst</t>
+        </is>
+      </c>
+      <c r="B1032" s="6" t="inlineStr">
+        <is>
+          <t>Global Alliant</t>
+        </is>
+      </c>
+      <c r="C1032" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1032" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1032" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1032" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1032" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1032" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/global-alliant/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="8" t="inlineStr">
+        <is>
+          <t>IAM Governance &amp; User Access Review Analyst</t>
+        </is>
+      </c>
+      <c r="B1033" s="8" t="inlineStr">
+        <is>
+          <t>OmegaHires</t>
+        </is>
+      </c>
+      <c r="C1033" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1033" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1033" s="8" t="inlineStr"/>
+      <c r="F1033" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1033" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1033" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/omegahires/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="6" t="inlineStr">
+        <is>
+          <t>Data Architect Python (ESP/UK)</t>
+        </is>
+      </c>
+      <c r="B1034" s="6" t="inlineStr">
+        <is>
+          <t>Parser</t>
+        </is>
+      </c>
+      <c r="C1034" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1034" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1034" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1034" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1034" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1034" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/parser/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="8" t="inlineStr">
+        <is>
+          <t>Cyber Security Analyst - GRC</t>
+        </is>
+      </c>
+      <c r="B1035" s="8" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1035" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1035" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1035" s="8" t="inlineStr"/>
+      <c r="F1035" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1035" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1035" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/baringa/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="6" t="inlineStr">
+        <is>
+          <t>Data Protection &amp; Identity Manager</t>
+        </is>
+      </c>
+      <c r="B1036" s="6" t="inlineStr">
+        <is>
+          <t>Extreme Networks</t>
+        </is>
+      </c>
+      <c r="C1036" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1036" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1036" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1036" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1036" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1036" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/extreme-networks/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="8" t="inlineStr">
+        <is>
+          <t>Compliance Analyst - Advertising Review</t>
+        </is>
+      </c>
+      <c r="B1037" s="8" t="inlineStr">
+        <is>
+          <t>Cetera</t>
+        </is>
+      </c>
+      <c r="C1037" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1037" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1037" s="8" t="inlineStr"/>
+      <c r="F1037" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1037" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1037" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cetera/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="6" t="inlineStr">
+        <is>
+          <t>Commercial Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B1038" s="6" t="inlineStr">
+        <is>
+          <t>Yellow Social Interactive</t>
+        </is>
+      </c>
+      <c r="C1038" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1038" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1038" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Tableau、Looker</t>
+        </is>
+      </c>
+      <c r="F1038" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1038" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1038" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/yellow-social-interactive/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H981"/>
+  <autoFilter ref="A1:H1038"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41171,19 +43485,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>399</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3">
@@ -41193,7 +43507,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>4</v>
@@ -41205,7 +43519,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -41215,7 +43529,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>43</v>
@@ -41224,10 +43538,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -41237,7 +43551,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -41249,7 +43563,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -41259,7 +43573,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>14</v>
@@ -41268,10 +43582,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
@@ -41281,7 +43595,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>8</v>
@@ -41293,7 +43607,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -41378,10 +43692,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1038</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1065</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-07 01:36 UTC</t>
+          <t>数据日期 2026-08-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-07 23:03 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4076923076923077</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.375</v>
+        <v>0.3923076923076923</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.275</v>
+        <v>0.2615384615384616</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.36875</v>
+        <v>0.3692307692307693</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.26875</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1769230769230769</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.16875</v>
+        <v>0.1769230769230769</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.05625</v>
+        <v>0.06153846153846154</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.14375</v>
+        <v>0.1461538461538462</v>
       </c>
     </row>
     <row r="16">
@@ -819,62 +819,62 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1375</v>
+        <v>0.1076923076923077</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1125</v>
+        <v>0.09230769230769231</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1</v>
+        <v>0.08461538461538462</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08461538461538462</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1038"/>
+  <dimension ref="A1:H1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -43423,8 +43423,1094 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" s="8" t="inlineStr">
+        <is>
+          <t>Solution Consultant – Snke Data</t>
+        </is>
+      </c>
+      <c r="B1039" s="8" t="inlineStr">
+        <is>
+          <t>Snke</t>
+        </is>
+      </c>
+      <c r="C1039" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1039" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1039" s="8" t="inlineStr"/>
+      <c r="F1039" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1039" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1039" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/snke/solution-consultant-snke-data-munchen-273597</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Energy Data Scientist – Energiedaten &amp; Automatisierung (MSB) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1040" s="6" t="inlineStr">
+        <is>
+          <t>Vrey</t>
+        </is>
+      </c>
+      <c r="C1040" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1040" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1040" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1040" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1040" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1040" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vrey/junior-energy-data-scientist-energiedaten-automatisierung-msb-berlin-71106</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="8" t="inlineStr">
+        <is>
+          <t>Business Technology Analyst</t>
+        </is>
+      </c>
+      <c r="B1041" s="8" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="C1041" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1041" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1041" s="8" t="inlineStr"/>
+      <c r="F1041" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1041" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1041" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/faculty/business-technology-analyst-london-427122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="6" t="inlineStr">
+        <is>
+          <t>Senior Information Security Analyst</t>
+        </is>
+      </c>
+      <c r="B1042" s="6" t="inlineStr">
+        <is>
+          <t>Cirrus</t>
+        </is>
+      </c>
+      <c r="C1042" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1042" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1042" s="6" t="inlineStr"/>
+      <c r="F1042" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1042" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1042" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/cirrus/senior-information-security-analyst-edinburgh-scotland-481897</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1043" s="8" t="inlineStr">
+        <is>
+          <t>Grahamcapitalmanagement</t>
+        </is>
+      </c>
+      <c r="C1043" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1043" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1043" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1043" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1043" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1043" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/grahamcapitalmanagement/machine-learning-engineer-london-90466</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager, Data, UK</t>
+        </is>
+      </c>
+      <c r="B1044" s="6" t="inlineStr">
+        <is>
+          <t>Eucalyptus</t>
+        </is>
+      </c>
+      <c r="C1044" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1044" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1044" s="6" t="inlineStr">
+        <is>
+          <t>GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1044" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1044" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1044" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/eucalyptus/senior-manager-data-uk-458133</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B1045" s="8" t="inlineStr">
+        <is>
+          <t>KAYAK</t>
+        </is>
+      </c>
+      <c r="C1045" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1045" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1045" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1045" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1045" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1045" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kayak/senior-machine-learning-ops-engineer-berlin-267492</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="6" t="inlineStr">
+        <is>
+          <t>Team Lead Data Products &amp; Analytics (gn)</t>
+        </is>
+      </c>
+      <c r="B1046" s="6" t="inlineStr">
+        <is>
+          <t>Bikeleasing-Service GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1046" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1046" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1046" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt</t>
+        </is>
+      </c>
+      <c r="F1046" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1046" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1046" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bikeleasing-service-gmbh-co-kg/team-lead-data-products-analytics-gn-berlin-141780</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="8" t="inlineStr">
+        <is>
+          <t>Team Lead Data Products &amp; Analytics (gn)</t>
+        </is>
+      </c>
+      <c r="B1047" s="8" t="inlineStr">
+        <is>
+          <t>Bikeleasing-Service GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1047" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1047" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1047" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt</t>
+        </is>
+      </c>
+      <c r="F1047" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1047" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1047" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bikeleasing-service-gmbh-co-kg/team-lead-data-products-analytics-gn-berlin-77346</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1048" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C1048" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1048" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1048" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F1048" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1048" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1048" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/data-platform-engineer-berlin-59805</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="8" t="inlineStr">
+        <is>
+          <t>Remote Part-time Media Search Analyst - German (DE)</t>
+        </is>
+      </c>
+      <c r="B1049" s="8" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C1049" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1049" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1049" s="8" t="inlineStr"/>
+      <c r="F1049" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1049" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1049" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/telus-digital/remote-part-time-media-search-analyst-german-de-berlin-206269</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="6" t="inlineStr">
+        <is>
+          <t>IT-Forensiker / Analysten (mIwId)</t>
+        </is>
+      </c>
+      <c r="B1050" s="6" t="inlineStr">
+        <is>
+          <t>LeySelect GmbH</t>
+        </is>
+      </c>
+      <c r="C1050" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1050" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1050" s="6" t="inlineStr"/>
+      <c r="F1050" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1050" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1050" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/leyselect-gmbh/it-forensiker-analysten-miwid-frankfurt-am-main-490055</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="8" t="inlineStr">
+        <is>
+          <t>Master Data Management Lead (gn)</t>
+        </is>
+      </c>
+      <c r="B1051" s="8" t="inlineStr">
+        <is>
+          <t>thequalitygroupgmbh2</t>
+        </is>
+      </c>
+      <c r="C1051" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1051" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1051" s="8" t="inlineStr"/>
+      <c r="F1051" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1051" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1051" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/thequalitygroupgmbh2/remote-master-data-management-lead-gn-140944</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (f/m/x) - Enpal Energy</t>
+        </is>
+      </c>
+      <c r="B1052" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1052" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1052" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1052" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Snowflake、dbt、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1052" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1052" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1052" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/senior-analytics-engineer-enpal-energy-berlin-138477</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="8" t="inlineStr">
+        <is>
+          <t>Venture Development Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1053" s="8" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1053" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1053" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1053" s="8" t="inlineStr"/>
+      <c r="F1053" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1053" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1053" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/venture-development-analyst-berlin-406540</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst – Strategy &amp; Operations (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1054" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1054" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1054" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1054" s="6" t="inlineStr"/>
+      <c r="F1054" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1054" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1054" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/business-analyst-strategy-operations-berlin-137687</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="8" t="inlineStr">
+        <is>
+          <t>Business Operations Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1055" s="8" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1055" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1055" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1055" s="8" t="inlineStr"/>
+      <c r="F1055" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1055" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1055" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/business-operations-analyst-berlin-311003</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Operations Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1056" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1056" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1056" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1056" s="6" t="inlineStr"/>
+      <c r="F1056" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1056" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1056" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/growth-operations-analyst-berlin-314220</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="8" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Business Operations Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1057" s="8" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1057" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1057" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1057" s="8" t="inlineStr"/>
+      <c r="F1057" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1057" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1057" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/strategy-business-operations-analyst-berlin-100707</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent - Sales Business Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1058" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1058" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1058" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1058" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Snowflake</t>
+        </is>
+      </c>
+      <c r="F1058" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1058" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1058" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/werkstudent-sales-business-analytics-berlin-388176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Consultant (m/w/d) - Quereinsteiger willkommen! DSDE 14 - 01. März 2027</t>
+        </is>
+      </c>
+      <c r="B1059" s="8" t="inlineStr">
+        <is>
+          <t>Theinformationlab</t>
+        </is>
+      </c>
+      <c r="C1059" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1059" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1059" s="8" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F1059" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1059" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1059" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/theinformationlab/data-analyst-consultant-quereinsteiger-willkommen-dsde-14-01-marz-2027-hamburg-397594</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="6" t="inlineStr">
+        <is>
+          <t>Senior Security Analyst</t>
+        </is>
+      </c>
+      <c r="B1060" s="6" t="inlineStr">
+        <is>
+          <t>Zoom Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="C1060" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1060" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1060" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R</t>
+        </is>
+      </c>
+      <c r="F1060" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1060" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1060" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zoom-communications-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="8" t="inlineStr">
+        <is>
+          <t>Sales Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1061" s="8" t="inlineStr">
+        <is>
+          <t>Abnormal Security</t>
+        </is>
+      </c>
+      <c r="C1061" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1061" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1061" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1061" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1061" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1061" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/abnormal/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="6" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1062" s="6" t="inlineStr">
+        <is>
+          <t>Armis</t>
+        </is>
+      </c>
+      <c r="C1062" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1062" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1062" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1062" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1062" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1062" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/armis/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="8" t="inlineStr">
+        <is>
+          <t>Senior Staff Data Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B1063" s="8" t="inlineStr">
+        <is>
+          <t>Armis</t>
+        </is>
+      </c>
+      <c r="C1063" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1063" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1063" s="8" t="inlineStr"/>
+      <c r="F1063" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1063" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1063" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/armis/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="6" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (Analytics)</t>
+        </is>
+      </c>
+      <c r="B1064" s="6" t="inlineStr">
+        <is>
+          <t>Shaped</t>
+        </is>
+      </c>
+      <c r="C1064" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1064" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1064" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1064" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1064" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1064" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/shaped/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1065" s="8" t="inlineStr">
+        <is>
+          <t>Shaped</t>
+        </is>
+      </c>
+      <c r="C1065" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1065" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1065" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、统计学</t>
+        </is>
+      </c>
+      <c r="F1065" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1065" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H1065" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/shaped/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1038"/>
+  <autoFilter ref="A1:H1065"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43485,19 +44571,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>435</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3">
@@ -43529,19 +44615,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1065</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1091</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-07 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-07 23:03 UTC</t>
+          <t>数据日期 2026-08-08 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-08 22:55 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1064</v>
+        <v>1090</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4076923076923077</v>
+        <v>0.4214876033057851</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3923076923076923</v>
+        <v>0.371900826446281</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2615384615384616</v>
+        <v>0.3223140495867768</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3223140495867768</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2809917355371901</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.231404958677686</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1769230769230769</v>
+        <v>0.1652892561983471</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.06153846153846154</v>
+        <v>0.0743801652892562</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1461538461538462</v>
+        <v>0.1239669421487603</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1076923076923077</v>
+        <v>0.115702479338843</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1074380165289256</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09230769230769231</v>
+        <v>0.1074380165289256</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +858,23 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.08461538461538462</v>
+        <v>0.09917355371900827</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08461538461538462</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1065"/>
+  <dimension ref="A1:H1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -44509,8 +44509,1084 @@
         </is>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B1066" s="6" t="inlineStr">
+        <is>
+          <t>Kayak</t>
+        </is>
+      </c>
+      <c r="C1066" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1066" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1066" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1066" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1066" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1066" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kayak/senior-machine-learning-ops-engineer-berlin-52422</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="8" t="inlineStr">
+        <is>
+          <t>InnoMaster Big Data Engineering - part-time Master's Program</t>
+        </is>
+      </c>
+      <c r="B1067" s="8" t="inlineStr">
+        <is>
+          <t>Innogames</t>
+        </is>
+      </c>
+      <c r="C1067" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1067" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1067" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1067" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1067" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1067" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/innogames/innomaster-big-data-engineering-part-time-masters-program-hamburg-384251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B1068" s="6" t="inlineStr">
+        <is>
+          <t>Gropyus</t>
+        </is>
+      </c>
+      <c r="C1068" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1068" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1068" s="6" t="inlineStr">
+        <is>
+          <t>Python、dbt、Azure、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1068" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1068" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1068" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gropyus/data-engineer-all-genders-berlin-berlin-461780</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="8" t="inlineStr">
+        <is>
+          <t>Visiting Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B1069" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1069" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1069" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1069" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1069" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1069" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1069" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/visiting-finance-analyst-berlin-181258</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="6" t="inlineStr">
+        <is>
+          <t>Specialist Account Executive, Data Security</t>
+        </is>
+      </c>
+      <c r="B1070" s="6" t="inlineStr">
+        <is>
+          <t>zscaler</t>
+        </is>
+      </c>
+      <c r="C1070" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1070" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1070" s="6" t="inlineStr"/>
+      <c r="F1070" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1070" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1070" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/zscaler/specialist-account-executive-data-security-city-of-london-corporation-gbr-418257</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Data Platform</t>
+        </is>
+      </c>
+      <c r="B1071" s="8" t="inlineStr">
+        <is>
+          <t>Addepar1</t>
+        </is>
+      </c>
+      <c r="C1071" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1071" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1071" s="8" t="inlineStr">
+        <is>
+          <t>Python、Spark、Snowflake、AWS</t>
+        </is>
+      </c>
+      <c r="F1071" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1071" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1071" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/addepar1/engineering-manager-data-platform-edinburgh-137521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="6" t="inlineStr">
+        <is>
+          <t>Alts Data Ops Analyst</t>
+        </is>
+      </c>
+      <c r="B1072" s="6" t="inlineStr">
+        <is>
+          <t>Addepar1</t>
+        </is>
+      </c>
+      <c r="C1072" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1072" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1072" s="6" t="inlineStr"/>
+      <c r="F1072" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1072" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1072" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/addepar1/alts-data-ops-analyst-edinburgh-129143</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst: Retail Media</t>
+        </is>
+      </c>
+      <c r="B1073" s="8" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C1073" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1073" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1073" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、A/B测试、pandas</t>
+        </is>
+      </c>
+      <c r="F1073" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1073" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1073" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/constructor/remote-data-analyst-retail-media-360467</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="6" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer: Machine Learning Infrastructure</t>
+        </is>
+      </c>
+      <c r="B1074" s="6" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C1074" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1074" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1074" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1074" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1074" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1074" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/constructor/remote-senior-backend-engineer-machine-learning-infrastructure-169800</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="8" t="inlineStr">
+        <is>
+          <t>Working Student - Market &amp; Business Intelligence (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1075" s="8" t="inlineStr">
+        <is>
+          <t>Ionity Gmbh</t>
+        </is>
+      </c>
+      <c r="C1075" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1075" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1075" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1075" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1075" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1075" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ionity-gmbh/remote-working-student-market-business-intelligence-277530</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer, Agents &amp; Reasoning</t>
+        </is>
+      </c>
+      <c r="B1076" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1076" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1076" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1076" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1076" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1076" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1076" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/ml-engineer-agents-reasoning-berlin-356036</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="8" t="inlineStr">
+        <is>
+          <t>Founding Forward-Deployed ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1077" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1077" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1077" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1077" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1077" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1077" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1077" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-forward-deployed-ml-engineer-295402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="6" t="inlineStr">
+        <is>
+          <t>Senior Geospatial Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1078" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1078" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1078" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1078" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F1078" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1078" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1078" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-senior-geospatial-machine-learning-engineer-452654</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="8" t="inlineStr">
+        <is>
+          <t>ML Engineer - Robotics</t>
+        </is>
+      </c>
+      <c r="B1079" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1079" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1079" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1079" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1079" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1079" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1079" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-ml-engineer-robotics-485884</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="6" t="inlineStr">
+        <is>
+          <t>Founding Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1080" s="6" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1080" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1080" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1080" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1080" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1080" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1080" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/remote-founding-machine-learning-engineer-379036</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="8" t="inlineStr">
+        <is>
+          <t>Bachelorarbeit (m/w/d) – KI-gestützte Automatisierung des Datenimports im Data Warehouse</t>
+        </is>
+      </c>
+      <c r="B1081" s="8" t="inlineStr">
+        <is>
+          <t>Accantec Group</t>
+        </is>
+      </c>
+      <c r="C1081" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1081" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1081" s="8" t="inlineStr">
+        <is>
+          <t>SQL、ETL</t>
+        </is>
+      </c>
+      <c r="F1081" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1081" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1081" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/accantec-group/bachelorarbeit-ki-gestutzte-automatisierung-des-datenimports-im-data-warehouse-heidelberg-197865</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="6" t="inlineStr">
+        <is>
+          <t>Working Student Modeled Data</t>
+        </is>
+      </c>
+      <c r="B1082" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C1082" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1082" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1082" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、统计学</t>
+        </is>
+      </c>
+      <c r="F1082" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1082" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1082" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/working-student-modeled-data-hamburg-37351</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="8" t="inlineStr">
+        <is>
+          <t>Scientific Data Architect - Germany Expression of interest</t>
+        </is>
+      </c>
+      <c r="B1083" s="8" t="inlineStr">
+        <is>
+          <t>Tetrascience</t>
+        </is>
+      </c>
+      <c r="C1083" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1083" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1083" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F1083" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1083" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1083" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tetrascience/scientific-data-architect-germany-expression-of-interest-dusseldorf-260904</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="6" t="inlineStr">
+        <is>
+          <t>Scientific Data Architect - Germany Expression of interest</t>
+        </is>
+      </c>
+      <c r="B1084" s="6" t="inlineStr">
+        <is>
+          <t>Tetrascience</t>
+        </is>
+      </c>
+      <c r="C1084" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1084" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1084" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F1084" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1084" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1084" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tetrascience/scientific-data-architect-germany-expression-of-interest-darmstadt-440802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="8" t="inlineStr">
+        <is>
+          <t>Scientific Data Architect - Germany Expression of interest</t>
+        </is>
+      </c>
+      <c r="B1085" s="8" t="inlineStr">
+        <is>
+          <t>Tetrascience</t>
+        </is>
+      </c>
+      <c r="C1085" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1085" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1085" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、机器学习</t>
+        </is>
+      </c>
+      <c r="F1085" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1085" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1085" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tetrascience/scientific-data-architect-germany-expression-of-interest-frankfurt-am-main-457514</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="6" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (AI Research/ Portability)</t>
+        </is>
+      </c>
+      <c r="B1086" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C1086" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1086" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1086" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1086" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1086" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1086" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nebius/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare Statistical Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1087" s="8" t="inlineStr">
+        <is>
+          <t>SmartLight Analytics</t>
+        </is>
+      </c>
+      <c r="C1087" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1087" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1087" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1087" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1087" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1087" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/smartlight-analytics/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="6" t="inlineStr">
+        <is>
+          <t>Chargeback Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1088" s="6" t="inlineStr">
+        <is>
+          <t>Sezzle</t>
+        </is>
+      </c>
+      <c r="C1088" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1088" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1088" s="6" t="inlineStr"/>
+      <c r="F1088" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1088" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1088" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sezzle/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="8" t="inlineStr">
+        <is>
+          <t>PMO Analyst - US</t>
+        </is>
+      </c>
+      <c r="B1089" s="8" t="inlineStr">
+        <is>
+          <t>PMO Strategies / Global Transformation Group</t>
+        </is>
+      </c>
+      <c r="C1089" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1089" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1089" s="8" t="inlineStr"/>
+      <c r="F1089" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1089" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1089" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pmo-strategies-global-transformation-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1090" s="6" t="inlineStr">
+        <is>
+          <t>Newsela</t>
+        </is>
+      </c>
+      <c r="C1090" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1090" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1090" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1090" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1090" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1090" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/newsela/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B1091" s="8" t="inlineStr">
+        <is>
+          <t>Dane Street</t>
+        </is>
+      </c>
+      <c r="C1091" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1091" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1091" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Power BI、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1091" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1091" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H1091" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/danestreet/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1065"/>
+  <autoFilter ref="A1:H1091"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44571,19 +45647,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>456</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3">
@@ -44596,7 +45672,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0</v>
@@ -44605,7 +45681,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -44615,19 +45691,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -44659,7 +45735,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>14</v>
@@ -44671,7 +45747,7 @@
         <v>78</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1091</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-08 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-08 22:55 UTC</t>
+          <t>数据日期 2026-08-09 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-09 22:58 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1090</v>
+        <v>1113</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4214876033057851</v>
+        <v>0.3504273504273504</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.371900826446281</v>
+        <v>0.3504273504273504</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3223140495867768</v>
+        <v>0.2905982905982906</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3223140495867768</v>
+        <v>0.3504273504273504</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2809917355371901</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.231404958677686</v>
+        <v>0.188034188034188</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1652892561983471</v>
+        <v>0.1452991452991453</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0743801652892562</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1239669421487603</v>
+        <v>0.1196581196581197</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>14</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.115702479338843</v>
+        <v>0.1196581196581197</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1074380165289256</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1074380165289256</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="19">
@@ -861,20 +861,20 @@
         <v>12</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09917355371900827</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.09401709401709402</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1091"/>
+  <dimension ref="A1:H1114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -45585,8 +45585,934 @@
         </is>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent Business Analytics &amp; Management Reporting (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1092" s="6" t="inlineStr">
+        <is>
+          <t>Deutsche GigaNetz GmbH</t>
+        </is>
+      </c>
+      <c r="C1092" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1092" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1092" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1092" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1092" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1092" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/deutsche-giganetz-gmbh/werkstudent-business-analytics-management-reporting-hamburg-401031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="8" t="inlineStr">
+        <is>
+          <t>Visiting Finance Analyst</t>
+        </is>
+      </c>
+      <c r="B1093" s="8" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="C1093" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1093" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1093" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1093" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1093" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1093" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/clera/visiting-finance-analyst-berlin-88065</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="6" t="inlineStr">
+        <is>
+          <t>Product Manager (Data) - Fluent French &amp; English</t>
+        </is>
+      </c>
+      <c r="B1094" s="6" t="inlineStr">
+        <is>
+          <t>Kaluza</t>
+        </is>
+      </c>
+      <c r="C1094" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1094" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1094" s="6" t="inlineStr"/>
+      <c r="F1094" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1094" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1094" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/kaluza/product-manager-data-fluent-french-english-bristol-london-496588</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="8" t="inlineStr">
+        <is>
+          <t>Senior Process Improvement Analyst (12 Month Fixed Term Contract)</t>
+        </is>
+      </c>
+      <c r="B1095" s="8" t="inlineStr">
+        <is>
+          <t>Ovoenergy</t>
+        </is>
+      </c>
+      <c r="C1095" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1095" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1095" s="8" t="inlineStr"/>
+      <c r="F1095" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1095" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1095" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ovoenergy/senior-process-improvement-analyst-12-month-fixed-term-contract-any-of-our-offices-143187</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="6" t="inlineStr">
+        <is>
+          <t>Technical Product Manager (Data Platform)</t>
+        </is>
+      </c>
+      <c r="B1096" s="6" t="inlineStr">
+        <is>
+          <t>Globalwebindex</t>
+        </is>
+      </c>
+      <c r="C1096" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1096" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1096" s="6" t="inlineStr">
+        <is>
+          <t>dbt、Airflow、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F1096" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1096" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1096" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/globalwebindex/technical-product-manager-data-platform-london-427659</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="8" t="inlineStr">
+        <is>
+          <t>Technical Product Manager (Data Platform)</t>
+        </is>
+      </c>
+      <c r="B1097" s="8" t="inlineStr">
+        <is>
+          <t>Globalwebindex</t>
+        </is>
+      </c>
+      <c r="C1097" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1097" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1097" s="8" t="inlineStr">
+        <is>
+          <t>dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1097" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1097" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1097" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/globalwebindex/technical-product-manager-data-platform-athens-gr-300766</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="6" t="inlineStr">
+        <is>
+          <t>C++ Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B1098" s="6" t="inlineStr">
+        <is>
+          <t>Worldquant</t>
+        </is>
+      </c>
+      <c r="C1098" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1098" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1098" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1098" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1098" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1098" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/worldquant/c-software-engineer-data-platform-london-409704</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="8" t="inlineStr">
+        <is>
+          <t>Sales Manager - Data Platforms</t>
+        </is>
+      </c>
+      <c r="B1099" s="8" t="inlineStr">
+        <is>
+          <t>Intersystems</t>
+        </is>
+      </c>
+      <c r="C1099" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1099" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1099" s="8" t="inlineStr"/>
+      <c r="F1099" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1099" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1099" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/intersystems/sales-manager-data-platforms-248810</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="6" t="inlineStr">
+        <is>
+          <t>Software Developer - Risk Data Pipelines</t>
+        </is>
+      </c>
+      <c r="B1100" s="6" t="inlineStr">
+        <is>
+          <t>Squarepointcapital</t>
+        </is>
+      </c>
+      <c r="C1100" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1100" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1100" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、pandas</t>
+        </is>
+      </c>
+      <c r="F1100" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1100" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1100" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/squarepointcapital/software-developer-risk-data-pipelines-bangalore-montreal-warsaw-242689</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer - Data Pipelines (Python)</t>
+        </is>
+      </c>
+      <c r="B1101" s="8" t="inlineStr">
+        <is>
+          <t>Squarepointcapital</t>
+        </is>
+      </c>
+      <c r="C1101" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1101" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1101" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS</t>
+        </is>
+      </c>
+      <c r="F1101" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1101" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1101" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/squarepointcapital/software-developer-data-pipelines-python-london-montreal-madrid-bangalore-66834</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Real time analytics</t>
+        </is>
+      </c>
+      <c r="B1102" s="6" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C1102" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1102" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1102" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1102" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1102" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1102" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/aircall/senior-data-engineer-real-time-analytics-london-office-417529</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="8" t="inlineStr">
+        <is>
+          <t>Director Enterprise IT &amp; Data (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1103" s="8" t="inlineStr">
+        <is>
+          <t>Isaraerospace</t>
+        </is>
+      </c>
+      <c r="C1103" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1103" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1103" s="8" t="inlineStr"/>
+      <c r="F1103" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1103" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1103" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/isaraerospace/director-enterprise-it-data-parsdorf-bavaria-351383</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="6" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer Lead</t>
+        </is>
+      </c>
+      <c r="B1104" s="6" t="inlineStr">
+        <is>
+          <t>Sutherland</t>
+        </is>
+      </c>
+      <c r="C1104" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1104" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1104" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Looker、Airflow、GCP、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F1104" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1104" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1104" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sutherland/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="8" t="inlineStr">
+        <is>
+          <t>Senior Oracle Cloud HCM Technical Analyst</t>
+        </is>
+      </c>
+      <c r="B1105" s="8" t="inlineStr">
+        <is>
+          <t>Fortive</t>
+        </is>
+      </c>
+      <c r="C1105" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1105" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1105" s="8" t="inlineStr"/>
+      <c r="F1105" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1105" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1105" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fortive/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="6" t="inlineStr">
+        <is>
+          <t>Document Management and Archiving Support Analyst</t>
+        </is>
+      </c>
+      <c r="B1106" s="6" t="inlineStr">
+        <is>
+          <t>Highmark Health</t>
+        </is>
+      </c>
+      <c r="C1106" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1106" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1106" s="6" t="inlineStr"/>
+      <c r="F1106" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1106" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1106" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/highmark-health/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="8" t="inlineStr">
+        <is>
+          <t>Digital Analytics Senior</t>
+        </is>
+      </c>
+      <c r="B1107" s="8" t="inlineStr">
+        <is>
+          <t>Gauge</t>
+        </is>
+      </c>
+      <c r="C1107" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1107" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1107" s="8" t="inlineStr"/>
+      <c r="F1107" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1107" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1107" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gauge/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="6" t="inlineStr">
+        <is>
+          <t>Language Data Quality Reviewer for Swiss German (Freelance/Task-based)</t>
+        </is>
+      </c>
+      <c r="B1108" s="6" t="inlineStr">
+        <is>
+          <t>Volga Partners</t>
+        </is>
+      </c>
+      <c r="C1108" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1108" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1108" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1108" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1108" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1108" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/volga-partners/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="8" t="inlineStr">
+        <is>
+          <t>Risk Analyst</t>
+        </is>
+      </c>
+      <c r="B1109" s="8" t="inlineStr">
+        <is>
+          <t>Public Partnerships LLC</t>
+        </is>
+      </c>
+      <c r="C1109" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1109" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1109" s="8" t="inlineStr"/>
+      <c r="F1109" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1109" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1109" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/public-partnerships-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="6" t="inlineStr">
+        <is>
+          <t>Sr. Bank Reconciliation Analyst</t>
+        </is>
+      </c>
+      <c r="B1110" s="6" t="inlineStr">
+        <is>
+          <t>Selene</t>
+        </is>
+      </c>
+      <c r="C1110" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1110" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1110" s="6" t="inlineStr"/>
+      <c r="F1110" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1110" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1110" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/selene/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Credit Risk Analytics</t>
+        </is>
+      </c>
+      <c r="B1111" s="8" t="inlineStr">
+        <is>
+          <t>Prosper</t>
+        </is>
+      </c>
+      <c r="C1111" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1111" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1111" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1111" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1111" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1111" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/prosper/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="6" t="inlineStr">
+        <is>
+          <t>VP Finance Data Strategy &amp; Governance</t>
+        </is>
+      </c>
+      <c r="B1112" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1112" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1112" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1112" s="6" t="inlineStr"/>
+      <c r="F1112" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1112" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1112" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/empower-com/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="8" t="inlineStr">
+        <is>
+          <t>125SA-123TEL | Collections Analyst</t>
+        </is>
+      </c>
+      <c r="B1113" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1113" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1113" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1113" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1113" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1113" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1113" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/talentcross/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="6" t="inlineStr">
+        <is>
+          <t>Senior Principal Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1114" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1114" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1114" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1114" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1114" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1114" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H1114" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/beigene/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1091"/>
+  <autoFilter ref="A1:H1114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45647,19 +46573,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>118</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3">
@@ -45691,19 +46617,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
@@ -45713,7 +46639,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -45725,7 +46651,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -45735,7 +46661,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>14</v>
@@ -45744,10 +46670,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
@@ -45807,13 +46733,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-09 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-09 22:58 UTC</t>
+          <t>数据日期 2026-08-10 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-10 23:05 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1113</v>
+        <v>1161</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3504273504273504</v>
+        <v>0.3455882352941176</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3504273504273504</v>
+        <v>0.3602941176470588</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2905982905982906</v>
+        <v>0.3161764705882353</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3504273504273504</v>
+        <v>0.3161764705882353</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.282051282051282</v>
+        <v>0.3161764705882353</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.188034188034188</v>
+        <v>0.2058823529411765</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1452991452991453</v>
+        <v>0.1691176470588235</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1196581196581197</v>
+        <v>0.1323529411764706</v>
       </c>
     </row>
     <row r="16">
@@ -819,62 +819,62 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1196581196581197</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1102941176470588</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.1102941176470588</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09401709401709402</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1114"/>
+  <dimension ref="A1:H1162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -46511,8 +46511,1976 @@
         </is>
       </c>
     </row>
+    <row r="1115">
+      <c r="A1115" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Consumer</t>
+        </is>
+      </c>
+      <c r="B1115" s="8" t="inlineStr">
+        <is>
+          <t>wolt</t>
+        </is>
+      </c>
+      <c r="C1115" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1115" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1115" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、Snowflake、dbt、Airflow、A/B测试、ETL</t>
+        </is>
+      </c>
+      <c r="F1115" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1115" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1115" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt/senior-analytics-engineer-consumer-berlin-101121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B1116" s="6" t="inlineStr">
+        <is>
+          <t>wolt</t>
+        </is>
+      </c>
+      <c r="C1116" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1116" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1116" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、统计学</t>
+        </is>
+      </c>
+      <c r="F1116" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1116" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1116" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt/analytics-manager-marketing-analytics-berlin-263899</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Marketing Analyst (m/f/d) - Hamburg</t>
+        </is>
+      </c>
+      <c r="B1117" s="8" t="inlineStr">
+        <is>
+          <t>freenow</t>
+        </is>
+      </c>
+      <c r="C1117" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1117" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1117" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、R、统计学</t>
+        </is>
+      </c>
+      <c r="F1117" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1117" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1117" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/freenow/senior-marketing-analyst-hamburg-370149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="6" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (JetBrains Research)</t>
+        </is>
+      </c>
+      <c r="B1118" s="6" t="inlineStr">
+        <is>
+          <t>jetbrains</t>
+        </is>
+      </c>
+      <c r="C1118" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1118" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1118" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1118" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1118" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1118" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jetbrains/remote-senior-ml-engineer-jetbrains-research-270325</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Machine Learning Developer (Junie)</t>
+        </is>
+      </c>
+      <c r="B1119" s="8" t="inlineStr">
+        <is>
+          <t>jetbrains</t>
+        </is>
+      </c>
+      <c r="C1119" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1119" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1119" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1119" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1119" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1119" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jetbrains/remote-senior-machine-learning-developer-junie-361256</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="6" t="inlineStr">
+        <is>
+          <t>Founding ML Engineer (Spectrum)</t>
+        </is>
+      </c>
+      <c r="B1120" s="6" t="inlineStr">
+        <is>
+          <t>jetbrains</t>
+        </is>
+      </c>
+      <c r="C1120" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1120" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1120" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1120" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1120" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1120" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jetbrains/remote-founding-ml-engineer-spectrum-228679</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1121" s="8" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="C1121" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1121" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1121" s="8" t="inlineStr">
+        <is>
+          <t>Python、Spark、AWS、Azure、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1121" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1121" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1121" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/awin/machine-learning-engineer-berlin-berlin-munchen-bavaria-180645</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1122" s="6" t="inlineStr">
+        <is>
+          <t>autoscout24</t>
+        </is>
+      </c>
+      <c r="C1122" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1122" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1122" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1122" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1122" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1122" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/autoscout24/principal-data-scientist-481617</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1123" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C1123" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1123" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1123" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、机器学习</t>
+        </is>
+      </c>
+      <c r="F1123" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1123" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1123" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/machine-learning-consultant-munich-170946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="6" t="inlineStr">
+        <is>
+          <t>Finance Data &amp; Systems Analyst (FP&amp;A)</t>
+        </is>
+      </c>
+      <c r="B1124" s="6" t="inlineStr">
+        <is>
+          <t>Lovehoney Group</t>
+        </is>
+      </c>
+      <c r="C1124" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1124" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1124" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1124" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1124" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1124" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/lovehoney-group/finance-data-systems-analyst-fpa-berlin-224340</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Campaign Data Management</t>
+        </is>
+      </c>
+      <c r="B1125" s="8" t="inlineStr">
+        <is>
+          <t>Blue Incite GmbH (A company of Allianz)</t>
+        </is>
+      </c>
+      <c r="C1125" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1125" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1125" s="8" t="inlineStr"/>
+      <c r="F1125" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1125" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1125" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/blue-incite-gmbh-a-company-of-allianz/werkstudent-campaign-data-management-munich-406349</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="6" t="inlineStr">
+        <is>
+          <t>AI-Native Business Analyst - DACH</t>
+        </is>
+      </c>
+      <c r="B1126" s="6" t="inlineStr">
+        <is>
+          <t>Oper</t>
+        </is>
+      </c>
+      <c r="C1126" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1126" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1126" s="6" t="inlineStr"/>
+      <c r="F1126" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1126" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/oper/ai-native-business-analyst-dach-mannheim-198122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst &amp; Design (m/w/d) · Freelance · remote</t>
+        </is>
+      </c>
+      <c r="B1127" s="8" t="inlineStr">
+        <is>
+          <t>ZWW Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C1127" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1127" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1127" s="8" t="inlineStr"/>
+      <c r="F1127" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1127" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1127" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/zww-deutschland-gmbh/business-analyst-design-freelance-remote-karlsruhe-347499</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="6" t="inlineStr">
+        <is>
+          <t>Senior SAP ABAP Developer - HR Data Migration Support (Freelance, Remote)</t>
+        </is>
+      </c>
+      <c r="B1128" s="6" t="inlineStr">
+        <is>
+          <t>Sidekick Network GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1128" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1128" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1128" s="6" t="inlineStr"/>
+      <c r="F1128" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1128" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1128" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sidekick-network-gmbh-co-kg/senior-sap-abap-developer-hr-data-migration-support-freelance-remote-bonn-24417</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d) - Azure Cloud &amp; MS Fabric</t>
+        </is>
+      </c>
+      <c r="B1129" s="8" t="inlineStr">
+        <is>
+          <t>Doehle</t>
+        </is>
+      </c>
+      <c r="C1129" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1129" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1129" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1129" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1129" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1129" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/doehle/data-engineer-azure-cloud-ms-fabric-hamburg-94631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="6" t="inlineStr">
+        <is>
+          <t>Senior Snowflake Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1130" s="6" t="inlineStr">
+        <is>
+          <t>Jobrad Loop</t>
+        </is>
+      </c>
+      <c r="C1130" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1130" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1130" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、Snowflake、dbt、Airflow、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1130" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1130" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1130" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobrad-loop/senior-snowflake-data-engineer-munchen-299676</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1131" s="8" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1131" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1131" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1131" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1131" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1131" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1131" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-platform-engineer-working-student-munchen-4377</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="6" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics Lead</t>
+        </is>
+      </c>
+      <c r="B1132" s="6" t="inlineStr">
+        <is>
+          <t>Openfx</t>
+        </is>
+      </c>
+      <c r="C1132" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1132" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1132" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Snowflake、dbt、Airflow、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1132" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1132" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1132" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/openfx/data-science-analytics-lead-miami-usa-dubai-uae-bengaluru-india-382681</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager or Director, Data &amp; AI Delivery Lead (Life Sciences &amp; Health)</t>
+        </is>
+      </c>
+      <c r="B1133" s="8" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1133" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1133" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1133" s="8" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1133" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1133" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1133" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/senior-manager-or-director-data-ai-delivery-lead-life-sciences-health-london-246854</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager or Director, Data &amp; AI Delivery Lead (Financial Services)</t>
+        </is>
+      </c>
+      <c r="B1134" s="6" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1134" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1134" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1134" s="6" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1134" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1134" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1134" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/senior-manager-or-director-data-ai-delivery-lead-financial-services-london-454251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager or Director, Data &amp; AI Delivery Lead (Central Government)</t>
+        </is>
+      </c>
+      <c r="B1135" s="8" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1135" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1135" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1135" s="8" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1135" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1135" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1135" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/senior-manager-or-director-data-ai-delivery-lead-central-government-london-364919</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1136" s="6" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1136" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1136" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1136" s="6" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1136" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1136" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1136" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/senior-manager-data-engineering-london-414352</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1137" s="8" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1137" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1137" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1137" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1137" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1137" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1137" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/machine-learning-engineer-london-86760</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Products Engineer</t>
+        </is>
+      </c>
+      <c r="B1138" s="6" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1138" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1138" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1138" s="6" t="inlineStr"/>
+      <c r="F1138" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1138" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1138" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/remote-lead-data-products-engineer-380765</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (London, UK)</t>
+        </is>
+      </c>
+      <c r="B1139" s="8" t="inlineStr">
+        <is>
+          <t>B Lab</t>
+        </is>
+      </c>
+      <c r="C1139" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1139" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1139" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F1139" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1139" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1139" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/b-lab/data-analyst-london-uk-8381</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="6" t="inlineStr">
+        <is>
+          <t>Director, Data Strategy</t>
+        </is>
+      </c>
+      <c r="B1140" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1140" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1140" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1140" s="6" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1140" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1140" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1140" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/director-data-strategy-london-194188</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="8" t="inlineStr">
+        <is>
+          <t>AI Research Engineer (Pre-training - LLM &amp; Multi-Modal) - 100% Remote Worldwide</t>
+        </is>
+      </c>
+      <c r="B1141" s="8" t="inlineStr">
+        <is>
+          <t>Tether Operations Limited</t>
+        </is>
+      </c>
+      <c r="C1141" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1141" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1141" s="8" t="inlineStr"/>
+      <c r="F1141" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1141" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1141" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tether-operations-limited/ai-research-engineer-pre-training-llm-multi-modal-100-remote-worldwide-united-kindom-168124</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1142" s="6" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1142" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1142" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1142" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、R、ETL</t>
+        </is>
+      </c>
+      <c r="F1142" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1142" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1142" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-engineer-working-student-koln-454384</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Consumer</t>
+        </is>
+      </c>
+      <c r="B1143" s="8" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C1143" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1143" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1143" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、Snowflake、dbt、Airflow、A/B测试、ETL</t>
+        </is>
+      </c>
+      <c r="F1143" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1143" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1143" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/senior-analytics-engineer-consumer-berlin-462072</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="6" t="inlineStr">
+        <is>
+          <t>Product Owner Data &amp; AI (m/f/d) – fluege.de</t>
+        </is>
+      </c>
+      <c r="B1144" s="6" t="inlineStr">
+        <is>
+          <t>TC Flights Germany GmbH</t>
+        </is>
+      </c>
+      <c r="C1144" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1144" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1144" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F1144" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1144" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1144" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tc-flights-germany-gmbh/product-owner-data-ai-fluegede-leipzig-104383</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Science Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1145" s="8" t="inlineStr">
+        <is>
+          <t>cigus GmbH</t>
+        </is>
+      </c>
+      <c r="C1145" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1145" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1145" s="8" t="inlineStr">
+        <is>
+          <t>Python、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1145" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1145" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1145" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cigus-gmbh/ai-data-science-engineer-oberkochen-124893</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent:in Generative Engine Optimization (GEO) Data &amp; Backend (m/w/d) vor Ort | hybrid</t>
+        </is>
+      </c>
+      <c r="B1146" s="6" t="inlineStr">
+        <is>
+          <t>Palmer Hargreaves GmbH</t>
+        </is>
+      </c>
+      <c r="C1146" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1146" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1146" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1146" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1146" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/palmer-hargreaves-gmbh/werkstudentin-generative-engine-optimization-geo-data-backend-vor-ort-hybrid-cologne-324217</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="8" t="inlineStr">
+        <is>
+          <t>Working Student Data Engineering (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1147" s="8" t="inlineStr">
+        <is>
+          <t>Pricenow</t>
+        </is>
+      </c>
+      <c r="C1147" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1147" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1147" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F1147" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1147" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1147" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pricenow/working-student-data-engineering-munich-60415</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="6" t="inlineStr">
+        <is>
+          <t>Business Analytics Intern</t>
+        </is>
+      </c>
+      <c r="B1148" s="6" t="inlineStr">
+        <is>
+          <t>trawa</t>
+        </is>
+      </c>
+      <c r="C1148" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1148" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1148" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1148" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1148" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1148" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trawa/business-analytics-intern-berlin-469587</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Energy Data Scientist – Energiedaten &amp; Automatisierung (MSB) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1149" s="8" t="inlineStr">
+        <is>
+          <t>VREY</t>
+        </is>
+      </c>
+      <c r="C1149" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1149" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1149" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1149" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1149" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1149" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vrey/junior-energy-data-scientist-energiedaten-automatisierung-msb-berlin-113278</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineering Lead, Agentic Infrastructure</t>
+        </is>
+      </c>
+      <c r="B1150" s="6" t="inlineStr">
+        <is>
+          <t>Vivenu</t>
+        </is>
+      </c>
+      <c r="C1150" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1150" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1150" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1150" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1150" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1150" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vivenu/remote-data-engineering-lead-agentic-infrastructure-320633</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="8" t="inlineStr">
+        <is>
+          <t>Lead Engineer - Applied AI &amp; Data Products</t>
+        </is>
+      </c>
+      <c r="B1151" s="8" t="inlineStr">
+        <is>
+          <t>Squer</t>
+        </is>
+      </c>
+      <c r="C1151" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1151" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1151" s="8" t="inlineStr"/>
+      <c r="F1151" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1151" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1151" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/squer/lead-engineer-applied-ai-data-products-munchen-296872</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer - Data Migration &amp; Lakehouse</t>
+        </is>
+      </c>
+      <c r="B1152" s="6" t="inlineStr">
+        <is>
+          <t>Squer</t>
+        </is>
+      </c>
+      <c r="C1152" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1152" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1152" s="6" t="inlineStr"/>
+      <c r="F1152" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1152" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/squer/lead-data-engineer-data-migration-lakehouse-munchen-495833</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="8" t="inlineStr">
+        <is>
+          <t>Content Solutions Analyst I</t>
+        </is>
+      </c>
+      <c r="B1153" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1153" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1153" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1153" s="8" t="inlineStr"/>
+      <c r="F1153" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1153" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1153" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cotiviti/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="6" t="inlineStr">
+        <is>
+          <t>Associate Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1154" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1154" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1154" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1154" s="6" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F1154" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1154" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1154" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zoomph/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="8" t="inlineStr">
+        <is>
+          <t>Deal Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B1155" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1155" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1155" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1155" s="8" t="inlineStr"/>
+      <c r="F1155" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1155" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1155" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/quantum-metric/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="6" t="inlineStr">
+        <is>
+          <t>Generalist for Data Annotation</t>
+        </is>
+      </c>
+      <c r="B1156" s="6" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C1156" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1156" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1156" s="6" t="inlineStr"/>
+      <c r="F1156" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1156" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1156" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1157" s="8" t="inlineStr">
+        <is>
+          <t>Applaudo Studios</t>
+        </is>
+      </c>
+      <c r="C1157" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1157" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1157" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1157" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1157" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1157" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/applaudo-studios/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="6" t="inlineStr">
+        <is>
+          <t>Media Search Analyst - Turkish (TR)</t>
+        </is>
+      </c>
+      <c r="B1158" s="6" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C1158" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1158" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1158" s="6" t="inlineStr"/>
+      <c r="F1158" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1158" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1158" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/telus-digital/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="8" t="inlineStr">
+        <is>
+          <t>Data Center Virtualization Engineer</t>
+        </is>
+      </c>
+      <c r="B1159" s="8" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies</t>
+        </is>
+      </c>
+      <c r="C1159" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1159" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1159" s="8" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1159" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1159" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1159" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bright-vision-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="6" t="inlineStr">
+        <is>
+          <t>HR Senior Total Rewards Analyst</t>
+        </is>
+      </c>
+      <c r="B1160" s="6" t="inlineStr">
+        <is>
+          <t>Silvaco</t>
+        </is>
+      </c>
+      <c r="C1160" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1160" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1160" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1160" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1160" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1160" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/silvaco/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="8" t="inlineStr">
+        <is>
+          <t>Business Intelligence Team Leader I</t>
+        </is>
+      </c>
+      <c r="B1161" s="8" t="inlineStr">
+        <is>
+          <t>Job Duck</t>
+        </is>
+      </c>
+      <c r="C1161" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1161" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1161" s="8" t="inlineStr">
+        <is>
+          <t>Power BI、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1161" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1161" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1161" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/job-duck/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1162" s="6" t="inlineStr">
+        <is>
+          <t>Zero Hash</t>
+        </is>
+      </c>
+      <c r="C1162" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1162" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1162" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1162" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1162" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H1162" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/zero-hash/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1114"/>
+  <autoFilter ref="A1:H1162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46573,19 +48541,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>488</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3">
@@ -46601,13 +48569,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -46617,7 +48585,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>47</v>
@@ -46626,10 +48594,10 @@
         <v>21</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -46648,10 +48616,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -46661,10 +48629,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>28</v>
@@ -46673,7 +48641,7 @@
         <v>79</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
@@ -46727,7 +48695,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -46739,7 +48707,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-10 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-10 23:05 UTC</t>
+          <t>数据日期 2026-08-11 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-11 23:10 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1161</v>
+        <v>1196</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,58 +710,58 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3455882352941176</v>
+        <v>0.3432835820895522</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>其他数据岗</t>
+          <t>数据分析/BI</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3602941176470588</v>
+        <v>0.3805970149253731</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3161764705882353</v>
+        <v>0.3208955223880597</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>数据分析/BI</t>
+          <t>其他数据岗</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3161764705882353</v>
+        <v>0.3358208955223881</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3161764705882353</v>
+        <v>0.3059701492537313</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2014925373134328</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1691176470588235</v>
+        <v>0.1716417910447761</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.08208955223880597</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1323529411764706</v>
+        <v>0.1417910447761194</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1044776119402985</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1102941176470588</v>
+        <v>0.09701492537313433</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1102941176470588</v>
+        <v>0.09701492537313433</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.09701492537313433</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08955223880597014</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1162"/>
+  <dimension ref="A1:H1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -48479,8 +48479,1418 @@
         </is>
       </c>
     </row>
+    <row r="1163">
+      <c r="A1163" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Science Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1163" s="8" t="inlineStr">
+        <is>
+          <t>encontec GmbH</t>
+        </is>
+      </c>
+      <c r="C1163" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1163" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1163" s="8" t="inlineStr">
+        <is>
+          <t>Python、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1163" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1163" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1163" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/encontec-gmbh/ai-data-science-manager-oberkochen-412033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="6" t="inlineStr">
+        <is>
+          <t>Restaurant Onboarding Specialist - Data Validation</t>
+        </is>
+      </c>
+      <c r="B1164" s="6" t="inlineStr">
+        <is>
+          <t>wolt</t>
+        </is>
+      </c>
+      <c r="C1164" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1164" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1164" s="6" t="inlineStr"/>
+      <c r="F1164" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1164" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1164" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt/restaurant-onboarding-specialist-data-validation-berlin-287543</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="8" t="inlineStr">
+        <is>
+          <t>Visiting Analyst (F/M/D) - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B1165" s="8" t="inlineStr">
+        <is>
+          <t>xdeck GmbH</t>
+        </is>
+      </c>
+      <c r="C1165" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1165" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1165" s="8" t="inlineStr"/>
+      <c r="F1165" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1165" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1165" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/xdeck-gmbh/visiting-analyst-summer-2027-cologne-369124</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="6" t="inlineStr">
+        <is>
+          <t>Restaurant Onboarding Specialist - Data Validation</t>
+        </is>
+      </c>
+      <c r="B1166" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C1166" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1166" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1166" s="6" t="inlineStr"/>
+      <c r="F1166" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1166" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1166" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/restaurant-onboarding-specialist-data-validation-berlin-247449</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="8" t="inlineStr">
+        <is>
+          <t>Senior Crypto Threat Analyst - Terrorism</t>
+        </is>
+      </c>
+      <c r="B1167" s="8" t="inlineStr">
+        <is>
+          <t>Elliptic</t>
+        </is>
+      </c>
+      <c r="C1167" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1167" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1167" s="8" t="inlineStr"/>
+      <c r="F1167" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1167" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1167" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elliptic/senior-crypto-threat-analyst-terrorism-london-united-kingdom-212963</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="6" t="inlineStr">
+        <is>
+          <t>Senior Crypto Threat Analyst - Sanctions</t>
+        </is>
+      </c>
+      <c r="B1168" s="6" t="inlineStr">
+        <is>
+          <t>Elliptic</t>
+        </is>
+      </c>
+      <c r="C1168" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1168" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1168" s="6" t="inlineStr"/>
+      <c r="F1168" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1168" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1168" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elliptic/senior-crypto-threat-analyst-sanctions-london-united-kingdom-467871</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data</t>
+        </is>
+      </c>
+      <c r="B1169" s="8" t="inlineStr">
+        <is>
+          <t>Elliptic</t>
+        </is>
+      </c>
+      <c r="C1169" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1169" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1169" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Spark、Airflow、AWS、Azure、GCP、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1169" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1169" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1169" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elliptic/senior-software-engineer-data-london-united-kingdom-276115</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="6" t="inlineStr">
+        <is>
+          <t>Senior Financial Planning Analyst</t>
+        </is>
+      </c>
+      <c r="B1170" s="6" t="inlineStr">
+        <is>
+          <t>Elliptic</t>
+        </is>
+      </c>
+      <c r="C1170" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1170" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1170" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1170" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1170" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1170" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elliptic/senior-financial-planning-analyst-london-united-kingdom-253441</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="8" t="inlineStr">
+        <is>
+          <t>Senior Insight analyst</t>
+        </is>
+      </c>
+      <c r="B1171" s="8" t="inlineStr">
+        <is>
+          <t>Verve</t>
+        </is>
+      </c>
+      <c r="C1171" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1171" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1171" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1171" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1171" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1171" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/verve/senior-insight-analyst-london-69619</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Machine Learning Developer (Junie)</t>
+        </is>
+      </c>
+      <c r="B1172" s="6" t="inlineStr">
+        <is>
+          <t>Jetbrains</t>
+        </is>
+      </c>
+      <c r="C1172" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1172" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1172" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1172" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1172" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1172" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jetbrains/senior-machine-learning-developer-junie-london-168371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="8" t="inlineStr">
+        <is>
+          <t>Founding ML Engineer (Spectrum)</t>
+        </is>
+      </c>
+      <c r="B1173" s="8" t="inlineStr">
+        <is>
+          <t>Jetbrains</t>
+        </is>
+      </c>
+      <c r="C1173" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1173" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1173" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1173" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1173" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1173" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jetbrains/founding-ml-engineer-spectrum-london-471148</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="6" t="inlineStr">
+        <is>
+          <t>Payment and Treasury Analyst</t>
+        </is>
+      </c>
+      <c r="B1174" s="6" t="inlineStr">
+        <is>
+          <t>Fanvue.com</t>
+        </is>
+      </c>
+      <c r="C1174" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1174" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1174" s="6" t="inlineStr"/>
+      <c r="F1174" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1174" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1174" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fanvuecom/payment-and-treasury-analyst-london-290390</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="8" t="inlineStr">
+        <is>
+          <t>Senior Payment Analyst</t>
+        </is>
+      </c>
+      <c r="B1175" s="8" t="inlineStr">
+        <is>
+          <t>Fanvue.com</t>
+        </is>
+      </c>
+      <c r="C1175" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1175" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1175" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1175" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1175" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1175" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fanvuecom/senior-payment-analyst-london-445327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="6" t="inlineStr">
+        <is>
+          <t>Senior Treasury Analyst</t>
+        </is>
+      </c>
+      <c r="B1176" s="6" t="inlineStr">
+        <is>
+          <t>Octopus Energy Group</t>
+        </is>
+      </c>
+      <c r="C1176" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1176" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1176" s="6" t="inlineStr"/>
+      <c r="F1176" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1176" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1176" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/octopus-energy-group/senior-treasury-analyst-london-gb-195079</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1177" s="8" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C1177" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1177" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1177" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F1177" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1177" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1177" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/numan/head-of-data-engineering-london-94050</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer - fully remote (working hours 5am-2pm CEST) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1178" s="6" t="inlineStr">
+        <is>
+          <t>JobLeads Careers</t>
+        </is>
+      </c>
+      <c r="C1178" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1178" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1178" s="6" t="inlineStr"/>
+      <c r="F1178" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1178" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1178" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobleads-careers/data-engineer-fully-remote-working-hours-5am-2pm-cest-313475</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) im Bereich Datenmanagement</t>
+        </is>
+      </c>
+      <c r="B1179" s="8" t="inlineStr">
+        <is>
+          <t>Wirtschaftsrat Der Cdu E V</t>
+        </is>
+      </c>
+      <c r="C1179" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1179" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1179" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1179" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1179" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1179" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wirtschaftsrat-der-cdu-e-v/werkstudent-im-bereich-datenmanagement-bundesgeschaftsstelle-berlin-379014</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Plattform Engineering (m/w/d) Azure und Databricks</t>
+        </is>
+      </c>
+      <c r="B1180" s="6" t="inlineStr">
+        <is>
+          <t>Natalie Felsinger Consulting</t>
+        </is>
+      </c>
+      <c r="C1180" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1180" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1180" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1180" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1180" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1180" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/natalie-felsinger-consulting/senior-data-plattform-engineering-azure-und-databricks-frechen-259814</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (Live Chat Channel Analytics)</t>
+        </is>
+      </c>
+      <c r="B1181" s="8" t="inlineStr">
+        <is>
+          <t>Market Cloud</t>
+        </is>
+      </c>
+      <c r="C1181" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1181" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1181" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau</t>
+        </is>
+      </c>
+      <c r="F1181" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1181" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1181" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/market-cloud/data-analyst-live-chat-channel-analytics-eschborn-90500</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="6" t="inlineStr">
+        <is>
+          <t>Data Center Engineer II</t>
+        </is>
+      </c>
+      <c r="B1182" s="6" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C1182" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1182" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1182" s="6" t="inlineStr"/>
+      <c r="F1182" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1182" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1182" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/digitalocean/data-center-engineer-ii-41239</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – PostgreSQL (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1183" s="8" t="inlineStr">
+        <is>
+          <t>IP Dynamics GmbH</t>
+        </is>
+      </c>
+      <c r="C1183" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1183" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1183" s="8" t="inlineStr">
+        <is>
+          <t>SQL、ETL</t>
+        </is>
+      </c>
+      <c r="F1183" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1183" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1183" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ip-dynamics-gmbh/senior-data-engineer-postgresql-hamburg-461678</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="6" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA Data Controller (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1184" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots SE - Personio</t>
+        </is>
+      </c>
+      <c r="C1184" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1184" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1184" s="6" t="inlineStr"/>
+      <c r="F1184" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1184" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1184" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se-personio/sap-s-4hana-data-controller-germany-munich-hq-337077</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="8" t="inlineStr">
+        <is>
+          <t>Head of Talent Growth &amp; Analytics (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1185" s="8" t="inlineStr">
+        <is>
+          <t>Agile Robots SE - Personio</t>
+        </is>
+      </c>
+      <c r="C1185" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1185" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1185" s="8" t="inlineStr"/>
+      <c r="F1185" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1185" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1185" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se-personio/head-of-talent-growth-analytics-germany-munich-hq-207726</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="6" t="inlineStr">
+        <is>
+          <t>Data Quality Coordinator (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1186" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots SE - Personio</t>
+        </is>
+      </c>
+      <c r="C1186" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1186" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1186" s="6" t="inlineStr"/>
+      <c r="F1186" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1186" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1186" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se-personio/data-quality-coordinator-germany-munich-hq-380440</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="8" t="inlineStr">
+        <is>
+          <t>Team Lead Data Products &amp; Analytics (gn)</t>
+        </is>
+      </c>
+      <c r="B1187" s="8" t="inlineStr">
+        <is>
+          <t>Bikeleasing</t>
+        </is>
+      </c>
+      <c r="C1187" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1187" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1187" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F1187" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1187" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1187" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bikeleasing/remote-team-lead-data-products-analytics-gn-398648</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="6" t="inlineStr">
+        <is>
+          <t>Fraud Analyst - Fully Remote | Upto $55/hr</t>
+        </is>
+      </c>
+      <c r="B1188" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1188" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1188" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1188" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1188" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1188" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1188" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer - AI Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B1189" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1189" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1189" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1189" s="8" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="F1189" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1189" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1189" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="6" t="inlineStr">
+        <is>
+          <t>Data Science Expert - AI Evaluation</t>
+        </is>
+      </c>
+      <c r="B1190" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1190" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1190" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1190" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1190" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1190" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1190" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="8" t="inlineStr">
+        <is>
+          <t>Subject Matter Expert – Chart &amp; Data Visualization Analysis (AI Training)</t>
+        </is>
+      </c>
+      <c r="B1191" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1191" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1191" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1191" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F1191" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1191" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1191" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="6" t="inlineStr">
+        <is>
+          <t>Banking Analyst - Fully Remote | Upto $220/hr</t>
+        </is>
+      </c>
+      <c r="B1192" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1192" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1192" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1192" s="6" t="inlineStr"/>
+      <c r="F1192" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1192" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1192" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="8" t="inlineStr">
+        <is>
+          <t>Quality Assurance Analyst</t>
+        </is>
+      </c>
+      <c r="B1193" s="8" t="inlineStr">
+        <is>
+          <t>TELUS</t>
+        </is>
+      </c>
+      <c r="C1193" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1193" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1193" s="8" t="inlineStr"/>
+      <c r="F1193" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1193" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1193" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/telus/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1194" s="6" t="inlineStr">
+        <is>
+          <t>Brighty App</t>
+        </is>
+      </c>
+      <c r="C1194" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1194" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1194" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、BigQuery、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1194" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1194" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1194" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/brighty-app/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="8" t="inlineStr">
+        <is>
+          <t>Senior Security Analyst</t>
+        </is>
+      </c>
+      <c r="B1195" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1195" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1195" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1195" s="8" t="inlineStr"/>
+      <c r="F1195" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1195" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1195" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="6" t="inlineStr">
+        <is>
+          <t>Lead Senior Technical Analyst (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B1196" s="6" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C1196" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1196" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1196" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1196" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1196" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1196" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/vetsez/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="8" t="inlineStr">
+        <is>
+          <t>Market Operations Analyst (International Remote Hire)</t>
+        </is>
+      </c>
+      <c r="B1197" s="8" t="inlineStr">
+        <is>
+          <t>MEMX</t>
+        </is>
+      </c>
+      <c r="C1197" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1197" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1197" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1197" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1197" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H1197" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/memx/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1162"/>
+  <autoFilter ref="A1:H1197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48541,19 +49951,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>526</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3">
@@ -48563,7 +49973,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>5</v>
@@ -48575,7 +49985,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -48585,7 +49995,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>47</v>
@@ -48597,7 +50007,7 @@
         <v>62</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -48607,7 +50017,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -48616,10 +50026,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -48629,7 +50039,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>15</v>
@@ -48641,7 +50051,7 @@
         <v>79</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -48651,19 +50061,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -48695,7 +50105,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -48707,7 +50117,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-11 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-11 23:10 UTC</t>
+          <t>数据日期 2026-08-12 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-12 23:08 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1196</v>
+        <v>1239</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3432835820895522</v>
+        <v>0.3858267716535433</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3805970149253731</v>
+        <v>0.3700787401574803</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3208955223880597</v>
+        <v>0.2834645669291339</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3358208955223881</v>
+        <v>0.3228346456692913</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3059701492537313</v>
+        <v>0.2519685039370079</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2014925373134328</v>
+        <v>0.2283464566929134</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1716417910447761</v>
+        <v>0.1653543307086614</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.07874015748031496</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1417910447761194</v>
+        <v>0.1653543307086614</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1044776119402985</v>
+        <v>0.09448818897637795</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.09448818897637795</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.08661417322834646</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.07874015748031496</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.07874015748031496</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1197"/>
+  <dimension ref="A1:H1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -49889,8 +49889,1754 @@
         </is>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" s="6" t="inlineStr">
+        <is>
+          <t>Senior Director of Machine Learning Engineering</t>
+        </is>
+      </c>
+      <c r="B1198" s="6" t="inlineStr">
+        <is>
+          <t>hellofresh</t>
+        </is>
+      </c>
+      <c r="C1198" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1198" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1198" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1198" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1198" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1198" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hellofresh/senior-director-of-machine-learning-engineering-berlin-berlin-421334</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1199" s="8" t="inlineStr">
+        <is>
+          <t>Berlitz</t>
+        </is>
+      </c>
+      <c r="C1199" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1199" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1199" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1199" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1199" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1199" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/berlitz/remote-senior-machine-learning-engineer-284220</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B1200" s="6" t="inlineStr">
+        <is>
+          <t>Makersite GmbH</t>
+        </is>
+      </c>
+      <c r="C1200" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1200" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1200" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1200" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1200" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1200" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/makersite-gmbh/remote-senior-data-scientist-berlin-323426</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="8" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (f/m/x) - Computer Vision for Earth Observation</t>
+        </is>
+      </c>
+      <c r="B1201" s="8" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C1201" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1201" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1201" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1201" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1201" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1201" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/senior-ml-engineer-computer-vision-for-earth-observation-liveeo-gmbh-berlin-office-hybrid-284398</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1202" s="6" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C1202" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1202" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1202" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1202" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1202" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1202" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/data-engineer-liveeo-gmbh-berlin-office-hybrid-64519</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Earth Observation Data Supplier Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1203" s="8" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C1203" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1203" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1203" s="8" t="inlineStr"/>
+      <c r="F1203" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1203" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1203" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/senior-earth-observation-data-supplier-manager-liveeo-gmbh-berlin-office-hybrid-198852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="6" t="inlineStr">
+        <is>
+          <t>UAV Operations Engineer / Pilot – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1204" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1204" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1204" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1204" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1204" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1204" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1204" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/uav-operations-engineer-pilot-data-operations-all-genders-munich-176855</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="8" t="inlineStr">
+        <is>
+          <t>Field Robotics Engineer – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1205" s="8" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1205" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1205" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1205" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1205" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1205" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1205" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/field-robotics-engineer-data-operations-all-genders-munich-19785</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1206" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1206" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1206" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1206" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、BigQuery、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1206" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1206" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1206" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/data-platform-engineer-data-operations-all-genders-munich-196411</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="8" t="inlineStr">
+        <is>
+          <t>Trainee (m/w/d) KI &amp; Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B1207" s="8" t="inlineStr">
+        <is>
+          <t>planinja Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C1207" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1207" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1207" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F1207" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1207" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1207" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/planinja-consulting-gmbh/trainee-ki-marketing-analytics-cologne-480439</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="6" t="inlineStr">
+        <is>
+          <t>Senior Technology Advisory Analyst</t>
+        </is>
+      </c>
+      <c r="B1208" s="6" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C1208" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1208" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1208" s="6" t="inlineStr"/>
+      <c r="F1208" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1208" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1208" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/thoughtworks/senior-technology-advisory-analyst-newcastle-23526</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="8" t="inlineStr">
+        <is>
+          <t>Senior Technology Advisory Analyst</t>
+        </is>
+      </c>
+      <c r="B1209" s="8" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C1209" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1209" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1209" s="8" t="inlineStr"/>
+      <c r="F1209" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1209" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1209" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/thoughtworks/senior-technology-advisory-analyst-manchester-280131</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="6" t="inlineStr">
+        <is>
+          <t>Senior Technology Advisory Analyst</t>
+        </is>
+      </c>
+      <c r="B1210" s="6" t="inlineStr">
+        <is>
+          <t>thoughtworks</t>
+        </is>
+      </c>
+      <c r="C1210" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1210" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1210" s="6" t="inlineStr"/>
+      <c r="F1210" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1210" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1210" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/thoughtworks/senior-technology-advisory-analyst-london-396412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data Science (12m fixed-term contract)</t>
+        </is>
+      </c>
+      <c r="B1211" s="8" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="C1211" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1211" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1211" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、Snowflake、dbt、Airflow、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F1211" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1211" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1211" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/marshmallow/head-of-data-science-12m-fixed-term-contract-london-7439</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="6" t="inlineStr">
+        <is>
+          <t>Senior Fraud Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B1212" s="6" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="C1212" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1212" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1212" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1212" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1212" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1212" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/marshmallow/senior-fraud-intelligence-analyst-london-250083</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="8" t="inlineStr">
+        <is>
+          <t>Data Science Manager, Pricing</t>
+        </is>
+      </c>
+      <c r="B1213" s="8" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="C1213" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1213" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1213" s="8" t="inlineStr"/>
+      <c r="F1213" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1213" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1213" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/marshmallow/data-science-manager-pricing-london-133607</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1214" s="6" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="C1214" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1214" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1214" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1214" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1214" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1214" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/marshmallow/staff-data-scientist-london-319476</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="8" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1215" s="8" t="inlineStr">
+        <is>
+          <t>Marshmallow</t>
+        </is>
+      </c>
+      <c r="C1215" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1215" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1215" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1215" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1215" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1215" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/marshmallow/principal-data-scientist-london-81973</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="6" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (AI Research/ Portability)</t>
+        </is>
+      </c>
+      <c r="B1216" s="6" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C1216" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1216" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1216" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1216" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1216" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1216" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/nebius/senior-ml-engineer-ai-research-portability-365560</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="8" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (AI Research, Physical AI)</t>
+        </is>
+      </c>
+      <c r="B1217" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C1217" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1217" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1217" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1217" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1217" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1217" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/nebius/senior-ml-engineer-ai-research-physical-ai-131896</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="6" t="inlineStr">
+        <is>
+          <t>Data Strategy Associate Director</t>
+        </is>
+      </c>
+      <c r="B1218" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1218" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1218" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1218" s="6" t="inlineStr"/>
+      <c r="F1218" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1218" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1218" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/data-strategy-associate-director-london-197821</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="8" t="inlineStr">
+        <is>
+          <t>Associate Director, Applied Analytics</t>
+        </is>
+      </c>
+      <c r="B1219" s="8" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1219" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1219" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1219" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F1219" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1219" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1219" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/associate-director-applied-analytics-london-100357</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="6" t="inlineStr">
+        <is>
+          <t>Catalyst Academy - UK - Data</t>
+        </is>
+      </c>
+      <c r="B1220" s="6" t="inlineStr">
+        <is>
+          <t>Wundermanthompson</t>
+        </is>
+      </c>
+      <c r="C1220" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1220" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1220" s="6" t="inlineStr"/>
+      <c r="F1220" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1220" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1220" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wundermanthompson/catalyst-academy-uk-data-london-471424</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1221" s="8" t="inlineStr">
+        <is>
+          <t>Rewire</t>
+        </is>
+      </c>
+      <c r="C1221" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1221" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1221" s="8" t="inlineStr"/>
+      <c r="F1221" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1221" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1221" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rewire/data-engineer-heidelberg-51709</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="6" t="inlineStr">
+        <is>
+          <t>Backend Developer (m/w/d) – API &amp; Data Integrations</t>
+        </is>
+      </c>
+      <c r="B1222" s="6" t="inlineStr">
+        <is>
+          <t>Octopus Energy Group</t>
+        </is>
+      </c>
+      <c r="C1222" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1222" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1222" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1222" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1222" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1222" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/octopus-energy-group/backend-developer-api-data-integrations-berlin-de-64748</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="8" t="inlineStr">
+        <is>
+          <t>IT Business Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1223" s="8" t="inlineStr">
+        <is>
+          <t>FlexIT Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C1223" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1223" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1223" s="8" t="inlineStr"/>
+      <c r="F1223" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1223" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1223" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flexit-consulting-gmbh/it-business-analyst-koln-350765</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="6" t="inlineStr">
+        <is>
+          <t>Head of Data &amp; Analytics (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1224" s="6" t="inlineStr">
+        <is>
+          <t>FlexIT Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C1224" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1224" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1224" s="6" t="inlineStr"/>
+      <c r="F1224" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1224" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1224" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flexit-consulting-gmbh/head-of-data-analytics-koln-156541</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="8" t="inlineStr">
+        <is>
+          <t>Marketing Tech Entwickler / Data Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1225" s="8" t="inlineStr">
+        <is>
+          <t>D-I-S commerce engineering</t>
+        </is>
+      </c>
+      <c r="C1225" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1225" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1225" s="8" t="inlineStr"/>
+      <c r="F1225" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1225" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1225" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/d-i-s-commerce-engineering/marketing-tech-entwickler-data-analyst-stuttgart-132841</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1226" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1226" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1226" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1226" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1226" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1226" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1226" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-321482</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1227" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1227" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1227" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1227" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1227" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1227" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1227" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-300290</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Category Management &amp; Product Data</t>
+        </is>
+      </c>
+      <c r="B1228" s="6" t="inlineStr">
+        <is>
+          <t>ADDVANCE Consumer Health Group GmbH</t>
+        </is>
+      </c>
+      <c r="C1228" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1228" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1228" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1228" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1228" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1228" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/addvance-consumer-health-group-gmbh/werkstudent-category-management-product-data-munich-383869</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="8" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (AI Research, Physical AI)</t>
+        </is>
+      </c>
+      <c r="B1229" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C1229" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1229" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1229" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1229" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1229" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1229" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150592-senior-ml-engineer-ai-research-physical-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (Marketing Systems)</t>
+        </is>
+      </c>
+      <c r="B1230" s="6" t="inlineStr">
+        <is>
+          <t>Ruby Labs</t>
+        </is>
+      </c>
+      <c r="C1230" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1230" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1230" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1230" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1230" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1230" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150584-data-engineer-marketing-systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="8" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist (Architectures Research)</t>
+        </is>
+      </c>
+      <c r="B1231" s="8" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C1231" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1231" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1231" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1231" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1231" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1231" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150577-senior-research-scientist-architectures-research</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1232" s="6" t="inlineStr">
+        <is>
+          <t>Nielsen</t>
+        </is>
+      </c>
+      <c r="C1232" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1232" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1232" s="6" t="inlineStr"/>
+      <c r="F1232" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1232" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1232" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150549-salesforce-business-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="8" t="inlineStr">
+        <is>
+          <t>Lead Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1233" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1233" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1233" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1233" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1233" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1233" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1233" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sequoia-connect/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="6" t="inlineStr">
+        <is>
+          <t>Area Revenue Analyst</t>
+        </is>
+      </c>
+      <c r="B1234" s="6" t="inlineStr">
+        <is>
+          <t>Makeready</t>
+        </is>
+      </c>
+      <c r="C1234" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1234" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1234" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1234" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1234" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1234" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/makeready/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst, AFS Operations</t>
+        </is>
+      </c>
+      <c r="B1235" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1235" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1235" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1235" s="8" t="inlineStr"/>
+      <c r="F1235" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1235" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1235" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/altisource/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="6" t="inlineStr">
+        <is>
+          <t>Healthcare Solutions &amp; Project Analyst</t>
+        </is>
+      </c>
+      <c r="B1236" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1236" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1236" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1236" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1236" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1236" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1236" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hurc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="8" t="inlineStr">
+        <is>
+          <t>Specialized Research Analyst</t>
+        </is>
+      </c>
+      <c r="B1237" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1237" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1237" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1237" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1237" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1237" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1237" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/u-s-bank/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="6" t="inlineStr">
+        <is>
+          <t>Remote Media Search Analyst - German (CH)</t>
+        </is>
+      </c>
+      <c r="B1238" s="6" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C1238" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1238" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1238" s="6" t="inlineStr"/>
+      <c r="F1238" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1238" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1238" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/telus-digital/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1239" s="8" t="inlineStr">
+        <is>
+          <t>Guidehouse</t>
+        </is>
+      </c>
+      <c r="C1239" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1239" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1239" s="8" t="inlineStr"/>
+      <c r="F1239" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1239" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1239" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/guidehouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1240" s="6" t="inlineStr">
+        <is>
+          <t>Valtech</t>
+        </is>
+      </c>
+      <c r="C1240" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1240" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1240" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1240" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1240" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H1240" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/valtech/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1197"/>
+  <autoFilter ref="A1:H1240"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49951,19 +51697,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D2" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>115</v>
-      </c>
       <c r="F2" s="6" t="n">
-        <v>552</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3">
@@ -49995,19 +51741,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>47</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>62</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -50039,7 +51785,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>15</v>
@@ -50051,7 +51797,7 @@
         <v>79</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
@@ -50064,7 +51810,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>3</v>
@@ -50073,7 +51819,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -50105,7 +51851,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -50117,7 +51863,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -50152,16 +51898,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1273</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-12 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-12 23:08 UTC</t>
+          <t>数据日期 2026-08-13 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-13 23:11 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1239</v>
+        <v>1272</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3858267716535433</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3700787401574803</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2834645669291339</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3228346456692913</v>
+        <v>0.3170731707317073</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2519685039370079</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2283464566929134</v>
+        <v>0.1951219512195122</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1653543307086614</v>
+        <v>0.1544715447154472</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.07874015748031496</v>
+        <v>0.1544715447154472</v>
       </c>
     </row>
     <row r="15">
@@ -806,23 +806,23 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1653543307086614</v>
+        <v>0.1544715447154472</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.09448818897637795</v>
+        <v>0.1382113821138211</v>
       </c>
     </row>
     <row r="17">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.09448818897637795</v>
+        <v>0.1219512195121951</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.08661417322834646</v>
+        <v>0.1219512195121951</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.07874015748031496</v>
+        <v>0.1219512195121951</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.07874015748031496</v>
+        <v>0.0975609756097561</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1240"/>
+  <dimension ref="A1:H1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -51635,8 +51635,1354 @@
         </is>
       </c>
     </row>
+    <row r="1241">
+      <c r="A1241" s="8" t="inlineStr">
+        <is>
+          <t>Working Student Data Scientist  (d/f/m)</t>
+        </is>
+      </c>
+      <c r="B1241" s="8" t="inlineStr">
+        <is>
+          <t>limehome</t>
+        </is>
+      </c>
+      <c r="C1241" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1241" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1241" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1241" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1241" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1241" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/limehome/working-student-data-scientist-munchen-455490</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1242" s="6" t="inlineStr">
+        <is>
+          <t>Celus</t>
+        </is>
+      </c>
+      <c r="C1242" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1242" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1242" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F1242" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1242" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1242" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/celus/data-engineer-munich-germany-273750</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Data Platform Engineer (all genders) - Parental leave cover 12 months</t>
+        </is>
+      </c>
+      <c r="B1243" s="8" t="inlineStr">
+        <is>
+          <t>moia</t>
+        </is>
+      </c>
+      <c r="C1243" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1243" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1243" s="8" t="inlineStr">
+        <is>
+          <t>Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1243" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1243" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1243" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/moia/senior-data-platform-engineer-all-genders-parental-leave-cover-12-months-berlin-hamburg-226153</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Data Platform Engineer (all genders) - Parental leave cover 12 months</t>
+        </is>
+      </c>
+      <c r="B1244" s="6" t="inlineStr">
+        <is>
+          <t>moia</t>
+        </is>
+      </c>
+      <c r="C1244" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1244" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1244" s="6" t="inlineStr">
+        <is>
+          <t>Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1244" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1244" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1244" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/moia/senior-data-platform-engineer-all-genders-parental-leave-cover-12-months-hamburg-252854</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Schwerpunkt Healthcare / Krankenhaus (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1245" s="8" t="inlineStr">
+        <is>
+          <t>Lohfert &amp; Lohfert AG</t>
+        </is>
+      </c>
+      <c r="C1245" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1245" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1245" s="8" t="inlineStr"/>
+      <c r="F1245" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1245" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1245" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/lohfert-lohfert-ag/data-analyst-schwerpunkt-healthcare-krankenhaus-hamburg-129670</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="6" t="inlineStr">
+        <is>
+          <t>Data Protection Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1246" s="6" t="inlineStr">
+        <is>
+          <t>Voize</t>
+        </is>
+      </c>
+      <c r="C1246" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1246" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1246" s="6" t="inlineStr"/>
+      <c r="F1246" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1246" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1246" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/voize/data-protection-manager-berlin-60829</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Data &amp; AI Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1247" s="8" t="inlineStr">
+        <is>
+          <t>EMPA Data &amp; Management Consulting GmbH</t>
+        </is>
+      </c>
+      <c r="C1247" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1247" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1247" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1247" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1247" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1247" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/empa-data-management-consulting-gmbh/senior-data-ai-consultant-frankfurt-am-main-200542</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B1248" s="6" t="inlineStr">
+        <is>
+          <t>wolt</t>
+        </is>
+      </c>
+      <c r="C1248" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1248" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1248" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、统计学</t>
+        </is>
+      </c>
+      <c r="F1248" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1248" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1248" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wolt/analytics-manager-marketing-analytics-london-346373</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="8" t="inlineStr">
+        <is>
+          <t>Principal Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B1249" s="8" t="inlineStr">
+        <is>
+          <t>tripadvisor</t>
+        </is>
+      </c>
+      <c r="C1249" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1249" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1249" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1249" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1249" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1249" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/tripadvisor/principal-machine-learning-scientist-london-317599</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (6 month contract)</t>
+        </is>
+      </c>
+      <c r="B1250" s="6" t="inlineStr">
+        <is>
+          <t>Lendable</t>
+        </is>
+      </c>
+      <c r="C1250" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1250" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1250" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F1250" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1250" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1250" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lendable/senior-analytics-engineer-6-month-contract-london-98590</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1251" s="8" t="inlineStr">
+        <is>
+          <t>Trainline</t>
+        </is>
+      </c>
+      <c r="C1251" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1251" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1251" s="8" t="inlineStr">
+        <is>
+          <t>Python、Spark、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1251" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1251" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1251" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/trainline/senior-machine-learning-engineer-london-56946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="6" t="inlineStr">
+        <is>
+          <t>Senior Technical Support Analyst</t>
+        </is>
+      </c>
+      <c r="B1252" s="6" t="inlineStr">
+        <is>
+          <t>Trainline</t>
+        </is>
+      </c>
+      <c r="C1252" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1252" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1252" s="6" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="F1252" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1252" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1252" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/trainline/senior-technical-support-analyst-london-45497</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Real time analytics</t>
+        </is>
+      </c>
+      <c r="B1253" s="8" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C1253" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1253" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1253" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1253" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1253" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1253" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/aircall/senior-data-engineer-real-time-analytics-london-office-114269</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="6" t="inlineStr">
+        <is>
+          <t>Innovative Planning Manager (Data Centres/Buildings/High-tech/Infrastructure) - Germany (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B1254" s="6" t="inlineStr">
+        <is>
+          <t>Laminar Projects</t>
+        </is>
+      </c>
+      <c r="C1254" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1254" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1254" s="6" t="inlineStr"/>
+      <c r="F1254" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1254" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1254" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/laminar-projects/innovative-planning-manager-data-centres-buildings-high-tech-infrastructure-germany-hybrid-378245</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (German)</t>
+        </is>
+      </c>
+      <c r="B1255" s="8" t="inlineStr">
+        <is>
+          <t>Economicmodeling</t>
+        </is>
+      </c>
+      <c r="C1255" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1255" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1255" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、机器学习</t>
+        </is>
+      </c>
+      <c r="F1255" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1255" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1255" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/economicmodeling/remote-data-analyst-german-10864</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant Cloud Data Engineering (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1256" s="6" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1256" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1256" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1256" s="6" t="inlineStr">
+        <is>
+          <t>SQL、R、Spark、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1256" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1256" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1256" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-consultant-cloud-data-engineering-frankfurt-am-main-144526</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1257" s="8" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1257" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1257" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1257" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、dbt、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1257" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1257" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1257" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-data-engineer-databricks-stuttgart-156226</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1258" s="6" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1258" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1258" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1258" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、dbt、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1258" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1258" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1258" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-data-engineer-databricks-stuttgart-496917</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1259" s="8" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1259" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1259" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1259" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Spark、dbt、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1259" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1259" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1259" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-data-engineer-databricks-berlin-352892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant Cloud Data Engineering (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1260" s="6" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1260" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1260" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1260" s="6" t="inlineStr">
+        <is>
+          <t>SQL、R、Spark、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1260" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1260" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1260" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-consultant-cloud-data-engineering-munich-406721</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="8" t="inlineStr">
+        <is>
+          <t>Strategic Account Executive - Data and Analytics</t>
+        </is>
+      </c>
+      <c r="B1261" s="8" t="inlineStr">
+        <is>
+          <t>interworks</t>
+        </is>
+      </c>
+      <c r="C1261" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1261" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1261" s="8" t="inlineStr"/>
+      <c r="F1261" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1261" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1261" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/interworks/strategic-account-executive-data-and-analytics-berlin-berlin-1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="6" t="inlineStr">
+        <is>
+          <t>Professor (m/f/d) of Data Science</t>
+        </is>
+      </c>
+      <c r="B1262" s="6" t="inlineStr">
+        <is>
+          <t>Global University Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1262" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1262" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1262" s="6" t="inlineStr"/>
+      <c r="F1262" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1262" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1262" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/global-university-systems-gmbh/professor-of-data-science-potsdam-18563</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="8" t="inlineStr">
+        <is>
+          <t>Professor (m/f/d) of Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1263" s="8" t="inlineStr">
+        <is>
+          <t>Global University Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1263" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1263" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1263" s="8" t="inlineStr"/>
+      <c r="F1263" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1263" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1263" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/global-university-systems-gmbh/professor-of-data-engineering-potsdam-273800</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="6" t="inlineStr">
+        <is>
+          <t>AI Data Specialist - German</t>
+        </is>
+      </c>
+      <c r="B1264" s="6" t="inlineStr">
+        <is>
+          <t>RWS TrainAI</t>
+        </is>
+      </c>
+      <c r="C1264" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1264" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1264" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1264" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1264" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1264" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/rws-trainai/ai-data-specialist-german-berlin-449304</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="8" t="inlineStr">
+        <is>
+          <t>Revenue Operations Analyst - Working Student</t>
+        </is>
+      </c>
+      <c r="B1265" s="8" t="inlineStr">
+        <is>
+          <t>Planetlabs</t>
+        </is>
+      </c>
+      <c r="C1265" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1265" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1265" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1265" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1265" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1265" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/planetlabs/revenue-operations-analyst-working-student-berlin-250212</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="6" t="inlineStr">
+        <is>
+          <t>Client Data &amp; Analytics Lead (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1266" s="6" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C1266" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1266" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1266" s="6" t="inlineStr"/>
+      <c r="F1266" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1266" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1266" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kraken/client-data-analytics-lead-berlin-313655</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Transformation Analyst - Commercials</t>
+        </is>
+      </c>
+      <c r="B1267" s="8" t="inlineStr">
+        <is>
+          <t>Intersnack Group GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1267" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1267" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1267" s="8" t="inlineStr"/>
+      <c r="F1267" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1267" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1267" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/intersnack-group-gmbh-co-kg/senior-business-transformation-analyst-commercials-dusseldorf-226</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="6" t="inlineStr">
+        <is>
+          <t>Data Science Specialist - Fully Remote | Upto $170/hr</t>
+        </is>
+      </c>
+      <c r="B1268" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1268" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1268" s="6" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1268" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1268" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1268" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1268" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="8" t="inlineStr">
+        <is>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
+        </is>
+      </c>
+      <c r="B1269" s="8" t="inlineStr">
+        <is>
+          <t>UT Health San Antonio</t>
+        </is>
+      </c>
+      <c r="C1269" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1269" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1269" s="8" t="inlineStr"/>
+      <c r="F1269" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1269" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1269" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ut-health-san-antonio/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1270" s="6" t="inlineStr">
+        <is>
+          <t>Beacon Biosignals</t>
+        </is>
+      </c>
+      <c r="C1270" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1270" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1270" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1270" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1270" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1270" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/beacon-biosignals/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="8" t="inlineStr">
+        <is>
+          <t>Junior Investment Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="B1271" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1271" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1271" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1271" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F1271" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1271" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1271" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="6" t="inlineStr">
+        <is>
+          <t>Data Evaluator - Fully Remote | Upto $120/hr</t>
+        </is>
+      </c>
+      <c r="B1272" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1272" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1272" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1272" s="6" t="inlineStr"/>
+      <c r="F1272" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1272" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1272" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1273" s="8" t="inlineStr">
+        <is>
+          <t>Fox Point Recruitment LLC</t>
+        </is>
+      </c>
+      <c r="C1273" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1273" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1273" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Spark、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1273" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1273" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H1273" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fox-point-recruitment-llc/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1240"/>
+  <autoFilter ref="A1:H1273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51697,19 +53043,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>583</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
@@ -51741,19 +53087,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>47</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>62</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
@@ -51807,10 +53153,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>3</v>
@@ -51819,7 +53165,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -51857,13 +53203,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-13 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-13 23:11 UTC</t>
+          <t>数据日期 2026-08-14 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-14 22:47 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1272</v>
+        <v>1318</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3609022556390977</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4060150375939849</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3458646616541353</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3157894736842105</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>36</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2706766917293233</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.1729323308270677</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1954887218045113</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,49 +793,49 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1382113821138211</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1278195488721804</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1203007518796992</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.112781954887218</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1273"/>
+  <dimension ref="A1:H1319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -52981,8 +52981,1896 @@
         </is>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1274" s="6" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C1274" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1274" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1274" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1274" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1274" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1274" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-data-engineer-lemon-io-1136594</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="8" t="inlineStr">
+        <is>
+          <t>Face Deduplication Collection</t>
+        </is>
+      </c>
+      <c r="B1275" s="8" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C1275" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1275" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1275" s="8" t="inlineStr"/>
+      <c r="F1275" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G1275" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1275" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/all-others/face-deduplication-collection-2091093</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1276" s="6" t="inlineStr">
+        <is>
+          <t>Quantum-Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1276" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1276" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1276" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1276" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1276" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1276" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/quantum-systems-gmbh/data-analyst-gilching-395414</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1277" s="8" t="inlineStr">
+        <is>
+          <t>Hilobyaktiia</t>
+        </is>
+      </c>
+      <c r="C1277" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1277" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1277" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、GCP、统计学</t>
+        </is>
+      </c>
+      <c r="F1277" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1277" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1277" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hilobyaktiia/remote-data-scientist-germany-475338</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="6" t="inlineStr">
+        <is>
+          <t>Data Protection Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1278" s="6" t="inlineStr">
+        <is>
+          <t>Voize</t>
+        </is>
+      </c>
+      <c r="C1278" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1278" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1278" s="6" t="inlineStr"/>
+      <c r="F1278" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1278" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1278" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/voize/data-protection-manager-berlin-424133</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1279" s="8" t="inlineStr">
+        <is>
+          <t>Quantum-Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1279" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1279" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1279" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1279" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1279" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1279" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/quantum-systems-gmbh/data-analyst-gilching-41978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="6" t="inlineStr">
+        <is>
+          <t>Finance Analyst (m/w/d) - Erneuerbare Energien</t>
+        </is>
+      </c>
+      <c r="B1280" s="6" t="inlineStr">
+        <is>
+          <t>feld.energy GmbH</t>
+        </is>
+      </c>
+      <c r="C1280" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1280" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1280" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1280" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1280" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1280" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/feldenergy-gmbh/finance-analyst-erneuerbare-energien-munich-356810</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="8" t="inlineStr">
+        <is>
+          <t>Working Student (f/m/d) - Data Compliance Team</t>
+        </is>
+      </c>
+      <c r="B1281" s="8" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C1281" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1281" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1281" s="8" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F1281" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1281" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1281" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/working-student-data-compliance-team-berlin-362145</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="6" t="inlineStr">
+        <is>
+          <t>Product Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1282" s="6" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C1282" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1282" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1282" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、Snowflake、BigQuery、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1282" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1282" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1282" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/product-data-analyst-cologne-244551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="8" t="inlineStr">
+        <is>
+          <t>Senior Service Analyst, 12 Month Fixed Term Contract</t>
+        </is>
+      </c>
+      <c r="B1283" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C1283" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1283" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1283" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker</t>
+        </is>
+      </c>
+      <c r="F1283" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1283" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1283" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/senior-service-analyst-12-month-fixed-term-contract-207845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="6" t="inlineStr">
+        <is>
+          <t>Graduate Data Scientist - Cyber Analytics (Position located in Cheltenham, United Kingdom)</t>
+        </is>
+      </c>
+      <c r="B1284" s="6" t="inlineStr">
+        <is>
+          <t>knowbe4</t>
+        </is>
+      </c>
+      <c r="C1284" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1284" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1284" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1284" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1284" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1284" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/knowbe4/graduate-data-scientist-cyber-analytics-position-located-in-cheltenham-united-kingdom-254481</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="8" t="inlineStr">
+        <is>
+          <t>Technical Support Analyst, Tier 1 (UK)</t>
+        </is>
+      </c>
+      <c r="B1285" s="8" t="inlineStr">
+        <is>
+          <t>Docebo</t>
+        </is>
+      </c>
+      <c r="C1285" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1285" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1285" s="8" t="inlineStr"/>
+      <c r="F1285" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1285" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1285" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/docebo/technical-support-analyst-tier-1-uk-london-30959</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1286" s="6" t="inlineStr">
+        <is>
+          <t>Paddle</t>
+        </is>
+      </c>
+      <c r="C1286" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1286" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1286" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F1286" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1286" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1286" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/paddle/senior-analytics-engineer-uk-252033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1287" s="8" t="inlineStr">
+        <is>
+          <t>Paddle</t>
+        </is>
+      </c>
+      <c r="C1287" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1287" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1287" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker</t>
+        </is>
+      </c>
+      <c r="F1287" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1287" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1287" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/paddle/business-analyst-uk-226366</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="6" t="inlineStr">
+        <is>
+          <t>Staff Insights Analyst</t>
+        </is>
+      </c>
+      <c r="B1288" s="6" t="inlineStr">
+        <is>
+          <t>Paddle</t>
+        </is>
+      </c>
+      <c r="C1288" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1288" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1288" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、统计学</t>
+        </is>
+      </c>
+      <c r="F1288" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1288" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1288" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/paddle/staff-insights-analyst-uk-23239</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer - Marketing</t>
+        </is>
+      </c>
+      <c r="B1289" s="8" t="inlineStr">
+        <is>
+          <t>Paddle</t>
+        </is>
+      </c>
+      <c r="C1289" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1289" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1289" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker、Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F1289" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1289" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1289" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/paddle/senior-analytics-engineer-marketing-uk-404195</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst, Accounting Data and Systems</t>
+        </is>
+      </c>
+      <c r="B1290" s="6" t="inlineStr">
+        <is>
+          <t>Deliveroo</t>
+        </is>
+      </c>
+      <c r="C1290" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1290" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1290" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F1290" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1290" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1290" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deliveroo/data-analyst-accounting-data-and-systems-london-49799</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant/Manager, AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1291" s="8" t="inlineStr">
+        <is>
+          <t>Baringa</t>
+        </is>
+      </c>
+      <c r="C1291" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1291" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1291" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1291" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1291" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1291" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/baringa/senior-consultant-manager-ai-ml-engineer-london-253486</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1292" s="6" t="inlineStr">
+        <is>
+          <t>MoonPay</t>
+        </is>
+      </c>
+      <c r="C1292" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1292" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1292" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1292" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1292" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1292" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/moonpay/staff-data-engineer-london-hybrid-34944</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="8" t="inlineStr">
+        <is>
+          <t>Data Assurance consultant - Contract role</t>
+        </is>
+      </c>
+      <c r="B1293" s="8" t="inlineStr">
+        <is>
+          <t>Project Blackbook</t>
+        </is>
+      </c>
+      <c r="C1293" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1293" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1293" s="8" t="inlineStr"/>
+      <c r="F1293" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1293" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1293" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/project-blackbook/data-assurance-contract-role-london-311179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Product Owner (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1294" s="6" t="inlineStr">
+        <is>
+          <t>Yepoda</t>
+        </is>
+      </c>
+      <c r="C1294" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1294" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1294" s="6" t="inlineStr">
+        <is>
+          <t>SQL、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1294" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1294" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1294" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yepoda/senior-data-analytics-product-owner-berlin-492129</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI Data Platform Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1295" s="8" t="inlineStr">
+        <is>
+          <t>Recare Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C1295" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1295" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1295" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1295" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1295" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1295" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/recare-deutschland-gmbh/remote-senior-ai-data-platform-engineer-berlin-232493</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent:in (m/w/d) Sales Operations</t>
+        </is>
+      </c>
+      <c r="B1296" s="6" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C1296" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1296" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1296" s="6" t="inlineStr"/>
+      <c r="F1296" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1296" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1296" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/1komma5grad/werkstudentin-sales-operations-berlin-305185</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="8" t="inlineStr">
+        <is>
+          <t>Senior Bid &amp; Pursuit Manager / Proposal Manager (m/w/d) – Cloud, Data &amp; AI Consulting</t>
+        </is>
+      </c>
+      <c r="B1297" s="8" t="inlineStr">
+        <is>
+          <t>Synvert</t>
+        </is>
+      </c>
+      <c r="C1297" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1297" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1297" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1297" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1297" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1297" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/synvert/senior-bid-pursuit-manager-proposal-manager-cloud-data-ai-consulting-hamburg-228959</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="6" t="inlineStr">
+        <is>
+          <t>Senior / Principal Cloud / Data Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B1298" s="6" t="inlineStr">
+        <is>
+          <t>Synvert</t>
+        </is>
+      </c>
+      <c r="C1298" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1298" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1298" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1298" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1298" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1298" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/synvert/senior-principal-cloud-data-engineer-all-genders-munster-263</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) FP&amp;A Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1299" s="8" t="inlineStr">
+        <is>
+          <t>Bees &amp; Bears GmbH</t>
+        </is>
+      </c>
+      <c r="C1299" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1299" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1299" s="8" t="inlineStr"/>
+      <c r="F1299" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1299" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1299" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bees-bears-gmbh/senior-fpa-analyst-berlin-286002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="6" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1300" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1300" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1300" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1300" s="6" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1300" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1300" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1300" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-242406</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="8" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1301" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1301" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1301" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1301" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1301" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1301" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1301" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-347806</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="6" t="inlineStr">
+        <is>
+          <t>Senior Marketing Business Intelligence Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1302" s="6" t="inlineStr">
+        <is>
+          <t>hellofresh</t>
+        </is>
+      </c>
+      <c r="C1302" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1302" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1302" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1302" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1302" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1302" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hellofresh/senior-marketing-business-intelligence-analyst-all-genders-berlin-berlin-242867</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Product Analytics</t>
+        </is>
+      </c>
+      <c r="B1303" s="8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C1303" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1303" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1303" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1303" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1303" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1303" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150667-data-scientist-product-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer, Product Analytics</t>
+        </is>
+      </c>
+      <c r="B1304" s="6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C1304" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1304" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1304" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1304" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1304" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1304" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150666-data-engineer-product-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="8" t="inlineStr">
+        <is>
+          <t>Research Analyst II</t>
+        </is>
+      </c>
+      <c r="B1305" s="8" t="inlineStr">
+        <is>
+          <t>Temple University</t>
+        </is>
+      </c>
+      <c r="C1305" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1305" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1305" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI、R、统计学</t>
+        </is>
+      </c>
+      <c r="F1305" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1305" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1305" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150661-research-analyst-ii</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Customer Experience</t>
+        </is>
+      </c>
+      <c r="B1306" s="6" t="inlineStr">
+        <is>
+          <t>Coursera</t>
+        </is>
+      </c>
+      <c r="C1306" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1306" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1306" s="6" t="inlineStr">
+        <is>
+          <t>Excel、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1306" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1306" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1306" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150655-senior-data-scientist-customer-experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1307" s="8" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C1307" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1307" s="8" t="inlineStr">
+        <is>
+          <t>北美</t>
+        </is>
+      </c>
+      <c r="E1307" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1307" s="8" t="inlineStr">
+        <is>
+          <t>workingnomads</t>
+        </is>
+      </c>
+      <c r="G1307" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1307" s="8" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/job/go/1792423/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="6" t="inlineStr">
+        <is>
+          <t>Financial Analyst (CR, Costa Rica , Virtual, Costa Rica, LATAM)</t>
+        </is>
+      </c>
+      <c r="B1308" s="6" t="inlineStr">
+        <is>
+          <t>BCD Travel</t>
+        </is>
+      </c>
+      <c r="C1308" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1308" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1308" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1308" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1308" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1308" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bcd-travel/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="8" t="inlineStr">
+        <is>
+          <t>Data Lead - Central Data Team</t>
+        </is>
+      </c>
+      <c r="B1309" s="8" t="inlineStr">
+        <is>
+          <t>YipitData</t>
+        </is>
+      </c>
+      <c r="C1309" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1309" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1309" s="8" t="inlineStr"/>
+      <c r="F1309" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1309" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1309" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/yipitdata/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="6" t="inlineStr">
+        <is>
+          <t>ServiceNow HR Application Analyst</t>
+        </is>
+      </c>
+      <c r="B1310" s="6" t="inlineStr">
+        <is>
+          <t>Sedgwick</t>
+        </is>
+      </c>
+      <c r="C1310" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1310" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1310" s="6" t="inlineStr"/>
+      <c r="F1310" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1310" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1310" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sedgwick/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="8" t="inlineStr">
+        <is>
+          <t>Compensation Analytics &amp; Intelligence Director (U.S.A. Remote)</t>
+        </is>
+      </c>
+      <c r="B1311" s="8" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="C1311" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1311" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1311" s="8" t="inlineStr"/>
+      <c r="F1311" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1311" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1311" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/danaher/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="6" t="inlineStr">
+        <is>
+          <t>Director, Data Analytics &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B1312" s="6" t="inlineStr">
+        <is>
+          <t>FiscalNote</t>
+        </is>
+      </c>
+      <c r="C1312" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1312" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1312" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F1312" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1312" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1312" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fiscalnote/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="8" t="inlineStr">
+        <is>
+          <t>Hadoop Big Data Developer</t>
+        </is>
+      </c>
+      <c r="B1313" s="8" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies</t>
+        </is>
+      </c>
+      <c r="C1313" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1313" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1313" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1313" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1313" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1313" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bright-vision-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="6" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst – Cloud Commerce &amp; SaaS (remote in Poland)</t>
+        </is>
+      </c>
+      <c r="B1314" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1314" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1314" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1314" s="6" t="inlineStr">
+        <is>
+          <t>Tableau、Looker、Snowflake、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1314" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1314" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1314" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mirantis/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="8" t="inlineStr">
+        <is>
+          <t>Lead Business Analyst/Project Manager</t>
+        </is>
+      </c>
+      <c r="B1315" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1315" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1315" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1315" s="8" t="inlineStr"/>
+      <c r="F1315" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1315" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1315" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/matrix-global/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="6" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B1316" s="6" t="inlineStr">
+        <is>
+          <t>IntegriChain</t>
+        </is>
+      </c>
+      <c r="C1316" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1316" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1316" s="6" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F1316" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1316" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1316" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/integrichain/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="8" t="inlineStr">
+        <is>
+          <t>Salesforce CRM Analyst</t>
+        </is>
+      </c>
+      <c r="B1317" s="8" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C1317" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1317" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1317" s="8" t="inlineStr"/>
+      <c r="F1317" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1317" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1317" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/experian/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Cycle Analyst (Temporary)</t>
+        </is>
+      </c>
+      <c r="B1318" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1318" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1318" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1318" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1318" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1318" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1318" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/clarvida-california/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="8" t="inlineStr">
+        <is>
+          <t>Senior Looker Developer, Data</t>
+        </is>
+      </c>
+      <c r="B1319" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1319" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1319" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1319" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Looker、Snowflake、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1319" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1319" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H1319" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/power-digital-marketing/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1273"/>
+  <autoFilter ref="A1:H1319"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53043,19 +54931,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>610</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3">
@@ -53087,19 +54975,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -53115,13 +55003,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -53131,7 +55019,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>15</v>
@@ -53140,10 +55028,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
@@ -53181,13 +55069,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1349</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-14 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-14 22:47 UTC</t>
+          <t>数据日期 2026-08-15 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-15 22:45 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1318</v>
+        <v>1348</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,38 +706,38 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>0.3609022556390977</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>数据分析/BI</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>54</v>
-      </c>
       <c r="H11" s="7" t="n">
-        <v>0.4060150375939849</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3458646616541353</v>
+        <v>0.36</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.2706766917293233</v>
+        <v>0.352</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1729323308270677</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1954887218045113</v>
+        <v>0.208</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1278195488721804</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1203007518796992</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.112781954887218</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.096</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1319"/>
+  <dimension ref="A1:H1349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -54869,8 +54869,1224 @@
         </is>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" s="6" t="inlineStr">
+        <is>
+          <t>Brand Protection &amp; Marketplace Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="B1320" s="6" t="inlineStr">
+        <is>
+          <t>MultiplyMii</t>
+        </is>
+      </c>
+      <c r="C1320" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1320" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1320" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1320" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1320" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1320" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-brand-protection-marketplace-compliance-analyst-multiplymii-1136687</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="8" t="inlineStr">
+        <is>
+          <t>ANALYST L3</t>
+        </is>
+      </c>
+      <c r="B1321" s="8" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C1321" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1321" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1321" s="8" t="inlineStr"/>
+      <c r="F1321" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1321" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1321" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-analyst-l3-wipro-1136784</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="6" t="inlineStr">
+        <is>
+          <t>Staff Analyst (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1322" s="6" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C1322" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1322" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1322" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、dbt、Airflow</t>
+        </is>
+      </c>
+      <c r="F1322" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1322" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1322" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/staff-analyst-hamburg-329143</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Experimentation &amp; A/B Testing (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1323" s="8" t="inlineStr">
+        <is>
+          <t>adjoe</t>
+        </is>
+      </c>
+      <c r="C1323" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1323" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1323" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、dbt、Airflow、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1323" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1323" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1323" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adjoe/senior-data-analyst-experimentation-a-b-testing-hamburg-125335</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="6" t="inlineStr">
+        <is>
+          <t>Data Operations &amp; Labeling Specialist (all genders)</t>
+        </is>
+      </c>
+      <c r="B1324" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1324" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1324" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1324" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1324" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1324" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1324" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/data-operations-labeling-specialist-all-genders-munich-393524</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1325" s="8" t="inlineStr">
+        <is>
+          <t>Westwing</t>
+        </is>
+      </c>
+      <c r="C1325" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1325" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1325" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、统计学</t>
+        </is>
+      </c>
+      <c r="F1325" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1325" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1325" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/westwing/senior-data-analyst-munich-office-439986</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="6" t="inlineStr">
+        <is>
+          <t>Senior Implementation Specialist Digital Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1326" s="6" t="inlineStr">
+        <is>
+          <t>FELD M</t>
+        </is>
+      </c>
+      <c r="C1326" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1326" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1326" s="6" t="inlineStr"/>
+      <c r="F1326" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1326" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1326" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/feld-m/senior-implementation-specialist-digital-analytics-munich-65145</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1327" s="8" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1327" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1327" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1327" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1327" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1327" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1327" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-platform-engineer-working-student-munchen-496680</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1328" s="6" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1328" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1328" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1328" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、R、ETL</t>
+        </is>
+      </c>
+      <c r="F1328" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1328" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1328" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-engineer-working-student-koln-371370</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="8" t="inlineStr">
+        <is>
+          <t>Sales Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1329" s="8" t="inlineStr">
+        <is>
+          <t>Metaview</t>
+        </is>
+      </c>
+      <c r="C1329" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1329" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1329" s="8" t="inlineStr"/>
+      <c r="F1329" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1329" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1329" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/metaview/sales-operations-analyst-london-326803</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Analytics Analyst</t>
+        </is>
+      </c>
+      <c r="B1330" s="6" t="inlineStr">
+        <is>
+          <t>Eucalyptus</t>
+        </is>
+      </c>
+      <c r="C1330" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1330" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1330" s="6" t="inlineStr">
+        <is>
+          <t>SQL、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1330" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1330" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1330" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/eucalyptus/marketing-analytics-analyst-260045</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="8" t="inlineStr">
+        <is>
+          <t>Technical Lead, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B1331" s="8" t="inlineStr">
+        <is>
+          <t>Bjak</t>
+        </is>
+      </c>
+      <c r="C1331" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1331" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1331" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1331" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1331" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1331" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/bjak/technical-lead-machine-learning-london-207981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="6" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1332" s="6" t="inlineStr">
+        <is>
+          <t>Bjak</t>
+        </is>
+      </c>
+      <c r="C1332" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1332" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1332" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1332" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1332" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1332" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/bjak/staff-machine-learning-engineer-london-431496</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="8" t="inlineStr">
+        <is>
+          <t>Business Intelligence &amp; Performance Manager</t>
+        </is>
+      </c>
+      <c r="B1333" s="8" t="inlineStr">
+        <is>
+          <t>Bjak</t>
+        </is>
+      </c>
+      <c r="C1333" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1333" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1333" s="8" t="inlineStr"/>
+      <c r="F1333" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1333" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1333" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/bjak/business-intelligence-performance-manager-london-495386</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="6" t="inlineStr">
+        <is>
+          <t>Performance Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B1334" s="6" t="inlineStr">
+        <is>
+          <t>Bjak</t>
+        </is>
+      </c>
+      <c r="C1334" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1334" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1334" s="6" t="inlineStr"/>
+      <c r="F1334" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1334" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1334" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/bjak/performance-analytics-manager-london-295019</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="8" t="inlineStr">
+        <is>
+          <t>Senior Technical Writer (Data Documentation)</t>
+        </is>
+      </c>
+      <c r="B1335" s="8" t="inlineStr">
+        <is>
+          <t>jetbrains</t>
+        </is>
+      </c>
+      <c r="C1335" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1335" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1335" s="8" t="inlineStr"/>
+      <c r="F1335" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1335" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1335" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jetbrains/remote-senior-technical-writer-data-documentation-51174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="6" t="inlineStr">
+        <is>
+          <t>Head of Integrity Data and Innovations (m-f-d)</t>
+        </is>
+      </c>
+      <c r="B1336" s="6" t="inlineStr">
+        <is>
+          <t>Fsc</t>
+        </is>
+      </c>
+      <c r="C1336" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1336" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1336" s="6" t="inlineStr"/>
+      <c r="F1336" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1336" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1336" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/fsc/head-of-integrity-data-and-innovations-m-f-d-bonn-germany-hybrid-431795</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="8" t="inlineStr">
+        <is>
+          <t>Analytics - Future Leaders Graduate Program</t>
+        </is>
+      </c>
+      <c r="B1337" s="8" t="inlineStr">
+        <is>
+          <t>Teampicnic</t>
+        </is>
+      </c>
+      <c r="C1337" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1337" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1337" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel</t>
+        </is>
+      </c>
+      <c r="F1337" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1337" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1337" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/teampicnic/analytics-future-leaders-graduate-program-dusseldorf-north-rhine-westphalia-238231</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B1338" s="6" t="inlineStr">
+        <is>
+          <t>Bjak</t>
+        </is>
+      </c>
+      <c r="C1338" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1338" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1338" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1338" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1338" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1338" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bjak/machine-learning-platform-engineer-germany-69326</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Finance Data Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1339" s="8" t="inlineStr">
+        <is>
+          <t>Homaris</t>
+        </is>
+      </c>
+      <c r="C1339" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1339" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1339" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1339" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1339" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1339" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/homaris/junior-finance-data-analyst-all-genders-berlin-235448</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Marketing Analyst (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="B1340" s="6" t="inlineStr">
+        <is>
+          <t>freenow</t>
+        </is>
+      </c>
+      <c r="C1340" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1340" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1340" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、R、统计学</t>
+        </is>
+      </c>
+      <c r="F1340" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1340" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1340" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/freenow/senior-marketing-analyst-berlin-458873</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="8" t="inlineStr">
+        <is>
+          <t>Data Protection Officer (Deputy) (F/M/D)</t>
+        </is>
+      </c>
+      <c r="B1341" s="8" t="inlineStr">
+        <is>
+          <t>360T</t>
+        </is>
+      </c>
+      <c r="C1341" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1341" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1341" s="8" t="inlineStr"/>
+      <c r="F1341" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1341" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1341" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/360t/data-protection-officer-deputy-frankfurt-am-main-433230</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B1342" s="6" t="inlineStr">
+        <is>
+          <t>Choco</t>
+        </is>
+      </c>
+      <c r="C1342" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1342" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1342" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、机器学习</t>
+        </is>
+      </c>
+      <c r="F1342" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1342" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1342" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/choco/senior-data-platform-engineer-berlin-111883</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="8" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1343" s="8" t="inlineStr">
+        <is>
+          <t>OpenX</t>
+        </is>
+      </c>
+      <c r="C1343" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1343" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1343" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1343" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1343" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1343" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/openx/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1344" s="6" t="inlineStr">
+        <is>
+          <t>Bloomreach</t>
+        </is>
+      </c>
+      <c r="C1344" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1344" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1344" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F1344" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1344" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1344" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bloomreach/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1345" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1345" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1345" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1345" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1345" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1345" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1345" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="6" t="inlineStr">
+        <is>
+          <t>Senior Security Analyst</t>
+        </is>
+      </c>
+      <c r="B1346" s="6" t="inlineStr">
+        <is>
+          <t>Marathon Health</t>
+        </is>
+      </c>
+      <c r="C1346" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1346" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1346" s="6" t="inlineStr">
+        <is>
+          <t>Excel、AWS</t>
+        </is>
+      </c>
+      <c r="F1346" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1346" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1346" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/marathon-health-com/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="8" t="inlineStr">
+        <is>
+          <t>Principal Insights Analyst (Healthcare)</t>
+        </is>
+      </c>
+      <c r="B1347" s="8" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C1347" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1347" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1347" s="8" t="inlineStr"/>
+      <c r="F1347" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1347" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1347" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/cotiviti/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="6" t="inlineStr">
+        <is>
+          <t>Home-Based Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1348" s="6" t="inlineStr">
+        <is>
+          <t>DCX PH</t>
+        </is>
+      </c>
+      <c r="C1348" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1348" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1348" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1348" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1348" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1348" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/dcx-ph/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="8" t="inlineStr">
+        <is>
+          <t>[新加坡/可远程] 智能体垂类赛道-寻找 AI 与数据工程师 / 技术合伙人</t>
+        </is>
+      </c>
+      <c r="B1349" s="8" t="inlineStr"/>
+      <c r="C1349" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1349" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1349" s="8" t="inlineStr"/>
+      <c r="F1349" s="8" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G1349" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H1349" s="8" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/XNf2L7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1319"/>
+  <autoFilter ref="A1:H1349"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54931,19 +56147,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>637</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3">
@@ -54975,10 +56191,10 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>24</v>
@@ -54987,7 +56203,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
@@ -54997,7 +56213,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -55009,7 +56225,7 @@
         <v>27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -55019,19 +56235,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-15 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-15 22:45 UTC</t>
+          <t>数据日期 2026-08-16 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-16 22:44 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1348</v>
+        <v>1378</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.368</v>
+        <v>0.3722627737226277</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.384</v>
+        <v>0.3941605839416059</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.36</v>
+        <v>0.3503649635036497</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.312</v>
+        <v>0.3138686131386861</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.352</v>
+        <v>0.343065693430657</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>26</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.208</v>
+        <v>0.1897810218978102</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +785,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.208</v>
+        <v>0.1897810218978102</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.096</v>
+        <v>0.1021897810218978</v>
       </c>
     </row>
     <row r="15">
@@ -809,33 +809,33 @@
         <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.152</v>
+        <v>0.1386861313868613</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.128</v>
+        <v>0.1167883211678832</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.112</v>
+        <v>0.1094890510948905</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.112</v>
+        <v>0.1094890510948905</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.104</v>
+        <v>0.1021897810218978</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.096</v>
+        <v>0.1021897810218978</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1349"/>
+  <dimension ref="A1:H1379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -56085,8 +56085,1224 @@
         </is>
       </c>
     </row>
+    <row r="1350">
+      <c r="A1350" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/w/d) BI &amp; Konsolidierung</t>
+        </is>
+      </c>
+      <c r="B1350" s="6" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C1350" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1350" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1350" s="6" t="inlineStr"/>
+      <c r="F1350" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1350" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1350" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/senior-consultant-bi-konsolidierung-stuttgart-437533</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="8" t="inlineStr">
+        <is>
+          <t>Senior Campaign Analyst</t>
+        </is>
+      </c>
+      <c r="B1351" s="8" t="inlineStr">
+        <is>
+          <t>JustWatch</t>
+        </is>
+      </c>
+      <c r="C1351" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1351" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1351" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1351" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1351" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1351" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/justwatch/senior-campaign-analyst-berlin-121645</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="6" t="inlineStr">
+        <is>
+          <t>Team Lead Data Products &amp; Analytics (gn)</t>
+        </is>
+      </c>
+      <c r="B1352" s="6" t="inlineStr">
+        <is>
+          <t>Bikeleasing</t>
+        </is>
+      </c>
+      <c r="C1352" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1352" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1352" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F1352" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1352" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1352" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bikeleasing/remote-team-lead-data-products-analytics-gn-162562</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1353" s="8" t="inlineStr">
+        <is>
+          <t>Metro Markets GmbH</t>
+        </is>
+      </c>
+      <c r="C1353" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1353" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1353" s="8" t="inlineStr"/>
+      <c r="F1353" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1353" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1353" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/metro-markets-gmbh/data-analyst-dusseldorf-370003</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent Business Analytics &amp; Management Reporting (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1354" s="6" t="inlineStr">
+        <is>
+          <t>Deutsche GigaNetz GmbH</t>
+        </is>
+      </c>
+      <c r="C1354" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1354" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1354" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1354" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1354" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1354" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/deutsche-giganetz-gmbh/werkstudent-business-analytics-management-reporting-hamburg-421627</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="8" t="inlineStr">
+        <is>
+          <t>Marketing Analytics Manager - THG Nutrition</t>
+        </is>
+      </c>
+      <c r="B1355" s="8" t="inlineStr">
+        <is>
+          <t>Thehutgroup</t>
+        </is>
+      </c>
+      <c r="C1355" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1355" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1355" s="8" t="inlineStr"/>
+      <c r="F1355" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1355" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1355" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/thehutgroup/marketing-analytics-manager-thg-nutrition-manchester-109702</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="6" t="inlineStr">
+        <is>
+          <t>Commercial Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B1356" s="6" t="inlineStr">
+        <is>
+          <t>hellofresh</t>
+        </is>
+      </c>
+      <c r="C1356" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1356" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1356" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau</t>
+        </is>
+      </c>
+      <c r="F1356" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1356" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1356" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/hellofresh/commercial-analytics-manager-london-153088</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="8" t="inlineStr">
+        <is>
+          <t>Staff ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1357" s="8" t="inlineStr">
+        <is>
+          <t>Cloudbedsthirdpartyboard</t>
+        </is>
+      </c>
+      <c r="C1357" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1357" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1357" s="8" t="inlineStr">
+        <is>
+          <t>Python、Airflow、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1357" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1357" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1357" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/cloudbedsthirdpartyboard/staff-ml-engineer-191647</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Manager (Data API)</t>
+        </is>
+      </c>
+      <c r="B1358" s="6" t="inlineStr">
+        <is>
+          <t>9Fin</t>
+        </is>
+      </c>
+      <c r="C1358" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1358" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1358" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F1358" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1358" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1358" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/9fin/senior-product-manager-data-api-london-110920</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="8" t="inlineStr">
+        <is>
+          <t>Graduate Paid Media Analyst</t>
+        </is>
+      </c>
+      <c r="B1359" s="8" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="C1359" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1359" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1359" s="8" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+      <c r="F1359" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1359" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1359" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/quantum/graduate-paid-media-analyst-london-168571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="6" t="inlineStr">
+        <is>
+          <t>Graduate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1360" s="6" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="C1360" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1360" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1360" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1360" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1360" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1360" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/quantum/graduate-data-engineer-london-410046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1361" s="8" t="inlineStr">
+        <is>
+          <t>Quberesearchandtechnologies</t>
+        </is>
+      </c>
+      <c r="C1361" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1361" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1361" s="8" t="inlineStr">
+        <is>
+          <t>Python、pandas</t>
+        </is>
+      </c>
+      <c r="F1361" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1361" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1361" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/quberesearchandtechnologies/data-scientist-london-479574</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="6" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B1362" s="6" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="C1362" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1362" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1362" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1362" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1362" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1362" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/pleo/senior-applied-ai-engineer-london-218725</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="8" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B1363" s="8" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="C1363" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1363" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1363" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1363" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1363" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1363" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/pleo/senior-applied-ai-engineer-united-kingdom-144957</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer (Commodities Data Team)</t>
+        </is>
+      </c>
+      <c r="B1364" s="6" t="inlineStr">
+        <is>
+          <t>Drweng</t>
+        </is>
+      </c>
+      <c r="C1364" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1364" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1364" s="6" t="inlineStr">
+        <is>
+          <t>Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1364" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1364" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1364" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/drweng/software-engineer-commodities-data-team-london-233227</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="8" t="inlineStr">
+        <is>
+          <t>Senior Deal Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B1365" s="8" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="C1365" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1365" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1365" s="8" t="inlineStr"/>
+      <c r="F1365" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1365" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1365" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/harvey/senior-deal-desk-analyst-london-459270</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="6" t="inlineStr">
+        <is>
+          <t>Strategic Account Executive - Data and Analytics</t>
+        </is>
+      </c>
+      <c r="B1366" s="6" t="inlineStr">
+        <is>
+          <t>interworks</t>
+        </is>
+      </c>
+      <c r="C1366" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1366" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1366" s="6" t="inlineStr"/>
+      <c r="F1366" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1366" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1366" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/interworks/strategic-account-executive-data-and-analytics-london-189931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist (Drug Discovery), London</t>
+        </is>
+      </c>
+      <c r="B1367" s="8" t="inlineStr">
+        <is>
+          <t>Isomorphiclabs</t>
+        </is>
+      </c>
+      <c r="C1367" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1367" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1367" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1367" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1367" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1367" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/isomorphiclabs/data-scientist-drug-discovery-london-174952</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="6" t="inlineStr">
+        <is>
+          <t>Data Science Intern (Customer Success)</t>
+        </is>
+      </c>
+      <c r="B1368" s="6" t="inlineStr">
+        <is>
+          <t>Cresta</t>
+        </is>
+      </c>
+      <c r="C1368" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1368" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1368" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Spark、AWS、Azure、GCP、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1368" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1368" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1368" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150863-data-science-intern-customer-success</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1369" s="8" t="inlineStr">
+        <is>
+          <t>Gopuff</t>
+        </is>
+      </c>
+      <c r="C1369" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1369" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1369" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、Airflow、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1369" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1369" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1369" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150836-data-engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="6" t="inlineStr">
+        <is>
+          <t>Quality Management Analyst</t>
+        </is>
+      </c>
+      <c r="B1370" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1370" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1370" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1370" s="6" t="inlineStr"/>
+      <c r="F1370" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1370" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1370" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/general-dynamics-information-technology/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="8" t="inlineStr">
+        <is>
+          <t>[Job -31071] Data Architect, Brazil</t>
+        </is>
+      </c>
+      <c r="B1371" s="8" t="inlineStr">
+        <is>
+          <t>CI&amp;T</t>
+        </is>
+      </c>
+      <c r="C1371" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1371" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1371" s="8" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1371" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1371" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1371" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ci-t/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="6" t="inlineStr">
+        <is>
+          <t>AI Trainer - Freelance Data Annotator</t>
+        </is>
+      </c>
+      <c r="B1372" s="6" t="inlineStr">
+        <is>
+          <t>Toloka AI</t>
+        </is>
+      </c>
+      <c r="C1372" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1372" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1372" s="6" t="inlineStr"/>
+      <c r="F1372" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1372" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1372" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/toloka-ai/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="8" t="inlineStr">
+        <is>
+          <t>Vice President, Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B1373" s="8" t="inlineStr">
+        <is>
+          <t>Hillenbrand</t>
+        </is>
+      </c>
+      <c r="C1373" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1373" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1373" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt、机器学习</t>
+        </is>
+      </c>
+      <c r="F1373" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1373" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1373" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/hillenbrand/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="6" t="inlineStr">
+        <is>
+          <t>OSINT Analyst - Vessel Identification</t>
+        </is>
+      </c>
+      <c r="B1374" s="6" t="inlineStr">
+        <is>
+          <t>Kpler</t>
+        </is>
+      </c>
+      <c r="C1374" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1374" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1374" s="6" t="inlineStr"/>
+      <c r="F1374" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1374" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1374" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kpler/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="8" t="inlineStr">
+        <is>
+          <t>Databricks Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1375" s="8" t="inlineStr">
+        <is>
+          <t>Guidehouse</t>
+        </is>
+      </c>
+      <c r="C1375" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1375" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1375" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1375" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1375" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1375" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/guidehouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="6" t="inlineStr">
+        <is>
+          <t>Creative Director - Marketing &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B1376" s="6" t="inlineStr">
+        <is>
+          <t>Leap Event Technology</t>
+        </is>
+      </c>
+      <c r="C1376" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1376" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1376" s="6" t="inlineStr"/>
+      <c r="F1376" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1376" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1376" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/leap-event-technology/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="8" t="inlineStr">
+        <is>
+          <t>Senior Professional Services Analyst (Remote US/CAN)</t>
+        </is>
+      </c>
+      <c r="B1377" s="8" t="inlineStr">
+        <is>
+          <t>Sayari</t>
+        </is>
+      </c>
+      <c r="C1377" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1377" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1377" s="8" t="inlineStr"/>
+      <c r="F1377" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1377" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1377" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sayari/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="6" t="inlineStr">
+        <is>
+          <t>Associate Architect - Data Science</t>
+        </is>
+      </c>
+      <c r="B1378" s="6" t="inlineStr">
+        <is>
+          <t>Axonect</t>
+        </is>
+      </c>
+      <c r="C1378" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1378" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1378" s="6" t="inlineStr">
+        <is>
+          <t>Python、AWS、Azure、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1378" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1378" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1378" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/axonect/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst</t>
+        </is>
+      </c>
+      <c r="B1379" s="8" t="inlineStr">
+        <is>
+          <t>Pair Team</t>
+        </is>
+      </c>
+      <c r="C1379" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1379" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1379" s="8" t="inlineStr"/>
+      <c r="F1379" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1379" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H1379" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pair-team/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1349"/>
+  <autoFilter ref="A1:H1379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -56147,19 +57363,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>658</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3">
@@ -56169,7 +57385,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>5</v>
@@ -56178,10 +57394,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -56191,19 +57407,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>65</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -56238,16 +57454,16 @@
         <v>90</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1439</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-16 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-16 22:44 UTC</t>
+          <t>数据日期 2026-08-17 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-17 22:48 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1378</v>
+        <v>1438</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3722627737226277</v>
+        <v>0.3710691823899371</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3941605839416059</v>
+        <v>0.3773584905660378</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3503649635036497</v>
+        <v>0.3522012578616352</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>43</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3138686131386861</v>
+        <v>0.270440251572327</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.343065693430657</v>
+        <v>0.3459119496855346</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1897810218978102</v>
+        <v>0.1949685534591195</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1897810218978102</v>
+        <v>0.1572327044025157</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.1572327044025157</v>
       </c>
     </row>
     <row r="15">
@@ -806,23 +806,23 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1386861313868613</v>
+        <v>0.1383647798742138</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1167883211678832</v>
+        <v>0.1320754716981132</v>
       </c>
     </row>
     <row r="17">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1094890510948905</v>
+        <v>0.119496855345912</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1094890510948905</v>
+        <v>0.1069182389937107</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.1006289308176101</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1021897810218978</v>
+        <v>0.09433962264150944</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1379"/>
+  <dimension ref="A1:H1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -57301,8 +57301,2452 @@
         </is>
       </c>
     </row>
+    <row r="1380">
+      <c r="A1380" s="6" t="inlineStr">
+        <is>
+          <t>Real Time Drilling Ops Centre Analyst</t>
+        </is>
+      </c>
+      <c r="B1380" s="6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C1380" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1380" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1380" s="6" t="inlineStr"/>
+      <c r="F1380" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1380" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1380" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-real-time-drilling-ops-centre-analyst-slb-1136857</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="8" t="inlineStr">
+        <is>
+          <t>Senior GenAI Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1381" s="8" t="inlineStr">
+        <is>
+          <t>autoscout24</t>
+        </is>
+      </c>
+      <c r="C1381" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1381" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1381" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1381" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1381" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1381" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/autoscout24/senior-genai-data-scientist-134739</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst FlixTrain Operations (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1382" s="6" t="inlineStr">
+        <is>
+          <t>Flix</t>
+        </is>
+      </c>
+      <c r="C1382" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1382" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1382" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Snowflake</t>
+        </is>
+      </c>
+      <c r="F1382" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1382" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1382" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/flix/data-analyst-flixtrain-operations-berlin-326565</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer: Search Quality</t>
+        </is>
+      </c>
+      <c r="B1383" s="8" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C1383" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1383" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1383" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1383" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1383" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1383" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/constructor/senior-machine-learning-engineer-search-quality-munich-265685</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="6" t="inlineStr">
+        <is>
+          <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1384" s="6" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM gGmbH</t>
+        </is>
+      </c>
+      <c r="C1384" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1384" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1384" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1384" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1384" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1384" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/unternehmertum-ggmbh/uvc-partners-junior-value-creation-analyst-intern-or-working-student-munchen-kreativquartier-461955</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d) - Hamburg</t>
+        </is>
+      </c>
+      <c r="B1385" s="8" t="inlineStr">
+        <is>
+          <t>freenow</t>
+        </is>
+      </c>
+      <c r="C1385" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1385" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1385" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1385" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1385" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1385" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/freenow/senior-data-analyst-hamburg-108326</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="B1386" s="6" t="inlineStr">
+        <is>
+          <t>freenow</t>
+        </is>
+      </c>
+      <c r="C1386" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1386" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1386" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1386" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1386" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1386" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/freenow/senior-data-analyst-berlin-364149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1387" s="8" t="inlineStr">
+        <is>
+          <t>Globaldimensionsllc</t>
+        </is>
+      </c>
+      <c r="C1387" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1387" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1387" s="8" t="inlineStr">
+        <is>
+          <t>Python、Tableau、Power BI、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1387" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1387" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1387" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/globaldimensionsllc/data-scientist-stuttgart-150390</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Revenue Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1388" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C1388" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1388" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1388" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F1388" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1388" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1388" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/senior-revenue-analyst-hamburg-or-berlin-329285</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1389" s="8" t="inlineStr">
+        <is>
+          <t>Hubject Gmbh</t>
+        </is>
+      </c>
+      <c r="C1389" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1389" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1389" s="8" t="inlineStr"/>
+      <c r="F1389" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1389" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1389" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hubject-gmbh/senior-financial-analyst-all-genders-deutschland-berlin-215716</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1390" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C1390" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1390" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1390" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、机器学习</t>
+        </is>
+      </c>
+      <c r="F1390" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1390" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1390" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/machine-learning-consultant-munich-280382</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="8" t="inlineStr">
+        <is>
+          <t>Praktikum - Political Data Engineering (w/d/m)</t>
+        </is>
+      </c>
+      <c r="B1391" s="8" t="inlineStr">
+        <is>
+          <t>Christundcompany</t>
+        </is>
+      </c>
+      <c r="C1391" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1391" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1391" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、dbt</t>
+        </is>
+      </c>
+      <c r="F1391" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1391" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1391" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/christundcompany/praktikum-political-data-engineering-berlin-285507</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1392" s="6" t="inlineStr">
+        <is>
+          <t>Dishdigital</t>
+        </is>
+      </c>
+      <c r="C1392" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1392" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1392" s="6" t="inlineStr"/>
+      <c r="F1392" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1392" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1392" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dishdigital/senior-data-engineer-dusseldorf-454148</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1393" s="8" t="inlineStr">
+        <is>
+          <t>Dishdigital</t>
+        </is>
+      </c>
+      <c r="C1393" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1393" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1393" s="8" t="inlineStr"/>
+      <c r="F1393" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1393" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1393" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dishdigital/data-engineer-dusseldorf-270143</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist with focus Bioinformatics / Diagnostics (f/m/d - part/full-time)</t>
+        </is>
+      </c>
+      <c r="B1394" s="6" t="inlineStr">
+        <is>
+          <t>Staburo</t>
+        </is>
+      </c>
+      <c r="C1394" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1394" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1394" s="6" t="inlineStr">
+        <is>
+          <t>R、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1394" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1394" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1394" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/staburo/data-scientist-with-focus-bioinformatics-diagnostics-part-full-time-munich-368417</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1395" s="8" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="C1395" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1395" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1395" s="8" t="inlineStr"/>
+      <c r="F1395" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1395" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1395" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/quantum/head-of-data-engineering-london-441668</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1396" s="6" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C1396" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1396" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1396" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1396" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1396" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1396" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-senior-analytics-engineer-373361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer - Data Platform (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1397" s="8" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C1397" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1397" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1397" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1397" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1397" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1397" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-junior-data-engineer-data-platform-159693</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Real time analytics</t>
+        </is>
+      </c>
+      <c r="B1398" s="6" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C1398" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1398" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1398" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1398" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1398" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1398" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/aircall/senior-data-engineer-real-time-analytics-london-office-368823</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="8" t="inlineStr">
+        <is>
+          <t>Senior Technical Advisor, Data Use and Decision Science (Remote - US, UK, France, DRC)</t>
+        </is>
+      </c>
+      <c r="B1399" s="8" t="inlineStr">
+        <is>
+          <t>Resolvetosavelives</t>
+        </is>
+      </c>
+      <c r="C1399" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1399" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1399" s="8" t="inlineStr"/>
+      <c r="F1399" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1399" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1399" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/resolvetosavelives/senior-technical-advisor-data-use-and-decision-science-remote-us-uk-france-drc-us-france-drc-362912</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="6" t="inlineStr">
+        <is>
+          <t>Support Specialist, Data (Multilingual)</t>
+        </is>
+      </c>
+      <c r="B1400" s="6" t="inlineStr">
+        <is>
+          <t>Hudl</t>
+        </is>
+      </c>
+      <c r="C1400" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1400" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1400" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、R、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1400" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1400" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1400" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/hudl/support-specialist-data-multilingual-london-88385</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="8" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer (São Paulo, BR)</t>
+        </is>
+      </c>
+      <c r="B1401" s="8" t="inlineStr">
+        <is>
+          <t>Blab</t>
+        </is>
+      </c>
+      <c r="C1401" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1401" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1401" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1401" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1401" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1401" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/blab/junior-data-engineer-sao-paulo-br-118043</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="6" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer (Philadelphia, PA)</t>
+        </is>
+      </c>
+      <c r="B1402" s="6" t="inlineStr">
+        <is>
+          <t>Blab</t>
+        </is>
+      </c>
+      <c r="C1402" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1402" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1402" s="6" t="inlineStr">
+        <is>
+          <t>机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1402" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1402" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1402" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/blab/junior-data-engineer-philadelphia-pa-philadelphia-pa-metro-area-384650</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="8" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer (New York, NY)</t>
+        </is>
+      </c>
+      <c r="B1403" s="8" t="inlineStr">
+        <is>
+          <t>Blab</t>
+        </is>
+      </c>
+      <c r="C1403" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1403" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1403" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1403" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1403" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1403" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/blab/junior-data-engineer-new-york-ny-new-york-city-ny-metro-area-354342</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst (London, UK)</t>
+        </is>
+      </c>
+      <c r="B1404" s="6" t="inlineStr">
+        <is>
+          <t>Blab</t>
+        </is>
+      </c>
+      <c r="C1404" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1404" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1404" s="6" t="inlineStr"/>
+      <c r="F1404" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1404" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1404" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/blab/data-analyst-london-uk-184054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (Amsterdam, NLD)</t>
+        </is>
+      </c>
+      <c r="B1405" s="8" t="inlineStr">
+        <is>
+          <t>Blab</t>
+        </is>
+      </c>
+      <c r="C1405" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1405" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1405" s="8" t="inlineStr"/>
+      <c r="F1405" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1405" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1405" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/blab/data-analyst-amsterdam-nld-124096</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="6" t="inlineStr">
+        <is>
+          <t>Senior Applications Developer and Data Specialist</t>
+        </is>
+      </c>
+      <c r="B1406" s="6" t="inlineStr">
+        <is>
+          <t>Brunswickgroup</t>
+        </is>
+      </c>
+      <c r="C1406" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1406" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1406" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F1406" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1406" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1406" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/brunswickgroup/senior-applications-developer-and-data-specialist-london-261871</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/x)</t>
+        </is>
+      </c>
+      <c r="B1407" s="8" t="inlineStr">
+        <is>
+          <t>K-tronik GmbH</t>
+        </is>
+      </c>
+      <c r="C1407" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1407" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1407" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow</t>
+        </is>
+      </c>
+      <c r="F1407" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1407" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1407" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/k-tronik-gmbh/senior-data-engineer-dresden-162970</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent Data Science / Business Intelligence (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1408" s="6" t="inlineStr">
+        <is>
+          <t>Meierhofer</t>
+        </is>
+      </c>
+      <c r="C1408" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1408" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1408" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI</t>
+        </is>
+      </c>
+      <c r="F1408" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1408" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1408" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/meierhofer/remote-werkstudent-data-science-business-intelligence-leipzig-246165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager, Performance Media Analytics CE &amp; EE (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1409" s="8" t="inlineStr">
+        <is>
+          <t>Sharkninjaoperatingllc</t>
+        </is>
+      </c>
+      <c r="C1409" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1409" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1409" s="8" t="inlineStr">
+        <is>
+          <t>Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F1409" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1409" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1409" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sharkninjaoperatingllc/senior-manager-performance-media-analytics-ce-ee-frankfurt-am-main-132628</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudentin im Bereich Datenanalyse / performance analytics (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1410" s="6" t="inlineStr">
+        <is>
+          <t>Gusti Leder GmbH</t>
+        </is>
+      </c>
+      <c r="C1410" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1410" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1410" s="6" t="inlineStr">
+        <is>
+          <t>Excel、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1410" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1410" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1410" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gusti-leder-gmbh/werkstudentin-im-bereich-datenanalyse-performance-analytics-rostock-252026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1411" s="8" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C1411" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1411" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1411" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1411" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1411" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1411" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/data-engineer-liveeo-gmbh-berlin-office-hybrid-140570</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Earth Observation Data Supplier Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1412" s="6" t="inlineStr">
+        <is>
+          <t>Liveeo Gmbh</t>
+        </is>
+      </c>
+      <c r="C1412" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1412" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1412" s="6" t="inlineStr"/>
+      <c r="F1412" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1412" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1412" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/senior-earth-observation-data-supplier-manager-liveeo-gmbh-berlin-office-hybrid-102001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst mit Schwerpunkt Power BI &amp; Databricks (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1413" s="8" t="inlineStr">
+        <is>
+          <t>pmX Group</t>
+        </is>
+      </c>
+      <c r="C1413" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1413" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1413" s="8" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F1413" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1413" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1413" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmx-group/data-analyst-mit-schwerpunkt-power-bi-databricks-stuttgart-292423</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="6" t="inlineStr">
+        <is>
+          <t>Product &amp; Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1414" s="6" t="inlineStr">
+        <is>
+          <t>Matchspace (Music) AG</t>
+        </is>
+      </c>
+      <c r="C1414" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1414" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1414" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1414" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1414" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1414" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/matchspace-music-ag/product-business-analyst-london-29946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="8" t="inlineStr">
+        <is>
+          <t>Senior Sales Operations &amp; Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="B1415" s="8" t="inlineStr">
+        <is>
+          <t>Rubrik</t>
+        </is>
+      </c>
+      <c r="C1415" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1415" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1415" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1415" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1415" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1415" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/rubrik/senior-sales-operations-strategy-analyst-london-186533</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="6" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer, Ads Foundational Representations</t>
+        </is>
+      </c>
+      <c r="B1416" s="6" t="inlineStr">
+        <is>
+          <t>reddit</t>
+        </is>
+      </c>
+      <c r="C1416" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1416" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1416" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1416" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1416" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1416" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/reddit/staff-machine-learning-engineer-ads-foundational-representations-104455</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1417" s="8" t="inlineStr">
+        <is>
+          <t>Pair</t>
+        </is>
+      </c>
+      <c r="C1417" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1417" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1417" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1417" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1417" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1417" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pair/data-scientist-berlin-hybrid-165503</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1418" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1418" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1418" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1418" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1418" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1418" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1418" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-146115</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1419" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1419" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1419" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1419" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1419" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1419" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1419" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-198909</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="6" t="inlineStr">
+        <is>
+          <t>Working Student - Digital Analytics (All Genders)</t>
+        </is>
+      </c>
+      <c r="B1420" s="6" t="inlineStr">
+        <is>
+          <t>Digitl GmbH</t>
+        </is>
+      </c>
+      <c r="C1420" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1420" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1420" s="6" t="inlineStr"/>
+      <c r="F1420" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1420" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1420" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/digitl-gmbh/working-student-digital-analytics-all-genders-hamburg-60980</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="8" t="inlineStr">
+        <is>
+          <t>Working Student - Tech Digital Analytics (All Genders)</t>
+        </is>
+      </c>
+      <c r="B1421" s="8" t="inlineStr">
+        <is>
+          <t>Digitl GmbH</t>
+        </is>
+      </c>
+      <c r="C1421" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1421" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1421" s="8" t="inlineStr"/>
+      <c r="F1421" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1421" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1421" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/digitl-gmbh/working-student-tech-digital-analytics-all-genders-hamburg-97457</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B1422" s="6" t="inlineStr">
+        <is>
+          <t>Makersite GmbH</t>
+        </is>
+      </c>
+      <c r="C1422" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1422" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1422" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1422" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1422" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1422" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/makersite-gmbh/remote-senior-data-scientist-berlin-371753</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1423" s="8" t="inlineStr">
+        <is>
+          <t>Sona</t>
+        </is>
+      </c>
+      <c r="C1423" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1423" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1423" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1423" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1423" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1423" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150930-senior-machine-learning-engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst, Value-Based Care Analytics</t>
+        </is>
+      </c>
+      <c r="B1424" s="6" t="inlineStr">
+        <is>
+          <t>Clover Health</t>
+        </is>
+      </c>
+      <c r="C1424" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1424" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1424" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Snowflake、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1424" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1424" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1424" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150925-data-analyst-value-based-care-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst, Clinical Data Effectiveness</t>
+        </is>
+      </c>
+      <c r="B1425" s="8" t="inlineStr">
+        <is>
+          <t>Clover Health</t>
+        </is>
+      </c>
+      <c r="C1425" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1425" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1425" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1425" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1425" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1425" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150923-data-analyst-clinical-data-effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="6" t="inlineStr">
+        <is>
+          <t>Decision Scientist</t>
+        </is>
+      </c>
+      <c r="B1426" s="6" t="inlineStr">
+        <is>
+          <t>Instructure</t>
+        </is>
+      </c>
+      <c r="C1426" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1426" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1426" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、R、Snowflake、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1426" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1426" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1426" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150911-decision-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="8" t="inlineStr">
+        <is>
+          <t>Senior Decision Scientist</t>
+        </is>
+      </c>
+      <c r="B1427" s="8" t="inlineStr">
+        <is>
+          <t>Instructure</t>
+        </is>
+      </c>
+      <c r="C1427" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1427" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1427" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Snowflake、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1427" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1427" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1427" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150909-senior-decision-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="6" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1428" s="6" t="inlineStr">
+        <is>
+          <t>Instructure</t>
+        </is>
+      </c>
+      <c r="C1428" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1428" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1428" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、dbt、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1428" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1428" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1428" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/150903-sr-data-engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="8" t="inlineStr">
+        <is>
+          <t>IT Senior Analyst - Remote based in the US</t>
+        </is>
+      </c>
+      <c r="B1429" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1429" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1429" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1429" s="8" t="inlineStr"/>
+      <c r="F1429" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1429" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1429" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/tenet-healthcare/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="6" t="inlineStr">
+        <is>
+          <t>Sr Analyst, Underwriting - Life</t>
+        </is>
+      </c>
+      <c r="B1430" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1430" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1430" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1430" s="6" t="inlineStr"/>
+      <c r="F1430" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1430" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1430" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nationwide/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="8" t="inlineStr">
+        <is>
+          <t>AD, Actuarial Analytics/Forecasting</t>
+        </is>
+      </c>
+      <c r="B1431" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1431" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1431" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1431" s="8" t="inlineStr"/>
+      <c r="F1431" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1431" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1431" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/humana/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="6" t="inlineStr">
+        <is>
+          <t>Provider Data Validation (PDV) Manager</t>
+        </is>
+      </c>
+      <c r="B1432" s="6" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C1432" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1432" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1432" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1432" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1432" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1432" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/humana/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="8" t="inlineStr">
+        <is>
+          <t>Sr Director Analyst, Cybersecurity Leadership</t>
+        </is>
+      </c>
+      <c r="B1433" s="8" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C1433" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1433" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1433" s="8" t="inlineStr"/>
+      <c r="F1433" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1433" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1433" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="6" t="inlineStr">
+        <is>
+          <t>OT Analyst/Consultant</t>
+        </is>
+      </c>
+      <c r="B1434" s="6" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C1434" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1434" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1434" s="6" t="inlineStr"/>
+      <c r="F1434" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1434" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1434" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/accenture/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="8" t="inlineStr">
+        <is>
+          <t>Entry Level Chemical Regulatory Analyst</t>
+        </is>
+      </c>
+      <c r="B1435" s="8" t="inlineStr">
+        <is>
+          <t>Pace Analytical Services</t>
+        </is>
+      </c>
+      <c r="C1435" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1435" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1435" s="8" t="inlineStr"/>
+      <c r="F1435" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1435" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1435" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/pace-analytical-services/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+        </is>
+      </c>
+      <c r="B1436" s="6" t="inlineStr">
+        <is>
+          <t>Fujifilm</t>
+        </is>
+      </c>
+      <c r="C1436" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1436" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1436" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1436" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1436" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1436" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/fujifilm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="8" t="inlineStr">
+        <is>
+          <t>Analyst, AI Opportunity &amp; Value Creation</t>
+        </is>
+      </c>
+      <c r="B1437" s="8" t="inlineStr">
+        <is>
+          <t>R1 RCM</t>
+        </is>
+      </c>
+      <c r="C1437" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1437" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1437" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、R</t>
+        </is>
+      </c>
+      <c r="F1437" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1437" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1437" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/r1-rcm/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="6" t="inlineStr">
+        <is>
+          <t>Senior Clinical Data Coordinator - FSP (Homebased - UK)</t>
+        </is>
+      </c>
+      <c r="B1438" s="6" t="inlineStr">
+        <is>
+          <t>Lifelancer</t>
+        </is>
+      </c>
+      <c r="C1438" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1438" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1438" s="6" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1438" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1438" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1438" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/lifelancer/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="8" t="inlineStr">
+        <is>
+          <t>海外网站数据录入</t>
+        </is>
+      </c>
+      <c r="B1439" s="8" t="inlineStr"/>
+      <c r="C1439" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1439" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1439" s="8" t="inlineStr"/>
+      <c r="F1439" s="8" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G1439" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H1439" s="8" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/b2fnza</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1379"/>
+  <autoFilter ref="A1:H1439"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -57363,19 +59807,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>676</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3">
@@ -57385,7 +59829,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>5</v>
@@ -57397,7 +59841,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -57407,19 +59851,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>53</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
@@ -57451,19 +59895,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
@@ -57564,7 +60008,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -57573,7 +60017,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1439</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1490</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-17 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-17 22:48 UTC</t>
+          <t>数据日期 2026-08-18 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-18 22:48 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1438</v>
+        <v>1489</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3710691823899371</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.3486842105263158</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3522012578616352</v>
+        <v>0.3815789473684211</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.270440251572327</v>
+        <v>0.3026315789473684</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
         <v>55</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3459119496855346</v>
+        <v>0.3618421052631579</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1949685534591195</v>
+        <v>0.2171052631578947</v>
       </c>
     </row>
     <row r="14">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1572327044025157</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1572327044025157</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="15">
@@ -806,36 +806,36 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1383647798742138</v>
+        <v>0.1513157894736842</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.1184210526315789</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.119496855345912</v>
+        <v>0.1184210526315789</v>
       </c>
     </row>
     <row r="18">
@@ -845,36 +845,36 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1069182389937107</v>
+        <v>0.1184210526315789</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1006289308176101</v>
+        <v>0.1118421052631579</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1439"/>
+  <dimension ref="A1:H1490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -59745,8 +59745,2086 @@
         </is>
       </c>
     </row>
+    <row r="1440">
+      <c r="A1440" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1440" s="6" t="inlineStr">
+        <is>
+          <t>Vomela</t>
+        </is>
+      </c>
+      <c r="C1440" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1440" s="6" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1440" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Snowflake、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1440" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1440" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1440" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-principal-data-engineer-vomela-1136860</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1441" s="8" t="inlineStr">
+        <is>
+          <t>Superhuman</t>
+        </is>
+      </c>
+      <c r="C1441" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1441" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1441" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1441" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1441" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1441" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/superhuman/data-engineer-berlin-89243</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="6" t="inlineStr">
+        <is>
+          <t>Customer Success Manager (m/f/d) – Software &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B1442" s="6" t="inlineStr">
+        <is>
+          <t>Kaskegroup</t>
+        </is>
+      </c>
+      <c r="C1442" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1442" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1442" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1442" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1442" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1442" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/kaskegroup/customer-success-manager-software-analytics-munchen-425576</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer, Security Log Intelligence</t>
+        </is>
+      </c>
+      <c r="B1443" s="8" t="inlineStr">
+        <is>
+          <t>RedMimicry GmbH</t>
+        </is>
+      </c>
+      <c r="C1443" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1443" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1443" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1443" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1443" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1443" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/redmimicry-gmbh/senior-ai-ml-engineer-security-log-intelligence-berlin-431641</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="6" t="inlineStr">
+        <is>
+          <t>Junior AI/ML Engineer, Data and Evaluation</t>
+        </is>
+      </c>
+      <c r="B1444" s="6" t="inlineStr">
+        <is>
+          <t>RedMimicry GmbH</t>
+        </is>
+      </c>
+      <c r="C1444" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1444" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1444" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1444" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1444" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1444" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/redmimicry-gmbh/junior-ai-ml-engineer-data-and-evaluation-berlin-438979</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Security Analytics</t>
+        </is>
+      </c>
+      <c r="B1445" s="8" t="inlineStr">
+        <is>
+          <t>RedMimicry GmbH</t>
+        </is>
+      </c>
+      <c r="C1445" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1445" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1445" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1445" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1445" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1445" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/redmimicry-gmbh/full-stack-engineer-security-analytics-berlin-400966</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Workforce Management Analytics</t>
+        </is>
+      </c>
+      <c r="B1446" s="6" t="inlineStr">
+        <is>
+          <t>wolt</t>
+        </is>
+      </c>
+      <c r="C1446" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1446" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1446" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、统计学</t>
+        </is>
+      </c>
+      <c r="F1446" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1446" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1446" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt/senior-data-scientist-workforce-management-analytics-berlin-311902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="8" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (EDW Enterprise Data Warehouse Migrations)</t>
+        </is>
+      </c>
+      <c r="B1447" s="8" t="inlineStr">
+        <is>
+          <t>databricks</t>
+        </is>
+      </c>
+      <c r="C1447" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1447" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1447" s="8" t="inlineStr">
+        <is>
+          <t>SQL、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1447" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1447" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1447" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/databricks/senior-solutions-architect-edw-enterprise-data-warehouse-migrations-berlin-munich-271828</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/w/d) BI &amp; Konsolidierung</t>
+        </is>
+      </c>
+      <c r="B1448" s="6" t="inlineStr">
+        <is>
+          <t>ANGEHEUERT GmbH</t>
+        </is>
+      </c>
+      <c r="C1448" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1448" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1448" s="6" t="inlineStr"/>
+      <c r="F1448" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1448" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1448" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/angeheuert-gmbh/remote-senior-consultant-bi-konsolidierung-stuttgart-342581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) IT Product Owner Data Platform (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1449" s="8" t="inlineStr">
+        <is>
+          <t>OXG Glasfaser GmbH</t>
+        </is>
+      </c>
+      <c r="C1449" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1449" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1449" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1449" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1449" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1449" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/oxg-glasfaser-gmbh/remote-senior-it-product-owner-data-platform-43391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager Data Science &amp; AI Engineering (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1450" s="6" t="inlineStr">
+        <is>
+          <t>Eraneos</t>
+        </is>
+      </c>
+      <c r="C1450" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1450" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1450" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1450" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1450" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1450" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eraneos/remote-senior-manager-data-science-ai-engineering-264219</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager Data Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1451" s="8" t="inlineStr">
+        <is>
+          <t>Eraneos</t>
+        </is>
+      </c>
+      <c r="C1451" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1451" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1451" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1451" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1451" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1451" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eraneos/remote-senior-manager-data-analytics-134976</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (all genders)</t>
+        </is>
+      </c>
+      <c r="B1452" s="6" t="inlineStr">
+        <is>
+          <t>Eraneos</t>
+        </is>
+      </c>
+      <c r="C1452" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1452" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1452" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Snowflake、dbt、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F1452" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1452" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1452" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eraneos/remote-senior-analytics-engineer-all-genders-281631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1453" s="8" t="inlineStr">
+        <is>
+          <t>Eraneos</t>
+        </is>
+      </c>
+      <c r="C1453" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1453" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1453" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1453" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1453" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1453" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eraneos/remote-senior-ai-engineer-300978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1454" s="6" t="inlineStr">
+        <is>
+          <t>Superhuman%20Platform%20Inc</t>
+        </is>
+      </c>
+      <c r="C1454" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1454" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1454" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1454" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1454" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1454" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/superhuman20platform20inc/data-engineer-berlin-279973</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Researcher</t>
+        </is>
+      </c>
+      <c r="B1455" s="8" t="inlineStr">
+        <is>
+          <t>Janestreet</t>
+        </is>
+      </c>
+      <c r="C1455" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1455" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1455" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1455" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1455" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1455" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/janestreet/machine-learning-researcher-london-326827</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Data Analyst- Consumer Growth</t>
+        </is>
+      </c>
+      <c r="B1456" s="6" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C1456" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1456" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1456" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1456" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1456" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1456" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sumup/senior-product-data-analyst-consumer-growth-london-424940</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="8" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (EDW Enterprise Data Warehouse Migrations)</t>
+        </is>
+      </c>
+      <c r="B1457" s="8" t="inlineStr">
+        <is>
+          <t>databricks</t>
+        </is>
+      </c>
+      <c r="C1457" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1457" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1457" s="8" t="inlineStr">
+        <is>
+          <t>SQL、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1457" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1457" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1457" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/databricks/senior-solutions-architect-edw-enterprise-data-warehouse-migrations-london-219495</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="6" t="inlineStr">
+        <is>
+          <t>Applied Machine Learning Engineer, EMEA</t>
+        </is>
+      </c>
+      <c r="B1458" s="6" t="inlineStr">
+        <is>
+          <t>Fireworks</t>
+        </is>
+      </c>
+      <c r="C1458" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1458" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1458" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1458" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1458" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1458" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fireworks/applied-machine-learning-engineer-emea-london-353394</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1459" s="8" t="inlineStr">
+        <is>
+          <t>Geniussports</t>
+        </is>
+      </c>
+      <c r="C1459" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1459" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1459" s="8" t="inlineStr"/>
+      <c r="F1459" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1459" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1459" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/geniussports/senior-data-scientist-london-414675</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Science Manager</t>
+        </is>
+      </c>
+      <c r="B1460" s="6" t="inlineStr">
+        <is>
+          <t>Geniussports</t>
+        </is>
+      </c>
+      <c r="C1460" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1460" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1460" s="6" t="inlineStr"/>
+      <c r="F1460" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1460" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1460" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/geniussports/senior-data-science-manager-london-98946</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="8" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer I</t>
+        </is>
+      </c>
+      <c r="B1461" s="8" t="inlineStr">
+        <is>
+          <t>Checkout.com</t>
+        </is>
+      </c>
+      <c r="C1461" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1461" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1461" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Looker、Snowflake、dbt、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1461" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1461" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1461" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/checkoutcom/data-analytics-engineer-i-london-438463</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="6" t="inlineStr">
+        <is>
+          <t>Softwareentwickler (m/w/d) Moodle / PHP / E-Learning</t>
+        </is>
+      </c>
+      <c r="B1462" s="6" t="inlineStr">
+        <is>
+          <t>Velptec</t>
+        </is>
+      </c>
+      <c r="C1462" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1462" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1462" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1462" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1462" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1462" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/velptec/remote-softwareentwickler-moodle-php-e-learning-380926</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="8" t="inlineStr">
+        <is>
+          <t>Professorship (W2) in Data Science and Digital Systems (100%) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1463" s="8" t="inlineStr">
+        <is>
+          <t>Velptec</t>
+        </is>
+      </c>
+      <c r="C1463" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1463" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1463" s="8" t="inlineStr"/>
+      <c r="F1463" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1463" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1463" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/velptec/remote-professorship-w2-in-data-science-and-digital-systems-100-95925</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Workforce Management Analytics</t>
+        </is>
+      </c>
+      <c r="B1464" s="6" t="inlineStr">
+        <is>
+          <t>Wolt - English</t>
+        </is>
+      </c>
+      <c r="C1464" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1464" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1464" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、Airflow、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1464" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1464" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1464" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wolt-english/senior-data-scientist-workforce-management-analytics-berlin-224838</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data - GSA (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1465" s="8" t="inlineStr">
+        <is>
+          <t>sonymusicentertainment</t>
+        </is>
+      </c>
+      <c r="C1465" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1465" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1465" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1465" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1465" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1465" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sonymusicentertainment/head-of-data-gsa-europe-berlin-58521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="6" t="inlineStr">
+        <is>
+          <t>Working Student – Robot Pilot / Data Collection (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1466" s="6" t="inlineStr">
+        <is>
+          <t>RobCo</t>
+        </is>
+      </c>
+      <c r="C1466" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1466" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1466" s="6" t="inlineStr"/>
+      <c r="F1466" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1466" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1466" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/robco/working-student-robot-pilot-data-collection-munich-457297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer (m/w/d) –  Generative AI + Legal AI</t>
+        </is>
+      </c>
+      <c r="B1467" s="8" t="inlineStr">
+        <is>
+          <t>Ypog Law</t>
+        </is>
+      </c>
+      <c r="C1467" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1467" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1467" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1467" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1467" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1467" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ypog-law/ai-ml-engineer-generative-ai-legal-ai-berlin-485095</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="6" t="inlineStr">
+        <is>
+          <t>SOC-Analyst/SIEM Engineer (W/M/D)</t>
+        </is>
+      </c>
+      <c r="B1468" s="6" t="inlineStr">
+        <is>
+          <t>secupay AG</t>
+        </is>
+      </c>
+      <c r="C1468" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1468" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1468" s="6" t="inlineStr"/>
+      <c r="F1468" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1468" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1468" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/secupay-ag/soc-analyst-siem-engineer-pulsnitz-11459</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="8" t="inlineStr">
+        <is>
+          <t>IT Business Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1469" s="8" t="inlineStr">
+        <is>
+          <t>Bell Food Group</t>
+        </is>
+      </c>
+      <c r="C1469" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1469" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1469" s="8" t="inlineStr"/>
+      <c r="F1469" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1469" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1469" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bell-food-group/it-business-analyst-radolfzell-492760</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="6" t="inlineStr">
+        <is>
+          <t>Research Analyst - Strategic Communications</t>
+        </is>
+      </c>
+      <c r="B1470" s="6" t="inlineStr">
+        <is>
+          <t>iwoca</t>
+        </is>
+      </c>
+      <c r="C1470" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1470" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1470" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、统计学</t>
+        </is>
+      </c>
+      <c r="F1470" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1470" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1470" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/iwoca/research-analyst-strategic-communications-london-497316</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="8" t="inlineStr">
+        <is>
+          <t>Senior Product Quality Analyst - AI Voice</t>
+        </is>
+      </c>
+      <c r="B1471" s="8" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C1471" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1471" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1471" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1471" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1471" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1471" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/spotify/senior-product-quality-analyst-ai-voice-london-134064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1472" s="6" t="inlineStr">
+        <is>
+          <t>Fanduel</t>
+        </is>
+      </c>
+      <c r="C1472" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1472" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1472" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1472" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1472" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1472" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fanduel/data-engineer-edinburgh-318318</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer - fully remote (working hours 5am-2pm CEST) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1473" s="8" t="inlineStr">
+        <is>
+          <t>JobLeads Careers</t>
+        </is>
+      </c>
+      <c r="C1473" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1473" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1473" s="8" t="inlineStr"/>
+      <c r="F1473" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1473" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1473" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobleads-careers/data-engineer-fully-remote-working-hours-5am-2pm-cest-45280</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="6" t="inlineStr">
+        <is>
+          <t>BI Specialist - Financial Reporting &amp; Data Analytics</t>
+        </is>
+      </c>
+      <c r="B1474" s="6" t="inlineStr">
+        <is>
+          <t>Bell Food Group</t>
+        </is>
+      </c>
+      <c r="C1474" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1474" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1474" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1474" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1474" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1474" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bell-food-group/bi-specialist-financial-reporting-data-analytics-radolfzell-10657</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="8" t="inlineStr">
+        <is>
+          <t>Data Quality Coordinator (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1475" s="8" t="inlineStr">
+        <is>
+          <t>Agile Robots SE - Personio</t>
+        </is>
+      </c>
+      <c r="C1475" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1475" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1475" s="8" t="inlineStr"/>
+      <c r="F1475" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1475" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1475" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/agile-robots-se-personio/data-quality-coordinator-germany-munich-hq-438526</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1476" s="6" t="inlineStr">
+        <is>
+          <t>exmox</t>
+        </is>
+      </c>
+      <c r="C1476" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1476" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1476" s="6" t="inlineStr"/>
+      <c r="F1476" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1476" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1476" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/exmox/senior-data-analyst-hamburg-265376</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="8" t="inlineStr">
+        <is>
+          <t>Data Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1477" s="8" t="inlineStr">
+        <is>
+          <t>exmox</t>
+        </is>
+      </c>
+      <c r="C1477" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1477" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1477" s="8" t="inlineStr"/>
+      <c r="F1477" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1477" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1477" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/exmox/data-manager-hamburg-372314</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1478" s="6" t="inlineStr">
+        <is>
+          <t>Peter Park</t>
+        </is>
+      </c>
+      <c r="C1478" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1478" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1478" s="6" t="inlineStr"/>
+      <c r="F1478" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1478" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1478" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/peter-park/senior-data-scientist-munchen-26297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="8" t="inlineStr">
+        <is>
+          <t>Marketing Analyst</t>
+        </is>
+      </c>
+      <c r="B1479" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1479" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1479" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1479" s="8" t="inlineStr"/>
+      <c r="F1479" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1479" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1479" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/saks-off-5th/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="6" t="inlineStr">
+        <is>
+          <t>Insider Risk Analyst (Remote, GBR)</t>
+        </is>
+      </c>
+      <c r="B1480" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1480" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1480" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1480" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F1480" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1480" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1480" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/crowdstrike/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="8" t="inlineStr">
+        <is>
+          <t>Program Analyst</t>
+        </is>
+      </c>
+      <c r="B1481" s="8" t="inlineStr">
+        <is>
+          <t>CLEAResult</t>
+        </is>
+      </c>
+      <c r="C1481" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1481" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1481" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1481" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1481" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1481" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/clearesult/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="6" t="inlineStr">
+        <is>
+          <t>Revenue Operations Analyst (Marketing Operations)</t>
+        </is>
+      </c>
+      <c r="B1482" s="6" t="inlineStr">
+        <is>
+          <t>Kami</t>
+        </is>
+      </c>
+      <c r="C1482" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1482" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1482" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Looker</t>
+        </is>
+      </c>
+      <c r="F1482" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1482" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1482" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/kami/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="8" t="inlineStr">
+        <is>
+          <t>Digital Analyst - Item set-up</t>
+        </is>
+      </c>
+      <c r="B1483" s="8" t="inlineStr">
+        <is>
+          <t>Saks OFF 5TH</t>
+        </is>
+      </c>
+      <c r="C1483" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1483" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1483" s="8" t="inlineStr"/>
+      <c r="F1483" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1483" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1483" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/saks-off-5th/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="6" t="inlineStr">
+        <is>
+          <t>Senior Compliance Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B1484" s="6" t="inlineStr">
+        <is>
+          <t>CCM CrossCountry Mortgage, LLC</t>
+        </is>
+      </c>
+      <c r="C1484" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1484" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1484" s="6" t="inlineStr"/>
+      <c r="F1484" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1484" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1484" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ccm-crosscountry-mortgage-llc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Manager, Growth</t>
+        </is>
+      </c>
+      <c r="B1485" s="8" t="inlineStr">
+        <is>
+          <t>Collectors</t>
+        </is>
+      </c>
+      <c r="C1485" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1485" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1485" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、dbt</t>
+        </is>
+      </c>
+      <c r="F1485" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1485" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1485" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/collectors/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Architect</t>
+        </is>
+      </c>
+      <c r="B1486" s="6" t="inlineStr">
+        <is>
+          <t>Henry Schein</t>
+        </is>
+      </c>
+      <c r="C1486" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1486" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1486" s="6" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、dbt、Airflow、AWS、Azure、GCP、BigQuery、机器学习、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1486" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1486" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1486" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/henry-schein/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="8" t="inlineStr">
+        <is>
+          <t>Remote Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1487" s="8" t="inlineStr">
+        <is>
+          <t>Spotter Labs</t>
+        </is>
+      </c>
+      <c r="C1487" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1487" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1487" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1487" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1487" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1487" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/spotter-labs/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="6" t="inlineStr">
+        <is>
+          <t>AML Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="B1488" s="6" t="inlineStr">
+        <is>
+          <t>Capitex</t>
+        </is>
+      </c>
+      <c r="C1488" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1488" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1488" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R</t>
+        </is>
+      </c>
+      <c r="F1488" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1488" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1488" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/capitex/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Data Driven Detroit</t>
+        </is>
+      </c>
+      <c r="B1489" s="8" t="inlineStr">
+        <is>
+          <t>Mondo Unlimited</t>
+        </is>
+      </c>
+      <c r="C1489" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1489" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1489" s="8" t="inlineStr"/>
+      <c r="F1489" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1489" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1489" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mondo-unlimited/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="6" t="inlineStr">
+        <is>
+          <t>ML Engineer - Coding Agent Expert - AI Trainer</t>
+        </is>
+      </c>
+      <c r="B1490" s="6" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1490" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1490" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1490" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1490" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1490" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H1490" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1439"/>
+  <autoFilter ref="A1:H1490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59807,19 +61885,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C2" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>164</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>157</v>
-      </c>
       <c r="E2" s="6" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>718</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3">
@@ -59829,7 +61907,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>5</v>
@@ -59841,7 +61919,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -59851,19 +61929,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>26</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
@@ -59876,16 +61954,16 @@
         <v>12</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -59961,7 +62039,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
@@ -59973,7 +62051,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1546</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-18 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-18 22:48 UTC</t>
+          <t>数据日期 2026-08-19 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-19 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1489</v>
+        <v>1545</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -706,175 +706,175 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4025974025974026</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>数据分析/BI</t>
+          <t>其他数据岗</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3486842105263158</v>
+        <v>0.3571428571428572</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.3896103896103896</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>其他数据岗</t>
+          <t>数据分析/BI</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3026315789473684</v>
+        <v>0.3311688311688312</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3618421052631579</v>
+        <v>0.3116883116883117</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>数据科学/算法</t>
+          <t>数据开发/工程</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2171052631578947</v>
+        <v>0.1623376623376623</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1623376623376623</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>数据开发/工程</t>
+          <t>数据科学/算法</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.131578947368421</v>
+        <v>0.1493506493506493</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1513157894736842</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1184210526315789</v>
+        <v>0.1363636363636364</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1184210526315789</v>
+        <v>0.1298701298701299</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1184210526315789</v>
+        <v>0.1298701298701299</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>GCP</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1118421052631579</v>
+        <v>0.1233766233766234</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.1168831168831169</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1490"/>
+  <dimension ref="A1:H1546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -61823,8 +61823,2308 @@
         </is>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" s="8" t="inlineStr">
+        <is>
+          <t>Consultant Data &amp; AI / Digitale Transformation Public Sector (all genders)</t>
+        </is>
+      </c>
+      <c r="B1491" s="8" t="inlineStr">
+        <is>
+          <t>Init Ag</t>
+        </is>
+      </c>
+      <c r="C1491" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1491" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1491" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1491" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1491" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1491" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/init-ag/consultant-data-ai-digitale-transformation-public-sector-all-genders-mainz-215643</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Category Management &amp; Product Data</t>
+        </is>
+      </c>
+      <c r="B1492" s="6" t="inlineStr">
+        <is>
+          <t>Vitafy</t>
+        </is>
+      </c>
+      <c r="C1492" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1492" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1492" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1492" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1492" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1492" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vitafy/werkstudent-category-management-product-data-munchen-370322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="8" t="inlineStr">
+        <is>
+          <t>Praktikant (all genders) Social Selling, Data &amp; CRM – Gestalte die Digitalisierung unseres Vertriebsmarketings mit</t>
+        </is>
+      </c>
+      <c r="B1493" s="8" t="inlineStr">
+        <is>
+          <t>Valuenet Group</t>
+        </is>
+      </c>
+      <c r="C1493" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1493" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1493" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1493" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1493" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1493" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/valuenet-group/praktikant-all-genders-social-selling-data-crm-gestalte-die-digitalisierung-unseres-vertriebsmarketings-mit-munchen-26532</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Data Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1494" s="6" t="inlineStr">
+        <is>
+          <t>ZDF Digital Medienproduktion GmbH</t>
+        </is>
+      </c>
+      <c r="C1494" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1494" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1494" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、GCP</t>
+        </is>
+      </c>
+      <c r="F1494" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1494" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1494" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/zdf-digital-medienproduktion-gmbh/junior-data-analyst-mainz-oder-berlin-409872</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="8" t="inlineStr">
+        <is>
+          <t>(Junior) Consultant - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B1495" s="8" t="inlineStr">
+        <is>
+          <t>pmOne AG</t>
+        </is>
+      </c>
+      <c r="C1495" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1495" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1495" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Snowflake、Azure</t>
+        </is>
+      </c>
+      <c r="F1495" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1495" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1495" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmone-ag/junior-consultant-data-analytics-munich-8899</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineering Senior Manager</t>
+        </is>
+      </c>
+      <c r="B1496" s="6" t="inlineStr">
+        <is>
+          <t>Fanduel</t>
+        </is>
+      </c>
+      <c r="C1496" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1496" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1496" s="6" t="inlineStr"/>
+      <c r="F1496" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1496" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1496" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fanduel/data-engineering-senior-manager-edinburgh-354097</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="8" t="inlineStr">
+        <is>
+          <t>BI Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1497" s="8" t="inlineStr">
+        <is>
+          <t>Motorway</t>
+        </is>
+      </c>
+      <c r="C1497" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1497" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1497" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker</t>
+        </is>
+      </c>
+      <c r="F1497" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1497" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1497" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/motorway/bi-data-analyst-london-485108</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="6" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="B1498" s="6" t="inlineStr">
+        <is>
+          <t>Axle Careers</t>
+        </is>
+      </c>
+      <c r="C1498" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1498" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1498" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1498" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1498" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1498" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/axle-careers/data-science-london-354286</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1499" s="8" t="inlineStr">
+        <is>
+          <t>Axle Careers</t>
+        </is>
+      </c>
+      <c r="C1499" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1499" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1499" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F1499" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1499" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1499" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/axle-careers/analytics-engineer-london-466020</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="6" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B1500" s="6" t="inlineStr">
+        <is>
+          <t>Techtorch</t>
+        </is>
+      </c>
+      <c r="C1500" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1500" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1500" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、AWS、Azure、GCP、BigQuery、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1500" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1500" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1500" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/techtorch/data-architect-eu-uk-339554</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="8" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="B1501" s="8" t="inlineStr">
+        <is>
+          <t>Techtorch</t>
+        </is>
+      </c>
+      <c r="C1501" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1501" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1501" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1501" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1501" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1501" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/techtorch/forward-deployed-ai-engineer-eu-uk-260204</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="6" t="inlineStr">
+        <is>
+          <t>Data-Plattform Engineer (Fabric / Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1502" s="6" t="inlineStr">
+        <is>
+          <t>Ailio GmbH</t>
+        </is>
+      </c>
+      <c r="C1502" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1502" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1502" s="6" t="inlineStr">
+        <is>
+          <t>Python、Azure</t>
+        </is>
+      </c>
+      <c r="F1502" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1502" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1502" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ailio-gmbh/data-plattform-engineer-fabric-databricks-bielefeld-273667</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="B1503" s="8" t="inlineStr">
+        <is>
+          <t>speechify</t>
+        </is>
+      </c>
+      <c r="C1503" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1503" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1503" s="8" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1503" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1503" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1503" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-hamburg-germany-252312</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="B1504" s="6" t="inlineStr">
+        <is>
+          <t>speechify</t>
+        </is>
+      </c>
+      <c r="C1504" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1504" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1504" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1504" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1504" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1504" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-berlin-germany-374168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="8" t="inlineStr">
+        <is>
+          <t>Projektmitarbeiter KI / Data Research (m/w/d) - Nebenjob / Freelancer - flexibel + remote</t>
+        </is>
+      </c>
+      <c r="B1505" s="8" t="inlineStr">
+        <is>
+          <t>Talentwert Digital Research Studio</t>
+        </is>
+      </c>
+      <c r="C1505" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1505" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1505" s="8" t="inlineStr"/>
+      <c r="F1505" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1505" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1505" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/talentwert-digital-research-studio/projektmitarbeiter-ki-data-research-nebenjob-freelancer-flexibel-remote-leipzig-401065</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1506" s="6" t="inlineStr">
+        <is>
+          <t>Planetlabs</t>
+        </is>
+      </c>
+      <c r="C1506" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1506" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1506" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1506" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1506" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1506" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/planetlabs/data-analyst-berlin-21502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Product Owner (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1507" s="8" t="inlineStr">
+        <is>
+          <t>Yepoda</t>
+        </is>
+      </c>
+      <c r="C1507" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1507" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1507" s="8" t="inlineStr">
+        <is>
+          <t>SQL、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1507" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1507" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1507" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/yepoda/senior-data-analytics-product-owner-berlin-201712</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1508" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C1508" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1508" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1508" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS</t>
+        </is>
+      </c>
+      <c r="F1508" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1508" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1508" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/data-engineer-hamburg-or-berlin-92068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="8" t="inlineStr">
+        <is>
+          <t>Senior IT Business Analyst Insurance (all genders) DE</t>
+        </is>
+      </c>
+      <c r="B1509" s="8" t="inlineStr">
+        <is>
+          <t>BSI Software</t>
+        </is>
+      </c>
+      <c r="C1509" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1509" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1509" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1509" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1509" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1509" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bsi-software/senior-it-business-analyst-insurance-all-genders-de-darmstadt-298153</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="6" t="inlineStr">
+        <is>
+          <t>Werkstudentin im Bereich Datenanalyse / performance analytics (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1510" s="6" t="inlineStr">
+        <is>
+          <t>Gusti Leder GmbH</t>
+        </is>
+      </c>
+      <c r="C1510" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1510" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1510" s="6" t="inlineStr">
+        <is>
+          <t>Excel、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1510" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1510" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1510" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gusti-leder-gmbh/werkstudentin-im-bereich-datenanalyse-performance-analytics-rostock-239018</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1511" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm Gmbh</t>
+        </is>
+      </c>
+      <c r="C1511" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1511" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1511" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS</t>
+        </is>
+      </c>
+      <c r="F1511" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1511" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1511" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-software-engineer-hybrid-munchen-146453</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Visualization Engineer - Microsoft Fabric (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1512" s="6" t="inlineStr">
+        <is>
+          <t>Alexander Thamm Gmbh</t>
+        </is>
+      </c>
+      <c r="C1512" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1512" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1512" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1512" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1512" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1512" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-visualization-engineer-microsoft-fabric-hybrid-munchen-1225</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/w/d) - Chemical Engineering &amp; Verfahrenstechnik</t>
+        </is>
+      </c>
+      <c r="B1513" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm Gmbh</t>
+        </is>
+      </c>
+      <c r="C1513" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1513" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1513" s="8" t="inlineStr">
+        <is>
+          <t>Python、R、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1513" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1513" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1513" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-scientist-chemical-engineering-verfahrenstechnik-hybrid-munchen-112102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="6" t="inlineStr">
+        <is>
+          <t>Senior AI Transformation Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1514" s="6" t="inlineStr">
+        <is>
+          <t>Alexander Thamm Gmbh</t>
+        </is>
+      </c>
+      <c r="C1514" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1514" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1514" s="6" t="inlineStr"/>
+      <c r="F1514" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1514" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1514" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-ai-transformation-consultant-hybrid-munchen-34081</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="8" t="inlineStr">
+        <is>
+          <t>Principal AI/ML Scientist &amp; Engineer</t>
+        </is>
+      </c>
+      <c r="B1515" s="8" t="inlineStr">
+        <is>
+          <t>Pipedrive</t>
+        </is>
+      </c>
+      <c r="C1515" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1515" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1515" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1515" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1515" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1515" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pipedrive/principal-ai-ml-scientist-engineer-germany-berlin-295398</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="6" t="inlineStr">
+        <is>
+          <t>Praktikum/Trainee als Financial Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1516" s="6" t="inlineStr">
+        <is>
+          <t>Horbach Wirtschaftsberatung Dresden</t>
+        </is>
+      </c>
+      <c r="C1516" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1516" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1516" s="6" t="inlineStr"/>
+      <c r="F1516" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1516" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1516" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/horbach-wirtschaftsberatung-dresden/praktikum-trainee-als-financial-analyst-dresden-4278</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="8" t="inlineStr">
+        <is>
+          <t>Private Equity „Intern to Analyst“-Programm (m/w/d) - Einstiegsperspektive im PE</t>
+        </is>
+      </c>
+      <c r="B1517" s="8" t="inlineStr">
+        <is>
+          <t>CAPCELLENCE Management GmbH</t>
+        </is>
+      </c>
+      <c r="C1517" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1517" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1517" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1517" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1517" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1517" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/capcellence-management-gmbh/private-equity-intern-to-analyst-programm-einstiegsperspektive-im-pe-hamburg-272118</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="6" t="inlineStr">
+        <is>
+          <t>VP, Data Strategy, UK</t>
+        </is>
+      </c>
+      <c r="B1518" s="6" t="inlineStr">
+        <is>
+          <t>Wppmedia</t>
+        </is>
+      </c>
+      <c r="C1518" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1518" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1518" s="6" t="inlineStr"/>
+      <c r="F1518" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1518" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1518" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/vp-data-strategy-uk-london-367070</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Senior Executive</t>
+        </is>
+      </c>
+      <c r="B1519" s="8" t="inlineStr">
+        <is>
+          <t>Wppmedia</t>
+        </is>
+      </c>
+      <c r="C1519" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1519" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1519" s="8" t="inlineStr">
+        <is>
+          <t>SQL、BigQuery、统计学</t>
+        </is>
+      </c>
+      <c r="F1519" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1519" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1519" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/analytics-senior-executive-london-262093</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="6" t="inlineStr">
+        <is>
+          <t>Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B1520" s="6" t="inlineStr">
+        <is>
+          <t>Wppmedia</t>
+        </is>
+      </c>
+      <c r="C1520" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1520" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1520" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1520" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1520" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1520" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/analytics-manager-london-37823</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="8" t="inlineStr">
+        <is>
+          <t>Digital Sharks: Performance Data Associate — Marketplace Intelligence (Early Careers)</t>
+        </is>
+      </c>
+      <c r="B1521" s="8" t="inlineStr">
+        <is>
+          <t>Sharkninjaoperatingllc</t>
+        </is>
+      </c>
+      <c r="C1521" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1521" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1521" s="8" t="inlineStr"/>
+      <c r="F1521" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1521" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1521" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sharkninjaoperatingllc/digital-sharks-performance-data-associate-marketplace-intelligence-early-careers-london-300833</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="6" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1522" s="6" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C1522" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1522" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1522" s="6" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F1522" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1522" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1522" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ripple/staff-software-engineer-data-engineering-london-158309</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1523" s="8" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C1523" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1523" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1523" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Spark、ETL</t>
+        </is>
+      </c>
+      <c r="F1523" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1523" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1523" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ripple/senior-software-engineer-data-engineering-london-155157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1524" s="6" t="inlineStr">
+        <is>
+          <t>Sohohouseco</t>
+        </is>
+      </c>
+      <c r="C1524" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1524" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1524" s="6" t="inlineStr">
+        <is>
+          <t>SQL、dbt</t>
+        </is>
+      </c>
+      <c r="F1524" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1524" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1524" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sohohouseco/senior-data-analyst-london-353435</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="8" t="inlineStr">
+        <is>
+          <t>Product Data Coordinator, Soho Home - 6-Month FTC</t>
+        </is>
+      </c>
+      <c r="B1525" s="8" t="inlineStr">
+        <is>
+          <t>Sohohouseco</t>
+        </is>
+      </c>
+      <c r="C1525" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1525" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1525" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1525" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1525" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1525" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sohohouseco/product-data-coordinator-soho-home-6-month-ftc-london-225008</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="6" t="inlineStr">
+        <is>
+          <t>Praktikum als IT-Administrator &amp; Data Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1526" s="6" t="inlineStr">
+        <is>
+          <t>Pflegia</t>
+        </is>
+      </c>
+      <c r="C1526" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1526" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1526" s="6" t="inlineStr"/>
+      <c r="F1526" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1526" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1526" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pflegia/praktikum-als-it-administrator-data-analyst-berlin-146121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="8" t="inlineStr">
+        <is>
+          <t>Teamlead Data &amp; AI (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1527" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1527" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1527" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1527" s="8" t="inlineStr"/>
+      <c r="F1527" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1527" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1527" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/teamlead-data-ai-munchen-252523</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1528" s="6" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1528" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1528" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1528" s="6" t="inlineStr">
+        <is>
+          <t>Python、Snowflake、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1528" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1528" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1528" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-engineer-munchen-361544</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Projektleitung - Schwerpunkt Defense (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1529" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1529" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1529" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1529" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1529" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1529" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1529" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-ai-projektleitung-schwerpunkt-defense-munchen-60328</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="6" t="inlineStr">
+        <is>
+          <t>Principal Data Scientist (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1530" s="6" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1530" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1530" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1530" s="6" t="inlineStr">
+        <is>
+          <t>Python、R、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1530" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1530" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1530" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/principal-data-scientist-munchen-118879</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="8" t="inlineStr">
+        <is>
+          <t>Principal Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1531" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1531" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1531" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1531" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1531" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1531" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1531" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/principal-data-engineer-munchen-77292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="6" t="inlineStr">
+        <is>
+          <t>UAV Operations Engineer / Pilot – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1532" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1532" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1532" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1532" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1532" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1532" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1532" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/uav-operations-engineer-pilot-data-operations-all-genders-munich-219556</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="8" t="inlineStr">
+        <is>
+          <t>Field Robotics Engineer – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1533" s="8" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1533" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1533" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1533" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1533" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1533" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1533" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/field-robotics-engineer-data-operations-all-genders-munich-6651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Data Operations (all genders)</t>
+        </is>
+      </c>
+      <c r="B1534" s="6" t="inlineStr">
+        <is>
+          <t>Stark</t>
+        </is>
+      </c>
+      <c r="C1534" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1534" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1534" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、GCP、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1534" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1534" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1534" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/stark/data-platform-engineer-data-operations-all-genders-munich-402129</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1535" s="8" t="inlineStr">
+        <is>
+          <t>celebrate company GmbH</t>
+        </is>
+      </c>
+      <c r="C1535" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1535" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1535" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、dbt、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1535" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1535" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1535" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/celebrate-company-gmbh/remote-senior-data-engineer-gilching-244485</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="6" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer (Senior)</t>
+        </is>
+      </c>
+      <c r="B1536" s="6" t="inlineStr">
+        <is>
+          <t>Mactores</t>
+        </is>
+      </c>
+      <c r="C1536" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1536" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1536" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1536" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1536" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1536" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151146-aws-data-engineer-senior</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst (Technical Consultant) – Integrations</t>
+        </is>
+      </c>
+      <c r="B1537" s="8" t="inlineStr">
+        <is>
+          <t>Launchpad Technologies</t>
+        </is>
+      </c>
+      <c r="C1537" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1537" s="8" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="E1537" s="8" t="inlineStr"/>
+      <c r="F1537" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1537" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1537" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151143-business-analyst-technical-consultant-integrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="6" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer (Associate)</t>
+        </is>
+      </c>
+      <c r="B1538" s="6" t="inlineStr">
+        <is>
+          <t>Mactores</t>
+        </is>
+      </c>
+      <c r="C1538" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1538" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1538" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Spark、Airflow、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1538" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1538" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1538" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151141-aws-data-engineer-associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="8" t="inlineStr">
+        <is>
+          <t>Staff Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1539" s="8" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="C1539" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1539" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E1539" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1539" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1539" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1539" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151112-staff-analytics-engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer - Market Data</t>
+        </is>
+      </c>
+      <c r="B1540" s="6" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C1540" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1540" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1540" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1540" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1540" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1540" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/alpaca/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1541" s="8" t="inlineStr">
+        <is>
+          <t>Portcast</t>
+        </is>
+      </c>
+      <c r="C1541" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1541" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1541" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1541" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1541" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1541" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/portcast/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Consultant - Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1542" s="6" t="inlineStr">
+        <is>
+          <t>Guidehouse</t>
+        </is>
+      </c>
+      <c r="C1542" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1542" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1542" s="6" t="inlineStr"/>
+      <c r="F1542" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1542" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1542" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/guidehouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst, GTM Business Operations – Public Sector</t>
+        </is>
+      </c>
+      <c r="B1543" s="8" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C1543" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1543" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1543" s="8" t="inlineStr"/>
+      <c r="F1543" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1543" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1543" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/samsara/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="6" t="inlineStr">
+        <is>
+          <t>Key Account Commercial Coordinator - Data Centers</t>
+        </is>
+      </c>
+      <c r="B1544" s="6" t="inlineStr">
+        <is>
+          <t>Veolia</t>
+        </is>
+      </c>
+      <c r="C1544" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1544" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1544" s="6" t="inlineStr"/>
+      <c r="F1544" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1544" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1544" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/veolia/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="8" t="inlineStr">
+        <is>
+          <t>Revenue Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1545" s="8" t="inlineStr">
+        <is>
+          <t>Everway</t>
+        </is>
+      </c>
+      <c r="C1545" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1545" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1545" s="8" t="inlineStr"/>
+      <c r="F1545" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1545" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1545" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/everway/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst - Data Products II - WashU IT</t>
+        </is>
+      </c>
+      <c r="B1546" s="6" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="C1546" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1546" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1546" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R</t>
+        </is>
+      </c>
+      <c r="F1546" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1546" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H1546" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/washu/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1490"/>
+  <autoFilter ref="A1:H1546"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -61885,19 +64185,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>756</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3">
@@ -61913,13 +64213,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -61929,19 +64229,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>54</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
@@ -62042,7 +64342,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>8</v>
@@ -62051,7 +64351,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -62061,7 +64361,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
@@ -62073,7 +64373,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1546</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1589</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-19 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-19 22:49 UTC</t>
+          <t>数据日期 2026-08-20 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-20 22:53 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1545</v>
+        <v>1588</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,21 +710,21 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4025974025974026</v>
+        <v>0.4113475177304964</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>其他数据岗</t>
+          <t>数据分析/BI</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3475177304964539</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3896103896103896</v>
+        <v>0.3617021276595745</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>数据分析/BI</t>
+          <t>其他数据岗</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3311688311688312</v>
+        <v>0.2907801418439716</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3116883116883117</v>
+        <v>0.3049645390070922</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1623376623376623</v>
+        <v>0.2056737588652482</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1623376623376623</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,88 +793,88 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1493506493506493</v>
+        <v>0.1560283687943262</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1702127659574468</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1560283687943262</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1298701298701299</v>
+        <v>0.148936170212766</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>20</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1298701298701299</v>
+        <v>0.1418439716312057</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>GCP</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1233766233766234</v>
+        <v>0.1347517730496454</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
         <v>18</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1168831168831169</v>
+        <v>0.1276595744680851</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1546"/>
+  <dimension ref="A1:H1589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -64123,8 +64123,1778 @@
         </is>
       </c>
     </row>
+    <row r="1547">
+      <c r="A1547" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1547" s="8" t="inlineStr">
+        <is>
+          <t>MUVN</t>
+        </is>
+      </c>
+      <c r="C1547" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1547" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1547" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1547" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1547" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1547" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/muvn/data-analyst-all-genders-hamburg-222708</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="6" t="inlineStr">
+        <is>
+          <t>Director Data Strategy Consulting (Mensch)</t>
+        </is>
+      </c>
+      <c r="B1548" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1548" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1548" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1548" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1548" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1548" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1548" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wppmedia/director-data-strategy-consulting-mensch-dusseldorf-frankfurt-hamburg-munich-302990</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="8" t="inlineStr">
+        <is>
+          <t>Consultant Client Data (Mensch)</t>
+        </is>
+      </c>
+      <c r="B1549" s="8" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1549" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1549" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1549" s="8" t="inlineStr">
+        <is>
+          <t>Power BI、R</t>
+        </is>
+      </c>
+      <c r="F1549" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1549" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1549" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wppmedia/consultant-client-data-mensch-dusseldorf-467425</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="6" t="inlineStr">
+        <is>
+          <t>Associate Director Client Data (Mensch)</t>
+        </is>
+      </c>
+      <c r="B1550" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1550" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1550" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1550" s="6" t="inlineStr">
+        <is>
+          <t>Power BI、R</t>
+        </is>
+      </c>
+      <c r="F1550" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1550" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1550" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wppmedia/associate-director-client-data-mensch-dusseldorf-240056</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="8" t="inlineStr">
+        <is>
+          <t>Data Platform &amp; Data Architecture Consultant</t>
+        </is>
+      </c>
+      <c r="B1551" s="8" t="inlineStr">
+        <is>
+          <t>Netlight</t>
+        </is>
+      </c>
+      <c r="C1551" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1551" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1551" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、AWS、Azure、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1551" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1551" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1551" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/netlight/data-platform-data-architecture-consultant-berlin-248331</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d) – Fokus Messdatenmanagement &amp; Ownership</t>
+        </is>
+      </c>
+      <c r="B1552" s="6" t="inlineStr">
+        <is>
+          <t>Octopus Energy Group</t>
+        </is>
+      </c>
+      <c r="C1552" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1552" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1552" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、ETL</t>
+        </is>
+      </c>
+      <c r="F1552" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1552" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1552" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/octopus-energy-group/data-engineer-fokus-messdatenmanagement-ownership-berlin-de-197367</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1553" s="8" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1553" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1553" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1553" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R</t>
+        </is>
+      </c>
+      <c r="F1553" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1553" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1553" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/senior-data-engineer-databricks-stuttgart-187617</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (Professional) (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1554" s="6" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1554" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1554" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1554" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1554" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1554" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1554" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/data-engineer-professional-databricks-stuttgart-296815</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="8" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer (Databricks) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1555" s="8" t="inlineStr">
+        <is>
+          <t>Collaboration Betters The World GmbH</t>
+        </is>
+      </c>
+      <c r="C1555" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1555" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1555" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R</t>
+        </is>
+      </c>
+      <c r="F1555" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1555" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1555" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/collaboration-betters-the-world-gmbh/junior-data-engineer-databricks-stuttgart-267806</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="6" t="inlineStr">
+        <is>
+          <t>Data Protection Officer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1556" s="6" t="inlineStr">
+        <is>
+          <t>actago GmbH</t>
+        </is>
+      </c>
+      <c r="C1556" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1556" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1556" s="6" t="inlineStr"/>
+      <c r="F1556" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1556" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1556" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/actago-gmbh/data-protection-officer-landau-an-der-isar-94343</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist/ML Engineer - Financial Crime</t>
+        </is>
+      </c>
+      <c r="B1557" s="8" t="inlineStr">
+        <is>
+          <t>sumup</t>
+        </is>
+      </c>
+      <c r="C1557" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1557" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1557" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1557" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1557" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1557" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-data-scientist-ml-engineer-financial-crime-berlin-185839</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Data Analyst- Consumer Growth</t>
+        </is>
+      </c>
+      <c r="B1558" s="6" t="inlineStr">
+        <is>
+          <t>Sumup</t>
+        </is>
+      </c>
+      <c r="C1558" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1558" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1558" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F1558" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1558" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1558" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sumup/senior-product-data-analyst-consumer-growth-london-411940</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="8" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1559" s="8" t="inlineStr">
+        <is>
+          <t>Duck Duck Go</t>
+        </is>
+      </c>
+      <c r="C1559" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1559" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1559" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1559" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1559" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1559" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/duck-duck-go/remote-staff-data-scientist-152804</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1560" s="6" t="inlineStr">
+        <is>
+          <t>Ivcevidensia</t>
+        </is>
+      </c>
+      <c r="C1560" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1560" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1560" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Azure</t>
+        </is>
+      </c>
+      <c r="F1560" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1560" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1560" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ivcevidensia/data-engineer-keynsham-bristol-england-420378</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="8" t="inlineStr">
+        <is>
+          <t>Staff Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1561" s="8" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="C1561" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1561" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1561" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1561" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1561" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1561" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/pleo/staff-analytics-engineer-london-28392</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="6" t="inlineStr">
+        <is>
+          <t>Staff Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1562" s="6" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="C1562" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1562" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1562" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1562" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1562" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1562" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/pleo/staff-analytics-engineer-united-kingdom-420867</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="8" t="inlineStr">
+        <is>
+          <t>Head of Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1563" s="8" t="inlineStr">
+        <is>
+          <t>PHMG Careers</t>
+        </is>
+      </c>
+      <c r="C1563" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1563" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1563" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、BigQuery、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1563" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1563" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1563" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/phmg-careers/head-of-data-engineering-manchester-188111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer - GTM</t>
+        </is>
+      </c>
+      <c r="B1564" s="6" t="inlineStr">
+        <is>
+          <t>intercom</t>
+        </is>
+      </c>
+      <c r="C1564" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1564" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1564" s="6" t="inlineStr"/>
+      <c r="F1564" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1564" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1564" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/intercom/staff-data-engineer-gtm-london-473413</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1565" s="8" t="inlineStr">
+        <is>
+          <t>Everquote</t>
+        </is>
+      </c>
+      <c r="C1565" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1565" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1565" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1565" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1565" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1565" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/everquote/data-scientist-belfast-northern-ireland-165930</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist/ML Engineer - Financial Crime</t>
+        </is>
+      </c>
+      <c r="B1566" s="6" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C1566" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1566" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1566" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1566" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1566" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1566" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-data-scientist-ml-engineer-financial-crime-berlin-257478</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="8" t="inlineStr">
+        <is>
+          <t>Finance Analyst (m/w/d) - Erneuerbare Energien</t>
+        </is>
+      </c>
+      <c r="B1567" s="8" t="inlineStr">
+        <is>
+          <t>feld.energy GmbH</t>
+        </is>
+      </c>
+      <c r="C1567" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1567" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1567" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1567" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1567" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1567" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/feldenergy-gmbh/finance-analyst-erneuerbare-energien-weissenburg-in-bayern-252284</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer (f/m/d)_metrify</t>
+        </is>
+      </c>
+      <c r="B1568" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1568" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1568" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1568" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt、Airflow、Azure</t>
+        </is>
+      </c>
+      <c r="F1568" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1568" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1568" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/staff-data-engineer-metrify-berlin-347291</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst Business Operations (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1569" s="8" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1569" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1569" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1569" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Snowflake</t>
+        </is>
+      </c>
+      <c r="F1569" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1569" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1569" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/senior-analyst-business-operations-berlin-465086</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="6" t="inlineStr">
+        <is>
+          <t>Business Analytics Internship (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1570" s="6" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1570" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1570" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1570" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Tableau、Power BI、Looker</t>
+        </is>
+      </c>
+      <c r="F1570" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1570" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1570" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/business-analytics-internship-berlin-395567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (f/m/d)_metrify</t>
+        </is>
+      </c>
+      <c r="B1571" s="8" t="inlineStr">
+        <is>
+          <t>Enpal</t>
+        </is>
+      </c>
+      <c r="C1571" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1571" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1571" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt、Airflow、Azure</t>
+        </is>
+      </c>
+      <c r="F1571" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1571" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1571" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/enpal/senior-data-engineer-metrify-berlin-61854</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="6" t="inlineStr">
+        <is>
+          <t>Information Security Analyst - Audit, Compliance &amp; Cybersecurity</t>
+        </is>
+      </c>
+      <c r="B1572" s="6" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="C1572" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1572" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1572" s="6" t="inlineStr"/>
+      <c r="F1572" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1572" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1572" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/nice/information-security-analyst-audit-compliance-cybersecurity-5835</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analyst, FP&amp;A</t>
+        </is>
+      </c>
+      <c r="B1573" s="8" t="inlineStr">
+        <is>
+          <t>Angi</t>
+        </is>
+      </c>
+      <c r="C1573" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1573" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1573" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Excel、Looker</t>
+        </is>
+      </c>
+      <c r="F1573" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1573" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1573" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/angi/senior-analyst-fpa-london-455421</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="6" t="inlineStr">
+        <is>
+          <t>Platform Data Engineer - Cardiff</t>
+        </is>
+      </c>
+      <c r="B1574" s="6" t="inlineStr">
+        <is>
+          <t>Rocketsciencegg</t>
+        </is>
+      </c>
+      <c r="C1574" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1574" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1574" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、dbt、Airflow、AWS、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1574" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1574" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1574" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/rocketsciencegg/platform-data-engineer-cardiff-474975</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="8" t="inlineStr">
+        <is>
+          <t>Life Sciences Consulting Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B1575" s="8" t="inlineStr">
+        <is>
+          <t>Clearviewhealthcarepartners</t>
+        </is>
+      </c>
+      <c r="C1575" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1575" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1575" s="8" t="inlineStr"/>
+      <c r="F1575" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1575" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1575" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/clearviewhealthcarepartners/life-sciences-consulting-senior-analyst-london-301655</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="6" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - User and Lifecycle Analytics</t>
+        </is>
+      </c>
+      <c r="B1576" s="6" t="inlineStr">
+        <is>
+          <t>Contentsquare</t>
+        </is>
+      </c>
+      <c r="C1576" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1576" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1576" s="6" t="inlineStr"/>
+      <c r="F1576" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1576" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1576" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/contentsquare/senior-product-manager-user-and-lifecycle-analytics-germany-372508</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="8" t="inlineStr">
+        <is>
+          <t>Minijob Master Data (m/w/d) Bearbeitung von Stammdatenänderungen (Befristet bis zum 31.12.26)</t>
+        </is>
+      </c>
+      <c r="B1577" s="8" t="inlineStr">
+        <is>
+          <t>Culligan</t>
+        </is>
+      </c>
+      <c r="C1577" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1577" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1577" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1577" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1577" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1577" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/culligan/minijob-master-data-bearbeitung-von-stammdatenanderungen-befristet-bis-zum-311226-hamburg-357351</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer - US</t>
+        </is>
+      </c>
+      <c r="B1578" s="6" t="inlineStr">
+        <is>
+          <t>Luxury Presence</t>
+        </is>
+      </c>
+      <c r="C1578" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1578" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1578" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1578" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1578" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1578" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151266-senior-analytics-engineer-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer - CANADA</t>
+        </is>
+      </c>
+      <c r="B1579" s="8" t="inlineStr">
+        <is>
+          <t>Luxury Presence</t>
+        </is>
+      </c>
+      <c r="C1579" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1579" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1579" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1579" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1579" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1579" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151263-senior-analytics-engineer-canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="6" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst, Product Analytics</t>
+        </is>
+      </c>
+      <c r="B1580" s="6" t="inlineStr">
+        <is>
+          <t>Updater</t>
+        </is>
+      </c>
+      <c r="C1580" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1580" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1580" s="6" t="inlineStr">
+        <is>
+          <t>Looker、Snowflake、dbt、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1580" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1580" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1580" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151213-lead-data-analyst-product-analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1581" s="8" t="inlineStr">
+        <is>
+          <t>Alto Pharmacy</t>
+        </is>
+      </c>
+      <c r="C1581" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1581" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1581" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、AWS、Azure、GCP、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1581" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1581" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1581" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/alto-pharmacy/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="6" t="inlineStr">
+        <is>
+          <t>Cyber Analyst, Digital Forensics Incident Response</t>
+        </is>
+      </c>
+      <c r="B1582" s="6" t="inlineStr">
+        <is>
+          <t>At-Bay</t>
+        </is>
+      </c>
+      <c r="C1582" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1582" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1582" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1582" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1582" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1582" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/at-bay/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="8" t="inlineStr">
+        <is>
+          <t>Analyst, Supply Planning</t>
+        </is>
+      </c>
+      <c r="B1583" s="8" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="C1583" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1583" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1583" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1583" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1583" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1583" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/danaher/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="6" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B1584" s="6" t="inlineStr">
+        <is>
+          <t>Walker Smith</t>
+        </is>
+      </c>
+      <c r="C1584" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1584" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1584" s="6" t="inlineStr"/>
+      <c r="F1584" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1584" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1584" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/walker-smith/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="8" t="inlineStr">
+        <is>
+          <t>Media Search Analyst - English Speakers (India)</t>
+        </is>
+      </c>
+      <c r="B1585" s="8" t="inlineStr">
+        <is>
+          <t>TELUS International AI Inc</t>
+        </is>
+      </c>
+      <c r="C1585" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1585" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1585" s="8" t="inlineStr"/>
+      <c r="F1585" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1585" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1585" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/telus-international-ai-inc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="6" t="inlineStr">
+        <is>
+          <t>Applications Support Analyst - M365</t>
+        </is>
+      </c>
+      <c r="B1586" s="6" t="inlineStr">
+        <is>
+          <t>Sanford Health</t>
+        </is>
+      </c>
+      <c r="C1586" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1586" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1586" s="6" t="inlineStr"/>
+      <c r="F1586" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1586" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1586" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/sanford-health/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="8" t="inlineStr">
+        <is>
+          <t>Sr Workday Analyst</t>
+        </is>
+      </c>
+      <c r="B1587" s="8" t="inlineStr">
+        <is>
+          <t>Trellix Software India Private Limited</t>
+        </is>
+      </c>
+      <c r="C1587" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1587" s="8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1587" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1587" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1587" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1587" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/trellix-software-india-private-limited/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sr. Director Analyst, Marketing Measurement, Analytics &amp; AI Decisioning (Remote </t>
+        </is>
+      </c>
+      <c r="B1588" s="6" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C1588" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1588" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1588" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试</t>
+        </is>
+      </c>
+      <c r="F1588" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1588" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1588" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/gartner/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="8" t="inlineStr">
+        <is>
+          <t>岗位名称：全栈运维工程师 / 高级 DevOps &amp; 数据工程专家</t>
+        </is>
+      </c>
+      <c r="B1589" s="8" t="inlineStr"/>
+      <c r="C1589" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1589" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1589" s="8" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="F1589" s="8" t="inlineStr">
+        <is>
+          <t>eleduck</t>
+        </is>
+      </c>
+      <c r="G1589" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H1589" s="8" t="inlineStr">
+        <is>
+          <t>https://eleduck.com/posts/Ygf5XV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1546"/>
+  <autoFilter ref="A1:H1589"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -64185,19 +65955,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3">
@@ -64229,19 +65999,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>54</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>70</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
@@ -64273,7 +66043,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>17</v>
@@ -64282,10 +66052,10 @@
         <v>29</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
@@ -64301,13 +66071,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -64339,7 +66109,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>2</v>
@@ -64351,7 +66121,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1589</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1634</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-20 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-20 22:53 UTC</t>
+          <t>数据日期 2026-08-21 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-21 22:48 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1588</v>
+        <v>1633</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4113475177304964</v>
+        <v>0.3862068965517241</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3475177304964539</v>
+        <v>0.3448275862068966</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>51</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3617021276595745</v>
+        <v>0.3517241379310345</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -745,136 +745,136 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2907801418439716</v>
+        <v>0.2896551724137931</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3049645390070922</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>数据开发/工程</t>
+          <t>数据科学/算法</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
         <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2056737588652482</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.1862068965517241</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>0.1702127659574468</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>数据科学/算法</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>22</v>
-      </c>
       <c r="H14" s="7" t="n">
-        <v>0.1560283687943262</v>
+        <v>0.1655172413793103</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.1655172413793103</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1560283687943262</v>
+        <v>0.1655172413793103</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.148936170212766</v>
+        <v>0.1310344827586207</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Azure</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1418439716312057</v>
+        <v>0.1241379310344828</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1347517730496454</v>
+        <v>0.1172413793103448</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Airflow</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.1172413793103448</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1589"/>
+  <dimension ref="A1:H1634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -65893,8 +65893,1842 @@
         </is>
       </c>
     </row>
+    <row r="1590">
+      <c r="A1590" s="6" t="inlineStr">
+        <is>
+          <t>Vice President, Technology &amp; Digital Strategy</t>
+        </is>
+      </c>
+      <c r="B1590" s="6" t="inlineStr">
+        <is>
+          <t>Shatterproof</t>
+        </is>
+      </c>
+      <c r="C1590" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1590" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1590" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1590" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G1590" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1590" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/all-others/vice-president-technology-digital-strategy-2091104</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1591" s="8" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C1591" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1591" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1591" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Airflow、AWS、Azure、GCP、机器学习</t>
+        </is>
+      </c>
+      <c r="F1591" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G1591" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1591" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-data-engineer-2091097</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="6" t="inlineStr">
+        <is>
+          <t>Bank Relationship and Analytics Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1592" s="6" t="inlineStr">
+        <is>
+          <t>Raisin</t>
+        </is>
+      </c>
+      <c r="C1592" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1592" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1592" s="6" t="inlineStr"/>
+      <c r="F1592" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1592" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1592" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/raisin/bank-relationship-and-analytics-manager-berlin-berlin-456484</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1593" s="8" t="inlineStr">
+        <is>
+          <t>Hubject GmbH</t>
+        </is>
+      </c>
+      <c r="C1593" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1593" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1593" s="8" t="inlineStr"/>
+      <c r="F1593" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1593" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1593" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hubject-gmbh/senior-financial-analyst-all-genders-deutschland-berlin-264655</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst mit Schwerpunkt Power BI &amp; Databricks (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1594" s="6" t="inlineStr">
+        <is>
+          <t>pmX Group</t>
+        </is>
+      </c>
+      <c r="C1594" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1594" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1594" s="6" t="inlineStr">
+        <is>
+          <t>Power BI</t>
+        </is>
+      </c>
+      <c r="F1594" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1594" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1594" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmx-group/data-analyst-mit-schwerpunkt-power-bi-databricks-stuttgart-351483</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="8" t="inlineStr">
+        <is>
+          <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1595" s="8" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM gGmbH</t>
+        </is>
+      </c>
+      <c r="C1595" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1595" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1595" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1595" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1595" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1595" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/unternehmertum-ggmbh/uvc-partners-junior-value-creation-analyst-intern-or-working-student-munchen-kreativquartier-251770</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1596" s="6" t="inlineStr">
+        <is>
+          <t>Westwing Group SE</t>
+        </is>
+      </c>
+      <c r="C1596" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1596" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1596" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Snowflake、统计学</t>
+        </is>
+      </c>
+      <c r="F1596" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1596" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1596" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/westwing-group-se/senior-data-analyst-munich-office-472692</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="8" t="inlineStr">
+        <is>
+          <t>Lead / Principal Consultant - Data and AI</t>
+        </is>
+      </c>
+      <c r="B1597" s="8" t="inlineStr">
+        <is>
+          <t>celonis</t>
+        </is>
+      </c>
+      <c r="C1597" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1597" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1597" s="8" t="inlineStr"/>
+      <c r="F1597" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1597" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1597" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/celonis/lead-principal-consultant-data-and-ai-munich-360879</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="6" t="inlineStr">
+        <is>
+          <t>Veeam Data Cloud Vault Solution Specialist</t>
+        </is>
+      </c>
+      <c r="B1598" s="6" t="inlineStr">
+        <is>
+          <t>Veeamsoftware</t>
+        </is>
+      </c>
+      <c r="C1598" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1598" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1598" s="6" t="inlineStr"/>
+      <c r="F1598" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1598" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1598" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/veeamsoftware/remote-veeam-data-cloud-vault-solution-specialist-215456</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="8" t="inlineStr">
+        <is>
+          <t>Werkstudent Data Science / Business Intelligence (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1599" s="8" t="inlineStr">
+        <is>
+          <t>Meierhofer</t>
+        </is>
+      </c>
+      <c r="C1599" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1599" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1599" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI</t>
+        </is>
+      </c>
+      <c r="F1599" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1599" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1599" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/meierhofer/remote-werkstudent-data-science-business-intelligence-leipzig-326594</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="6" t="inlineStr">
+        <is>
+          <t>#49426 Video Annotation &amp; Data Labeling Project</t>
+        </is>
+      </c>
+      <c r="B1600" s="6" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C1600" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1600" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1600" s="6" t="inlineStr"/>
+      <c r="F1600" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1600" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1600" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobgether/49426-video-annotation-data-labeling-project-germany-191762</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering Manager – Finance &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="B1601" s="8" t="inlineStr">
+        <is>
+          <t>Deliveroo</t>
+        </is>
+      </c>
+      <c r="C1601" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1601" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1601" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt</t>
+        </is>
+      </c>
+      <c r="F1601" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1601" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1601" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deliveroo/data-engineering-manager-finance-accounting-london-426710</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="6" t="inlineStr">
+        <is>
+          <t>Professorship (W2) in Business Information Systems, Business Analytics and Applied AI (100 %) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1602" s="6" t="inlineStr">
+        <is>
+          <t>velpTEC edutainment</t>
+        </is>
+      </c>
+      <c r="C1602" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1602" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1602" s="6" t="inlineStr"/>
+      <c r="F1602" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1602" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1602" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/velptec-edutainment/remote-professorship-w2-in-business-information-systems-business-analytics-and-applied-ai-100-122066</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="8" t="inlineStr">
+        <is>
+          <t>Director of Data, Payments</t>
+        </is>
+      </c>
+      <c r="B1603" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C1603" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1603" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1603" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1603" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1603" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1603" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/monzo/director-of-data-payments-cardiff-339567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="6" t="inlineStr">
+        <is>
+          <t>#49426 Video Annotation &amp; Data Labeling Project</t>
+        </is>
+      </c>
+      <c r="B1604" s="6" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C1604" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1604" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1604" s="6" t="inlineStr"/>
+      <c r="F1604" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1604" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1604" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobgether/49426-video-annotation-data-labeling-project-uk-336711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Growth &amp; Personalisation</t>
+        </is>
+      </c>
+      <c r="B1605" s="8" t="inlineStr">
+        <is>
+          <t>Deliveroo</t>
+        </is>
+      </c>
+      <c r="C1605" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1605" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1605" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1605" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1605" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1605" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deliveroo/machine-learning-engineer-growth-personalisation-london-124862</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Routing &amp; ETA</t>
+        </is>
+      </c>
+      <c r="B1606" s="6" t="inlineStr">
+        <is>
+          <t>Deliveroo</t>
+        </is>
+      </c>
+      <c r="C1606" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1606" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1606" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1606" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1606" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1606" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deliveroo/machine-learning-engineer-routing-eta-london-5454</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1607" s="8" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="C1607" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1607" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1607" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake、dbt、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1607" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1607" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1607" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/swap/analytics-engineer-london-195310</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B1608" s="6" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C1608" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1608" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1608" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Spark、BigQuery、A/B测试</t>
+        </is>
+      </c>
+      <c r="F1608" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1608" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1608" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/spotify/senior-data-engineer-data-platform-london-25330</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="8" t="inlineStr">
+        <is>
+          <t>Senior System Analyst (Platform) (Hybrid or Remote)</t>
+        </is>
+      </c>
+      <c r="B1609" s="8" t="inlineStr">
+        <is>
+          <t>Vivid</t>
+        </is>
+      </c>
+      <c r="C1609" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1609" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1609" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Snowflake</t>
+        </is>
+      </c>
+      <c r="F1609" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1609" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1609" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/vivid/senior-system-analyst-platform-hybrid-or-remote-270705</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="6" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B1610" s="6" t="inlineStr">
+        <is>
+          <t>Flagshippioneeringinc</t>
+        </is>
+      </c>
+      <c r="C1610" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1610" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1610" s="6" t="inlineStr">
+        <is>
+          <t>AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F1610" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1610" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1610" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/flagshippioneeringinc/senior-engineer-data-infrastructure-cambridge-293079</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="8" t="inlineStr">
+        <is>
+          <t>Working Student (m/w/d) CRM &amp; Data</t>
+        </is>
+      </c>
+      <c r="B1611" s="8" t="inlineStr">
+        <is>
+          <t>Recare Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C1611" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1611" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1611" s="8" t="inlineStr">
+        <is>
+          <t>Excel、Looker</t>
+        </is>
+      </c>
+      <c r="F1611" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1611" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1611" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/recare-deutschland-gmbh/working-student-crm-data-berlin-394452</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1612" s="6" t="inlineStr">
+        <is>
+          <t>limehome</t>
+        </is>
+      </c>
+      <c r="C1612" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1612" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1612" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1612" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1612" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1612" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/limehome/data-scientist-munchen-56545</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1613" s="8" t="inlineStr">
+        <is>
+          <t>PAIR Finance</t>
+        </is>
+      </c>
+      <c r="C1613" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1613" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1613" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1613" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1613" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1613" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pair-finance/data-scientist-berlin-hybrid-467006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="6" t="inlineStr">
+        <is>
+          <t>Managing Consultant – Data &amp; Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1614" s="6" t="inlineStr">
+        <is>
+          <t>Pmone</t>
+        </is>
+      </c>
+      <c r="C1614" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1614" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1614" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Snowflake、Azure</t>
+        </is>
+      </c>
+      <c r="F1614" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1614" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1614" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmone/managing-consultant-data-analytics-munchen-415293</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="8" t="inlineStr">
+        <is>
+          <t>Consultant (Junior) – Data &amp; Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1615" s="8" t="inlineStr">
+        <is>
+          <t>Pmone</t>
+        </is>
+      </c>
+      <c r="C1615" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1615" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1615" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Snowflake、Azure</t>
+        </is>
+      </c>
+      <c r="F1615" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1615" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1615" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pmone/consultant-junior-data-analytics-munchen-145075</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Financial Analyst (m/w/d) – CFO Office</t>
+        </is>
+      </c>
+      <c r="B1616" s="6" t="inlineStr">
+        <is>
+          <t>Prokuras Beteiligungs GmbH</t>
+        </is>
+      </c>
+      <c r="C1616" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1616" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1616" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1616" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1616" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1616" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/prokuras-beteiligungs-gmbh/senior-financial-analyst-cfo-office-hamburg-412880</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering Leader</t>
+        </is>
+      </c>
+      <c r="B1617" s="8" t="inlineStr">
+        <is>
+          <t>Cognite</t>
+        </is>
+      </c>
+      <c r="C1617" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1617" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1617" s="8" t="inlineStr"/>
+      <c r="F1617" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1617" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1617" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/cognite/data-engineering-leader-319108</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="6" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant (m/w/d) Microsoft Data &amp; Analytics / Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B1618" s="6" t="inlineStr">
+        <is>
+          <t>Windhoff Group</t>
+        </is>
+      </c>
+      <c r="C1618" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1618" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1618" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Spark、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1618" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1618" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1618" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/windhoff-group/senior-consultant-microsoft-data-analytics-microsoft-fabric-gescher-229953</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="8" t="inlineStr">
+        <is>
+          <t>DevOps/ML Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1619" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C1619" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1619" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1619" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、GCP、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1619" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1619" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1619" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/devops-ml-engineer-munich-201312</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="6" t="inlineStr">
+        <is>
+          <t>Solution Consultant – Snke Data</t>
+        </is>
+      </c>
+      <c r="B1620" s="6" t="inlineStr">
+        <is>
+          <t>Snke</t>
+        </is>
+      </c>
+      <c r="C1620" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1620" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1620" s="6" t="inlineStr"/>
+      <c r="F1620" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1620" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1620" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/snke/solution-consultant-snke-data-munchen-224557</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="8" t="inlineStr">
+        <is>
+          <t>DevOps/ML Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1621" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Reply</t>
+        </is>
+      </c>
+      <c r="C1621" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1621" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1621" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、Airflow、AWS、Azure、GCP、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1621" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1621" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1621" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/machine-learning-reply/devops-ml-engineer-munich-101304</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analyst - GTM Strategy</t>
+        </is>
+      </c>
+      <c r="B1622" s="6" t="inlineStr">
+        <is>
+          <t>Deepl</t>
+        </is>
+      </c>
+      <c r="C1622" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1622" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1622" s="6" t="inlineStr"/>
+      <c r="F1622" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1622" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1622" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deepl/senior-analyst-gtm-strategy-london-31790</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1623" s="8" t="inlineStr">
+        <is>
+          <t>TodayTix Group</t>
+        </is>
+      </c>
+      <c r="C1623" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1623" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1623" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F1623" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1623" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1623" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/todaytix-group/lead-data-engineer-london-uk-15503</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="6" t="inlineStr">
+        <is>
+          <t>IT-Forensik Analyst - Datensicherung</t>
+        </is>
+      </c>
+      <c r="B1624" s="6" t="inlineStr">
+        <is>
+          <t>Hassmann IT-Forensik GmbH</t>
+        </is>
+      </c>
+      <c r="C1624" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1624" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1624" s="6" t="inlineStr"/>
+      <c r="F1624" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1624" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1624" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hassmann-it-forensik-gmbh/it-forensik-analyst-datensicherung-teltow-333158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="8" t="inlineStr">
+        <is>
+          <t>Senior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1625" s="8" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1625" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1625" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1625" s="8" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="F1625" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1625" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1625" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/senior-google-performance-analytics-manager-stuttgart-325030</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="6" t="inlineStr">
+        <is>
+          <t>Junior Google Performance &amp; Analytics Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1626" s="6" t="inlineStr">
+        <is>
+          <t>eFLY Marketplace Services GmbH</t>
+        </is>
+      </c>
+      <c r="C1626" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1626" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1626" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1626" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1626" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1626" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/efly-marketplace-services-gmbh/junior-google-performance-analytics-manager-stuttgart-272787</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B1627" s="8" t="inlineStr">
+        <is>
+          <t>Nucs AI</t>
+        </is>
+      </c>
+      <c r="C1627" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1627" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1627" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1627" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1627" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1627" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/nucs-ai/remote-machine-learning-scientist-berlin-103209</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="6" t="inlineStr">
+        <is>
+          <t>Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1628" s="6" t="inlineStr">
+        <is>
+          <t>Metro Markets GmbH</t>
+        </is>
+      </c>
+      <c r="C1628" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1628" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1628" s="6" t="inlineStr"/>
+      <c r="F1628" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1628" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1628" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/metro-markets-gmbh/data-analyst-dusseldorf-497408</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1629" s="8" t="inlineStr">
+        <is>
+          <t>Liftoff</t>
+        </is>
+      </c>
+      <c r="C1629" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1629" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1629" s="8" t="inlineStr">
+        <is>
+          <t>机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1629" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1629" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1629" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151331-machine-learning-engineer-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="6" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (Europe-based/Remote)</t>
+        </is>
+      </c>
+      <c r="B1630" s="6" t="inlineStr">
+        <is>
+          <t>SWORD Health</t>
+        </is>
+      </c>
+      <c r="C1630" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1630" s="6" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1630" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1630" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1630" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1630" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151320-senior-ml-engineer-europe-based-remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="8" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1631" s="8" t="inlineStr">
+        <is>
+          <t>Ruby Labs</t>
+        </is>
+      </c>
+      <c r="C1631" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1631" s="8" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="E1631" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F1631" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1631" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1631" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151318-data-analytics-engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="6" t="inlineStr">
+        <is>
+          <t>Lead Process &amp; Solutions Finance Analyst (REMOTE, AL, US)</t>
+        </is>
+      </c>
+      <c r="B1632" s="6" t="inlineStr">
+        <is>
+          <t>Flowers Foods</t>
+        </is>
+      </c>
+      <c r="C1632" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1632" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1632" s="6" t="inlineStr"/>
+      <c r="F1632" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1632" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1632" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/flowers-foods/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="8" t="inlineStr">
+        <is>
+          <t>Real-Time Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1633" s="8" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies</t>
+        </is>
+      </c>
+      <c r="C1633" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1633" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1633" s="8" t="inlineStr">
+        <is>
+          <t>Python、Spark、AWS、Azure</t>
+        </is>
+      </c>
+      <c r="F1633" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1633" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1633" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bright-vision-technologies/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="6" t="inlineStr">
+        <is>
+          <t>Anwendungssicherheitsanalyst</t>
+        </is>
+      </c>
+      <c r="B1634" s="6" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="C1634" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1634" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1634" s="6" t="inlineStr"/>
+      <c r="F1634" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1634" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H1634" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/interval/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1589"/>
+  <autoFilter ref="A1:H1634"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65955,19 +67789,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>832</v>
+        <v>869</v>
       </c>
     </row>
     <row r="3">
@@ -65999,19 +67833,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -66156,16 +67990,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1634</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1675</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-21 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-21 22:48 UTC</t>
+          <t>数据日期 2026-08-22 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-22 22:45 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1633</v>
+        <v>1674</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>0.3517241379310345</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>其他数据岗</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>42</v>
-      </c>
       <c r="H12" s="7" t="n">
-        <v>0.2896551724137931</v>
+        <v>0.3207547169811321</v>
       </c>
     </row>
     <row r="13">
@@ -758,21 +758,21 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3379310344827586</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>数据科学/算法</t>
+          <t>数据开发/工程</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2</v>
+        <v>0.169811320754717</v>
       </c>
     </row>
     <row r="14">
@@ -785,18 +785,18 @@
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1862068965517241</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>数据开发/工程</t>
+          <t>数据科学/算法</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1655172413793103</v>
+        <v>0.169811320754717</v>
       </c>
     </row>
     <row r="15">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1655172413793103</v>
+        <v>0.1635220125786163</v>
       </c>
     </row>
     <row r="16">
@@ -822,46 +822,46 @@
         <v>24</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1655172413793103</v>
+        <v>0.1509433962264151</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1310344827586207</v>
+        <v>0.1383647798742138</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Azure</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1241379310344828</v>
+        <v>0.1257861635220126</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1172413793103448</v>
+        <v>0.119496855345912</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1172413793103448</v>
+        <v>0.1132075471698113</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1634"/>
+  <dimension ref="A1:H1675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -67727,8 +67727,1682 @@
         </is>
       </c>
     </row>
+    <row r="1635">
+      <c r="A1635" s="8" t="inlineStr">
+        <is>
+          <t>Data Steward</t>
+        </is>
+      </c>
+      <c r="B1635" s="8" t="inlineStr">
+        <is>
+          <t>Smartsheet</t>
+        </is>
+      </c>
+      <c r="C1635" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1635" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1635" s="8" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1635" s="8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1635" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1635" s="8" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-data-steward-smartsheet-1137080</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="6" t="inlineStr">
+        <is>
+          <t>Content Reviewer - English US</t>
+        </is>
+      </c>
+      <c r="B1636" s="6" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C1636" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1636" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1636" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1636" s="6" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G1636" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1636" s="6" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/all-others/content-reviewer-english-us-2091105</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="8" t="inlineStr">
+        <is>
+          <t>Senior Golang Developer</t>
+        </is>
+      </c>
+      <c r="B1637" s="8" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C1637" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1637" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1637" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1637" s="8" t="inlineStr">
+        <is>
+          <t>remotive</t>
+        </is>
+      </c>
+      <c r="G1637" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1637" s="8" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-golang-developer-2091098</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant (m/f/d) Data &amp; AI Strategy</t>
+        </is>
+      </c>
+      <c r="B1638" s="6" t="inlineStr">
+        <is>
+          <t>Artefact</t>
+        </is>
+      </c>
+      <c r="C1638" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1638" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1638" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1638" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1638" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1638" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/artefact/senior-consultant-data-ai-strategy-berlin-berlin-munchen-bavaria-7237</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="8" t="inlineStr">
+        <is>
+          <t>Consulting Manager (m/f/d) Data &amp; AI Strategy</t>
+        </is>
+      </c>
+      <c r="B1639" s="8" t="inlineStr">
+        <is>
+          <t>Artefact</t>
+        </is>
+      </c>
+      <c r="C1639" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1639" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1639" s="8" t="inlineStr"/>
+      <c r="F1639" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1639" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1639" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/artefact/consulting-manager-data-ai-strategy-berlin-berlin-munchen-bavaria-195243</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Reporting &amp; Insights (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1640" s="6" t="inlineStr">
+        <is>
+          <t>Statista</t>
+        </is>
+      </c>
+      <c r="C1640" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1640" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1640" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Snowflake</t>
+        </is>
+      </c>
+      <c r="F1640" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1640" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1640" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/statista/senior-data-analyst-reporting-insights-hamburg-29540</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="8" t="inlineStr">
+        <is>
+          <t>Working Student Data Analytics/Engineering eMobility (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1641" s="8" t="inlineStr">
+        <is>
+          <t>Edri</t>
+        </is>
+      </c>
+      <c r="C1641" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1641" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1641" s="8" t="inlineStr"/>
+      <c r="F1641" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1641" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1641" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/edri/working-student-data-analytics-engineering-emobility-essen-31053</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="6" t="inlineStr">
+        <is>
+          <t>Senior FP&amp;A Analyst (all genders)</t>
+        </is>
+      </c>
+      <c r="B1642" s="6" t="inlineStr">
+        <is>
+          <t>Gotphoto</t>
+        </is>
+      </c>
+      <c r="C1642" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1642" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1642" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F1642" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1642" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1642" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gotphoto/senior-fpa-analyst-all-genders-berlin-377651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="8" t="inlineStr">
+        <is>
+          <t>Team Lead Data Products &amp; Analytics (gn)</t>
+        </is>
+      </c>
+      <c r="B1643" s="8" t="inlineStr">
+        <is>
+          <t>Bikeleasing</t>
+        </is>
+      </c>
+      <c r="C1643" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1643" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1643" s="8" t="inlineStr">
+        <is>
+          <t>SQL、dbt、AWS</t>
+        </is>
+      </c>
+      <c r="F1643" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1643" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1643" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bikeleasing/remote-team-lead-data-products-analytics-gn-9339</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="6" t="inlineStr">
+        <is>
+          <t>Graduate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1644" s="6" t="inlineStr">
+        <is>
+          <t>Shifttechnology</t>
+        </is>
+      </c>
+      <c r="C1644" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1644" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1644" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1644" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1644" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1644" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/shifttechnology/graduate-data-scientist-342540</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="8" t="inlineStr">
+        <is>
+          <t>Senior Manager, Analytics</t>
+        </is>
+      </c>
+      <c r="B1645" s="8" t="inlineStr">
+        <is>
+          <t>Eucalyptus</t>
+        </is>
+      </c>
+      <c r="C1645" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1645" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1645" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt</t>
+        </is>
+      </c>
+      <c r="F1645" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1645" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1645" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/eucalyptus/senior-manager-analytics-140230</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="6" t="inlineStr">
+        <is>
+          <t>Senior Analyst - GTM Strategy</t>
+        </is>
+      </c>
+      <c r="B1646" s="6" t="inlineStr">
+        <is>
+          <t>DeepL</t>
+        </is>
+      </c>
+      <c r="C1646" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1646" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1646" s="6" t="inlineStr"/>
+      <c r="F1646" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1646" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1646" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/deepl/senior-analyst-gtm-strategy-london-392743</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Analytics Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1647" s="8" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C1647" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1647" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1647" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、dbt、BigQuery、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1647" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1647" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1647" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-senior-analytics-engineer-465811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="6" t="inlineStr">
+        <is>
+          <t>(Junior) Data Engineer - Data Platform (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1648" s="6" t="inlineStr">
+        <is>
+          <t>1Komma5Grad</t>
+        </is>
+      </c>
+      <c r="C1648" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1648" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1648" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、GCP、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1648" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1648" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1648" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/1komma5grad/remote-junior-data-engineer-data-platform-104347</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1649" s="8" t="inlineStr">
+        <is>
+          <t>Neko Health</t>
+        </is>
+      </c>
+      <c r="C1649" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1649" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1649" s="8" t="inlineStr">
+        <is>
+          <t>Python、Azure、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1649" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1649" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1649" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/neko-health/data-scientist-london-347976</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="6" t="inlineStr">
+        <is>
+          <t>GTM Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1650" s="6" t="inlineStr">
+        <is>
+          <t>Heidi</t>
+        </is>
+      </c>
+      <c r="C1650" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1650" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1650" s="6" t="inlineStr"/>
+      <c r="F1650" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1650" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1650" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/heidi/gtm-operations-analyst-london-398196</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Real time analytics</t>
+        </is>
+      </c>
+      <c r="B1651" s="8" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C1651" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1651" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1651" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Airflow、AWS</t>
+        </is>
+      </c>
+      <c r="F1651" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1651" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1651" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/aircall/senior-data-engineer-real-time-analytics-london-office-382266</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer - fully remote (working hours 5am-2pm CEST) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1652" s="6" t="inlineStr">
+        <is>
+          <t>JobLeads Careers</t>
+        </is>
+      </c>
+      <c r="C1652" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1652" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1652" s="6" t="inlineStr"/>
+      <c r="F1652" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1652" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1652" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobleads-careers/data-engineer-fully-remote-working-hours-5am-2pm-cest-387091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="8" t="inlineStr">
+        <is>
+          <t>Principal IAM Consultant, Identity Governance and Data Access</t>
+        </is>
+      </c>
+      <c r="B1653" s="8" t="inlineStr">
+        <is>
+          <t>Intelance</t>
+        </is>
+      </c>
+      <c r="C1653" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1653" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1653" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F1653" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1653" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1653" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/intelance/principal-iam-consultant-identity-governance-and-data-access-london-490046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="6" t="inlineStr">
+        <is>
+          <t>Data Privacy Lawyer</t>
+        </is>
+      </c>
+      <c r="B1654" s="6" t="inlineStr">
+        <is>
+          <t>Axiomtalentplatform</t>
+        </is>
+      </c>
+      <c r="C1654" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1654" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1654" s="6" t="inlineStr"/>
+      <c r="F1654" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1654" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1654" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/axiomtalentplatform/data-privacy-lawyer-425462</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="8" t="inlineStr">
+        <is>
+          <t>Senior European Credit Analyst</t>
+        </is>
+      </c>
+      <c r="B1655" s="8" t="inlineStr">
+        <is>
+          <t>Guidepoint</t>
+        </is>
+      </c>
+      <c r="C1655" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1655" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1655" s="8" t="inlineStr"/>
+      <c r="F1655" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1655" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1655" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/guidepoint/senior-european-credit-analyst-london-150399</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/f/x)</t>
+        </is>
+      </c>
+      <c r="B1656" s="6" t="inlineStr">
+        <is>
+          <t>Makersite GmbH</t>
+        </is>
+      </c>
+      <c r="C1656" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1656" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1656" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1656" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1656" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1656" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/makersite-gmbh/remote-senior-data-scientist-berlin-309145</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Data Ingestion &amp; Extraction (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1657" s="8" t="inlineStr">
+        <is>
+          <t>Certivity</t>
+        </is>
+      </c>
+      <c r="C1657" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1657" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1657" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1657" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1657" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1657" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/certivity/senior-software-engineer-data-ingestion-extraction-munchen-hq-218511</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/w/d) – Snowflake</t>
+        </is>
+      </c>
+      <c r="B1658" s="6" t="inlineStr">
+        <is>
+          <t>Jobrad Loop</t>
+        </is>
+      </c>
+      <c r="C1658" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1658" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1658" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Spark、Snowflake、Airflow、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1658" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1658" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1658" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobrad-loop/senior-data-engineer-snowflake-munchen-10090</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="8" t="inlineStr">
+        <is>
+          <t>Working Student - Data Science (Research &amp; Predictive Analytics)</t>
+        </is>
+      </c>
+      <c r="B1659" s="8" t="inlineStr">
+        <is>
+          <t>Justwatch</t>
+        </is>
+      </c>
+      <c r="C1659" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1659" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1659" s="8" t="inlineStr">
+        <is>
+          <t>Snowflake、dbt、Airflow、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1659" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1659" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1659" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/justwatch/working-student-data-science-research-predictive-analytics-berlin-108305</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="6" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1660" s="6" t="inlineStr">
+        <is>
+          <t>adorsys GmbH</t>
+        </is>
+      </c>
+      <c r="C1660" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1660" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1660" s="6" t="inlineStr"/>
+      <c r="F1660" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1660" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1660" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/adorsys-gmbh/senior-business-analyst-nurnberg-269884</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="8" t="inlineStr">
+        <is>
+          <t>Senior Financial Analyst DACH (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1661" s="8" t="inlineStr">
+        <is>
+          <t>Banyansoftware</t>
+        </is>
+      </c>
+      <c r="C1661" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1661" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1661" s="8" t="inlineStr"/>
+      <c r="F1661" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1661" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1661" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/banyansoftware/senior-financial-analyst-dach-munchen-bavaria-375869</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="6" t="inlineStr">
+        <is>
+          <t>Data Architecture Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1662" s="6" t="inlineStr">
+        <is>
+          <t>Invensity Group</t>
+        </is>
+      </c>
+      <c r="C1662" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1662" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1662" s="6" t="inlineStr">
+        <is>
+          <t>AWS、Azure、GCP</t>
+        </is>
+      </c>
+      <c r="F1662" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1662" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1662" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/invensity-group/data-architecture-consultant-wiesbaden-hybrid-87865</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Platform Lead (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1663" s="8" t="inlineStr">
+        <is>
+          <t>isaraerospace</t>
+        </is>
+      </c>
+      <c r="C1663" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1663" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1663" s="8" t="inlineStr"/>
+      <c r="F1663" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1663" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1663" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/isaraerospace/ai-data-platform-lead-parsdorf-bavaria-380393</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer, Global Client Solutions</t>
+        </is>
+      </c>
+      <c r="B1664" s="6" t="inlineStr">
+        <is>
+          <t>wppmedia</t>
+        </is>
+      </c>
+      <c r="C1664" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1664" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1664" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1664" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1664" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1664" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/wppmedia/data-engineer-global-client-solutions-london-278301</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="8" t="inlineStr">
+        <is>
+          <t>Manager, Media Analytics UK</t>
+        </is>
+      </c>
+      <c r="B1665" s="8" t="inlineStr">
+        <is>
+          <t>Sharkninjaoperatingllc</t>
+        </is>
+      </c>
+      <c r="C1665" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1665" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1665" s="8" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F1665" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1665" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1665" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sharkninjaoperatingllc/manager-media-analytics-uk-london-230756</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Media Analytics (DACH/FR)</t>
+        </is>
+      </c>
+      <c r="B1666" s="6" t="inlineStr">
+        <is>
+          <t>Sharkninjaoperatingllc</t>
+        </is>
+      </c>
+      <c r="C1666" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1666" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1666" s="6" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="F1666" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1666" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1666" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/sharkninjaoperatingllc/manager-media-analytics-dach-fr-london-184006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Product Manager</t>
+        </is>
+      </c>
+      <c r="B1667" s="8" t="inlineStr">
+        <is>
+          <t>Fundingcircle</t>
+        </is>
+      </c>
+      <c r="C1667" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1667" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1667" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1667" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1667" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1667" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/fundingcircle/senior-data-product-manager-london-173327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="6" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B1668" s="6" t="inlineStr">
+        <is>
+          <t>Oddball</t>
+        </is>
+      </c>
+      <c r="C1668" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1668" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1668" s="6" t="inlineStr">
+        <is>
+          <t>Power BI、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1668" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1668" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1668" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151390-cloud-data-architect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="8" t="inlineStr">
+        <is>
+          <t>Senior Revenue Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="B1669" s="8" t="inlineStr">
+        <is>
+          <t>1Password</t>
+        </is>
+      </c>
+      <c r="C1669" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1669" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1669" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、dbt</t>
+        </is>
+      </c>
+      <c r="F1669" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1669" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1669" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151358-senior-revenue-strategy-analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="6" t="inlineStr">
+        <is>
+          <t>Data Management Analyst, Denials AI</t>
+        </is>
+      </c>
+      <c r="B1670" s="6" t="inlineStr">
+        <is>
+          <t>Med-Metrix</t>
+        </is>
+      </c>
+      <c r="C1670" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1670" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1670" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、AWS、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1670" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1670" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1670" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/med-metrix/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="8" t="inlineStr">
+        <is>
+          <t>Business Intelligence (BI) Developer (Level 2)</t>
+        </is>
+      </c>
+      <c r="B1671" s="8" t="inlineStr">
+        <is>
+          <t>Boardroom Appointments</t>
+        </is>
+      </c>
+      <c r="C1671" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1671" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1671" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1671" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1671" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1671" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/boardroom-appointments/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="6" t="inlineStr">
+        <is>
+          <t>Manager, Data Platform Governance &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B1672" s="6" t="inlineStr">
+        <is>
+          <t>Genesys</t>
+        </is>
+      </c>
+      <c r="C1672" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1672" s="6" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="E1672" s="6" t="inlineStr">
+        <is>
+          <t>Snowflake、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F1672" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1672" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1672" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/genesys/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="8" t="inlineStr">
+        <is>
+          <t>Global Mobility Analyst</t>
+        </is>
+      </c>
+      <c r="B1673" s="8" t="inlineStr">
+        <is>
+          <t>Veralto</t>
+        </is>
+      </c>
+      <c r="C1673" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1673" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1673" s="8" t="inlineStr"/>
+      <c r="F1673" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1673" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1673" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/veralto/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="6" t="inlineStr">
+        <is>
+          <t>Workday Integrations Analyst Consultant (Global Delivery Center)</t>
+        </is>
+      </c>
+      <c r="B1674" s="6" t="inlineStr">
+        <is>
+          <t>Collaborative Solutions</t>
+        </is>
+      </c>
+      <c r="C1674" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1674" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1674" s="6" t="inlineStr"/>
+      <c r="F1674" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1674" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1674" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/collaborative-solutions/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="8" t="inlineStr">
+        <is>
+          <t>Director, Operations Analytics</t>
+        </is>
+      </c>
+      <c r="B1675" s="8" t="inlineStr">
+        <is>
+          <t>The RealReal</t>
+        </is>
+      </c>
+      <c r="C1675" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1675" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1675" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Looker、机器学习</t>
+        </is>
+      </c>
+      <c r="F1675" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1675" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H1675" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/the-realreal/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1634"/>
+  <autoFilter ref="A1:H1675"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -67789,19 +69463,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>869</v>
+        <v>899</v>
       </c>
     </row>
     <row r="3">
@@ -67833,7 +69507,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>55</v>
@@ -67842,10 +69516,10 @@
         <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5">
@@ -67877,7 +69551,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>17</v>
@@ -67886,10 +69560,10 @@
         <v>29</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
@@ -67949,13 +69623,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1675</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1713</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-22 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-22 22:45 UTC</t>
+          <t>数据日期 2026-08-23 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-23 22:45 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1674</v>
+        <v>1712</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,132 +710,132 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>数据分析/BI</t>
+          <t>其他数据岗</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3396226415094339</v>
+        <v>0.3580246913580247</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4012345679012346</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>其他数据岗</t>
+          <t>数据分析/BI</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.3207547169811321</v>
+        <v>0.2839506172839506</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3518518518518519</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>数据开发/工程</t>
+          <t>数据科学/算法</t>
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1851851851851852</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>数据科学/算法</t>
+          <t>数据开发/工程</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.169811320754717</v>
+        <v>0.1728395061728395</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
         <v>26</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1635220125786163</v>
+        <v>0.1604938271604938</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.154320987654321</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1383647798742138</v>
+        <v>0.1296296296296296</v>
       </c>
     </row>
     <row r="18">
@@ -848,7 +848,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1257861635220126</v>
+        <v>0.1234567901234568</v>
       </c>
     </row>
     <row r="19">
@@ -861,7 +861,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.119496855345912</v>
+        <v>0.1172839506172839</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.1172839506172839</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1675"/>
+  <dimension ref="A1:H1713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -69401,8 +69401,1564 @@
         </is>
       </c>
     </row>
+    <row r="1676">
+      <c r="A1676" s="6" t="inlineStr">
+        <is>
+          <t>Senior Governance Risk and Compliance Analyst</t>
+        </is>
+      </c>
+      <c r="B1676" s="6" t="inlineStr">
+        <is>
+          <t>RainFocus</t>
+        </is>
+      </c>
+      <c r="C1676" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1676" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1676" s="6" t="inlineStr"/>
+      <c r="F1676" s="6" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="G1676" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1676" s="6" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-governance-risk-and-compliance-analyst-rainfocus-1137061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="8" t="inlineStr">
+        <is>
+          <t>AI Founding Engineer: RF Machine Learning (SIGINT) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1677" s="8" t="inlineStr">
+        <is>
+          <t>Datacept</t>
+        </is>
+      </c>
+      <c r="C1677" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1677" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1677" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1677" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1677" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1677" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/datacept/ai-founding-engineer-rf-machine-learning-sigint-hamburg-8016</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="6" t="inlineStr">
+        <is>
+          <t>OSINT Analyst/ Data Effects Cell (DEC)/Tactical Mission Networks (TMN)</t>
+        </is>
+      </c>
+      <c r="B1678" s="6" t="inlineStr">
+        <is>
+          <t>Smxtech</t>
+        </is>
+      </c>
+      <c r="C1678" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1678" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1678" s="6" t="inlineStr"/>
+      <c r="F1678" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1678" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1678" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/smxtech/osint-analyst-data-effects-cell-dec-tactical-mission-networks-tmn-stuttgart-342492</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="8" t="inlineStr">
+        <is>
+          <t>Data Strategist &amp; Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B1679" s="8" t="inlineStr">
+        <is>
+          <t>Smxtech</t>
+        </is>
+      </c>
+      <c r="C1679" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1679" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1679" s="8" t="inlineStr"/>
+      <c r="F1679" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1679" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1679" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/smxtech/data-strategist-analytics-specialist-stuttgart-398292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="6" t="inlineStr">
+        <is>
+          <t>Data Effects Cell Coordinator - Tactical Mission Networks (TMN) - Eastern Europe</t>
+        </is>
+      </c>
+      <c r="B1680" s="6" t="inlineStr">
+        <is>
+          <t>Smxtech</t>
+        </is>
+      </c>
+      <c r="C1680" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1680" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1680" s="6" t="inlineStr"/>
+      <c r="F1680" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1680" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1680" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/smxtech/data-effects-cell-coordinator-tactical-mission-networks-tmn-eastern-europe-stuttgart-364837</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="8" t="inlineStr">
+        <is>
+          <t>Senior Robotics &amp; Machine Learning Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1681" s="8" t="inlineStr">
+        <is>
+          <t>Quantum-Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1681" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1681" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1681" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1681" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1681" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1681" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/quantum-systems-gmbh/senior-robotics-machine-learning-engineer-munchen-401688</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="6" t="inlineStr">
+        <is>
+          <t>Working Student (m/w/d) CRM &amp; Data</t>
+        </is>
+      </c>
+      <c r="B1682" s="6" t="inlineStr">
+        <is>
+          <t>Recare Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C1682" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1682" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1682" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Looker</t>
+        </is>
+      </c>
+      <c r="F1682" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1682" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1682" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/recare-deutschland-gmbh/remote-working-student-crm-data-berlin-178515</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="8" t="inlineStr">
+        <is>
+          <t>Data Protection Officer (Deputy) (F/M/D)</t>
+        </is>
+      </c>
+      <c r="B1683" s="8" t="inlineStr">
+        <is>
+          <t>360T</t>
+        </is>
+      </c>
+      <c r="C1683" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1683" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1683" s="8" t="inlineStr"/>
+      <c r="F1683" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1683" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1683" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/360t/data-protection-officer-deputy-frankfurt-am-main-265379</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="6" t="inlineStr">
+        <is>
+          <t>Head of Data &amp; Business Intelligence (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1684" s="6" t="inlineStr">
+        <is>
+          <t>Pammys™ (dieseo GmbH)</t>
+        </is>
+      </c>
+      <c r="C1684" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1684" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1684" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python</t>
+        </is>
+      </c>
+      <c r="F1684" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1684" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1684" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/pammys-dieseo-gmbh/head-of-data-business-intelligence-hamburg-91733</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Visualization Engineer - Microsoft Fabric (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1685" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1685" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1685" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1685" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、AWS、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1685" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1685" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1685" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-visualization-engineer-microsoft-fabric-hybrid-munchen-273332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (m/w/d) - Chemical Engineering &amp; Verfahrenstechnik</t>
+        </is>
+      </c>
+      <c r="B1686" s="6" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1686" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1686" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1686" s="6" t="inlineStr">
+        <is>
+          <t>Python、R、AWS、Azure、机器学习</t>
+        </is>
+      </c>
+      <c r="F1686" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1686" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1686" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-data-scientist-chemical-engineering-verfahrenstechnik-hybrid-munchen-53405</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="8" t="inlineStr">
+        <is>
+          <t>Senior AI Transformation Consultant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1687" s="8" t="inlineStr">
+        <is>
+          <t>Alexander Thamm GmbH</t>
+        </is>
+      </c>
+      <c r="C1687" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1687" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1687" s="8" t="inlineStr"/>
+      <c r="F1687" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1687" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1687" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/alexander-thamm-gmbh/senior-ai-transformation-consultant-hybrid-munchen-189035</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Cologne, Germany</t>
+        </is>
+      </c>
+      <c r="B1688" s="6" t="inlineStr">
+        <is>
+          <t>speechify</t>
+        </is>
+      </c>
+      <c r="C1688" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1688" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1688" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1688" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1688" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1688" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-cologne-germany-352635</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="8" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher in geospatial political data (SDC-32)</t>
+        </is>
+      </c>
+      <c r="B1689" s="8" t="inlineStr">
+        <is>
+          <t>GESIS – Leibniz-Institut für Sozialwissenschaften</t>
+        </is>
+      </c>
+      <c r="C1689" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1689" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1689" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1689" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1689" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1689" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/gesis-leibniz-institut-fur-sozialwissenschaften/postdoctoral-researcher-in-geospatial-political-data-sdc-32-koln-413762</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="6" t="inlineStr">
+        <is>
+          <t>Senior Implementation Specialist Digital Analytics (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1690" s="6" t="inlineStr">
+        <is>
+          <t>FELD M</t>
+        </is>
+      </c>
+      <c r="C1690" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1690" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1690" s="6" t="inlineStr"/>
+      <c r="F1690" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1690" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1690" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/feld-m/senior-implementation-specialist-digital-analytics-munich-55614</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Expert (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="B1691" s="8" t="inlineStr">
+        <is>
+          <t>Authority.inc</t>
+        </is>
+      </c>
+      <c r="C1691" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1691" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1691" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1691" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1691" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1691" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/authorityinc/ai-data-expert-united-kingdom-london-410090</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="6" t="inlineStr">
+        <is>
+          <t>Director of Data (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1692" s="6" t="inlineStr">
+        <is>
+          <t>Moonfare</t>
+        </is>
+      </c>
+      <c r="C1692" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1692" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1692" s="6" t="inlineStr"/>
+      <c r="F1692" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1692" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1692" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/moonfare/director-of-data-london-3168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer | Betty CA</t>
+        </is>
+      </c>
+      <c r="B1693" s="8" t="inlineStr">
+        <is>
+          <t>Bettyjobboard</t>
+        </is>
+      </c>
+      <c r="C1693" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1693" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1693" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、Snowflake、dbt、Airflow、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1693" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1693" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1693" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/bettyjobboard/senior-data-engineer-betty-ca-london-169535</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="6" t="inlineStr">
+        <is>
+          <t>Technical Product Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1694" s="6" t="inlineStr">
+        <is>
+          <t>ucm.agency</t>
+        </is>
+      </c>
+      <c r="C1694" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1694" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1694" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1694" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1694" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1694" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/ucmagency/technical-product-manager-berlin-283901</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer - Data (All Genders)</t>
+        </is>
+      </c>
+      <c r="B1695" s="8" t="inlineStr">
+        <is>
+          <t>PREMATCH Sports GmbH</t>
+        </is>
+      </c>
+      <c r="C1695" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1695" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1695" s="8" t="inlineStr">
+        <is>
+          <t>Python、AWS</t>
+        </is>
+      </c>
+      <c r="F1695" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1695" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1695" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/prematch-sports-gmbh/software-engineer-data-all-genders-koln-358585</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="6" t="inlineStr">
+        <is>
+          <t>Softwareentwickler (m/w/d) Moodle / PHP / E-Learning</t>
+        </is>
+      </c>
+      <c r="B1696" s="6" t="inlineStr">
+        <is>
+          <t>Velptec</t>
+        </is>
+      </c>
+      <c r="C1696" s="6" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1696" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1696" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1696" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1696" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1696" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/velptec/remote-softwareentwickler-moodle-php-e-learning-257464</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="8" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1697" s="8" t="inlineStr">
+        <is>
+          <t>DISH Digital Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C1697" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1697" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1697" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、dbt、Airflow、GCP、BigQuery、机器学习</t>
+        </is>
+      </c>
+      <c r="F1697" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1697" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1697" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dishdigital/senior-data-engineer-dusseldorf-259265</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/f/d)</t>
+        </is>
+      </c>
+      <c r="B1698" s="6" t="inlineStr">
+        <is>
+          <t>DISH Digital Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C1698" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1698" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1698" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Spark、dbt、Airflow、GCP、BigQuery、A/B测试、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1698" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1698" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1698" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/dishdigital/data-engineer-dusseldorf-363424</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="8" t="inlineStr">
+        <is>
+          <t>Praktikum - Political Data Engineering (w/d/m)</t>
+        </is>
+      </c>
+      <c r="B1699" s="8" t="inlineStr">
+        <is>
+          <t>Christundcompany</t>
+        </is>
+      </c>
+      <c r="C1699" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1699" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1699" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、dbt</t>
+        </is>
+      </c>
+      <c r="F1699" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1699" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1699" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/christundcompany/praktikum-political-data-engineering-berlin-255318</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist, Buyer</t>
+        </is>
+      </c>
+      <c r="B1700" s="6" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C1700" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1700" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1700" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1700" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1700" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1700" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/data-scientist-buyer-berlin-440456</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, Payments Intelligence</t>
+        </is>
+      </c>
+      <c r="B1701" s="8" t="inlineStr">
+        <is>
+          <t>Vinteden</t>
+        </is>
+      </c>
+      <c r="C1701" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1701" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1701" s="8" t="inlineStr"/>
+      <c r="F1701" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1701" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1701" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/vinteden/analytics-engineer-payments-intelligence-berlin-224168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="6" t="inlineStr">
+        <is>
+          <t>Senior Staff Machine Learning Engineer, Menu Personalisation (m,f,x)</t>
+        </is>
+      </c>
+      <c r="B1702" s="6" t="inlineStr">
+        <is>
+          <t>hellofresh</t>
+        </is>
+      </c>
+      <c r="C1702" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1702" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1702" s="6" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习</t>
+        </is>
+      </c>
+      <c r="F1702" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1702" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1702" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/hellofresh/senior-staff-machine-learning-engineer-menu-personalisation-mfx-berlin-berlin-287242</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="8" t="inlineStr">
+        <is>
+          <t>Product Data Analyst (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="B1703" s="8" t="inlineStr">
+        <is>
+          <t>freenow</t>
+        </is>
+      </c>
+      <c r="C1703" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1703" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1703" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、R、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1703" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1703" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1703" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/freenow/product-data-analyst-berlin-56919</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer (m/w/d) - Azure Cloud &amp; MS Fabric</t>
+        </is>
+      </c>
+      <c r="B1704" s="6" t="inlineStr">
+        <is>
+          <t>Doehle</t>
+        </is>
+      </c>
+      <c r="C1704" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1704" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1704" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1704" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1704" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1704" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/doehle/data-engineer-azure-cloud-ms-fabric-hamburg-82581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+        </is>
+      </c>
+      <c r="B1705" s="8" t="inlineStr">
+        <is>
+          <t>Clickhouse</t>
+        </is>
+      </c>
+      <c r="C1705" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1705" s="8" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E1705" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI、Spark、dbt、ETL</t>
+        </is>
+      </c>
+      <c r="F1705" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1705" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1705" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/clickhouse/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="6" t="inlineStr">
+        <is>
+          <t>Manager of Data Science Production Engineering, Data Engineering &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="B1706" s="6" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C1706" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1706" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1706" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、R、dbt、AWS、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1706" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1706" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1706" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/natera/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="8" t="inlineStr">
+        <is>
+          <t>Qlik Sense Data Consultant</t>
+        </is>
+      </c>
+      <c r="B1707" s="8" t="inlineStr">
+        <is>
+          <t>Keyrus</t>
+        </is>
+      </c>
+      <c r="C1707" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1707" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1707" s="8" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1707" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1707" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1707" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/keyrus/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1708" s="6" t="inlineStr">
+        <is>
+          <t>Magna Legal Services</t>
+        </is>
+      </c>
+      <c r="C1708" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1708" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1708" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Snowflake、dbt、Azure、机器学习、ETL</t>
+        </is>
+      </c>
+      <c r="F1708" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1708" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1708" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/magna-legal-services/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="8" t="inlineStr">
+        <is>
+          <t>Fraud Analyst</t>
+        </is>
+      </c>
+      <c r="B1709" s="8" t="inlineStr">
+        <is>
+          <t>Nymbus</t>
+        </is>
+      </c>
+      <c r="C1709" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1709" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1709" s="8" t="inlineStr"/>
+      <c r="F1709" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1709" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1709" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/nymbus/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="6" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (Topic Analytics, GenAI &amp; Reporting)</t>
+        </is>
+      </c>
+      <c r="B1710" s="6" t="inlineStr">
+        <is>
+          <t>Abstra</t>
+        </is>
+      </c>
+      <c r="C1710" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1710" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1710" s="6" t="inlineStr">
+        <is>
+          <t>Python、A/B测试、机器学习、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1710" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1710" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1710" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/abstra-co/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant (m/w/d) Microsoft Data &amp; Analytics / Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B1711" s="8" t="inlineStr">
+        <is>
+          <t>Windhoff Group</t>
+        </is>
+      </c>
+      <c r="C1711" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1711" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1711" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、Spark、Azure、ETL</t>
+        </is>
+      </c>
+      <c r="F1711" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1711" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1711" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/windhoff-group/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="6" t="inlineStr">
+        <is>
+          <t>Research Analyst - Chinese - (Remote Work)</t>
+        </is>
+      </c>
+      <c r="B1712" s="6" t="inlineStr">
+        <is>
+          <t>Integrated Language Solutions</t>
+        </is>
+      </c>
+      <c r="C1712" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1712" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1712" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1712" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1712" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1712" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/integrated-language-solutions/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="8" t="inlineStr">
+        <is>
+          <t>Data Processing Engineer - I/O</t>
+        </is>
+      </c>
+      <c r="B1713" s="8" t="inlineStr">
+        <is>
+          <t>DataPelago</t>
+        </is>
+      </c>
+      <c r="C1713" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1713" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1713" s="8" t="inlineStr">
+        <is>
+          <t>Spark、机器学习</t>
+        </is>
+      </c>
+      <c r="F1713" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1713" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H1713" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/datapelago/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1675"/>
+  <autoFilter ref="A1:H1713"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -69463,19 +71019,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>899</v>
+        <v>928</v>
       </c>
     </row>
     <row r="3">
@@ -69507,19 +71063,19 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -69551,19 +71107,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>29</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
@@ -69582,10 +71138,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1713</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1758</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>数据日期 2026-08-23 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-23 22:45 UTC</t>
+          <t>数据日期 2026-08-24 · 样本为7个公开API的国际远程数据岗 · 报表由export_excel.py自动生成于 2026-08-24 22:51 UTC</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1712</v>
+        <v>1757</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -710,21 +710,21 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4197530864197531</v>
+        <v>0.4635761589403973</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>其他数据岗</t>
+          <t>数据分析/BI</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.3580246913580247</v>
+        <v>0.3509933774834437</v>
       </c>
     </row>
     <row r="12">
@@ -734,21 +734,21 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.4012345679012346</v>
+        <v>0.3841059602649007</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>数据分析/BI</t>
+          <t>其他数据岗</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2839506172839506</v>
+        <v>0.2781456953642384</v>
       </c>
     </row>
     <row r="13">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.3518518518518519</v>
+        <v>0.3443708609271523</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1920529801324503</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>A/B测试</t>
+          <t>统计学</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1788079470198675</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.1728395061728395</v>
+        <v>0.1788079470198675</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.1604938271604938</v>
+        <v>0.1589403973509934</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>A/B测试</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.154320987654321</v>
+        <v>0.1589403973509934</v>
       </c>
     </row>
     <row r="17">
@@ -832,36 +832,36 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1296296296296296</v>
+        <v>0.1258278145695364</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.1234567901234568</v>
+        <v>0.1258278145695364</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
         <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.1172839506172839</v>
+        <v>0.1258278145695364</v>
       </c>
     </row>
     <row r="20">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1172839506172839</v>
+        <v>0.1125827814569536</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1713"/>
+  <dimension ref="A1:H1758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -70957,8 +70957,1854 @@
         </is>
       </c>
     </row>
+    <row r="1714">
+      <c r="A1714" s="6" t="inlineStr">
+        <is>
+          <t>Professor (m/f/d) of Data Science</t>
+        </is>
+      </c>
+      <c r="B1714" s="6" t="inlineStr">
+        <is>
+          <t>Global University Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1714" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1714" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1714" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、R、统计学、pandas</t>
+        </is>
+      </c>
+      <c r="F1714" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1714" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1714" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/global-university-systems-gmbh/professor-of-data-science-potsdam-309460</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="8" t="inlineStr">
+        <is>
+          <t>Professor (m/f/d) of Data Engineering</t>
+        </is>
+      </c>
+      <c r="B1715" s="8" t="inlineStr">
+        <is>
+          <t>Global University Systems GmbH</t>
+        </is>
+      </c>
+      <c r="C1715" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1715" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1715" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Spark、dbt、Airflow</t>
+        </is>
+      </c>
+      <c r="F1715" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1715" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1715" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/global-university-systems-gmbh/professor-of-data-engineering-potsdam-354082</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="6" t="inlineStr">
+        <is>
+          <t>Geospatial Data Analyst (f/m/x) in the field of AI &amp; Satellite Data</t>
+        </is>
+      </c>
+      <c r="B1716" s="6" t="inlineStr">
+        <is>
+          <t>LiveEO GmbH</t>
+        </is>
+      </c>
+      <c r="C1716" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1716" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1716" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1716" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1716" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1716" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/geospatial-data-analyst-in-the-field-of-ai-satellite-data-liveeo-gmbh-berlin-office-hybrid-135984</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) Earth Observation Data Supplier Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="B1717" s="8" t="inlineStr">
+        <is>
+          <t>LiveEO GmbH</t>
+        </is>
+      </c>
+      <c r="C1717" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1717" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1717" s="8" t="inlineStr"/>
+      <c r="F1717" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1717" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1717" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/liveeo-gmbh/senior-earth-observation-data-supplier-manager-liveeo-gmbh-berlin-office-hybrid-49577</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant Digital Analytics (m/w/d), München</t>
+        </is>
+      </c>
+      <c r="B1718" s="6" t="inlineStr">
+        <is>
+          <t>Towa</t>
+        </is>
+      </c>
+      <c r="C1718" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1718" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1718" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1718" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1718" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1718" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/towa/senior-consultant-digital-analytics-munchen-191278</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant Digital Analytics (m/w/d), Düsseldorf</t>
+        </is>
+      </c>
+      <c r="B1719" s="8" t="inlineStr">
+        <is>
+          <t>Towa</t>
+        </is>
+      </c>
+      <c r="C1719" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1719" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1719" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1719" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1719" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1719" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/towa/senior-consultant-digital-analytics-dusseldorf-351058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="6" t="inlineStr">
+        <is>
+          <t>Praktikum Digital Analytics (m/w/d)| Ab September, München</t>
+        </is>
+      </c>
+      <c r="B1720" s="6" t="inlineStr">
+        <is>
+          <t>Towa</t>
+        </is>
+      </c>
+      <c r="C1720" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1720" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1720" s="6" t="inlineStr"/>
+      <c r="F1720" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1720" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1720" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/towa/praktikum-digital-analytics-ab-september-munchen-260258</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="8" t="inlineStr">
+        <is>
+          <t>(Senior) IT Product Owner Data Platform (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1721" s="8" t="inlineStr">
+        <is>
+          <t>OXG Glasfaser GmbH</t>
+        </is>
+      </c>
+      <c r="C1721" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1721" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1721" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、ETL</t>
+        </is>
+      </c>
+      <c r="F1721" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1721" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1721" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/oxg-glasfaser-gmbh/remote-senior-it-product-owner-data-platform-146430</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="6" t="inlineStr">
+        <is>
+          <t>Strategic Valuation &amp; Modeling - Senior Analysts - Manager</t>
+        </is>
+      </c>
+      <c r="B1722" s="6" t="inlineStr">
+        <is>
+          <t>EIGHT ADVISORY SAS</t>
+        </is>
+      </c>
+      <c r="C1722" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1722" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1722" s="6" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="F1722" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1722" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1722" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/eight-advisory-sas/strategic-valuation-modeling-senior-analysts-manager-frankfurt-am-main-383067</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="8" t="inlineStr">
+        <is>
+          <t>Junior Market Data Analyst – Chartering</t>
+        </is>
+      </c>
+      <c r="B1723" s="8" t="inlineStr">
+        <is>
+          <t>Kpler</t>
+        </is>
+      </c>
+      <c r="C1723" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1723" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1723" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、机器学习</t>
+        </is>
+      </c>
+      <c r="F1723" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1723" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1723" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/kpler/junior-market-data-analyst-chartering-united-kingdom-164308</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="6" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1724" s="6" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C1724" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1724" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1724" s="6" t="inlineStr"/>
+      <c r="F1724" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1724" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1724" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/ripple/staff-data-scientist-london-283841</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="8" t="inlineStr">
+        <is>
+          <t>Senior Energy Market Analyst - Trading</t>
+        </is>
+      </c>
+      <c r="B1725" s="8" t="inlineStr">
+        <is>
+          <t>Energyexemplarllc</t>
+        </is>
+      </c>
+      <c r="C1725" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1725" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1725" s="8" t="inlineStr"/>
+      <c r="F1725" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1725" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1725" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/energyexemplarllc/senior-energy-market-analyst-trading-63992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="6" t="inlineStr">
+        <is>
+          <t>Future Interest: Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1726" s="6" t="inlineStr">
+        <is>
+          <t>Kaluza</t>
+        </is>
+      </c>
+      <c r="C1726" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1726" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1726" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1726" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1726" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1726" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/kaluza/future-interest-analytics-engineer-bristol-edinburgh-london-427433</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="8" t="inlineStr">
+        <is>
+          <t>Staff Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B1727" s="8" t="inlineStr">
+        <is>
+          <t>MoonPay</t>
+        </is>
+      </c>
+      <c r="C1727" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1727" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1727" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1727" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1727" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1727" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/moonpay/staff-machine-learning-engineer-london-hybrid-361552</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="6" t="inlineStr">
+        <is>
+          <t>Business System Analyst ( APRISO and CMES experience)</t>
+        </is>
+      </c>
+      <c r="B1728" s="6" t="inlineStr">
+        <is>
+          <t>Kryptos Technologies limited</t>
+        </is>
+      </c>
+      <c r="C1728" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1728" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1728" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1728" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1728" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1728" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/kryptos-technologies-limited/business-system-analyst-apriso-and-cmes-experience-darlington-115701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="8" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1729" s="8" t="inlineStr">
+        <is>
+          <t>LemFi</t>
+        </is>
+      </c>
+      <c r="C1729" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1729" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1729" s="8" t="inlineStr">
+        <is>
+          <t>A/B测试、机器学习、统计学</t>
+        </is>
+      </c>
+      <c r="F1729" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1729" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1729" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/lemfi/staff-data-scientist-london-270161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="6" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B1730" s="6" t="inlineStr">
+        <is>
+          <t>PHMG Careers</t>
+        </is>
+      </c>
+      <c r="C1730" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1730" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1730" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、ETL</t>
+        </is>
+      </c>
+      <c r="F1730" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1730" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1730" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/phmg-careers/data-engineer-manchester-268122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="8" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B1731" s="8" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="C1731" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1731" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1731" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Looker、Snowflake、dbt、BigQuery、ETL</t>
+        </is>
+      </c>
+      <c r="F1731" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1731" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1731" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/perk/senior-analytics-engineer-london-101557</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="6" t="inlineStr">
+        <is>
+          <t>Technical Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1732" s="6" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="C1732" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1732" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1732" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1732" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1732" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1732" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/openai/technical-operations-analyst-london-33766</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1733" s="8" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C1733" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1733" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1733" s="8" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1733" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1733" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1733" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/jobgether/ai-ml-engineer-uk-407119</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Cologne, Germany</t>
+        </is>
+      </c>
+      <c r="B1734" s="6" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C1734" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1734" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1734" s="6" t="inlineStr">
+        <is>
+          <t>Python、GCP</t>
+        </is>
+      </c>
+      <c r="F1734" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1734" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1734" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-cologne-germany-114349</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="8" t="inlineStr">
+        <is>
+          <t>Senior Consultant Digital Analytics (m/w/d), München</t>
+        </is>
+      </c>
+      <c r="B1735" s="8" t="inlineStr">
+        <is>
+          <t>TOWA - the digital growth company</t>
+        </is>
+      </c>
+      <c r="C1735" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1735" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1735" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1735" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1735" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1735" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/towa-the-digital-growth-company/senior-consultant-digital-analytics-munchen-munich-48766</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="6" t="inlineStr">
+        <is>
+          <t>Senior Consultant Digital Analytics (m/w/d), Düsseldorf</t>
+        </is>
+      </c>
+      <c r="B1736" s="6" t="inlineStr">
+        <is>
+          <t>TOWA - the digital growth company</t>
+        </is>
+      </c>
+      <c r="C1736" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1736" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1736" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Power BI、Looker、BigQuery</t>
+        </is>
+      </c>
+      <c r="F1736" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1736" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1736" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/towa-the-digital-growth-company/senior-consultant-digital-analytics-dusseldorf-69263</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="8" t="inlineStr">
+        <is>
+          <t>Working Student / Intern – Control Team (Systems &amp; Data Infrastructure) (f/m/d)</t>
+        </is>
+      </c>
+      <c r="B1737" s="8" t="inlineStr">
+        <is>
+          <t>Phlair</t>
+        </is>
+      </c>
+      <c r="C1737" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1737" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1737" s="8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1737" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1737" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1737" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/phlair/working-student-intern-control-team-systems-data-infrastructure-munchen-252125</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="6" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B1738" s="6" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C1738" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1738" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1738" s="6" t="inlineStr">
+        <is>
+          <t>Python、机器学习</t>
+        </is>
+      </c>
+      <c r="F1738" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1738" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1738" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/jobgether/ai-ml-engineer-germany-366385</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer (m/f/d) Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="B1739" s="8" t="inlineStr">
+        <is>
+          <t>MOTOR Ai</t>
+        </is>
+      </c>
+      <c r="C1739" s="8" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1739" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1739" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、A/B测试、机器学习、pandas</t>
+        </is>
+      </c>
+      <c r="F1739" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1739" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1739" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/motor-ai/ai-ml-engineer-autonomous-systems-berlin-374054</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="6" t="inlineStr">
+        <is>
+          <t>Lead Engineer (m/f/d) Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B1740" s="6" t="inlineStr">
+        <is>
+          <t>MOTOR Ai</t>
+        </is>
+      </c>
+      <c r="C1740" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1740" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1740" s="6" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1740" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1740" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1740" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/motor-ai/lead-engineer-data-infrastructure-berlin-249418</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="8" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst - Health Insurance (Fully Remote)</t>
+        </is>
+      </c>
+      <c r="B1741" s="8" t="inlineStr">
+        <is>
+          <t>Covergo</t>
+        </is>
+      </c>
+      <c r="C1741" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1741" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1741" s="8" t="inlineStr"/>
+      <c r="F1741" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1741" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1741" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/covergo/senior-business-analyst-health-insurance-fully-remote-frankfurt-am-main-201760</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="6" t="inlineStr">
+        <is>
+          <t>Senior Business Analyst - Health Insurance (Fully Remote)</t>
+        </is>
+      </c>
+      <c r="B1742" s="6" t="inlineStr">
+        <is>
+          <t>Covergo</t>
+        </is>
+      </c>
+      <c r="C1742" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1742" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1742" s="6" t="inlineStr"/>
+      <c r="F1742" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1742" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1742" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/covergo/senior-business-analyst-health-insurance-fully-remote-munich-372429</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="8" t="inlineStr">
+        <is>
+          <t>Product Owner Data &amp; AI (m/w/d) – fluege.de</t>
+        </is>
+      </c>
+      <c r="B1743" s="8" t="inlineStr">
+        <is>
+          <t>TC Flights Germany GmbH</t>
+        </is>
+      </c>
+      <c r="C1743" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1743" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1743" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、机器学习</t>
+        </is>
+      </c>
+      <c r="F1743" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1743" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1743" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/tc-flights-germany-gmbh/product-owner-data-ai-fluegede-berlin-85158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="6" t="inlineStr">
+        <is>
+          <t>IT Consultant &amp; Business Analyst (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1744" s="6" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1744" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1744" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1744" s="6" t="inlineStr"/>
+      <c r="F1744" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1744" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1744" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/it-consultant-business-analyst-munster-89037</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="8" t="inlineStr">
+        <is>
+          <t>IT Business Analyst - Banking Regulation &amp; Reporting (w/m/d)</t>
+        </is>
+      </c>
+      <c r="B1745" s="8" t="inlineStr">
+        <is>
+          <t>BBHT Beratungsgesellschaft mbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="C1745" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1745" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1745" s="8" t="inlineStr"/>
+      <c r="F1745" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1745" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1745" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/bbht-beratungsgesellschaft-mbh-co-kg/it-business-analyst-banking-regulation-reporting-munster-42026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="6" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1746" s="6" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1746" s="6" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1746" s="6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1746" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、AWS、Azure、GCP、ETL</t>
+        </is>
+      </c>
+      <c r="F1746" s="6" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1746" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1746" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-platform-engineer-working-student-munchen-230477</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer Working Student (m/w/d)</t>
+        </is>
+      </c>
+      <c r="B1747" s="8" t="inlineStr">
+        <is>
+          <t>Trusteq Gmbh</t>
+        </is>
+      </c>
+      <c r="C1747" s="8" t="inlineStr">
+        <is>
+          <t>数据开发/工程</t>
+        </is>
+      </c>
+      <c r="D1747" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E1747" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Power BI、ETL</t>
+        </is>
+      </c>
+      <c r="F1747" s="8" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="G1747" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1747" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/data-engineer-working-student-koln-358872</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="6" t="inlineStr">
+        <is>
+          <t>Business Intelligence Lead, Performance Marketing</t>
+        </is>
+      </c>
+      <c r="B1748" s="6" t="inlineStr">
+        <is>
+          <t>Launch Potato</t>
+        </is>
+      </c>
+      <c r="C1748" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1748" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1748" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Tableau、Power BI</t>
+        </is>
+      </c>
+      <c r="F1748" s="6" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1748" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1748" s="6" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151514-business-intelligence-lead-performance-marketing-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst (Product &amp; Customer Analytics)</t>
+        </is>
+      </c>
+      <c r="B1749" s="8" t="inlineStr">
+        <is>
+          <t>Oowlish Technology</t>
+        </is>
+      </c>
+      <c r="C1749" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1749" s="8" t="inlineStr">
+        <is>
+          <t>拉美</t>
+        </is>
+      </c>
+      <c r="E1749" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、Looker、R、BigQuery、A/B测试、统计学</t>
+        </is>
+      </c>
+      <c r="F1749" s="8" t="inlineStr">
+        <is>
+          <t>jobicy</t>
+        </is>
+      </c>
+      <c r="G1749" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1749" s="8" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/151486-data-analyst-product-customer-analytics-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="6" t="inlineStr">
+        <is>
+          <t>Implementation Analyst - Grad Program 2027</t>
+        </is>
+      </c>
+      <c r="B1750" s="6" t="inlineStr">
+        <is>
+          <t>CO_UK Alfa Financial Software Limited</t>
+        </is>
+      </c>
+      <c r="C1750" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1750" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1750" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F1750" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1750" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1750" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/co_uk-alfa-financial-software-limited/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="8" t="inlineStr">
+        <is>
+          <t>Quality Assurance Analyst (Part-Time Contractor)</t>
+        </is>
+      </c>
+      <c r="B1751" s="8" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="C1751" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1751" s="8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1751" s="8" t="inlineStr"/>
+      <c r="F1751" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1751" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1751" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/domaine/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="6" t="inlineStr">
+        <is>
+          <t>Jr. Financial Operations Analyst</t>
+        </is>
+      </c>
+      <c r="B1752" s="6" t="inlineStr">
+        <is>
+          <t>Bold</t>
+        </is>
+      </c>
+      <c r="C1752" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1752" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1752" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Excel</t>
+        </is>
+      </c>
+      <c r="F1752" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1752" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1752" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/bold/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="8" t="inlineStr">
+        <is>
+          <t>Network Engineer - Data Annotation</t>
+        </is>
+      </c>
+      <c r="B1753" s="8" t="inlineStr">
+        <is>
+          <t>mercor</t>
+        </is>
+      </c>
+      <c r="C1753" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1753" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1753" s="8" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="F1753" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1753" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1753" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/mercor/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="6" t="inlineStr">
+        <is>
+          <t>Senior Portfolio Analyst - Infrastructure Finance</t>
+        </is>
+      </c>
+      <c r="B1754" s="6" t="inlineStr">
+        <is>
+          <t>Farmer Mac (Federal Agricultural Mortgage Corporation)</t>
+        </is>
+      </c>
+      <c r="C1754" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1754" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1754" s="6" t="inlineStr"/>
+      <c r="F1754" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1754" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1754" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/farmer-mac-federal-agricultural-mortgage-corporation/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B1755" s="8" t="inlineStr">
+        <is>
+          <t>Talent Sam</t>
+        </is>
+      </c>
+      <c r="C1755" s="8" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1755" s="8" t="inlineStr">
+        <is>
+          <t>全球远程</t>
+        </is>
+      </c>
+      <c r="E1755" s="8" t="inlineStr">
+        <is>
+          <t>SQL、Python、Excel、Tableau、Power BI、Looker、R、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1755" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1755" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1755" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/talent-sam/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="6" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B1756" s="6" t="inlineStr">
+        <is>
+          <t>Business Changers</t>
+        </is>
+      </c>
+      <c r="C1756" s="6" t="inlineStr">
+        <is>
+          <t>数据科学/算法</t>
+        </is>
+      </c>
+      <c r="D1756" s="6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="E1756" s="6" t="inlineStr">
+        <is>
+          <t>SQL、Python、Tableau、Power BI、R、Spark、统计学、ETL</t>
+        </is>
+      </c>
+      <c r="F1756" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1756" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1756" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/business-changers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="8" t="inlineStr">
+        <is>
+          <t>Geospatial Scientist, Data Collection and Quality</t>
+        </is>
+      </c>
+      <c r="B1757" s="8" t="inlineStr">
+        <is>
+          <t>Ardent MC</t>
+        </is>
+      </c>
+      <c r="C1757" s="8" t="inlineStr">
+        <is>
+          <t>其他数据岗</t>
+        </is>
+      </c>
+      <c r="D1757" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1757" s="8" t="inlineStr"/>
+      <c r="F1757" s="8" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1757" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1757" s="8" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/ardent-mc/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="6" t="inlineStr">
+        <is>
+          <t>Manager  - Revenue Strategy and Analytics</t>
+        </is>
+      </c>
+      <c r="B1758" s="6" t="inlineStr">
+        <is>
+          <t>Blue Stream Fiber</t>
+        </is>
+      </c>
+      <c r="C1758" s="6" t="inlineStr">
+        <is>
+          <t>数据分析/BI</t>
+        </is>
+      </c>
+      <c r="D1758" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E1758" s="6" t="inlineStr">
+        <is>
+          <t>Excel、Power BI</t>
+        </is>
+      </c>
+      <c r="F1758" s="6" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="G1758" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H1758" s="6" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/blue-stream-fiber/jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1713"/>
+  <autoFilter ref="A1:H1758"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -71019,19 +72865,19 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>928</v>
+        <v>962</v>
       </c>
     </row>
     <row r="3">
@@ -71063,7 +72909,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>56</v>
@@ -71072,10 +72918,10 @@
         <v>33</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
@@ -71085,7 +72931,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>1</v>
@@ -71097,7 +72943,7 @@
         <v>27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -71107,10 +72953,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>29</v>
@@ -71119,7 +72965,7 @@
         <v>88</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
@@ -71195,7 +73041,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
@@ -71207,7 +73053,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">

--- a/reports/数据岗位周报.xlsx
+++ b/reports/数据岗位周报.xlsx
@@ -12,7 +12,7 @@
     <sheet name="地区x类别" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'!$A$1:$H$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'岗位明细'